--- a/games-research-starter-pack.xlsx
+++ b/games-research-starter-pack.xlsx
@@ -58023,7 +58023,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Live service means games built on an ongoing content and monetization cadence rather than a one-time sale. Entrants keep failing in a crowded field: Anthem went offline in January, Highguard lasted under two months. In 2026 the retreat sharpened — Guerrilla stripped live service out of Horizon Hunters Gathering mid-development, and Amazon exited MMO publishing entirely. In September 2026 Sega said it had cancelled its Super Game, a live-service project it judged too big to reach service scale, and Riot's co-founder said the free-to-play publisher is considering premium titles.</t>
+          <t>Live service means games built on an ongoing content and monetization cadence rather than a one-time sale. Entrants keep failing in a crowded field: Anthem went offline in January, Highguard lasted under two months. In 2026 the retreat sharpened — Guerrilla stripped live service out of Horizon Hunters Gathering mid-development, and Amazon exited MMO publishing entirely. In September 2026 Sega said it had cancelled its Super Game, a live-service project it judged too big to reach service scale, and Riot's co-founder said the free-to-play publisher is considering premium titles. The incumbents are not absorbing the space the entrants vacate: Newzoo's first-half 2026 read, reported in September 2026, found most established live-service and evergreen titles flat or down year on year, with growth confined to a handful of them.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -58065,7 +58065,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Game Pass is reportedly down to about 30 million paying subscribers, against an internal projection of ~77 million by 2026 revealed in FTC proceedings, after a price hike to $29.99 a month in October 2025 drove churn; Microsoft rolled Ultimate back to $22.99 on 26 April 2026. Sony has stopped reporting PS Plus subscriber counts. From November 2026 Xbox meters cloud streaming rather than bundling it: 15 hours a month on Ultimate, 10 on Premium, 5 on Essential, with extra hours sold separately. Microsoft puts the affected share at 4% of subscribers. Within a week of the cloud cap Microsoft began offering lapsed and some current Ultimate subscribers 12-month discounts reported at $16 to $20 a month against list, a segmented win-back test rather than a price change.</t>
+          <t>Game Pass is reportedly down to about 30 million paying subscribers, against an internal projection of ~77 million by 2026 revealed in FTC proceedings, after a price hike to $29.99 a month in October 2025 drove churn; Microsoft rolled Ultimate back to $22.99 on 26 April 2026. Sony has stopped reporting PS Plus subscriber counts. From November 2026 Xbox meters cloud streaming rather than bundling it: 15 hours a month on Ultimate, 10 on Premium, 5 on Essential, with extra hours sold separately. Microsoft puts the affected share at 4% of subscribers. Within a week of the cloud cap Microsoft began offering lapsed and some current Ultimate subscribers 12-month discounts reported at $16 to $20 a month against list, a segmented win-back test rather than a price change. Price is now the stated reason: Circana's tracking, reported in September 2026, puts more than 40% of US cancellations of Xbox Game Pass, PlayStation Plus and Nintendo Switch Online down to cost. That is the share of reasons given by people who cancelled, not evidence that more of them are cancelling.</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -58107,7 +58107,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Roblox pays the users who build its games in a platform currency redeemable for cash (over US$1.5 billion in 2025). Distribution is extreme: the top 1,000 creators take roughly 73% of all payouts, while around 85% of developers earn under US$100 a month.</t>
+          <t>Roblox pays the users who build its games in a platform currency redeemable for cash (over US$1.5 billion in 2025, and $1.7 billion across the twelve months to September 2026 on the company’s own count). Distribution is extreme: the top 1,000 creators take roughly 73% of all payouts, while around 85% of developers earn under US$100 a month. At its September 2026 Developers Conference the platform began unbuilding its own walls: creators will be able to export a Roblox game as a standalone app for PC, console and mobile under a programme called Play Roblox Everywhere, and payouts move onto external rails through Roblox Wallet, which pays out every business day to a bank account, and Roblox Card, a debit card spending the Wallet balance directly. Both are US-only for creators 18 and over to start, with global expansion stated for 2027.</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -58122,7 +58122,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
     </row>
@@ -58191,7 +58191,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>India's parliament passed a law banning online games played with money, threatening the survival of the fantasy-gaming sector that had been projected to reach $3.6 billion by 2029. Industry groups are challenging it constitutionally, and critics argue players will shift to offshore platforms.</t>
+          <t>India's parliament passed a law banning online games played with money, threatening the survival of the fantasy-gaming sector that had been projected to reach $3.6 billion by 2029. Industry groups are challenging it constitutionally, and critics argue players will shift to offshore platforms. The ban is also collapsing the disputes that sat above the sector: in September 2026 the Competition Commission of India closed WinZO’s antitrust case against Google, the market the complaint concerned having been legislated out of existence.</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -58206,7 +58206,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
     </row>
@@ -58359,7 +58359,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>The FTC's amended COPPA Rule took effect June 23, 2025. Its April 22, 2026 compliance deadline has now passed, expanding protected data to biometrics and unbundling consent for child-directed services, including many games. Enforcement, not drafting, is now the story: TikTok settled with DOJ for $400M in August 2026, following Epic's $275M and HoYoverse's $20M. Parallel regimes - UK Age Appropriate Design Code, EU GDPR, and Australia's eSafety Act - are converging on audited age assurance rather than self-attestation.</t>
+          <t>The FTC's amended COPPA Rule took effect June 23, 2025. Its April 22, 2026 compliance deadline has now passed, expanding protected data to biometrics and unbundling consent for child-directed services, including many games. Enforcement, not drafting, is now the story: TikTok settled with DOJ for $400M in August 2026, following Epic's $275M and HoYoverse's $20M. Parallel regimes - UK Age Appropriate Design Code, EU GDPR, and Australia's eSafety Act - are converging on audited age assurance rather than self-attestation. US state law is now a third layer beneath the federal rule: California enacted social media curbs for under-16s in September 2026, and Australia moved in the same week to require user control over algorithmic feeds, so a game with social features meets a different obligation in each jurisdiction it ships to.</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -58374,7 +58374,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
     </row>
@@ -58485,7 +58485,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Saudi Arabia's PIF has assembled a layered gaming portfolio (Savvy, Scopely, ESL FACEIT, listed stakes) capped by taking EA private, closed August 2026. PIF holds 93.4% directly, held outside Savvy alongside Silver Lake and Affinity Partners. Roughly $20B of purchase debt now sits on EA's own books, so the debate has shifted from sportswashing and esports capture toward layoffs, cancelled projects, and quiet self-censorship. Brian Ward, who built the portfolio from 2021, stepped down as Savvy's CEO on 1 September 2026, twelve days after the EA deal closed; PIF deputy governor Turqi Alnowaiser took over on an interim basis, moving day-to-day control closer to the fund.</t>
+          <t>Saudi Arabia's PIF has assembled a layered gaming portfolio (Savvy, Scopely, ESL FACEIT, listed stakes) capped by taking EA private, closed August 2026. PIF holds 93.4% directly, held outside Savvy alongside Silver Lake and Affinity Partners. Roughly $20B of purchase debt now sits on EA's own books, so the debate has shifted from sportswashing and esports capture toward layoffs, cancelled projects, and quiet self-censorship. Brian Ward, who built the portfolio from 2021, stepped down as Savvy's CEO on 1 September 2026, twelve days after the EA deal closed; PIF deputy governor Turqi Alnowaiser took over on an interim basis, moving day-to-day control closer to the fund. Consolidation of the portfolio itself is now reportedly under discussion: in September 2026 Bloomberg reported, and several trade outlets relayed, that PIF is weighing a merger of EA with Savvy that would put EA Sports FC, Madden, Battlefield, The Sims, Pokémon Go and Monopoly Go under one company. Treat it as one outlet’s anonymous sourcing — EA, Savvy and PIF all declined to comment and no decision has been taken.</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -58611,7 +58611,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Adoption keeps rising while sentiment collapses: 52% of surveyed game professionals now say generative AI is harming the industry, up from 30% the year before and 18% the year prior, with art and narrative roles most negative. Company-level use (52%) has decoupled from individual use (36%), and the argument has moved from opinion to enforcement. A European survey by Values Value and InGame Job, reported in September 2026, found the fear is pace before replacement: 61 percent expect generative AI to push them to work faster against 35 percent who fear for their role, and 35 percent of founders say they have already declined a hire because AI could do the work.</t>
+          <t>Adoption keeps rising while sentiment collapses: 52% of surveyed game professionals now say generative AI is harming the industry, up from 30% the year before and 18% the year prior, with art and narrative roles most negative. Adoption is also moving below the studio's decision: in September 2026 Unity shipped a first-party agentic coding plugin with 29 built-in engine skills, so the question for a team using the engine moves from whether to adopt to whether to switch it off. Company-level use (52%) has decoupled from individual use (36%), and the argument has moved from opinion to enforcement. A European survey by Values Value and InGame Job, reported in September 2026, found the fear is pace before replacement: 61 percent expect generative AI to push them to work faster against 35 percent who fear for their role, and 35 percent of founders say they have already declined a hire because AI could do the work.</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -58695,7 +58695,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>SAG-AFTRA members ratified the 2025 Interactive Media Agreement, ending the nearly yearlong video game strike, with consent and disclosure requirements for digital-replica use plus pay increases.The live disputes now involve people the agreement never covered — non-union writers like Saber's Stella Sacco, streamers auto-enrolled in Amazon's AI training, modded voices. Studios deny AI use, get caught, and disclose late.</t>
+          <t>SAG-AFTRA members ratified the 2025 Interactive Media Agreement, ending the nearly yearlong video game strike, with consent and disclosure requirements for digital-replica use plus pay increases.The live disputes now involve people the agreement never covered — non-union writers like Saber's Stella Sacco, streamers auto-enrolled in Amazon's AI training, modded voices, and now sports broadcasters: in September 2026 a commentator said EA had used generative AI to produce commentator voiceover in NHL 27, a category of voice the interactive agreement never reached. Studios deny AI use, get caught, and disclose late.</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -58710,7 +58710,7 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
     </row>
@@ -58779,7 +58779,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>The live-streaming audience is un-bundling from any single platform. Twitch stayed the most-watched at 19.2 billion hours in 2025 but shed 8.3 points of share, its Q4 the lowest since early 2020, while Kick grew 131% and Korea's Chzzk 44%. Creators now multi-home by default: Twitch anchors ~56% of the average simulcaster's hours, but the clip layer driving discovery runs through TikTok and YouTube.</t>
+          <t>The live-streaming audience is un-bundling from any single platform. Twitch stayed the most-watched at 19.2 billion hours in 2025 but shed 8.3 points of share, its Q4 the lowest since early 2020, while Kick grew 131% and Korea's Chzzk 44%. Creators now multi-home by default: Twitch anchors ~56% of the average simulcaster's hours, but the clip layer driving discovery runs through TikTok and YouTube. The money has begun to follow: across comparable brand deals in 2026, YouTube gaming creators commanded about 23% higher rates than Twitch streamers on Collabstr's data, so the hours-watched charts and the earnings charts no longer rank the platforms the same way.</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -58794,7 +58794,7 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
     </row>
@@ -58947,7 +58947,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>A long-running argument about whether buying a game confers ownership, reignited each time a publisher shuts down servers and renders a purchased title unplayable. Its most visible chapter, Stop Killing Games, gathered 1,294,188 verified signatures across 24 EU member states. On 16 June 2026 the Commission declined to propose a legal obligation, citing intellectual property constraints, offering a voluntary industry code of conduct instead; the campaign has pivoted to amending the Digital Fairness Act, due Q4 2026. The fight has since globalised into three tracks. Legislation: Brazil's PL 3612/2026 would mandate point-of-sale disclosure of server dependence, a two-year minimum support window, and a state preservation fund framed as digital cultural heritage. Litigation: UFC-Que Choisir is suing Ubisoft over The Crew, and a Dutch class action targets the PlayStation Store. Archives: Japan mandates legal deposit yet bars access without rightsholder consent, pushing its Game Preservation Society to open a US office. Sony's 2028 disc cutoff has pulled the question mainstream. In September 2026 the argument reached the console itself: Xbox's Disc-to-Digital, which converts a disc into a digital licence, launched to Insiders with Sega, Square Enix, Ubisoft and Bandai Namco discs returning "not participating", while GOG began printing big-box artwork under its preservation programme.</t>
+          <t>A long-running argument about whether buying a game confers ownership, reignited each time a publisher shuts down servers and renders a purchased title unplayable. Its most visible chapter, Stop Killing Games, gathered 1,294,188 verified signatures across 24 EU member states. On 16 June 2026 the Commission declined to propose a legal obligation, citing intellectual property constraints, offering a voluntary industry code of conduct instead; the campaign has pivoted to amending the Digital Fairness Act, due Q4 2026. The fight has since globalised into three tracks. Legislation: Brazil's PL 3612/2026 would mandate point-of-sale disclosure of server dependence, a two-year minimum support window, and a state preservation fund framed as digital cultural heritage. Litigation: UFC-Que Choisir is suing Ubisoft over The Crew, a Dutch class action targets the PlayStation Store, and in a US class action over the PlayStation Store’s “buy” button Sony argued in September 2026 that a reasonable consumer would not be misled into believing a digital purchase is owned — the first time the argument has been put on the record by a platform holder rather than inferred from a licence agreement. Archives: Japan mandates legal deposit yet bars access without rightsholder consent, pushing its Game Preservation Society to open a US office. Sony's 2028 disc cutoff has pulled the question mainstream. In September 2026 the argument reached the console itself: Xbox's Disc-to-Digital, which converts a disc into a digital licence, launched to Insiders with Sega, Square Enix, Ubisoft and Bandai Namco discs returning "not participating", while GOG began printing big-box artwork under its preservation programme.</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -58989,7 +58989,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Union drives hardened into institutions during the layoff era: 82% of US-based respondents to GDC's 2026 survey support unionisation, and one in four were laid off in the last two years. Microsoft's studios host the largest US unions and CWA's direct-join model now recruits across employers. Six European unions signed a cross-border action plan; France struck nationally. Nordic sectoral agreements remain the mature template. In September 2026 about 1,900 Blizzard workers ratified a CWA master contract with layoff recall rights, four extra weeks of severance and a duty on Microsoft to bargain over AI use, while the final tribunal hearing over Rockstar North's dismissal of union members opened in the UK.</t>
+          <t>Union drives hardened into institutions during the layoff era: 82% of US-based respondents to GDC's 2026 survey support unionisation, and one in four were laid off in the last two years. Microsoft's studios host the largest US unions and CWA's direct-join model now recruits across employers. Six European unions signed a cross-border action plan; France struck nationally. Nordic sectoral agreements remain the mature template. In September 2026 about 1,900 Blizzard workers ratified a CWA master contract with layoff recall rights, four extra weeks of severance and a duty on Microsoft to bargain over AI use, while the final tribunal hearing over Rockstar North's dismissal of union members opened in the UK, where the company confirmed it had kept an informant inside the union workers' Discord server for over two and a half years. Rockstar rejects the claims and says it will defend itself vigorously.</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -59157,7 +59157,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Studio investment has fallen about 85% from its 2021 peak to below 2019 levels while revenues rose 30 to 40%, and Matthew Ball's 2026 report argues the industry now invests less in new game development, as a share of net revenue, than at any point on record. Marvel's Spider-Man went from just over $100M to more than $300M across three games without proportionate sales. Studios are shipping smaller. The argument is whether that is a chosen strategy or a budget line.</t>
+          <t>Studio investment has fallen about 85% from its 2021 peak to below 2019 levels while revenues rose 30 to 40%, and Matthew Ball's 2026 report argues the industry now invests less in new game development, as a share of net revenue, than at any point on record. Marvel's Spider-Man went from just over $100M to more than $300M across three games without proportionate sales. Studios are shipping smaller. The argument is whether that is a chosen strategy or a budget line. The composition is moving as well as the total: Values Value's Talent Signals report, reported in September 2026, puts European studio spending on external talent up 63% in 2025 against 55% globally, and describes a two-tier team model of a small permanent core with a contractor periphery hired by project phase. A falling investment line and a rising outside-hands line are the same decision seen twice.</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
@@ -59172,7 +59172,7 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Aug 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
     </row>
@@ -59199,7 +59199,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>After five years of dissolving platform walls, 2026 partly rebuilt them. Xbox, which had begun publishing on PlayStation and Nintendo, named Gears of War: E-Day and Clockwork Revolution as console exclusives that are not timed, while saying multiplayer and live-service titles stay multiplatform. Sony runs the mirror policy, multiplayer everywhere and single-player held back. Circana's Q1 2026 survey finds 41% of US players cite exclusives as their main reason for owning a console.</t>
+          <t>After five years of dissolving platform walls, 2026 partly rebuilt them. Xbox, which had begun publishing on PlayStation and Nintendo, named Gears of War: E-Day and Clockwork Revolution as console exclusives that are not timed, while saying multiplayer and live-service titles stay multiplatform. Sony runs the mirror policy, multiplayer everywhere and single-player held back. Circana's Q1 2026 survey finds 41% of US players cite exclusives as their main reason for owning a console. The rebuilding is not one-directional. In September 2026 Kojima Productions said it had “unexpectedly received notice” from PlayStation that Physint, its Metal Gear successor, would be cancelled, and Xbox Game Studios took over publishing; reporting the following day attributed Sony's exit to budget overruns, missed deadlines, Death Stranding's revenue against expectations, and the fact that Physint was planned for PlayStation and PC rather than as a true exclusive. Read it as the limit of the policy: a platform holder will drop a marquee single-player project when the exclusivity it buys is partial and the budget is not.</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -59214,7 +59214,7 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t>Aug 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
     </row>
@@ -59715,7 +59715,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Market saturation is a developer concern in GDC's 2026 State of Gaming</t>
+          <t>Newzoo: Most established live-service and evergreen titles were flat or down year over year in H1 2026</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -59726,7 +59726,7 @@
       <c r="D12" s="3" t="inlineStr"/>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>https://reg.gdconf.com/2026-SOTI/</t>
+          <t>https://www.gamesindustry.biz/newzoo-most-established-live-service-and-evergreen-titles-were-flat-or-down-year-over-year-in-h1-2026</t>
         </is>
       </c>
     </row>
@@ -59807,7 +59807,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Xbox introduces cloud streaming limits for Game Pass, purchase options for ad-hoc use</t>
+          <t>More than 40% of people cancelling Xbox Game Pass, PlayStation Plus and Nintendo Switch Online subscriptions blame rising costs</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -59818,7 +59818,7 @@
       <c r="D16" s="3" t="inlineStr"/>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>https://thisweekinvideogames.com/news/xbox-introduces-cloud-streaming-limits-for-game-pass-purchase-options-for-ad-hoc-use/</t>
+          <t>https://www.eurogamer.net/xbox-game-pass-playstation-plus-nintendo-cancellations-rising-costs</t>
         </is>
       </c>
     </row>
@@ -59876,18 +59876,18 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Increasing DevEx — Creators Will Now Earn 8.5% More</t>
+          <t>Roblox says it'll help developers release their games as standalone apps across PC, mobile, and consoles</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Community</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr"/>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>https://devforum.roblox.com/t/increasing-devex-%E2%80%94-creators-will-now-earn-85-more/3920159</t>
+          <t>https://www.tubefilter.com/2026/09/11/roblox-developers-conference-2026-game-apps-creator-payouts-roblox-wallet-roblox-card/</t>
         </is>
       </c>
     </row>
@@ -60014,22 +60014,18 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>The shutdown from a lawyer's POV</t>
+          <t>CCI Closes Winzo's Google Antitrust Case After Money Gaming Ban</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Analysis</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr"/>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1UoKPb6qKRY</t>
+          <t>https://respawn.outlookindia.com/gaming/gaming-news/cci-closes-winzos-google-antitrust-case-after-money-gaming-ban</t>
         </is>
       </c>
     </row>
@@ -60298,22 +60294,18 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Roblox is Being Forced To Fix Their Safety Issues</t>
+          <t>California enacts new social media curbs for children under 16</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Community</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>video</t>
-        </is>
-      </c>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr"/>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>https://www.tiktok.com/@justsaysteven/video/7676171623145229582</t>
+          <t>https://www.pocketgamer.biz/california-enacts-new-social-media-curbs-for-children-under-16/</t>
         </is>
       </c>
     </row>
@@ -60490,7 +60482,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>EA could be set for 'mass layoffs' as it aims to cut costs following Saudi acquisition</t>
+          <t>Saudi Arabia's PIF reportedly considering to combine EA with Savvy Games Group</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -60501,7 +60493,7 @@
       <c r="D45" s="3" t="inlineStr"/>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>https://www.videogameschronicle.com/news/ea-could-be-set-for-mass-layoffs-as-it-aims-to-cut-costs-following-saudi-acquisition/</t>
+          <t>https://www.gamesindustry.biz/saudi-arabias-pif-reportedly-considering-to-combine-ea-with-savvy-games-group</t>
         </is>
       </c>
     </row>
@@ -60839,7 +60831,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Video game lawyer says all her clients have anti-AI contracts because gamers hate it</t>
+          <t>Report: EA's NHL 27 is using genAI to create voiceover, claims a sports commentator</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -60850,7 +60842,7 @@
       <c r="D60" s="3" t="inlineStr"/>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>https://www.gamesradar.com/games/echoing-palworld-dev-video-game-lawyer-says-all-her-clients-have-anti-ai-contracts-because-gamers-hate-it-and-its-a-copyright-landmine-i-think-were-going-to-see-lawsuits/</t>
+          <t>https://www.gamedeveloper.com/business/report-ea-s-nhl-27-is-using-genai-to-create-voiceover-claims-a-sports-commentator</t>
         </is>
       </c>
     </row>
@@ -60977,18 +60969,18 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Twitch now uses channel VODs, clips and chat messages to train generative AI by default</t>
+          <t>YouTube gaming creators "command 23% higher deal rates than Twitch"</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Community</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr"/>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>https://www.reddit.com/r/LivestreamFail/comments/1vmnkfz/twitch_now_uses_channel_vods_clips_and_chat/</t>
+          <t>https://www.pocketgamer.biz/youtube-gaming-creators-command-23-higher-deal-rates-than-twitch/</t>
         </is>
       </c>
     </row>
@@ -61606,18 +61598,18 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>GDC: The State of the Game Industry 2026</t>
+          <t>European studio expenditure on external talent rises 63% in 2025</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr"/>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>https://gamedevreports.substack.com/p/gdc-the-state-of-the-game-industry-fcf</t>
+          <t>https://www.gamesindustry.biz/european-studio-expenditure-on-external-talent-rises-63-in-2025</t>
         </is>
       </c>
     </row>
@@ -61675,7 +61667,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Xbox multiplayer and live service games will still be multiplatform, Matt Booty says</t>
+          <t>Xbox to publish Kojima Productions' Physint after PlayStation said it would cancel the project</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -61686,7 +61678,7 @@
       <c r="D96" s="3" t="inlineStr"/>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>https://www.videogameschronicle.com/news/xbox-multiplayer-and-live-service-games-will-still-be-multiplatform-going-forward-matt-booty-says/</t>
+          <t>https://www.gamesindustry.biz/xbox-to-publish-kojima-productions-physint-after-it-unexpectedly-received-notice-from-playstation-that-it-would-cancel-the-project</t>
         </is>
       </c>
     </row>

--- a/games-research-starter-pack.xlsx
+++ b/games-research-starter-pack.xlsx
@@ -58368,7 +58368,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
     </row>

--- a/games-research-starter-pack.xlsx
+++ b/games-research-starter-pack.xlsx
@@ -58606,7 +58606,7 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
     </row>
@@ -58648,7 +58648,7 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
     </row>
@@ -58732,7 +58732,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
     </row>
@@ -58774,7 +58774,7 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
     </row>
@@ -58865,7 +58865,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>China's banhao throttles games</t>
+          <t>China throttles game approvals</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -58885,12 +58885,12 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Every game monetized in China needs an NPPA publication license (版号, banhao), and only a licensed Chinese publisher can hold one — foreign studios apply through a partner or not at all. Supply is a dial the regulator turns: total freeze in 2021-22, then 1,771 approvals in 2025, and 2026 running ~19% ahead of that pace at 1,110 domestic and 37 imported licenses by the July batch. Imports now clear on a roughly two-month cadence. The binding constraint has quietly moved downstream — real-name verification SDKs and server-side minor-cutoff enforcement are now the harder half.</t>
+          <t>Foreign games now get approved roughly every two months. The license itself is no longer the hardest part. The bigger hurdle now comes after approval: games must verify each player's real identity and automatically enforce the limits on how long and when minors can play.</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Batch cadence is the cleanest public read on Chinese market access and regulatory mood — but approvals rose while H1 gacha revenue fell 8.97%, so permission and commercial outcome have decoupled.</t>
+          <t>China controls how many games reach its market by adjusting how many licenses it approves. That license is called a banhao (版号), and China began issuing far fewer beginning in 2018.</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -58900,7 +58900,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
     </row>
@@ -58984,7 +58984,7 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
     </row>
@@ -59152,7 +59152,7 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
     </row>
@@ -59236,7 +59236,7 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
     </row>
@@ -59362,7 +59362,7 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
     </row>
@@ -59446,7 +59446,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
     </row>
@@ -59572,7 +59572,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Aug 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
     </row>
@@ -59698,7 +59698,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>Aug 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
     </row>
@@ -59740,7 +59740,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Aug 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
     </row>
@@ -60885,7 +60885,7 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>China's banhao throttles games</t>
+          <t>China throttles game approvals</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -60908,7 +60908,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>China's banhao throttles games</t>
+          <t>China throttles game approvals</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -60931,7 +60931,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>China's banhao throttles games</t>
+          <t>China throttles game approvals</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">

--- a/games-research-starter-pack.xlsx
+++ b/games-research-starter-pack.xlsx
@@ -58759,12 +58759,12 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>After Black Myth: Wukong made China's AAA case, studios moved from one-off proof to franchise construction. Game Science skipped a Wukong sequel for Black Myth: Zhong Kui, meaning that mythology is being treated as a catalog, not a hook. S-GAME, Everstone/NetEase and miHoYo ship parallel original IP. Beijing formalized it: gaming entered the 15th Five-Year Plan, and overseas revenue hit $12.37B in H1 2026, up 30%.</t>
+          <t>Black Myth: Wukong, a 2024 action game based on a classic Chinese legend, proved a Chinese studio could make a global big-budget hit. Studios are now trying to turn that one success into lasting series. Its developer, Game Science, is following it with Black Myth: Zhong Kui, a game about a different figure from Chinese folklore rather than a direct sequel. That suggests it sees Chinese mythology as a deep source of future games, not a one-time hook. Other Chinese studios, including S-GAME, Everstone (working with NetEase), and miHoYo, are building original worlds of their own. The government is backing the shift: games are now part of China's 15th Five-Year Plan, its national economic roadmap. Chinese games also earned $12.37 billion outside China in the first half of 2026, up 30%.</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Premium games are no longer a JP/US/EU default. It resets competitive analysis, soft-power framing, and talent flows — while rising AAA costs, publicly acknowledged by studios, become the first real constraint.</t>
+          <t>China's games industry is known for free-to-play mobile games, and big-budget games you buy up front used to come mostly from Japan, the US, and Europe. That's changing, which affects who counts as a competitor, how China uses games to spread its culture abroad, and where skilled developers want to work. The first real limit on this growth is cost: studios themselves say big-budget games are getting more expensive to make.</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">

--- a/games-research-starter-pack.xlsx
+++ b/games-research-starter-pack.xlsx
@@ -58838,17 +58838,17 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>BR; CN; Global; IN; SEA</t>
+          <t>CN; Global</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Matthew Ball's analysis of where 2025's growth actually went: of the ~$10 billion industry increase versus 2021, about $4 billion was in China and another $1.5 billion went to China-made games in global markets, with 84% of Chinese game revenue going to domestically made games. This means that growth is concentrated in places and platforms many Western publishers can't reach. Niko Partners puts China's 2025 games revenue at $51.8 billion, up 5.4 percent and above $50 billion for the first time, with annual ARPU past $70 and mini games near a fifth of mobile spend; it forecasts $53.9 billion for 2026 and $59.8 billion by 2030.</t>
+          <t>The games industry earned about $10 billion more in 2025 than in 2021. According to analyst Matthew Ball's analysis, about $4 billion of that increase came from China, and another $1.5 billion from Chinese-made games sold abroad. Inside China, about 83% of game revenue goes to Chinese-made games by the official industry report's 2025 count; Ball puts it at 84%. So much of the growth is in places many Western publishers can't compete. Research firm Niko Partners puts China's 2025 game revenue at $51.8 billion, up 5.4% and over $50 billion for the first time. The average player spent more than $70 that year, and mini games (small games played inside apps like WeChat, with no download) made up nearly a fifth of mobile spending. Niko expects $53.9 billion in 2026 and $59.8 billion by 2030.</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Prevents the classic error of citing 'industry growth' as if it were evenly distributed. The divergence between player growth and accessible revenue is the real story.</t>
+          <t>When people say “the games industry is growing,” much of that growth is happening in China, where Western companies have limited access. The real story is the gap between where players are growing and where Western publishers can actually make money.</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">

--- a/games-research-starter-pack.xlsx
+++ b/games-research-starter-pack.xlsx
@@ -59075,7 +59075,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Streamers fragment across platforms</t>
+          <t>Streaming audiences split across platforms</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -59095,12 +59095,12 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>The live-streaming audience is un-bundling from any single platform. Twitch stayed the most-watched at 19.2 billion hours in 2025 but shed 8.3 points of share, its Q4 the lowest since early 2020, while Kick grew 131% and Korea's Chzzk 44%. Creators now multi-home by default: Twitch anchors ~56% of the average simulcaster's hours, but the clip layer driving discovery runs through TikTok and YouTube. The money has begun to follow: across comparable brand deals in 2026, YouTube gaming creators commanded about 23% higher rates than Twitch streamers on Collabstr's data, so the hours-watched charts and the earnings charts no longer rank the platforms the same way.</t>
+          <t>Twitch is still the most-watched live-streaming platform, but it has been losing ground each year while its rivals grow. Most streamers now broadcast on several platforms at once, usually keeping Twitch as their main home. New viewers, though, tend to find them through short clips on TikTok and YouTube. The money is following: YouTube gaming creators now earn more per brand deal than Twitch streamers, so the platform with the most viewing is no longer the one that pays best.</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Fragmentation is the end state, not a transition. Korea settled into a SOOP/Chzzk duopoly two years after Twitch left. And Kick's growth is IRL and combat sports, not the gaming audience Twitch lost, so share charts mislead. Single-platform reads of "streaming culture" break.</t>
+          <t>Live-streaming viewers used to gather mostly on Twitch. Now they're spread across YouTube, TikTok, newer rivals like Kick, and local services in countries such as South Korea, and there's no sign they're coming back together. Any single platform now shows only part of the picture, and share charts can mislead, since platforms grow with different audiences.</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -61234,7 +61234,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>Streamers fragment across platforms</t>
+          <t>Streaming audiences split across platforms</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -61257,7 +61257,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Streamers fragment across platforms</t>
+          <t>Streaming audiences split across platforms</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -61280,7 +61280,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>Streamers fragment across platforms</t>
+          <t>Streaming audiences split across platforms</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">

--- a/games-research-starter-pack.xlsx
+++ b/games-research-starter-pack.xlsx
@@ -59599,12 +59599,12 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Paid reach is contracting while creator-led discovery grows. GDC's 2026 survey of more than 2,300 professionals put streamers ahead of paid advertising as a user-acquisition channel, 39% against 31%, behind social media at 65%. On mobile, 68% of the top 100 US-grossing games running acquisition in 2025 lost at least 10% of their US channel impression share year over year. On Steam, a game that would have opened to 500 concurrent players eight years ago now opens to 100 or fewer, against a record 18,597 releases in 2024. GameDiscoverCo's read of 2,569 Steam launches from January 2024 to August 2026 puts the median ratio of peak demo concurrent users to peak launch concurrent users at 3.0x, 6.2x for the strongest demos and 1.3x for the weakest, which makes the demo the discovery instrument a launch is judged by before it happens.</t>
+          <t>Paid ads are reaching fewer players, and more people now find games through social media, streamers, and YouTubers. Developers now rate streamers as a better way to find players than paid advertising. Meanwhile, Steam releases far more games each year than it used to, so even good games launch to much smaller crowds. That has made free demos important: how many people play a demo is now the best early sign of how the full game will launch.</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Visibility rather than production is now the binding constraint on a game reaching anyone, and the cheapest remaining channel is a creator deciding to play it, which nobody can buy reliably.</t>
+          <t>Making a game has gotten easier, and Steam, the store where most new PC games come out, now releases so many each year that the hard part is getting anyone to notice an individual title. The cheapest way to get noticed is a streamer or YouTuber choosing to play it, and money can't reliably buy that.</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">

--- a/games-research-starter-pack.xlsx
+++ b/games-research-starter-pack.xlsx
@@ -6166,12 +6166,12 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>family-gaming-database</t>
+          <t>nintendo-ir</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Family Gaming Database</t>
+          <t>Nintendo IR</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -6181,27 +6181,27 @@
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Data tool</t>
+          <t>Company disclosure</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Corporate IR</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>A hand-curated, searchable database of about 3,600 video games and 200 board games, written for parents and carers: each entry carries age ratings, costs and in-game spending, and accessibility detail across difficulty, reading, navigation, controls, visuals, audio and communication, and the whole set filters by platform, age and those features. Founded and edited by the journalist Andy Robertson. Use it to see how a game is explained to a family audience, or to find games by accessibility feature. | Curated, not complete: the team picks the games that matter to families, so a game's absence says nothing about the game. Built in the UK but not UK-only; its partners include Australia's IGEA and the US ratings board.</t>
+          <t>Hardware/software splits per region, million-seller lists, management Q&amp;A</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>Global; UK</t>
+          <t>Global; JP</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>English; Japanese</t>
         </is>
       </c>
       <c r="I82" s="3" t="inlineStr">
@@ -6211,20 +6211,12 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>https://www.familygamingdatabase.com/</t>
+          <t>https://nintendo.co.jp/ir</t>
         </is>
       </c>
       <c r="K82" s="3" t="inlineStr"/>
-      <c r="L82" s="3" t="inlineStr">
-        <is>
-          <t>Independent</t>
-        </is>
-      </c>
-      <c r="M82" s="3" t="inlineStr">
-        <is>
-          <t>States that it is editorially independent, free and without adverts, and funded by partnerships and labelled sponsored activity. The partners it names include PlayStation and Xbox, whose games it lists, plus HSBC UK, the VSC Rating Board, Hookshot Media, Kidas, IGEA and Ask About Games.</t>
-        </is>
-      </c>
+      <c r="L82" s="3" t="inlineStr"/>
+      <c r="M82" s="3" t="inlineStr"/>
       <c r="N82" s="3" t="inlineStr"/>
       <c r="O82" s="3" t="inlineStr"/>
       <c r="P82" s="3" t="inlineStr"/>
@@ -6234,12 +6226,12 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>nintendo-ir</t>
+          <t>sony-game-and-network-services</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Nintendo IR</t>
+          <t>Sony Game &amp; Network Services (IR)</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -6259,7 +6251,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>Hardware/software splits per region, million-seller lists, management Q&amp;A</t>
+          <t>PS5 sell-through, PS Plus, first-party performance in segment reporting</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -6279,7 +6271,7 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
-          <t>https://nintendo.co.jp/ir</t>
+          <t>https://sony.com/en/SonyInfo/IR</t>
         </is>
       </c>
       <c r="K83" s="3" t="inlineStr"/>
@@ -6294,12 +6286,12 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>sony-game-and-network-services</t>
+          <t>tencent-ir</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Sony Game &amp; Network Services (IR)</t>
+          <t>Tencent IR</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -6319,17 +6311,17 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>PS5 sell-through, PS Plus, first-party performance in segment reporting</t>
+          <t>The single best free window into Chinese gaming and its global ownership web (Riot, Supercell, stakes everywhere)</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>Global; JP</t>
+          <t>CN; Global</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>English; Japanese</t>
+          <t>Chinese; English</t>
         </is>
       </c>
       <c r="I84" s="3" t="inlineStr">
@@ -6339,7 +6331,7 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>https://sony.com/en/SonyInfo/IR</t>
+          <t>https://tencent.com/en-us/investors</t>
         </is>
       </c>
       <c r="K84" s="3" t="inlineStr"/>
@@ -6354,12 +6346,12 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>tencent-ir</t>
+          <t>netease-ir</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Tencent IR</t>
+          <t>NetEase IR</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -6379,12 +6371,12 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>The single best free window into Chinese gaming and its global ownership web (Riot, Supercell, stakes everywhere)</t>
+          <t>Second biggest CN major with notable JP studio investments</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>CN; Global</t>
+          <t>CN; JP</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
@@ -6399,7 +6391,7 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>https://tencent.com/en-us/investors</t>
+          <t>https://ir.netease.com</t>
         </is>
       </c>
       <c r="K85" s="3" t="inlineStr"/>
@@ -6414,12 +6406,12 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>netease-ir</t>
+          <t>nexon-ir</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>NetEase IR</t>
+          <t>Nexon IR</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -6439,17 +6431,17 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>Second biggest CN major with notable JP studio investments</t>
+          <t>Founded in Korea but listed in Tokyo, offers per-title and per-region detail and the economics of live-ops</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>CN; JP</t>
+          <t>JP; KR</t>
         </is>
       </c>
       <c r="H86" s="3" t="inlineStr">
         <is>
-          <t>Chinese; English</t>
+          <t>English; Japanese</t>
         </is>
       </c>
       <c r="I86" s="3" t="inlineStr">
@@ -6459,7 +6451,7 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>https://ir.netease.com</t>
+          <t>https://ir.nexon.co.jp</t>
         </is>
       </c>
       <c r="K86" s="3" t="inlineStr"/>
@@ -6474,12 +6466,12 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>nexon-ir</t>
+          <t>krafton-ir</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Nexon IR</t>
+          <t>Krafton IR</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -6499,17 +6491,17 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>Founded in Korea but listed in Tokyo, offers per-title and per-region detail and the economics of live-ops</t>
+          <t>PUBG economics and India exposure</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>JP; KR</t>
+          <t>Global; KR</t>
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr">
         <is>
-          <t>English; Japanese</t>
+          <t>English; Korean</t>
         </is>
       </c>
       <c r="I87" s="3" t="inlineStr">
@@ -6519,7 +6511,7 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>https://ir.nexon.co.jp</t>
+          <t>https://krafton.com</t>
         </is>
       </c>
       <c r="K87" s="3" t="inlineStr"/>
@@ -6534,12 +6526,12 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>krafton-ir</t>
+          <t>ncsoft-ir</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Krafton IR</t>
+          <t>NCSoft IR</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -6559,12 +6551,12 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>PUBG economics and India exposure</t>
+          <t>Lineage economics, which is important for the ongoing MMO monetization story (i.e., people getting tired of being bilked by games show up in the numbers first here)</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>Global; KR</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="H88" s="3" t="inlineStr">
@@ -6579,7 +6571,7 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
-          <t>https://krafton.com</t>
+          <t>https://ncsoft.com</t>
         </is>
       </c>
       <c r="K88" s="3" t="inlineStr"/>
@@ -6594,12 +6586,12 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>ncsoft-ir</t>
+          <t>netmarble-kakao-games-ir</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>NCSoft IR</t>
+          <t>Netmarble / Kakao Games IR</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -6619,7 +6611,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>Lineage economics, which is important for the ongoing MMO monetization story (i.e., people getting tired of being bilked by games show up in the numbers first here)</t>
+          <t>KR mobile publishing economics</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
@@ -6639,7 +6631,7 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
-          <t>https://ncsoft.com</t>
+          <t>https://netmarble.com</t>
         </is>
       </c>
       <c r="K89" s="3" t="inlineStr"/>
@@ -6654,12 +6646,12 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>netmarble-kakao-games-ir</t>
+          <t>capcom-ir</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Netmarble / Kakao Games IR</t>
+          <t>Capcom IR</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -6679,17 +6671,17 @@
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>KR mobile publishing economics</t>
+          <t>Per-title lifetime sales through the Platinum Titles database, which is the most detailed public disclosure any Japanese publisher offers. Regional revenue splits and digital share are given each quarter.</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Global; JP</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>English; Korean</t>
+          <t>English; Japanese</t>
         </is>
       </c>
       <c r="I90" s="3" t="inlineStr">
@@ -6699,7 +6691,7 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
-          <t>https://netmarble.com</t>
+          <t>https://www.capcom.co.jp/ir/english/</t>
         </is>
       </c>
       <c r="K90" s="3" t="inlineStr"/>
@@ -6714,12 +6706,12 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>capcom-ir</t>
+          <t>electronic-arts-ir</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Capcom IR</t>
+          <t>Electronic Arts IR</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -6739,17 +6731,17 @@
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>Per-title lifetime sales through the Platinum Titles database, which is the most detailed public disclosure any Japanese publisher offers. Regional revenue splits and digital share are given each quarter.</t>
+          <t>Live service and sports franchise economics, with net bookings rather than revenue as the headline measure. Read the non-GAAP footnotes before citing any figure.</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>Global; JP</t>
+          <t>Global; US</t>
         </is>
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>English; Japanese</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I91" s="3" t="inlineStr">
@@ -6759,7 +6751,7 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
-          <t>https://www.capcom.co.jp/ir/english/</t>
+          <t>https://ir.ea.com/</t>
         </is>
       </c>
       <c r="K91" s="3" t="inlineStr"/>
@@ -6774,12 +6766,12 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>electronic-arts-ir</t>
+          <t>roblox-ir-sec-filings</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Electronic Arts IR</t>
+          <t>Roblox IR + SEC filings</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -6799,7 +6791,7 @@
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>Live service and sports franchise economics, with net bookings rather than revenue as the headline measure. Read the non-GAAP footnotes before citing any figure.</t>
+          <t>DAUs, hours engaged, bookings and developer payouts, with DAUs by region every quarter. The under-13 and 13-and-over DAU split, self-reported, ran in the quarterly supplemental deck through Q3 2025 and was dropped for the move to age checks; since Q1 2026 the shareholder letter gives only a percentage split of age-checked users, with a note that it is not comparable to the old series. The supplemental deck lives on ir.roblox.com, not in the 10-Q.</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
@@ -6819,7 +6811,7 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
-          <t>https://ir.ea.com/</t>
+          <t>https://ir.roblox.com</t>
         </is>
       </c>
       <c r="K92" s="3" t="inlineStr"/>
@@ -6834,12 +6826,12 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>roblox-ir-sec-filings</t>
+          <t>microsoft-10-k-10-q</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Roblox IR + SEC filings</t>
+          <t>Microsoft 10-K/10-Q (Gaming segment)</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -6854,12 +6846,12 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Corporate IR</t>
+          <t>Corporate filings</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>DAUs, hours engaged, bookings and developer payouts, with DAUs by region every quarter. The under-13 and 13-and-over DAU split, self-reported, ran in the quarterly supplemental deck through Q3 2025 and was dropped for the move to age checks; since Q1 2026 the shareholder letter gives only a percentage split of age-checked users, with a note that it is not comparable to the old series. The supplemental deck lives on ir.roblox.com, not in the 10-Q.</t>
+          <t>Post-Activision gaming segment scale, Game Pass signals in commentary</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -6879,7 +6871,7 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>https://ir.roblox.com</t>
+          <t>https://microsoft.com/investor</t>
         </is>
       </c>
       <c r="K93" s="3" t="inlineStr"/>
@@ -6894,12 +6886,12 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>microsoft-10-k-10-q</t>
+          <t>gamesquare-ir</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Microsoft 10-K/10-Q (Gaming segment)</t>
+          <t>GameSquare IR (Stream Hatchet reports)</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -6914,17 +6906,17 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>Corporate filings</t>
+          <t>Corporate IR</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>Post-Activision gaming segment scale, Game Pass signals in commentary</t>
+          <t>Where Stream Hatchet quarterly livestreaming reports publish free</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>Global; US</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
@@ -6939,7 +6931,7 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>https://microsoft.com/investor</t>
+          <t>https://gamesquare.com</t>
         </is>
       </c>
       <c r="K94" s="3" t="inlineStr"/>
@@ -6954,12 +6946,12 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>gamesquare-ir</t>
+          <t>anycolor-ir</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>GameSquare IR (Stream Hatchet reports)</t>
+          <t>ANYCOLOR IR (にじさんじ / Nijisanji)</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -6979,17 +6971,17 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>Where Stream Hatchet quarterly livestreaming reports publish free</t>
+          <t>Quarterly filings disclose talent counts, revenue mix, and per-segment economics of the VTuber business</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Global; JP</t>
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>English; Japanese</t>
         </is>
       </c>
       <c r="I95" s="3" t="inlineStr">
@@ -6999,7 +6991,7 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>https://gamesquare.com</t>
+          <t>https://ir.anycolor.co.jp</t>
         </is>
       </c>
       <c r="K95" s="3" t="inlineStr"/>
@@ -7014,12 +7006,12 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>anycolor-ir</t>
+          <t>cover-corp-ir</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>ANYCOLOR IR (にじさんじ / Nijisanji)</t>
+          <t>Cover Corp IR (ホロライブ / hololive production, Hororaibu)</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -7039,7 +7031,7 @@
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>Quarterly filings disclose talent counts, revenue mix, and per-segment economics of the VTuber business</t>
+          <t>Primary disclosure for hololives</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
@@ -7059,7 +7051,7 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>https://ir.anycolor.co.jp</t>
+          <t>https://cover-corp.com/ir/</t>
         </is>
       </c>
       <c r="K96" s="3" t="inlineStr"/>
@@ -7074,12 +7066,12 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>cover-corp-ir</t>
+          <t>nazara-technologies</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Cover Corp IR (ホロライブ / hololive production, Hororaibu)</t>
+          <t>Nazara Technologies (NSE: NAZARA)</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -7099,17 +7091,17 @@
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>Primary disclosure for hololives</t>
+          <t>A quarterly X-ray of the ecosystem: owns/holds NODWIN (esports events, AFK Gaming), Sportskeeda, Kiddopia, WCC, plus ad tech and location-based entertainment. Its calls narrate the whole Indian games economy, including the RMG-ban fallout (PokerBaazi)</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>Global; JP</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>English; Japanese</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I97" s="3" t="inlineStr">
@@ -7119,7 +7111,7 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>https://cover-corp.com/ir/</t>
+          <t>https://investors.nazara.com/</t>
         </is>
       </c>
       <c r="K97" s="3" t="inlineStr"/>
@@ -7134,12 +7126,12 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>nazara-technologies</t>
+          <t>sea-limited-garena</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Nazara Technologies (NSE: NAZARA)</t>
+          <t>Sea Limited (NYSE: SE): Garena</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -7154,17 +7146,17 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>Corporate IR</t>
+          <t>Corporate filings</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>A quarterly X-ray of the ecosystem: owns/holds NODWIN (esports events, AFK Gaming), Sportskeeda, Kiddopia, WCC, plus ad tech and location-based entertainment. Its calls narrate the whole Indian games economy, including the RMG-ban fallout (PokerBaazi)</t>
+          <t>The closest thing to a quarterly census of SEA gaming: Garena's bookings, QAU/QPU (quarterly active/paying users), and management commentary on Free Fire's markets. Read alongside Shopee/SeaMoney segments that shape the same wallets. Vertically integrated: Sea owns the publisher, the payment rail, and esports circuits it reports on Singapore-based, region-wide.</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
@@ -7179,7 +7171,7 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>https://investors.nazara.com/</t>
+          <t>https://www.sea.com/investor/home</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr"/>
@@ -7194,12 +7186,12 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>sea-limited-garena</t>
+          <t>vng-corporation</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Sea Limited (NYSE: SE): Garena</t>
+          <t>VNG Corporation (UPCoM: VNZ)</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -7219,7 +7211,7 @@
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>The closest thing to a quarterly census of SEA gaming: Garena's bookings, QAU/QPU (quarterly active/paying users), and management commentary on Free Fire's markets. Read alongside Shopee/SeaMoney segments that shape the same wallets. Vertically integrated: Sea owns the publisher, the payment rail, and esports circuits it reports on Singapore-based, region-wide.</t>
+          <t>The inside view of the post-Decree-147 Vietnamese market from its principal beneficiary: licensing costs, title portfolio, and the economics of a market foreign publishers just exited</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
@@ -7229,7 +7221,7 @@
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>English; Vietnamese</t>
         </is>
       </c>
       <c r="I99" s="3" t="inlineStr">
@@ -7239,7 +7231,7 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>https://www.sea.com/investor/home</t>
+          <t>https://www.vng.com.vn/</t>
         </is>
       </c>
       <c r="K99" s="3" t="inlineStr"/>
@@ -7254,12 +7246,12 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>vng-corporation</t>
+          <t>playside-studios</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>VNG Corporation (UPCoM: VNZ)</t>
+          <t>PlaySide Studios (ASX: PLY)</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -7274,22 +7266,22 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>Corporate filings</t>
+          <t>Corporate IR</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>The inside view of the post-Decree-147 Vietnamese market from its principal beneficiary: licensing costs, title portfolio, and the economics of a market foreign publishers just exited</t>
+          <t>A rare public window on AU development economics: original-IP vs work-for-hire revenue split, licensing economics (Dumb Ways to Die, Game of Thrones/WBIE, Warcraft 3), and the volatility of a mid-size studio's P&amp;L in real time</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>English; Vietnamese</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I100" s="3" t="inlineStr">
@@ -7299,7 +7291,7 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>https://www.vng.com.vn/</t>
+          <t>https://www.listcorp.com/asx/ply/playside-studios-limited</t>
         </is>
       </c>
       <c r="K100" s="3" t="inlineStr"/>
@@ -7314,12 +7306,12 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>playside-studios</t>
+          <t>embracer-group</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>PlaySide Studios (ASX: PLY)</t>
+          <t>Embracer Group (Nasdaq Stockholm: EMBRAC B)</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -7339,12 +7331,12 @@
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>A rare public window on AU development economics: original-IP vs work-for-hire revenue split, licensing economics (Dumb Ways to Die, Game of Thrones/WBIE, Warcraft 3), and the volatility of a mid-size studio's P&amp;L in real time</t>
+          <t>The most consequential single filing stream in European games, tracking the acquisition-boom-to-restructuring arc in real time: SEK 7.2bn impairments, studio closures, the Coffee Stain spin-off (Dec 2025) and the planned Fellowship Entertainment separation targeted for 2027. Essential context for dozens of studios worldwide that Embracer owns or shed Focused on Sweden.</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Nordics</t>
         </is>
       </c>
       <c r="H101" s="3" t="inlineStr">
@@ -7359,7 +7351,7 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>https://www.listcorp.com/asx/ply/playside-studios-limited</t>
+          <t>https://embracer.com/investors/</t>
         </is>
       </c>
       <c r="K101" s="3" t="inlineStr"/>
@@ -7374,12 +7366,12 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>embracer-group</t>
+          <t>paradox-interactive</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Embracer Group (Nasdaq Stockholm: EMBRAC B)</t>
+          <t>Paradox Interactive (Nasdaq Stockholm: PDX)</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -7399,7 +7391,7 @@
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>The most consequential single filing stream in European games, tracking the acquisition-boom-to-restructuring arc in real time: SEK 7.2bn impairments, studio closures, the Coffee Stain spin-off (Dec 2025) and the planned Fellowship Entertainment separation targeted for 2027. Essential context for dozens of studios worldwide that Embracer owns or shed Focused on Sweden.</t>
+          <t>The clearest public data on a niche-deep PC publisher's economics: DLC/expansion revenue models, catalog longevity, and studio-acquisition strategy. Tencent holds ~10%, worth noting when reading strategy commentary Focused on Sweden.</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
@@ -7419,7 +7411,7 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>https://embracer.com/investors/</t>
+          <t>https://paradoxinteractive.com/en/section/investors</t>
         </is>
       </c>
       <c r="K102" s="3" t="inlineStr"/>
@@ -7434,12 +7426,12 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>paradox-interactive</t>
+          <t>remedy-entertainment</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Paradox Interactive (Nasdaq Stockholm: PDX)</t>
+          <t>Remedy Entertainment (Nasdaq Helsinki: REMEDY)</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -7459,7 +7451,7 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>The clearest public data on a niche-deep PC publisher's economics: DLC/expansion revenue models, catalog longevity, and studio-acquisition strategy. Tencent holds ~10%, worth noting when reading strategy commentary Focused on Sweden.</t>
+          <t>The economics of AAA-adjacent single-player development laid bare: co-development/publisher deal structures, royalty timing, and project-by-project risk. Tencent holds ~14% Focused on Finland.</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
@@ -7469,7 +7461,7 @@
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>English; Finnish</t>
         </is>
       </c>
       <c r="I103" s="3" t="inlineStr">
@@ -7479,7 +7471,7 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>https://paradoxinteractive.com/en/section/investors</t>
+          <t>https://investors.remedygames.com/</t>
         </is>
       </c>
       <c r="K103" s="3" t="inlineStr"/>
@@ -7494,12 +7486,12 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>remedy-entertainment</t>
+          <t>stillfront-group</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Remedy Entertainment (Nasdaq Helsinki: REMEDY)</t>
+          <t>Stillfront Group (Nasdaq Stockholm: SF)</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -7519,7 +7511,7 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>The economics of AAA-adjacent single-player development laid bare: co-development/publisher deal structures, royalty timing, and project-by-project risk. Tencent holds ~14% Focused on Finland.</t>
+          <t>The mobile counterpart to Embracer's PC/console story: F2P portfolio economics, UA spend, studio divestments (e.g. the OFM Studios management buyout) and the sharp valuation compression across the roll-up model Focused on Sweden.</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
@@ -7529,7 +7521,7 @@
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>English; Finnish</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I104" s="3" t="inlineStr">
@@ -7539,7 +7531,7 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>https://investors.remedygames.com/</t>
+          <t>https://www.stillfront.com/en/investors/</t>
         </is>
       </c>
       <c r="K104" s="3" t="inlineStr"/>
@@ -7554,12 +7546,12 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>stillfront-group</t>
+          <t>wig-games-index</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Stillfront Group (Nasdaq Stockholm: SF)</t>
+          <t>WIG.GAMES index (Giełda Papierów Wartościowych, Warsaw Stock Exchange)</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -7569,27 +7561,27 @@
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>Company disclosure</t>
+          <t>Data tool</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>Corporate IR</t>
+          <t>Sector index</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>The mobile counterpart to Embracer's PC/console story: F2P portfolio economics, UA spend, studio divestments (e.g. the OFM Studios management buyout) and the sharp valuation compression across the roll-up model Focused on Sweden.</t>
+          <t>Unique in this pack: an actual exchange-published sector index for video games, plus structured certificates on it. The index composition and weighting are themselves a market map, and its long-run decline against the WIG20 is the clearest single indicator of how Polish gaming's investor story has changed since Cyberpunk 2077</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>Nordics</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>English; Polish</t>
         </is>
       </c>
       <c r="I105" s="3" t="inlineStr">
@@ -7599,7 +7591,7 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>https://www.stillfront.com/en/investors/</t>
+          <t>https://www.gpw.pl/</t>
         </is>
       </c>
       <c r="K105" s="3" t="inlineStr"/>
@@ -7614,12 +7606,12 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>wig-games-index</t>
+          <t>cd-projekt</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>WIG.GAMES index (Giełda Papierów Wartościowych, Warsaw Stock Exchange)</t>
+          <t>CD Projekt (GPW: CDR)</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -7629,17 +7621,17 @@
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Data tool</t>
+          <t>Company disclosure</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>Sector index</t>
+          <t>Corporate IR</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>Unique in this pack: an actual exchange-published sector index for video games, plus structured certificates on it. The index composition and weighting are themselves a market map, and its long-run decline against the WIG20 is the clearest single indicator of how Polish gaming's investor story has changed since Cyberpunk 2077</t>
+          <t>The dominant component of WIG.GAMES (~42% at times), so its results move the whole Polish sector's sentiment. Reports cover both development (CD Projekt RED) and, until the December 2025 sale of GOG, digital distribution, making the split itself a documented strategic event</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -7659,7 +7651,7 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>https://www.gpw.pl/</t>
+          <t>https://www.cdprojekt.com/en/investors/</t>
         </is>
       </c>
       <c r="K106" s="3" t="inlineStr"/>
@@ -7674,12 +7666,12 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>cd-projekt</t>
+          <t>11-bit-studios</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>CD Projekt (GPW: CDR)</t>
+          <t>11 bit studios (GPW: 11BIT)</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -7699,7 +7691,7 @@
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>The dominant component of WIG.GAMES (~42% at times), so its results move the whole Polish sector's sentiment. Reports cover both development (CD Projekt RED) and, until the December 2025 sale of GOG, digital distribution, making the split itself a documented strategic event</t>
+          <t>The mid-cap counterweight to CD Projekt: development-plus-publishing economics at a studio that also funds third-party titles. Write-offs, delays and release timing are disclosed in unusual detail</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
@@ -7719,7 +7711,7 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>https://www.cdprojekt.com/en/investors/</t>
+          <t>https://ir.11bitstudios.com/</t>
         </is>
       </c>
       <c r="K107" s="3" t="inlineStr"/>
@@ -7734,12 +7726,12 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>11-bit-studios</t>
+          <t>playway</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>11 bit studios (GPW: 11BIT)</t>
+          <t>PlayWay (GPW: PLW)</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -7759,7 +7751,7 @@
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>The mid-cap counterweight to CD Projekt: development-plus-publishing economics at a studio that also funds third-party titles. Write-offs, delays and release timing are disclosed in unusual detail</t>
+          <t>A distinctive business model to have public data on: many low-budget titles across a network of part-owned studios (House Flipper, Car Mechanic Simulator, 70+ titles), a strategy no other listed company in this pack runs at this scale</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
@@ -7779,7 +7771,7 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>https://ir.11bitstudios.com/</t>
+          <t>https://playway.com/en/investor-relations/</t>
         </is>
       </c>
       <c r="K108" s="3" t="inlineStr"/>
@@ -7794,12 +7786,12 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>playway</t>
+          <t>international-games-system</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>PlayWay (GPW: PLW)</t>
+          <t>鈊象電子 International Games System (TPEx: 3293)</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -7819,17 +7811,17 @@
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>A distinctive business model to have public data on: many low-budget titles across a network of part-owned studios (House Flipper, Car Mechanic Simulator, 70+ titles), a strategy no other listed company in this pack runs at this scale</t>
+          <t>The clearest public data on Taiwan's actual games business model: licensing-led revenue (NT$14.98bn in 2025, +45% YoY, 68% of total, near-100% gross margin on the licensing line) plus social-casino products aimed at the US and Southeast Asia. A useful corrective to assuming Taiwan's industry is domestic-facing English coverage is partial.</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>English; Polish</t>
+          <t>English; Traditional Chinese</t>
         </is>
       </c>
       <c r="I109" s="3" t="inlineStr">
@@ -7839,7 +7831,7 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>https://playway.com/en/investor-relations/</t>
+          <t>https://www.igs.com.tw/</t>
         </is>
       </c>
       <c r="K109" s="3" t="inlineStr"/>
@@ -7854,12 +7846,12 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>international-games-system</t>
+          <t>tpex-6180</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>鈊象電子 International Games System (TPEx: 3293)</t>
+          <t>遊戲橘子 Gamania (TPEx: 6180)</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -7874,12 +7866,12 @@
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>Corporate IR</t>
+          <t>Corporate filings</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
-          <t>The clearest public data on Taiwan's actual games business model: licensing-led revenue (NT$14.98bn in 2025, +45% YoY, 68% of total, near-100% gross margin on the licensing line) plus social-casino products aimed at the US and Southeast Asia. A useful corrective to assuming Taiwan's industry is domestic-facing English coverage is partial.</t>
+          <t>The licensing-and-operations side: decades of operating Korean and Japanese titles in Taiwan (Lineage M, MapleStory, KartRider), plus the 2024 sale of 53% of its game-points subsidiary 樂點, a rare public window on the game-currency/payment layer's value</t>
         </is>
       </c>
       <c r="G110" s="3" t="inlineStr">
@@ -7889,7 +7881,7 @@
       </c>
       <c r="H110" s="3" t="inlineStr">
         <is>
-          <t>English; Traditional Chinese</t>
+          <t>Traditional Chinese</t>
         </is>
       </c>
       <c r="I110" s="3" t="inlineStr">
@@ -7899,7 +7891,7 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>https://www.igs.com.tw/</t>
+          <t>https://www.gamania.com/</t>
         </is>
       </c>
       <c r="K110" s="3" t="inlineStr"/>
@@ -7914,12 +7906,12 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>tpex-6180</t>
+          <t>soft-world</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>遊戲橘子 Gamania (TPEx: 6180)</t>
+          <t>智冠科技 Soft-World (TPEx: 5478)</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -7939,7 +7931,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>The licensing-and-operations side: decades of operating Korean and Japanese titles in Taiwan (Lineage M, MapleStory, KartRider), plus the 2024 sale of 53% of its game-points subsidiary 樂點, a rare public window on the game-currency/payment layer's value</t>
+          <t>The distribution and channel layer, historically central to how games reach Taiwanese players. Useful for understanding physical/retail and point-card economics that global data misses</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
@@ -7959,7 +7951,7 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>https://www.gamania.com/</t>
+          <t>https://www.soft-world.com.tw/</t>
         </is>
       </c>
       <c r="K111" s="3" t="inlineStr"/>
@@ -7974,12 +7966,12 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>soft-world</t>
+          <t>square-enix-holdings-ir</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>智冠科技 Soft-World (TPEx: 5478)</t>
+          <t>Square Enix Holdings IR</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -7994,22 +7986,22 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>Corporate filings</t>
+          <t>Corporate IR</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>The distribution and channel layer, historically central to how games reach Taiwanese players. Useful for understanding physical/retail and point-card economics that global data misses</t>
+          <t>Segment reporting across HD games, MMO, mobile and publishing, plus write-downs that show which strategies were abandoned. Fiscal year ends 31 March.</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>Global; JP</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>Traditional Chinese</t>
+          <t>English; Japanese</t>
         </is>
       </c>
       <c r="I112" s="3" t="inlineStr">
@@ -8019,7 +8011,7 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>https://www.soft-world.com.tw/</t>
+          <t>https://www.hd.square-enix.com/eng/ir/</t>
         </is>
       </c>
       <c r="K112" s="3" t="inlineStr"/>
@@ -8034,12 +8026,12 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>square-enix-holdings-ir</t>
+          <t>bandai-namco-holdings-ir</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Square Enix Holdings IR</t>
+          <t>Bandai Namco Holdings IR</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -8059,7 +8051,7 @@
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>Segment reporting across HD games, MMO, mobile and publishing, plus write-downs that show which strategies were abandoned. Fiscal year ends 31 March.</t>
+          <t>The clearest public view of an IP axis strategy, with toys, games, arcade and visual media reported side by side. Useful for understanding character IP economics rather than games alone.</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
@@ -8079,7 +8071,7 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>https://www.hd.square-enix.com/eng/ir/</t>
+          <t>https://www.bandainamco.co.jp/en/ir/index.html</t>
         </is>
       </c>
       <c r="K113" s="3" t="inlineStr"/>
@@ -8094,12 +8086,12 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>bandai-namco-holdings-ir</t>
+          <t>konami-group-ir</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Bandai Namco Holdings IR</t>
+          <t>Konami Group IR</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -8119,7 +8111,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>The clearest public view of an IP axis strategy, with toys, games, arcade and visual media reported side by side. Useful for understanding character IP economics rather than games alone.</t>
+          <t>Digital entertainment reported alongside amusement, gaming and sports segments. Shows how a Japanese publisher balances games against pachinko and casino gaming machines.</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
@@ -8139,7 +8131,7 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>https://www.bandainamco.co.jp/en/ir/index.html</t>
+          <t>https://www.konami.com/ir/en/</t>
         </is>
       </c>
       <c r="K114" s="3" t="inlineStr"/>
@@ -8154,12 +8146,12 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>konami-group-ir</t>
+          <t>sega-sammy-holdings-ir</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Konami Group IR</t>
+          <t>Sega Sammy Holdings IR</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -8179,7 +8171,7 @@
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>Digital entertainment reported alongside amusement, gaming and sports segments. Shows how a Japanese publisher balances games against pachinko and casino gaming machines.</t>
+          <t>Entertainment contents reported next to pachislot, pachinko and resorts. Impairments on acquisitions such as Rovio are visible here before they reach trade coverage.</t>
         </is>
       </c>
       <c r="G115" s="3" t="inlineStr">
@@ -8199,7 +8191,7 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>https://www.konami.com/ir/en/</t>
+          <t>https://www.segasammy.co.jp/en/ir/</t>
         </is>
       </c>
       <c r="K115" s="3" t="inlineStr"/>
@@ -8214,12 +8206,12 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>sega-sammy-holdings-ir</t>
+          <t>take-two-interactive-ir</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Sega Sammy Holdings IR</t>
+          <t>Take-Two Interactive IR</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -8239,17 +8231,17 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>Entertainment contents reported next to pachislot, pachinko and resorts. Impairments on acquisitions such as Rovio are visible here before they reach trade coverage.</t>
+          <t>Net bookings by geographic region, distribution channel and platform mix, which is an unusually clean regional breakdown. Covers Rockstar, 2K and Zynga, so console and mobile sit in one filing.</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>Global; JP</t>
+          <t>Global; US</t>
         </is>
       </c>
       <c r="H116" s="3" t="inlineStr">
         <is>
-          <t>English; Japanese</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I116" s="3" t="inlineStr">
@@ -8259,7 +8251,7 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>https://www.segasammy.co.jp/en/ir/</t>
+          <t>https://www.take2games.com/ir</t>
         </is>
       </c>
       <c r="K116" s="3" t="inlineStr"/>
@@ -8274,12 +8266,12 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>take-two-interactive-ir</t>
+          <t>ubisoft-entertainment-ir</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Take-Two Interactive IR</t>
+          <t>Ubisoft Entertainment IR</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -8299,17 +8291,17 @@
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>Net bookings by geographic region, distribution channel and platform mix, which is an unusually clean regional breakdown. Covers Rockstar, 2K and Zynga, so console and mobile sit in one filing.</t>
+          <t>The most detailed public record of a large publisher in restructuring, including the Tencent investment and portfolio rationalisation. Recurring player investment is reported separately from net bookings.</t>
         </is>
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>Global; US</t>
+          <t>FR; Global</t>
         </is>
       </c>
       <c r="H117" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>English; French</t>
         </is>
       </c>
       <c r="I117" s="3" t="inlineStr">
@@ -8319,7 +8311,7 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
-          <t>https://www.take2games.com/ir</t>
+          <t>https://www.ubisoft.com/en-us/company/about-us/investors</t>
         </is>
       </c>
       <c r="K117" s="3" t="inlineStr"/>
@@ -8334,42 +8326,42 @@
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>ubisoft-entertainment-ir</t>
+          <t>digra-australia</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>Ubisoft Entertainment IR</t>
+          <t>DiGRA Australia (DiGRAA)</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Company disclosure</t>
+          <t>Organisation</t>
         </is>
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>Corporate IR</t>
+          <t>Learned society</t>
         </is>
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>The most detailed public record of a large publisher in restructuring, including the Tencent investment and portfolio rationalisation. Recurring player investment is reported separately from net bookings.</t>
+          <t>The most transparent DiGRA chapter for an outsider. Extended abstracts and programmes back to 2014 are posted publicly and talks go to its YouTube channel, so a researcher can follow a national conference without membership.</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>FR; Global</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="H118" s="3" t="inlineStr">
         <is>
-          <t>English; French</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I118" s="3" t="inlineStr">
@@ -8379,7 +8371,7 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>https://www.ubisoft.com/en-us/company/about-us/investors</t>
+          <t>https://digraa.org/conference/</t>
         </is>
       </c>
       <c r="K118" s="3" t="inlineStr"/>
@@ -8394,12 +8386,12 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>digra-australia</t>
+          <t>australian-classification-board-computer-games</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>DiGRA Australia (DiGRAA)</t>
+          <t>Australian Classification Board: computer games (incl. 2024 gambling-content rules)</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -8414,12 +8406,12 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>Learned society</t>
+          <t>Rating body</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>The most transparent DiGRA chapter for an outsider. Extended abstracts and programmes back to 2014 are posted publicly and talks go to its YouTube channel, so a researcher can follow a national conference without membership.</t>
+          <t>Tier-A regulatory reference: paid loot boxes → mandatory minimum M, simulated gambling → legally restricted R18+ (world-leading strictness), redeemable-for-currency gambling content → refused classification. The searchable database shows every decision. The gambling-content rules are in force since 22 Sep 2024. Most game ratings flow through the automated IARC tool rather than board review.</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
@@ -8439,7 +8431,7 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
-          <t>https://digraa.org/conference/</t>
+          <t>https://www.classification.gov.au/</t>
         </is>
       </c>
       <c r="K119" s="3" t="inlineStr"/>
@@ -8454,12 +8446,12 @@
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>australian-classification-board-computer-games</t>
+          <t>esafety-commissioner-social-media-minimum-age</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Australian Classification Board: computer games (incl. 2024 gambling-content rules)</t>
+          <t>eSafety Commissioner: Social Media Minimum Age (under-16 ban)</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -8474,12 +8466,12 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>Rating body</t>
+          <t>Regulator</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>Tier-A regulatory reference: paid loot boxes → mandatory minimum M, simulated gambling → legally restricted R18+ (world-leading strictness), redeemable-for-currency gambling content → refused classification. The searchable database shows every decision. The gambling-content rules are in force since 22 Sep 2024. Most game ratings flow through the automated IARC tool rather than board review.</t>
+          <t>Administers the world-first under-16 social media account ban, in force 10 Dec 2025. Essential for anyone researching young Australians' play. Platforms report monthly account-removal numbers.</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
@@ -8499,7 +8491,7 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
-          <t>https://www.classification.gov.au/</t>
+          <t>https://www.esafety.gov.au/about-us/industry-regulation/social-media-age-restrictions</t>
         </is>
       </c>
       <c r="K120" s="3" t="inlineStr"/>
@@ -8514,12 +8506,12 @@
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>esafety-commissioner-social-media-minimum-age</t>
+          <t>igea-interactive-games-and-entertainment-association</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>eSafety Commissioner: Social Media Minimum Age (under-16 ban)</t>
+          <t>IGEA: Interactive Games &amp; Entertainment Association</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -8534,12 +8526,12 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>Regulator</t>
+          <t>Industry association</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>Administers the world-first under-16 social media account ban, in force 10 Dec 2025. Essential for anyone researching young Australians' play. Platforms report monthly account-removal numbers.</t>
+          <t>The industry's voice on classification reform, tax incentives and platform policy. Publisher of both national data series above and the running record of policy positions. Covers Australia and New Zealand. Runs the IGEA Educates podcast. Trade-body advocacy. Its dual role as data publisher and lobbyist means its framing of findings serves policy goals</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
@@ -8559,7 +8551,7 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>https://www.esafety.gov.au/about-us/industry-regulation/social-media-age-restrictions</t>
+          <t>https://igea.net/</t>
         </is>
       </c>
       <c r="K121" s="3" t="inlineStr"/>
@@ -8574,12 +8566,12 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>igea-interactive-games-and-entertainment-association</t>
+          <t>abragames-pesquisa-da-industria-brasileira-de-games</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>IGEA: Interactive Games &amp; Entertainment Association</t>
+          <t>Abragames: Pesquisa da Indústria Brasileira de Games</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -8599,17 +8591,17 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>The industry's voice on classification reform, tax incentives and platform policy. Publisher of both national data series above and the running record of policy positions. Covers Australia and New Zealand. Runs the IGEA Educates podcast. Trade-body advocacy. Its dual role as data publisher and lobbyist means its framing of findings serves policy goals</t>
+          <t>Supply-side numbers: studio counts, employment, revenue and regional distribution of the Brazilian dev industry, the counterpart to PGB's demand side. The mapping is produced with ApexBrasil. Advocacy framing: the association exists to promote the sector. English is limited to fact sheets.</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>English; Portuguese</t>
         </is>
       </c>
       <c r="I122" s="3" t="inlineStr">
@@ -8619,7 +8611,7 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>https://igea.net/</t>
+          <t>https://brazilgames.org/en/</t>
         </is>
       </c>
       <c r="K122" s="3" t="inlineStr"/>
@@ -8634,12 +8626,12 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>abragames-pesquisa-da-industria-brasileira-de-games</t>
+          <t>classind-mjsp</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>Abragames: Pesquisa da Indústria Brasileira de Games</t>
+          <t>ClassInd (Classificação Indicativa): MJSP</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -8654,12 +8646,12 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>Industry association</t>
+          <t>Rating body</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
-          <t>Supply-side numbers: studio counts, employment, revenue and regional distribution of the Brazilian dev industry, the counterpart to PGB's demand side. The mapping is produced with ApexBrasil. Advocacy framing: the association exists to promote the sector. English is limited to fact sheets.</t>
+          <t>Brazil's official age-rating decisions for games and apps. Searchable portal plus raw datasets on dados.mj.gov.br, a Tier-A record of what was rated, when, and at what level. Ratings are advisory ("indicativa") rather than sales-restrictive. Database interface is Portuguese-only and clunky English coverage is partial.</t>
         </is>
       </c>
       <c r="G123" s="3" t="inlineStr">
@@ -8679,7 +8671,7 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
-          <t>https://brazilgames.org/en/</t>
+          <t>https://classindportal.mj.gov.br/</t>
         </is>
       </c>
       <c r="K123" s="3" t="inlineStr"/>
@@ -8694,12 +8686,12 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>classind-mjsp</t>
+          <t>sbgames-anais</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>ClassInd (Classificação Indicativa): MJSP</t>
+          <t>SBGames: Anais (SBC/CEJOGOS)</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
@@ -8709,17 +8701,17 @@
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Organisation</t>
+          <t>Report or document</t>
         </is>
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>Rating body</t>
+          <t>Report or data series</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>Brazil's official age-rating decisions for games and apps. Searchable portal plus raw datasets on dados.mj.gov.br, a Tier-A record of what was rated, when, and at what level. Ratings are advisory ("indicativa") rather than sales-restrictive. Database interface is Portuguese-only and clunky English coverage is partial.</t>
+          <t>Peer-reviewed Brazilian games scholarship across culture, education, industry and health tracks, the academic layer most English-language searches miss entirely. Latin America's largest games research symposium, around 200 papers a year. Academic lag (papers describe fieldwork 1 to 2 years old). Some English papers.</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
@@ -8739,7 +8731,7 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>https://classindportal.mj.gov.br/</t>
+          <t>https://sol.sbc.org.br/index.php/sbgames</t>
         </is>
       </c>
       <c r="K124" s="3" t="inlineStr"/>
@@ -8754,12 +8746,12 @@
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>sbgames-anais</t>
+          <t>canadian-game-studies-association-association-canadienne</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>SBGames: Anais (SBC/CEJOGOS)</t>
+          <t>Canadian Game Studies Association / Association canadienne d'études des jeux</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -8769,27 +8761,27 @@
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>Report or document</t>
+          <t>Organisation</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>Report or data series</t>
+          <t>Learned society</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>Peer-reviewed Brazilian games scholarship across culture, education, industry and health tracks, the academic layer most English-language searches miss entirely. Latin America's largest games research symposium, around 200 papers a year. Academic lag (papers describe fieldwork 1 to 2 years old). Some English papers.</t>
+          <t>Canada's bilingual games studies association and its annual conference. Its journal Loading has published nothing since 2022 while the association remains active, so treat the two separately.</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
-          <t>English; Portuguese</t>
+          <t>English; French</t>
         </is>
       </c>
       <c r="I125" s="3" t="inlineStr">
@@ -8799,7 +8791,7 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
-          <t>https://sol.sbc.org.br/index.php/sbgames</t>
+          <t>https://gamestudies.ca/</t>
         </is>
       </c>
       <c r="K125" s="3" t="inlineStr"/>
@@ -8814,12 +8806,12 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>canadian-game-studies-association-association-canadienne</t>
+          <t>esac</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>Canadian Game Studies Association / Association canadienne d'études des jeux</t>
+          <t>ESAC (Entertainment Software Association of Canada)</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
@@ -8834,12 +8826,12 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>Learned society</t>
+          <t>Industry association</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>Canada's bilingual games studies association and its annual conference. Its journal Loading has published nothing since 2022 while the association remains active, so treat the two separately.</t>
+          <t>Real Canadian Gamer Essential Facts plus the Nordicity industry impact report, 2025, which together form the national data baseline. Advocacy body of publishers with advocacy framing. Bilingual publications</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
@@ -8859,7 +8851,7 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>https://gamestudies.ca/</t>
+          <t>https://theesa.ca/</t>
         </is>
       </c>
       <c r="K126" s="3" t="inlineStr"/>
@@ -8874,12 +8866,12 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>esac</t>
+          <t>la-guilde-du-jeu-video-du-quebec</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>ESAC (Entertainment Software Association of Canada)</t>
+          <t>La Guilde du jeu vidéo du Québec</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
@@ -8899,7 +8891,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>Real Canadian Gamer Essential Facts plus the Nordicity industry impact report, 2025, which together form the national data baseline. Advocacy body of publishers with advocacy framing. Bilingual publications</t>
+          <t>The voice of Québec's 330+ studios includes sector data, tax-credit advocacy, DEI programs. Advocacy cooperative. An essential source on the world's densest games cluster per capita.</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
@@ -8919,7 +8911,7 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>https://theesa.ca/</t>
+          <t>https://laguilde.quebec</t>
         </is>
       </c>
       <c r="K127" s="3" t="inlineStr"/>
@@ -8934,12 +8926,12 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>la-guilde-du-jeu-video-du-quebec</t>
+          <t>interactive-ontario</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>La Guilde du jeu vidéo du Québec</t>
+          <t>Interactive Ontario</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -8959,7 +8951,7 @@
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>The voice of Québec's 330+ studios includes sector data, tax-credit advocacy, DEI programs. Advocacy cooperative. An essential source on the world's densest games cluster per capita.</t>
+          <t>Ontario's interactive-media sector data and policy positions.</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
@@ -8969,7 +8961,7 @@
       </c>
       <c r="H128" s="3" t="inlineStr">
         <is>
-          <t>English; French</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I128" s="3" t="inlineStr">
@@ -8979,7 +8971,7 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>https://laguilde.quebec</t>
+          <t>https://interactiveontario.com</t>
         </is>
       </c>
       <c r="K128" s="3" t="inlineStr"/>
@@ -8994,12 +8986,12 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>interactive-ontario</t>
+          <t>canada-media-fund</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Interactive Ontario</t>
+          <t>Canada Media Fund</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -9014,12 +9006,12 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>Industry association</t>
+          <t>Funding body</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>Ontario's interactive-media sector data and policy positions.</t>
+          <t>Public games funding data and trend reports. Canada treats games as cultural industry, like France's CNC.</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
@@ -9029,7 +9021,7 @@
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>English; French</t>
         </is>
       </c>
       <c r="I129" s="3" t="inlineStr">
@@ -9039,7 +9031,7 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>https://interactiveontario.com</t>
+          <t>https://cmf-fmc.ca</t>
         </is>
       </c>
       <c r="K129" s="3" t="inlineStr"/>
@@ -9054,12 +9046,12 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>canada-media-fund</t>
+          <t>canadian-game-awards</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>Canada Media Fund</t>
+          <t>Canadian Game Awards</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
@@ -9074,12 +9066,12 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>Funding body</t>
+          <t>Event or awards</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>Public games funding data and trend reports. Canada treats games as cultural industry, like France's CNC.</t>
+          <t>The national canon-marker for Canadian-made games (6th edition 2026, with the Eh! Game Showcase).</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
@@ -9089,7 +9081,7 @@
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>English; French</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I130" s="3" t="inlineStr">
@@ -9099,7 +9091,7 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>https://cmf-fmc.ca</t>
+          <t>https://canadiangameawards.ca/en</t>
         </is>
       </c>
       <c r="K130" s="3" t="inlineStr"/>
@@ -9114,12 +9106,12 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>canadian-game-awards</t>
+          <t>entertainment-software-association-of-canada</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>Canadian Game Awards</t>
+          <t>Entertainment Software Association of Canada</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
@@ -9134,12 +9126,12 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>Event or awards</t>
+          <t>Government agency</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>The national canon-marker for Canadian-made games (6th edition 2026, with the Eh! Game Showcase).</t>
+          <t>Statistics on Canada's video game industry, including studios, employment, and more</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
@@ -9149,7 +9141,7 @@
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>English; French</t>
         </is>
       </c>
       <c r="I131" s="3" t="inlineStr">
@@ -9159,7 +9151,7 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>https://canadiangameawards.ca/en</t>
+          <t>https://canadasvideogameindustry.ca/</t>
         </is>
       </c>
       <c r="K131" s="3" t="inlineStr"/>
@@ -9174,12 +9166,12 @@
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>entertainment-software-association-of-canada</t>
+          <t>queerness-and-games-conference</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>Entertainment Software Association of Canada</t>
+          <t>Queerness and Games Conference (QGCon)</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -9194,22 +9186,22 @@
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>Government agency</t>
+          <t>Event or awards</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>Statistics on Canada's video game industry, including studios, employment, and more</t>
+          <t>A free conference bringing academics, developers and players together on LGBTQ issues in games, running since 2013.</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>CA; US</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
-          <t>English; French</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I132" s="3" t="inlineStr">
@@ -9219,7 +9211,7 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>https://canadasvideogameindustry.ca/</t>
+          <t>https://www.qgcon.org/about</t>
         </is>
       </c>
       <c r="K132" s="3" t="inlineStr"/>
@@ -9234,12 +9226,12 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>queerness-and-games-conference</t>
+          <t>gpc-cadpa-game-working-committee</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Queerness and Games Conference (QGCon)</t>
+          <t>GPC / CADPA Game Working Committee</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
@@ -9254,22 +9246,22 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>Event or awards</t>
+          <t>Industry association</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>A free conference bringing academics, developers and players together on LGBTQ issues in games, running since 2013.</t>
+          <t>The official China Games Industry Report. State-supervised industry body. Numbers are the canonical record + the official narrative. Full PDFs circulate via third-party report sites.</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>CA; US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="I133" s="3" t="inlineStr">
@@ -9279,7 +9271,7 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>https://www.qgcon.org/about</t>
+          <t>https://www.cadpa.org.cn</t>
         </is>
       </c>
       <c r="K133" s="3" t="inlineStr"/>
@@ -9294,12 +9286,12 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>gpc-cadpa-game-working-committee</t>
+          <t>nppa</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>GPC / CADPA Game Working Committee</t>
+          <t>NPPA</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
@@ -9314,12 +9306,12 @@
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>Industry association</t>
+          <t>Regulator</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
-          <t>The official China Games Industry Report. State-supervised industry body. Numbers are the canonical record + the official narrative. Full PDFs circulate via third-party report sites.</t>
+          <t>Monthly game license (版号) approval lists, the primary source for what may legally publish in China. Government site, Chinese only. Loads from outside China but can be slow.</t>
         </is>
       </c>
       <c r="G134" s="3" t="inlineStr">
@@ -9339,7 +9331,7 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>https://www.cadpa.org.cn</t>
+          <t>https://www.nppa.gov.cn</t>
         </is>
       </c>
       <c r="K134" s="3" t="inlineStr"/>
@@ -9354,12 +9346,12 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>nppa</t>
+          <t>cnnic</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>NPPA</t>
+          <t>CNNIC</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
@@ -9374,12 +9366,12 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>Regulator</t>
+          <t>Government agency</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
-          <t>Monthly game license (版号) approval lists, the primary source for what may legally publish in China. Government site, Chinese only. Loads from outside China but can be slow.</t>
+          <t>Statistical reports on internet use incl. the annual minors' internet usage study, the China youth-media data source. State body.</t>
         </is>
       </c>
       <c r="G135" s="3" t="inlineStr">
@@ -9389,7 +9381,7 @@
       </c>
       <c r="H135" s="3" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>Chinese; English</t>
         </is>
       </c>
       <c r="I135" s="3" t="inlineStr">
@@ -9399,7 +9391,7 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
-          <t>https://www.nppa.gov.cn</t>
+          <t>https://www.cnnic.cn</t>
         </is>
       </c>
       <c r="K135" s="3" t="inlineStr"/>
@@ -9414,12 +9406,12 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>cnnic</t>
+          <t>chinese-digra</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>CNNIC</t>
+          <t>Chinese DiGRA (CDiGRA)</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
@@ -9434,17 +9426,17 @@
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>Government agency</t>
+          <t>Learned society</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>Statistical reports on internet use incl. the annual minors' internet usage study, the China youth-media data source. State body.</t>
+          <t>The scholarly body covering mainland China, Hong Kong, Macau and Taiwan plus researchers of Chinese gaming cultures elsewhere, running an annual conference.</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CN; TW</t>
         </is>
       </c>
       <c r="H136" s="3" t="inlineStr">
@@ -9459,7 +9451,7 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>https://www.cnnic.cn</t>
+          <t>https://www.chinesedigra.org</t>
         </is>
       </c>
       <c r="K136" s="3" t="inlineStr"/>
@@ -9474,12 +9466,12 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>chinese-digra</t>
+          <t>game-verband</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>Chinese DiGRA (CDiGRA)</t>
+          <t>game (Verband der deutschen Games-Branche)</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
@@ -9494,22 +9486,22 @@
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>Learned society</t>
+          <t>Industry association</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
         <is>
-          <t>The scholarly body covering mainland China, Hong Kong, Macau and Taiwan plus researchers of Chinese gaming cultures elsewhere, running an annual conference.</t>
+          <t>Official German market data produced with YouGov and Sensor Tower, employment figures, gamescom co-organizer, policy voice. Advocacy body. English coverage is partial.</t>
         </is>
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>CN; TW</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="H137" s="3" t="inlineStr">
         <is>
-          <t>Chinese; English</t>
+          <t>English; German</t>
         </is>
       </c>
       <c r="I137" s="3" t="inlineStr">
@@ -9519,7 +9511,7 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
-          <t>https://www.chinesedigra.org</t>
+          <t>https://www.game.de/</t>
         </is>
       </c>
       <c r="K137" s="3" t="inlineStr"/>
@@ -9534,12 +9526,12 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>game-verband</t>
+          <t>usk</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>game (Verband der deutschen Games-Branche)</t>
+          <t>USK</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
@@ -9554,12 +9546,12 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>Industry association</t>
+          <t>Rating body</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>Official German market data produced with YouGov and Sensor Tower, employment figures, gamescom co-organizer, policy voice. Advocacy body. English coverage is partial.</t>
+          <t>German rating decisions from the age-ratings database, plus youth-protection criteria, which makes it essential for parent and family research. Industry self-regulation under state oversight. Notable for being the strictest big-market regime historically. Ratings signal, not market data. EN summary pages exist</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
@@ -9569,7 +9561,7 @@
       </c>
       <c r="H138" s="3" t="inlineStr">
         <is>
-          <t>English; German</t>
+          <t>German</t>
         </is>
       </c>
       <c r="I138" s="3" t="inlineStr">
@@ -9579,7 +9571,7 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
-          <t>https://www.game.de/</t>
+          <t>https://usk.de/</t>
         </is>
       </c>
       <c r="K138" s="3" t="inlineStr"/>
@@ -9594,12 +9586,12 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>usk</t>
+          <t>games-germany</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>USK</t>
+          <t>Games Germany</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
@@ -9614,12 +9606,12 @@
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>Rating body</t>
+          <t>Funding body</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>German rating decisions from the age-ratings database, plus youth-protection criteria, which makes it essential for parent and family research. Industry self-regulation under state oversight. Notable for being the strictest big-market regime historically. Ratings signal, not market data. EN summary pages exist</t>
+          <t>Joint platform of the German federal states' games-funding institutions (public-funding side of the market). Distinct from the trade association 'game' (game.de). Funding/policy lens, not market data</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
@@ -9629,7 +9621,7 @@
       </c>
       <c r="H139" s="3" t="inlineStr">
         <is>
-          <t>German</t>
+          <t>English; German</t>
         </is>
       </c>
       <c r="I139" s="3" t="inlineStr">
@@ -9639,7 +9631,7 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
-          <t>https://usk.de/</t>
+          <t>https://www.games-germany.de/</t>
         </is>
       </c>
       <c r="K139" s="3" t="inlineStr"/>
@@ -9654,12 +9646,12 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>games-germany</t>
+          <t>mpfs</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>Games Germany</t>
+          <t>mpfs (JIM/KIM Studies)</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
@@ -9674,12 +9666,12 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>Funding body</t>
+          <t>Research institute</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>Joint platform of the German federal states' games-funding institutions (public-funding side of the market). Distinct from the trade association 'game' (game.de). Funding/policy lens, not market data</t>
+          <t>JIM (12-19) and KIM (6-13) studies, the gold-standard annual youth media-use data in Germany.</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
@@ -9689,7 +9681,7 @@
       </c>
       <c r="H140" s="3" t="inlineStr">
         <is>
-          <t>English; German</t>
+          <t>German</t>
         </is>
       </c>
       <c r="I140" s="3" t="inlineStr">
@@ -9699,7 +9691,7 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
-          <t>https://www.games-germany.de/</t>
+          <t>https://mpfs.de</t>
         </is>
       </c>
       <c r="K140" s="3" t="inlineStr"/>
@@ -9714,12 +9706,12 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>mpfs</t>
+          <t>stiftung-digitale-spielekultur</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>mpfs (JIM/KIM Studies)</t>
+          <t>Stiftung Digitale Spielekultur</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
@@ -9734,12 +9726,12 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>Research institute</t>
+          <t>Cultural institution</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
-          <t>JIM (12-19) and KIM (6-13) studies, the gold-standard annual youth media-use data in Germany.</t>
+          <t>Games-and-society projects, education initiatives, cultural programming around games. Co-founded by the game association, so industry-adjacent but genuinely public-interest. Owner: Industry-founded foundation.</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
@@ -9759,7 +9751,7 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
-          <t>https://mpfs.de</t>
+          <t>https://www.stiftung-digitale-spielekultur.de</t>
         </is>
       </c>
       <c r="K141" s="3" t="inlineStr"/>
@@ -9774,12 +9766,12 @@
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>stiftung-digitale-spielekultur</t>
+          <t>spielbar-de</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>Stiftung Digitale Spielekultur</t>
+          <t>spielbar.de</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
@@ -9794,12 +9786,12 @@
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>Cultural institution</t>
+          <t>Parent guidance platform</t>
         </is>
       </c>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>Games-and-society projects, education initiatives, cultural programming around games. Co-founded by the game association, so industry-adjacent but genuinely public-interest. Owner: Industry-founded foundation.</t>
+          <t>Pedagogical game assessments from the Federal Agency for Civic Education, from a parent/educator perspective. State-funded (bpb).</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr">
@@ -9819,7 +9811,7 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
-          <t>https://www.stiftung-digitale-spielekultur.de</t>
+          <t>https://www.spielbar.de</t>
         </is>
       </c>
       <c r="K142" s="3" t="inlineStr"/>
@@ -9834,12 +9826,12 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>spielbar-de</t>
+          <t>ard-zdf-medienstudie</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>spielbar.de</t>
+          <t>ARD/ZDF-Medienstudie</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
@@ -9849,17 +9841,17 @@
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>Organisation</t>
+          <t>Report or document</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>Parent guidance platform</t>
+          <t>Report or data series</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>Pedagogical game assessments from the Federal Agency for Civic Education, from a parent/educator perspective. State-funded (bpb).</t>
+          <t>Long-running population-level media use data (formerly Onlinestudie) for adult baselines. Methodology changed with the 2023 rebrand, so check series comparability.</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
@@ -9879,7 +9871,7 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
-          <t>https://www.spielbar.de</t>
+          <t>https://www.ard-zdf-medienstudie.de</t>
         </is>
       </c>
       <c r="K143" s="3" t="inlineStr"/>
@@ -9894,12 +9886,12 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>ard-zdf-medienstudie</t>
+          <t>leibniz-institut-fur-medienforschung-hans-bredow-institut</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>ARD/ZDF-Medienstudie</t>
+          <t>Leibniz-Institut für Medienforschung | Hans-Bredow-Institut</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
@@ -9909,17 +9901,17 @@
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Report or document</t>
+          <t>Organisation</t>
         </is>
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>Report or data series</t>
+          <t>Research institute</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>Long-running population-level media use data (formerly Onlinestudie) for adult baselines. Methodology changed with the 2023 rebrand, so check series comparability.</t>
+          <t>Academic research on platforms, youth media, regulation, with a good EN publication share.</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
@@ -9929,7 +9921,7 @@
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>German</t>
+          <t>English; German</t>
         </is>
       </c>
       <c r="I144" s="3" t="inlineStr">
@@ -9939,7 +9931,7 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>https://www.ard-zdf-medienstudie.de</t>
+          <t>https://www.hans-bredow-institut.de</t>
         </is>
       </c>
       <c r="K144" s="3" t="inlineStr"/>
@@ -9954,12 +9946,12 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>leibniz-institut-fur-medienforschung-hans-bredow-institut</t>
+          <t>jugendschutz-net</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>Leibniz-Institut für Medienforschung | Hans-Bredow-Institut</t>
+          <t>jugendschutz.net</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
@@ -9974,12 +9966,12 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Research institute</t>
+          <t>Safety and advocacy org</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>Academic research on platforms, youth media, regulation, with a good EN publication share.</t>
+          <t>Reports on risks to minors in games/apps (monetization, contact risks, dark patterns). Joint federal/state body.</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
@@ -9989,7 +9981,7 @@
       </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
-          <t>English; German</t>
+          <t>German</t>
         </is>
       </c>
       <c r="I145" s="3" t="inlineStr">
@@ -9999,7 +9991,7 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>https://www.hans-bredow-institut.de</t>
+          <t>https://www.jugendschutz.net</t>
         </is>
       </c>
       <c r="K145" s="3" t="inlineStr"/>
@@ -10014,12 +10006,12 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>jugendschutz-net</t>
+          <t>computerspielemuseum-berlin</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>jugendschutz.net</t>
+          <t>Computerspielemuseum Berlin</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
@@ -10034,12 +10026,12 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>Safety and advocacy org</t>
+          <t>Archive or museum</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>Reports on risks to minors in games/apps (monetization, contact risks, dark patterns). Joint federal/state body.</t>
+          <t>Over 35,000 original data carriers, 350 consoles and 12,000 magazines, the largest body of German-market physical game media in one place.</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
@@ -10049,17 +10041,17 @@
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>German</t>
+          <t>English; German</t>
         </is>
       </c>
       <c r="I146" s="3" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Paid</t>
         </is>
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>https://www.jugendschutz.net</t>
+          <t>https://www.computerspielemuseum.de/en/Museum/47-About-the-museum.htm</t>
         </is>
       </c>
       <c r="K146" s="3" t="inlineStr"/>
@@ -10074,12 +10066,12 @@
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>computerspielemuseum-berlin</t>
+          <t>aevi-asociacion-espanola-de-videojuegos</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>Computerspielemuseum Berlin</t>
+          <t>AEVI: Asociación Española de Videojuegos</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
@@ -10094,32 +10086,32 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>Archive or museum</t>
+          <t>Industry association</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>Over 35,000 original data carriers, 350 consoles and 12,000 magazines, the largest body of German-market physical game media in one place.</t>
+          <t>The publisher-side voice on Spanish policy: age-rating education (Spain uses PEGI, no national board), esports positions, and the industry's public-facing campaigns. Trade advocacy. Represents the multinational publisher side rather than Spanish developers (that's DEV)</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>English; German</t>
+          <t>Spanish</t>
         </is>
       </c>
       <c r="I147" s="3" t="inlineStr">
         <is>
-          <t>Paid</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>https://www.computerspielemuseum.de/en/Museum/47-About-the-museum.htm</t>
+          <t>https://aevi.org.es/</t>
         </is>
       </c>
       <c r="K147" s="3" t="inlineStr"/>
@@ -10134,12 +10126,12 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>aevi-asociacion-espanola-de-videojuegos</t>
+          <t>dev-asociacion-espanola-de-empresas-productoras-y</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>AEVI: Asociación Española de Videojuegos</t>
+          <t>DEV: Asociación Española de Empresas Productoras y Desarrolladoras</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
@@ -10159,7 +10151,7 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>The publisher-side voice on Spanish policy: age-rating education (Spain uses PEGI, no national board), esports positions, and the industry's public-facing campaigns. Trade advocacy. Represents the multinational publisher side rather than Spanish developers (that's DEV)</t>
+          <t>The developer-side voice on Spanish policy: fiscal-incentive advocacy, talent-pipeline programs, and the Libro Blanco. The address for questions about Spanish studios rather than the Spanish market. Around 100 member studios. Trade advocacy. Membership skews toward established studios</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
@@ -10179,7 +10171,7 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>https://aevi.org.es/</t>
+          <t>https://dev.org.es/</t>
         </is>
       </c>
       <c r="K148" s="3" t="inlineStr"/>
@@ -10194,12 +10186,12 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>dev-asociacion-espanola-de-empresas-productoras-y</t>
+          <t>spain-audiovisual-hub-icex-games-from-spain</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>DEV: Asociación Española de Empresas Productoras y Desarrolladoras</t>
+          <t>Spain Audiovisual Hub (Gobierno de España) + ICEX "Games from Spain"</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
@@ -10214,12 +10206,12 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>Industry association</t>
+          <t>Government agency</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>The developer-side voice on Spanish policy: fiscal-incentive advocacy, talent-pipeline programs, and the Libro Blanco. The address for questions about Spanish studios rather than the Spanish market. Around 100 member studios. Trade advocacy. Membership skews toward established studios</t>
+          <t>State support: funding lines, sector news, and the export apparatus that co-finances the Libro Blanco and trade-show presence. Spain treats games as audiovisual industrial policy.</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
@@ -10229,7 +10221,7 @@
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>English; Spanish</t>
         </is>
       </c>
       <c r="I149" s="3" t="inlineStr">
@@ -10239,7 +10231,7 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
-          <t>https://dev.org.es/</t>
+          <t>https://spainaudiovisualhub.digital.gob.es/</t>
         </is>
       </c>
       <c r="K149" s="3" t="inlineStr"/>
@@ -10254,12 +10246,12 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>spain-audiovisual-hub-icex-games-from-spain</t>
+          <t>efgamp</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>Spain Audiovisual Hub (Gobierno de España) + ICEX "Games from Spain"</t>
+          <t>EFGAMP (European Federation of Video Game Archives, Museums and Preservation Projects)</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
@@ -10274,22 +10266,22 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>Government agency</t>
+          <t>Archive or museum</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>State support: funding lines, sector news, and the export apparatus that co-finances the Libro Blanco and trade-show presence. Spain treats games as audiovisual industrial policy.</t>
+          <t>The member directory lists 25 or more archives and museums across seventeen European countries, which is the fastest way to find which institution in a given country holds game material.</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EU</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>English; Spanish</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I150" s="3" t="inlineStr">
@@ -10299,7 +10291,7 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
-          <t>https://spainaudiovisualhub.digital.gob.es/</t>
+          <t>https://efgamp.eu/</t>
         </is>
       </c>
       <c r="K150" s="3" t="inlineStr"/>
@@ -10314,12 +10306,12 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>efgamp</t>
+          <t>video-games-europe</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>EFGAMP (European Federation of Video Game Archives, Museums and Preservation Projects)</t>
+          <t>Video Games Europe (ex-ISFE)</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
@@ -10334,17 +10326,17 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>Archive or museum</t>
+          <t>Industry association</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>The member directory lists 25 or more archives and museums across seventeen European countries, which is the fastest way to find which institution in a given country holds game material.</t>
+          <t>EU-level games trade body with pan-European player surveys ("Key Facts"). Advocacy body</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>EU</t>
+          <t>DE; EU; FR; IT; UK</t>
         </is>
       </c>
       <c r="H151" s="3" t="inlineStr">
@@ -10359,7 +10351,7 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
-          <t>https://efgamp.eu/</t>
+          <t>https://www.videogameseurope.eu/</t>
         </is>
       </c>
       <c r="K151" s="3" t="inlineStr"/>
@@ -10374,12 +10366,12 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>video-games-europe</t>
+          <t>sell</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>Video Games Europe (ex-ISFE)</t>
+          <t>SELL (Syndicat des Éditeurs de Logiciels de Loisirs)</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
@@ -10399,17 +10391,17 @@
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>EU-level games trade body with pan-European player surveys ("Key Facts"). Advocacy body</t>
+          <t>L'Essentiel du Jeu Vidéo, the annual French market and player study produced with Médiamétrie. Advocacy body of publishers.</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>DE; EU; FR; IT; UK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>French</t>
         </is>
       </c>
       <c r="I152" s="3" t="inlineStr">
@@ -10419,7 +10411,7 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>https://www.videogameseurope.eu/</t>
+          <t>https://www.sell.fr/</t>
         </is>
       </c>
       <c r="K152" s="3" t="inlineStr"/>
@@ -10434,12 +10426,12 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>sell</t>
+          <t>cnc</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>SELL (Syndicat des Éditeurs de Logiciels de Loisirs)</t>
+          <t>CNC (France)</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
@@ -10454,12 +10446,12 @@
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>Industry association</t>
+          <t>Government agency</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>L'Essentiel du Jeu Vidéo, the annual French market and player study produced with Médiamétrie. Advocacy body of publishers.</t>
+          <t>French public funding data and commissioned studies on games as a cultural industry, providing a French institutional frame. State body. Policy and cultural lens rather than consumer data. Some EN summaries of major reports</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
@@ -10479,7 +10471,7 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>https://www.sell.fr/</t>
+          <t>https://www.cnc.fr/</t>
         </is>
       </c>
       <c r="K153" s="3" t="inlineStr"/>
@@ -10494,12 +10486,12 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>cnc</t>
+          <t>snjv</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>CNC (France)</t>
+          <t>SNJV</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
@@ -10514,12 +10506,12 @@
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>Government agency</t>
+          <t>Industry association</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>French public funding data and commissioned studies on games as a cultural industry, providing a French institutional frame. State body. Policy and cultural lens rather than consumer data. Some EN summaries of major reports</t>
+          <t>Annual Baromètre du jeu vidéo on French studios, employment, production. Advocacy body (developers).</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
@@ -10539,7 +10531,7 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>https://www.cnc.fr/</t>
+          <t>https://snjv.org</t>
         </is>
       </c>
       <c r="K154" s="3" t="inlineStr"/>
@@ -10554,12 +10546,12 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>snjv</t>
+          <t>france-esports</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>SNJV</t>
+          <t>France Esports</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
@@ -10574,12 +10566,12 @@
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>Industry association</t>
+          <t>Esports body</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>Annual Baromètre du jeu vidéo on French studios, employment, production. Advocacy body (developers).</t>
+          <t>Barometer data on French esports practice and audience. Association co-founded with state involvement.</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
@@ -10599,7 +10591,7 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>https://snjv.org</t>
+          <t>https://france-esports.org</t>
         </is>
       </c>
       <c r="K155" s="3" t="inlineStr"/>
@@ -10614,12 +10606,12 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>france-esports</t>
+          <t>pedagojeux</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>France Esports</t>
+          <t>PédaGoJeux</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
@@ -10634,12 +10626,12 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>Esports body</t>
+          <t>Parent guidance platform</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>Barometer data on French esports practice and audience. Association co-founded with state involvement.</t>
+          <t>The French parents' resource on games: age ratings explained, screen-time guidance, family practice. Coalition (ministry, SELL, UNAF, e-Enfance).</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
@@ -10659,7 +10651,7 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
-          <t>https://france-esports.org</t>
+          <t>https://www.pedagojeux.fr</t>
         </is>
       </c>
       <c r="K156" s="3" t="inlineStr"/>
@@ -10674,12 +10666,12 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>pedagojeux</t>
+          <t>e-enfance-3018</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>PédaGoJeux</t>
+          <t>e-Enfance / 3018</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
@@ -10694,12 +10686,12 @@
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>Parent guidance platform</t>
+          <t>Safety and advocacy org</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>The French parents' resource on games: age ratings explained, screen-time guidance, family practice. Coalition (ministry, SELL, UNAF, e-Enfance).</t>
+          <t>Cyberbullying and online-risk reporting for minors, incl. in-game contexts. Runs the national 3018 helpline. State-recognized association. Advocacy-inflected reports, useful incident data.</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
@@ -10719,7 +10711,7 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
-          <t>https://www.pedagojeux.fr</t>
+          <t>https://e-enfance.org</t>
         </is>
       </c>
       <c r="K157" s="3" t="inlineStr"/>
@@ -10734,12 +10726,12 @@
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>e-enfance-3018</t>
+          <t>bibliotheque-nationale-de-france-collections-de-jeux-video</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>e-Enfance / 3018</t>
+          <t>Bibliothèque nationale de France, collections de jeux vidéo</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
@@ -10754,12 +10746,12 @@
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>Safety and advocacy org</t>
+          <t>Archive or museum</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>Cyberbullying and online-risk reporting for minors, incl. in-game contexts. Runs the national 3018 helpline. State-recognized association. Advocacy-inflected reports, useful incident data.</t>
+          <t>Legal deposit of video games since 1992, over 22,000 titles on roughly 40,000 carriers across 55 console systems. The most complete run of French-market releases anywhere. Onsite in salle P on accreditation only.</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
@@ -10779,7 +10771,7 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
-          <t>https://e-enfance.org</t>
+          <t>https://www.bnf.fr/fr/les-jeux-video-la-bnf</t>
         </is>
       </c>
       <c r="K158" s="3" t="inlineStr"/>
@@ -10794,12 +10786,12 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>bibliotheque-nationale-de-france-collections-de-jeux-video</t>
+          <t>stjv</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>Bibliothèque nationale de France, collections de jeux vidéo</t>
+          <t>STJV (Syndicat des Travailleur·euses du Jeu Vidéo)</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
@@ -10814,12 +10806,12 @@
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>Archive or museum</t>
+          <t>Union or worker organisation</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>Legal deposit of video games since 1992, over 22,000 titles on roughly 40,000 carriers across 55 console systems. The most complete run of French-market releases anywhere. Onsite in salle P on accreditation only.</t>
+          <t>France's game workers union, publishing its own analysis of studio liquidations and calling national strike action. Not to be confused with SNJV, the employers' federation, which is also on this tab.</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
@@ -10829,7 +10821,7 @@
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>French</t>
+          <t>English; French</t>
         </is>
       </c>
       <c r="I159" s="3" t="inlineStr">
@@ -10839,7 +10831,7 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
-          <t>https://www.bnf.fr/fr/les-jeux-video-la-bnf</t>
+          <t>https://www.stjv.fr/en/</t>
         </is>
       </c>
       <c r="K159" s="3" t="inlineStr"/>
@@ -10854,12 +10846,12 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>stjv</t>
+          <t>digra</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>STJV (Syndicat des Travailleur·euses du Jeu Vidéo)</t>
+          <t>DiGRA (Digital Games Research Association)</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
@@ -10874,22 +10866,22 @@
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>Union or worker organisation</t>
+          <t>Learned society</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>France's game workers union, publishing its own analysis of studio liquidations and calling national strike action. Not to be confused with SNJV, the employers' federation, which is also on this tab.</t>
+          <t>An international association for academics and professionals who research digital games and associated phenomena. The chapters register states which of 22 national chapters are established, emerging or inactive, so a researcher can tell whether a functioning games research community exists in a country before writing to it.</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>English; French</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I160" s="3" t="inlineStr">
@@ -10899,7 +10891,7 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>https://www.stjv.fr/en/</t>
+          <t>https://digra.org/</t>
         </is>
       </c>
       <c r="K160" s="3" t="inlineStr"/>
@@ -10914,12 +10906,12 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>digra</t>
+          <t>foundations-of-digital-games</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>DiGRA (Digital Games Research Association)</t>
+          <t>Foundations of Digital Games (FDG)</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
@@ -10934,12 +10926,12 @@
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>Learned society</t>
+          <t>Event or awards</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>An international association for academics and professionals who research digital games and associated phenomena. The chapters register states which of 22 national chapters are established, emerging or inactive, so a researcher can tell whether a functioning games research community exists in a country before writing to it.</t>
+          <t>The main computationally inclined peer-reviewed games venue, complementary to DiGRA, covering game AI, procedural generation, playtesting methods and analytics.</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
@@ -10959,7 +10951,7 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
-          <t>https://digra.org/</t>
+          <t>https://fdg2026.org/</t>
         </is>
       </c>
       <c r="K161" s="3" t="inlineStr"/>
@@ -10974,12 +10966,12 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>foundations-of-digital-games</t>
+          <t>game-worker-solidarity</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>Foundations of Digital Games (FDG)</t>
+          <t>Game Worker Solidarity</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
@@ -10989,17 +10981,17 @@
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>Organisation</t>
+          <t>Report or document</t>
         </is>
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>Event or awards</t>
+          <t>Report or data series</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>The main computationally inclined peer-reviewed games venue, complementary to DiGRA, covering game AI, procedural generation, playtesting methods and analytics.</t>
+          <t>A mapping project documenting strikes and collective actions in games, supported by The Open University and the Digital Futures Institute at King's College London.</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
@@ -11019,7 +11011,7 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
-          <t>https://fdg2026.org/</t>
+          <t>https://gameworkersolidarity.com/</t>
         </is>
       </c>
       <c r="K162" s="3" t="inlineStr"/>
@@ -11034,12 +11026,12 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>game-worker-solidarity</t>
+          <t>who-addictive-behaviours-gaming-disorder</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>Game Worker Solidarity</t>
+          <t>WHO, Addictive behaviours: gaming disorder</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
@@ -11054,12 +11046,12 @@
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>Report or data series</t>
+          <t>Regulation or law</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>A mapping project documenting strikes and collective actions in games, supported by The Open University and the Digital Futures Institute at King's College London.</t>
+          <t>WHO's own wording of the gaming disorder diagnosis, including the twelve month duration requirement and WHO's statement that the condition affects only a small proportion of players.</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
@@ -11079,7 +11071,7 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>https://gameworkersolidarity.com/</t>
+          <t>https://www.who.int/news-room/questions-and-answers/item/addictive-behaviours-gaming-disorder</t>
         </is>
       </c>
       <c r="K163" s="3" t="inlineStr"/>
@@ -11094,12 +11086,12 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>who-addictive-behaviours-gaming-disorder</t>
+          <t>igda-game-accessibility-special-interest-group</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
         <is>
-          <t>WHO, Addictive behaviours: gaming disorder</t>
+          <t>IGDA Game Accessibility Special Interest Group</t>
         </is>
       </c>
       <c r="C164" s="3" t="inlineStr">
@@ -11109,17 +11101,17 @@
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Report or document</t>
+          <t>Organisation</t>
         </is>
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>Regulation or law</t>
+          <t>Industry association</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>WHO's own wording of the gaming disorder diagnosis, including the twelve month duration requirement and WHO's statement that the condition affects only a small proportion of players.</t>
+          <t>A volunteer group operating since 2003, publishing introductory accessibility material and GDC roundtable recaps that show what developers argue about year to year. Posting is irregular.</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
@@ -11139,7 +11131,7 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>https://www.who.int/news-room/questions-and-answers/item/addictive-behaviours-gaming-disorder</t>
+          <t>https://igda-gasig.org/</t>
         </is>
       </c>
       <c r="K164" s="3" t="inlineStr"/>
@@ -11154,12 +11146,12 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>igda-game-accessibility-special-interest-group</t>
+          <t>games-user-research</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>IGDA Game Accessibility Special Interest Group</t>
+          <t>Games User Research</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
@@ -11179,7 +11171,7 @@
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>A volunteer group operating since 2003, publishing introductory accessibility material and GDC roundtable recaps that show what developers argue about year to year. Posting is irregular.</t>
+          <t>The professional home of games user research, running a Discord, a jobs board, a mentoring programme and the annual summits. VERIFY. The SIG page and the IGDA overview page name different current leadership.</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
@@ -11199,7 +11191,7 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
-          <t>https://igda-gasig.org/</t>
+          <t>https://www.gamesur.com/</t>
         </is>
       </c>
       <c r="K165" s="3" t="inlineStr"/>
@@ -11214,12 +11206,12 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>games-user-research</t>
+          <t>thriving-in-games-group</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>Games User Research</t>
+          <t>Thriving in Games Group (formerly Fair Play Alliance)</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
@@ -11239,7 +11231,7 @@
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>The professional home of games user research, running a Discord, a jobs board, a mentoring programme and the annual summits. VERIFY. The SIG page and the IGDA overview page name different current leadership.</t>
+          <t>The Disruption and Harms in Online Gaming Framework, a shared vocabulary for classifying player misbehaviour that studios actually use.</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
@@ -11259,7 +11251,7 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
-          <t>https://www.gamesur.com/</t>
+          <t>https://thrivingingames.org/</t>
         </is>
       </c>
       <c r="K166" s="3" t="inlineStr"/>
@@ -11274,12 +11266,12 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>thriving-in-games-group</t>
+          <t>esports-federation-of-india</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
         <is>
-          <t>Thriving in Games Group (formerly Fair Play Alliance)</t>
+          <t>Esports Federation of India (ESFI)</t>
         </is>
       </c>
       <c r="C167" s="3" t="inlineStr">
@@ -11294,17 +11286,17 @@
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>Industry association</t>
+          <t>Esports body</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>The Disruption and Harms in Online Gaming Framework, a shared vocabulary for classifying player misbehaviour that studios actually use.</t>
+          <t>Who officially represents India at Asian Games/Global Esports Games, which titles are treated as medal esports, and national championship structures (NESC). Member of IESF, AESF and GEF. Federation-politics territory: rival bodies have contested representation claims over the years. Advocacy framing on esports policy</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="H167" s="3" t="inlineStr">
@@ -11319,7 +11311,7 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>https://thrivingingames.org/</t>
+          <t>https://esportsfederation.in/</t>
         </is>
       </c>
       <c r="K167" s="3" t="inlineStr"/>
@@ -11334,12 +11326,12 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>esports-federation-of-india</t>
+          <t>indian-digital-gaming-society</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>Esports Federation of India (ESFI)</t>
+          <t>Indian Digital Gaming Society (IDGS / CII)</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
@@ -11354,12 +11346,12 @@
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>Esports body</t>
+          <t>Industry association</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>Who officially represents India at Asian Games/Global Esports Games, which titles are treated as medal esports, and national championship structures (NESC). Member of IESF, AESF and GEF. Federation-politics territory: rival bodies have contested representation claims over the years. Advocacy framing on esports policy</t>
+          <t>The industry-establishment view: runs India Gaming Show and policy conclaves. Useful for tracking how developers/publishers (Krafton India et al.) position themselves with government. Operates under the Confederation of Indian Industry. Trade-body advocacy. Thinner published output than a research institution, so better for positions and events than data</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
@@ -11379,7 +11371,7 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
-          <t>https://esportsfederation.in/</t>
+          <t>https://gamingsociety.in/</t>
         </is>
       </c>
       <c r="K168" s="3" t="inlineStr"/>
@@ -11394,12 +11386,12 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>indian-digital-gaming-society</t>
+          <t>iidea</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
         <is>
-          <t>Indian Digital Gaming Society (IDGS / CII)</t>
+          <t>IIDEA (Italy)</t>
         </is>
       </c>
       <c r="C169" s="3" t="inlineStr">
@@ -11419,17 +11411,17 @@
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>The industry-establishment view: runs India Gaming Show and policy conclaves. Useful for tracking how developers/publishers (Krafton India et al.) position themselves with government. Operates under the Confederation of Indian Industry. Trade-body advocacy. Thinner published output than a research institution, so better for positions and events than data</t>
+          <t>The Italian data source, effectively substituting for Italy's missing trade press. Annual market report with Ipsos, 2.4bn EUR in 2025, esports report with Accenture, 2026, plus the IVGA awards and First Playable. Advocacy body. EN materials available English coverage is partial.</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>English; Italian</t>
         </is>
       </c>
       <c r="I169" s="3" t="inlineStr">
@@ -11439,7 +11431,7 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>https://gamingsociety.in/</t>
+          <t>https://iideassociation.com/en/</t>
         </is>
       </c>
       <c r="K169" s="3" t="inlineStr"/>
@@ -11454,12 +11446,12 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>iidea</t>
+          <t>cesa</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>IIDEA (Italy)</t>
+          <t>CESA</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
@@ -11479,27 +11471,27 @@
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>The Italian data source, effectively substituting for Italy's missing trade press. Annual market report with Ipsos, 2.4bn EUR in 2025, esports report with Accenture, 2026, plus the IVGA awards and First Playable. Advocacy body. EN materials available English coverage is partial.</t>
+          <t>CESAゲーム産業レポート (CESA Gēmu Sangyō Repōto), the JP industry reference survey, 2025 edition current. Also runs Tokyo Game Show. CORRECTION: the older CESAゲーム白書 (Games White Paper) was discontinued after 2023. DO NOT CITE THE WHITE PAPER. Paid physical publication, Japanese only. Nintendo is only a special supporting member and does not exhibit at TGS</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>English; Italian</t>
+          <t>Japanese</t>
         </is>
       </c>
       <c r="I170" s="3" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Paid</t>
         </is>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>https://iideassociation.com/en/</t>
+          <t>https://www.cesa.or.jp/</t>
         </is>
       </c>
       <c r="K170" s="3" t="inlineStr"/>
@@ -11514,12 +11506,12 @@
     <row r="171">
       <c r="A171" s="3" t="inlineStr">
         <is>
-          <t>cesa</t>
+          <t>famitsu-game-hakusho</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
         <is>
-          <t>CESA</t>
+          <t>Famitsu Game Hakusho (ゲーム白書)</t>
         </is>
       </c>
       <c r="C171" s="3" t="inlineStr">
@@ -11529,17 +11521,17 @@
       </c>
       <c r="D171" s="3" t="inlineStr">
         <is>
-          <t>Organisation</t>
+          <t>Report or document</t>
         </is>
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>Industry association</t>
+          <t>Report or data series</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>CESAゲーム産業レポート (CESA Gēmu Sangyō Repōto), the JP industry reference survey, 2025 edition current. Also runs Tokyo Game Show. CORRECTION: the older CESAゲーム白書 (Games White Paper) was discontinued after 2023. DO NOT CITE THE WHITE PAPER. Paid physical publication, Japanese only. Nintendo is only a special supporting member and does not exhibit at TGS</t>
+          <t>Annual JP market sizing including mobile/PC. Partnered with Sensor Tower. Expensive. Headline figures circulate free via trade coverage</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
@@ -11559,7 +11551,7 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>https://www.cesa.or.jp/</t>
+          <t>https://www.kadokawa.co.jp/product/322509000686/</t>
         </is>
       </c>
       <c r="K171" s="3" t="inlineStr"/>
@@ -11574,12 +11566,12 @@
     <row r="172">
       <c r="A172" s="3" t="inlineStr">
         <is>
-          <t>famitsu-game-hakusho</t>
+          <t>cero</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>Famitsu Game Hakusho (ゲーム白書)</t>
+          <t>CERO</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
@@ -11589,17 +11581,17 @@
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>Report or document</t>
+          <t>Organisation</t>
         </is>
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>Report or data series</t>
+          <t>Rating body</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>Annual JP market sizing including mobile/PC. Partnered with Sensor Tower. Expensive. Headline figures circulate free via trade coverage</t>
+          <t>JP rating records from the age-ratings body, an NPO established June 2002 which took over rating from CESA's own self-regulation. The Japanese analogue to Korea's GRAC. Shows what content norms look like officially. Ratings only. Thin as a data source but useful as a cultural signal</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
@@ -11614,12 +11606,12 @@
       </c>
       <c r="I172" s="3" t="inlineStr">
         <is>
-          <t>Paid</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
-          <t>https://www.kadokawa.co.jp/product/322509000686/</t>
+          <t>https://www.cero.gr.jp/</t>
         </is>
       </c>
       <c r="K172" s="3" t="inlineStr"/>
@@ -11634,12 +11626,12 @@
     <row r="173">
       <c r="A173" s="3" t="inlineStr">
         <is>
-          <t>cero</t>
+          <t>agency-for-cultural-affairs</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
         <is>
-          <t>CERO</t>
+          <t>Agency for Cultural Affairs</t>
         </is>
       </c>
       <c r="C173" s="3" t="inlineStr">
@@ -11654,12 +11646,12 @@
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>Rating body</t>
+          <t>Government agency</t>
         </is>
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
-          <t>JP rating records from the age-ratings body, an NPO established June 2002 which took over rating from CESA's own self-regulation. The Japanese analogue to Korea's GRAC. Shows what content norms look like officially. Ratings only. Thin as a data source but useful as a cultural signal</t>
+          <t>Media arts policy. The state's framing of games-as-culture.</t>
         </is>
       </c>
       <c r="G173" s="3" t="inlineStr">
@@ -11679,7 +11671,7 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>https://www.cero.gr.jp/</t>
+          <t>https://www.bunka.go.jp/english/</t>
         </is>
       </c>
       <c r="K173" s="3" t="inlineStr"/>
@@ -11694,12 +11686,12 @@
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>agency-for-cultural-affairs</t>
+          <t>mic</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>Agency for Cultural Affairs</t>
+          <t>MIC (Ministry of Internal Affairs and Communications)</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
@@ -11719,7 +11711,7 @@
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>Media arts policy. The state's framing of games-as-culture.</t>
+          <t>Communications ministry. ICT and media usage statistics.</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
@@ -11739,7 +11731,7 @@
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
-          <t>https://www.bunka.go.jp/english/</t>
+          <t>https://www.soumu.go.jp/</t>
         </is>
       </c>
       <c r="K174" s="3" t="inlineStr"/>
@@ -11754,12 +11746,12 @@
     <row r="175">
       <c r="A175" s="3" t="inlineStr">
         <is>
-          <t>mic</t>
+          <t>jesu</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
         <is>
-          <t>MIC (Ministry of Internal Affairs and Communications)</t>
+          <t>JESU (Japan Esports Union)</t>
         </is>
       </c>
       <c r="C175" s="3" t="inlineStr">
@@ -11774,12 +11766,12 @@
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>Government agency</t>
+          <t>Esports body</t>
         </is>
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>Communications ministry. ICT and media usage statistics.</t>
+          <t>Esports governing body.</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
@@ -11799,7 +11791,7 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
-          <t>https://www.soumu.go.jp/</t>
+          <t>https://jesu.or.jp</t>
         </is>
       </c>
       <c r="K175" s="3" t="inlineStr"/>
@@ -11814,12 +11806,12 @@
     <row r="176">
       <c r="A176" s="3" t="inlineStr">
         <is>
-          <t>jesu</t>
+          <t>nhk-broadcasting-culture-research-institute</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>JESU (Japan Esports Union)</t>
+          <t>NHK Broadcasting Culture Research Institute</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
@@ -11834,12 +11826,12 @@
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>Esports body</t>
+          <t>Research institute</t>
         </is>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
-          <t>Esports governing body.</t>
+          <t>国民生活時間調査 (time-use survey) + media consumption research. Primary data on how Japanese people actually spend time.</t>
         </is>
       </c>
       <c r="G176" s="3" t="inlineStr">
@@ -11859,7 +11851,7 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
-          <t>https://jesu.or.jp</t>
+          <t>https://www.nhk.or.jp/bunken/</t>
         </is>
       </c>
       <c r="K176" s="3" t="inlineStr"/>
@@ -11874,12 +11866,12 @@
     <row r="177">
       <c r="A177" s="3" t="inlineStr">
         <is>
-          <t>nhk-broadcasting-culture-research-institute</t>
+          <t>joga</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
         <is>
-          <t>NHK Broadcasting Culture Research Institute</t>
+          <t>JOGA</t>
         </is>
       </c>
       <c r="C177" s="3" t="inlineStr">
@@ -11894,12 +11886,12 @@
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>Research institute</t>
+          <t>Industry association</t>
         </is>
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
-          <t>国民生活時間調査 (time-use survey) + media consumption research. Primary data on how Japanese people actually spend time.</t>
+          <t>Online games association. Gacha and online self-regulation guidelines.</t>
         </is>
       </c>
       <c r="G177" s="3" t="inlineStr">
@@ -11919,7 +11911,7 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>https://www.nhk.or.jp/bunken/</t>
+          <t>https://japanonlinegame.org</t>
         </is>
       </c>
       <c r="K177" s="3" t="inlineStr"/>
@@ -11934,12 +11926,12 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t>joga</t>
+          <t>ritsumeikan-center-for-game-studies-collection</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>JOGA</t>
+          <t>立命館大学ゲーム研究センター RCGSコレクション (Ritsumeikan Center for Game Studies collection)</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
@@ -11954,12 +11946,12 @@
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>Industry association</t>
+          <t>Archive or museum</t>
         </is>
       </c>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>Online games association. Gacha and online self-regulation guidelines.</t>
+          <t>Catalogue records for Japanese game packages, related materials and devices, with CC0 metadata, a SPARQL endpoint and RDF dumps. No published procedure exists for consulting the physical collection.</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr">
@@ -11979,7 +11971,7 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
-          <t>https://japanonlinegame.org</t>
+          <t>https://collection.rcgs.jp/page/about</t>
         </is>
       </c>
       <c r="K178" s="3" t="inlineStr"/>
@@ -11994,12 +11986,12 @@
     <row r="179">
       <c r="A179" s="3" t="inlineStr">
         <is>
-          <t>ritsumeikan-center-for-game-studies-collection</t>
+          <t>kurihama-medical-and-addiction-center-tiar</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
         <is>
-          <t>立命館大学ゲーム研究センター RCGSコレクション (Ritsumeikan Center for Game Studies collection)</t>
+          <t>久里浜医療センター インターネット依存治療研究部門 (Kurihama Medical and Addiction Center, TIAR)</t>
         </is>
       </c>
       <c r="C179" s="3" t="inlineStr">
@@ -12014,12 +12006,12 @@
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>Archive or museum</t>
+          <t>Research institute</t>
         </is>
       </c>
       <c r="F179" s="3" t="inlineStr">
         <is>
-          <t>Catalogue records for Japanese game packages, related materials and devices, with CC0 metadata, a SPARQL endpoint and RDF dumps. No published procedure exists for consulting the physical collection.</t>
+          <t>Japan's first specialist internet and gaming addiction clinic, running outpatient treatment, family programmes and treatment camps, and participating in WHO gaming disorder work.</t>
         </is>
       </c>
       <c r="G179" s="3" t="inlineStr">
@@ -12039,7 +12031,7 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
-          <t>https://collection.rcgs.jp/page/about</t>
+          <t>https://kurihama.hosp.go.jp/hospital/section/internet.html</t>
         </is>
       </c>
       <c r="K179" s="3" t="inlineStr"/>
@@ -12054,12 +12046,12 @@
     <row r="180">
       <c r="A180" s="3" t="inlineStr">
         <is>
-          <t>kurihama-medical-and-addiction-center-tiar</t>
+          <t>kocca</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>久里浜医療センター インターネット依存治療研究部門 (Kurihama Medical and Addiction Center, TIAR)</t>
+          <t>KOCCA (한국콘텐츠진흥원)</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
@@ -12074,22 +12066,22 @@
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>Research institute</t>
+          <t>Government agency</t>
         </is>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
-          <t>Japan's first specialist internet and gaming addiction clinic, running outpatient treatment, family programmes and treatment camps, and participating in WHO gaming disorder work.</t>
+          <t>The annual Korea Game White Paper, the authoritative KR industry dataset, with usage surveys and policy signals. Korean-language and PDF-heavy, and the English summaries lag by a year or more. English coverage is partial.</t>
         </is>
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="H180" s="3" t="inlineStr">
         <is>
-          <t>Japanese</t>
+          <t>English; Korean</t>
         </is>
       </c>
       <c r="I180" s="3" t="inlineStr">
@@ -12099,7 +12091,7 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
-          <t>https://kurihama.hosp.go.jp/hospital/section/internet.html</t>
+          <t>https://www.kocca.kr/</t>
         </is>
       </c>
       <c r="K180" s="3" t="inlineStr"/>
@@ -12114,12 +12106,12 @@
     <row r="181">
       <c r="A181" s="3" t="inlineStr">
         <is>
-          <t>kocca</t>
+          <t>grac</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
         <is>
-          <t>KOCCA (한국콘텐츠진흥원)</t>
+          <t>GRAC (게임물관리위원회)</t>
         </is>
       </c>
       <c r="C181" s="3" t="inlineStr">
@@ -12134,12 +12126,12 @@
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>Government agency</t>
+          <t>Rating body</t>
         </is>
       </c>
       <c r="F181" s="3" t="inlineStr">
         <is>
-          <t>The annual Korea Game White Paper, the authoritative KR industry dataset, with usage surveys and policy signals. Korean-language and PDF-heavy, and the English summaries lag by a year or more. English coverage is partial.</t>
+          <t>KR rating decisions, a real-time public record of what is entering the market and how it is classified. Korean only, with clunky database navigation.</t>
         </is>
       </c>
       <c r="G181" s="3" t="inlineStr">
@@ -12149,7 +12141,7 @@
       </c>
       <c r="H181" s="3" t="inlineStr">
         <is>
-          <t>English; Korean</t>
+          <t>Korean</t>
         </is>
       </c>
       <c r="I181" s="3" t="inlineStr">
@@ -12159,7 +12151,7 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
-          <t>https://www.kocca.kr/</t>
+          <t>https://www.grac.or.kr/</t>
         </is>
       </c>
       <c r="K181" s="3" t="inlineStr"/>
@@ -12174,12 +12166,12 @@
     <row r="182">
       <c r="A182" s="3" t="inlineStr">
         <is>
-          <t>grac</t>
+          <t>k-games</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>GRAC (게임물관리위원회)</t>
+          <t>K-GAMES (한국게임산업협회)</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
@@ -12194,12 +12186,12 @@
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>Rating body</t>
+          <t>Industry association</t>
         </is>
       </c>
       <c r="F182" s="3" t="inlineStr">
         <is>
-          <t>KR rating decisions, a real-time public record of what is entering the market and how it is classified. Korean only, with clunky database navigation.</t>
+          <t>KR industry positions on regulation, esports and self-regulation. Advocacy body, so read as industry voice instead of as neutral data</t>
         </is>
       </c>
       <c r="G182" s="3" t="inlineStr">
@@ -12219,7 +12211,7 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
-          <t>https://www.grac.or.kr/</t>
+          <t>https://kgames.or.kr/</t>
         </is>
       </c>
       <c r="K182" s="3" t="inlineStr"/>
@@ -12234,12 +12226,12 @@
     <row r="183">
       <c r="A183" s="3" t="inlineStr">
         <is>
-          <t>k-games</t>
+          <t>korea-game-society</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
         <is>
-          <t>K-GAMES (한국게임산업협회)</t>
+          <t>한국게임학회 (Korea Game Society)</t>
         </is>
       </c>
       <c r="C183" s="3" t="inlineStr">
@@ -12254,12 +12246,12 @@
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>Industry association</t>
+          <t>Learned society</t>
         </is>
       </c>
       <c r="F183" s="3" t="inlineStr">
         <is>
-          <t>KR industry positions on regulation, esports and self-regulation. Advocacy body, so read as industry voice instead of as neutral data</t>
+          <t>Korea's games research society, publishing the bimonthly 한국게임학회 논문지 (Journal of Korea Game Society).</t>
         </is>
       </c>
       <c r="G183" s="3" t="inlineStr">
@@ -12279,7 +12271,7 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
-          <t>https://kgames.or.kr/</t>
+          <t>https://kcgs.or.kr/</t>
         </is>
       </c>
       <c r="K183" s="3" t="inlineStr"/>
@@ -12294,12 +12286,12 @@
     <row r="184">
       <c r="A184" s="3" t="inlineStr">
         <is>
-          <t>korea-game-society</t>
+          <t>saudi-esports-federation</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>한국게임학회 (Korea Game Society)</t>
+          <t>Saudi Esports Federation</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
@@ -12314,22 +12306,22 @@
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>Learned society</t>
+          <t>Esports body</t>
         </is>
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>Korea's games research society, publishing the bimonthly 한국게임학회 논문지 (Journal of Korea Game Society).</t>
+          <t>Government-backed body whose programs and event rosters define which creators get institutional platforming in the region's largest market. Organises national teams, tournaments and sector programs, and grants the region's esports media awards, so it shapes the media field that covers it. State body chaired within the Saudi sports establishment</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>MENA</t>
         </is>
       </c>
       <c r="H184" s="3" t="inlineStr">
         <is>
-          <t>Korean</t>
+          <t>Arabic; English</t>
         </is>
       </c>
       <c r="I184" s="3" t="inlineStr">
@@ -12339,7 +12331,7 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
-          <t>https://kcgs.or.kr/</t>
+          <t>https://saudiesports.sa</t>
         </is>
       </c>
       <c r="K184" s="3" t="inlineStr"/>
@@ -12354,12 +12346,12 @@
     <row r="185">
       <c r="A185" s="3" t="inlineStr">
         <is>
-          <t>saudi-esports-federation</t>
+          <t>esports-world-cup-foundation</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
         <is>
-          <t>Saudi Esports Federation</t>
+          <t>Esports World Cup Foundation</t>
         </is>
       </c>
       <c r="C185" s="3" t="inlineStr">
@@ -12374,12 +12366,12 @@
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>Esports body</t>
+          <t>Event or awards</t>
         </is>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
-          <t>Government-backed body whose programs and event rosters define which creators get institutional platforming in the region's largest market. Organises national teams, tournaments and sector programs, and grants the region's esports media awards, so it shapes the media field that covers it. State body chaired within the Saudi sports establishment</t>
+          <t>Primary source for the largest esports prize pool in the world ($75M, 2026) and its club ecosystem. PIF-funded nonprofit.</t>
         </is>
       </c>
       <c r="G185" s="3" t="inlineStr">
@@ -12399,7 +12391,7 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>https://saudiesports.sa</t>
+          <t>https://esportsworldcup.com</t>
         </is>
       </c>
       <c r="K185" s="3" t="inlineStr"/>
@@ -12414,12 +12406,12 @@
     <row r="186">
       <c r="A186" s="3" t="inlineStr">
         <is>
-          <t>esports-world-cup-foundation</t>
+          <t>savvy-games-group</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>Esports World Cup Foundation</t>
+          <t>Savvy Games Group</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
@@ -12434,12 +12426,12 @@
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>Event or awards</t>
+          <t>Government agency</t>
         </is>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
-          <t>Primary source for the largest esports prize pool in the world ($75M, 2026) and its club ecosystem. PIF-funded nonprofit.</t>
+          <t>Primary source for the PIF gaming strategy: ESL FACEIT, Moonton, stakes in Nintendo/Take-Two, National Gaming Strategy targets. The most important primary source on MENA games investment, but definitely not neutral.</t>
         </is>
       </c>
       <c r="G186" s="3" t="inlineStr">
@@ -12459,7 +12451,7 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
-          <t>https://esportsworldcup.com</t>
+          <t>https://savvygames.com</t>
         </is>
       </c>
       <c r="K186" s="3" t="inlineStr"/>
@@ -12474,12 +12466,12 @@
     <row r="187">
       <c r="A187" s="3" t="inlineStr">
         <is>
-          <t>savvy-games-group</t>
+          <t>ad-gaming</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
         <is>
-          <t>Savvy Games Group</t>
+          <t>AD Gaming</t>
         </is>
       </c>
       <c r="C187" s="3" t="inlineStr">
@@ -12499,7 +12491,7 @@
       </c>
       <c r="F187" s="3" t="inlineStr">
         <is>
-          <t>Primary source for the PIF gaming strategy: ESL FACEIT, Moonton, stakes in Nintendo/Take-Two, National Gaming Strategy targets. The most important primary source on MENA games investment, but definitely not neutral.</t>
+          <t>Abu Dhabi's games-industry development program, the UAE counterpart to Saudi's strategy (Dubai runs its own Program for Gaming 2033).</t>
         </is>
       </c>
       <c r="G187" s="3" t="inlineStr">
@@ -12519,7 +12511,7 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>https://savvygames.com</t>
+          <t>https://www.instagram.com/abudhabi_gaming/?hl=en</t>
         </is>
       </c>
       <c r="K187" s="3" t="inlineStr"/>
@@ -12534,12 +12526,12 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t>ad-gaming</t>
+          <t>frmje</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>AD Gaming</t>
+          <t>FRMJE</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
@@ -12554,12 +12546,12 @@
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>Government agency</t>
+          <t>Esports body</t>
         </is>
       </c>
       <c r="F188" s="3" t="inlineStr">
         <is>
-          <t>Abu Dhabi's games-industry development program, the UAE counterpart to Saudi's strategy (Dubai runs its own Program for Gaming 2033).</t>
+          <t>The Maghreb's most structured esports body with national competitions (E-DAWRY). Royal federation under ministry tutelage.</t>
         </is>
       </c>
       <c r="G188" s="3" t="inlineStr">
@@ -12569,7 +12561,7 @@
       </c>
       <c r="H188" s="3" t="inlineStr">
         <is>
-          <t>Arabic; English</t>
+          <t>Arabic; French</t>
         </is>
       </c>
       <c r="I188" s="3" t="inlineStr">
@@ -12579,7 +12571,7 @@
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/abudhabi_gaming/?hl=en</t>
+          <t>https://frmje.ma</t>
         </is>
       </c>
       <c r="K188" s="3" t="inlineStr"/>
@@ -12594,12 +12586,12 @@
     <row r="189">
       <c r="A189" s="3" t="inlineStr">
         <is>
-          <t>frmje</t>
+          <t>smeccv-sistema-mexicano-de-equivalencias-de-clasificacion</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
         <is>
-          <t>FRMJE</t>
+          <t>SMECCV: Sistema Mexicano de Equivalencias de Clasificación de Contenidos de Videojuegos (SEGOB/RTC)</t>
         </is>
       </c>
       <c r="C189" s="3" t="inlineStr">
@@ -12614,22 +12606,22 @@
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>Esports body</t>
+          <t>Rating body</t>
         </is>
       </c>
       <c r="F189" s="3" t="inlineStr">
         <is>
-          <t>The Maghreb's most structured esports body with national competitions (E-DAWRY). Royal federation under ministry tutelage.</t>
+          <t>Mexico's official classification frame (A/B/B15/C/D) with loot-box/microtransaction warning labels, the Tier-A reference for what content rules formally apply. Includes the ESRB equivalence table. Mandatory system in force since 27 May 2021 under DOF lineamientos. Applies mainly to physical distribution, and digital storefronts largely still show ESRB. Enforcement by RTC is light, a labeling system more than a review board</t>
         </is>
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>MENA</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="H189" s="3" t="inlineStr">
         <is>
-          <t>Arabic; French</t>
+          <t>Spanish</t>
         </is>
       </c>
       <c r="I189" s="3" t="inlineStr">
@@ -12639,7 +12631,7 @@
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
-          <t>https://frmje.ma</t>
+          <t>https://es.wikipedia.org/wiki/Sistema_Mexicano_de_Equivalencias_de_Clasificaci%C3%B3n_de_Contenidos_de_Videojuegos</t>
         </is>
       </c>
       <c r="K189" s="3" t="inlineStr"/>
@@ -12654,12 +12646,12 @@
     <row r="190">
       <c r="A190" s="3" t="inlineStr">
         <is>
-          <t>smeccv-sistema-mexicano-de-equivalencias-de-clasificacion</t>
+          <t>ift-estado-del-gaming-en-mexico</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>SMECCV: Sistema Mexicano de Equivalencias de Clasificación de Contenidos de Videojuegos (SEGOB/RTC)</t>
+          <t>IFT: "Estado del Gaming en México" (Somos Audiencias)</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
@@ -12669,17 +12661,17 @@
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Organisation</t>
+          <t>Report or document</t>
         </is>
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>Rating body</t>
+          <t>Report or data series</t>
         </is>
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>Mexico's official classification frame (A/B/B15/C/D) with loot-box/microtransaction warning labels, the Tier-A reference for what content rules formally apply. Includes the ESRB equivalence table. Mandatory system in force since 27 May 2021 under DOF lineamientos. Applies mainly to physical distribution, and digital storefronts largely still show ESRB. Enforcement by RTC is light, a labeling system more than a review board</t>
+          <t>Government data series on Mexican gaming audiences that synthesizes The CIU, Newzoo, Endeavor and its own audience framework, the closest thing to official gaming statistics.</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
@@ -12699,7 +12691,7 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
-          <t>https://es.wikipedia.org/wiki/Sistema_Mexicano_de_Equivalencias_de_Clasificaci%C3%B3n_de_Contenidos_de_Videojuegos</t>
+          <t>https://somosaudiencias.ift.org.mx/archivos/1_Videojuegos_1S2025.pdf</t>
         </is>
       </c>
       <c r="K190" s="3" t="inlineStr"/>
@@ -12714,12 +12706,12 @@
     <row r="191">
       <c r="A191" s="3" t="inlineStr">
         <is>
-          <t>ift-estado-del-gaming-en-mexico</t>
+          <t>gdmex-asociacion-mexicana-de-entretenimiento-interactivo</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
         <is>
-          <t>IFT: "Estado del Gaming en México" (Somos Audiencias)</t>
+          <t>GDMEX: Asociación Mexicana de Entretenimiento Interactivo VideojuegosMX (Game Devs México)</t>
         </is>
       </c>
       <c r="C191" s="3" t="inlineStr">
@@ -12729,17 +12721,17 @@
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>Report or document</t>
+          <t>Organisation</t>
         </is>
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>Report or data series</t>
+          <t>Industry association</t>
         </is>
       </c>
       <c r="F191" s="3" t="inlineStr">
         <is>
-          <t>Government data series on Mexican gaming audiences that synthesizes The CIU, Newzoo, Endeavor and its own audience framework, the closest thing to official gaming statistics.</t>
+          <t>The new official voice of Mexican game development: already delivered export tax benefits with the Economy Ministry (Nov 2025) and speaks for the sector on fiscal policy. The address for supply-side questions. Constituted May 2025 at the Secretaría de Economía. Very young organization. Published output is still thin and its website is partly placeholder, so track via trade-press coverage rather than the site itself</t>
         </is>
       </c>
       <c r="G191" s="3" t="inlineStr">
@@ -12749,7 +12741,7 @@
       </c>
       <c r="H191" s="3" t="inlineStr">
         <is>
-          <t>Spanish</t>
+          <t>English; Spanish</t>
         </is>
       </c>
       <c r="I191" s="3" t="inlineStr">
@@ -12759,7 +12751,7 @@
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
-          <t>https://somosaudiencias.ift.org.mx/archivos/1_Videojuegos_1S2025.pdf</t>
+          <t>https://mexicogames.org/</t>
         </is>
       </c>
       <c r="K191" s="3" t="inlineStr"/>
@@ -12774,12 +12766,12 @@
     <row r="192">
       <c r="A192" s="3" t="inlineStr">
         <is>
-          <t>gdmex-asociacion-mexicana-de-entretenimiento-interactivo</t>
+          <t>kansspelautoriteit-loot-box-enforcement-and-case-record</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>GDMEX: Asociación Mexicana de Entretenimiento Interactivo VideojuegosMX (Game Devs México)</t>
+          <t>Kansspelautoriteit (KSA): loot-box enforcement and case record</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
@@ -12794,22 +12786,22 @@
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>Industry association</t>
+          <t>Regulator</t>
         </is>
       </c>
       <c r="F192" s="3" t="inlineStr">
         <is>
-          <t>The new official voice of Mexican game development: already delivered export tax benefits with the Economy Ministry (Nov 2025) and speaks for the sector on fiscal policy. The address for supply-side questions. Constituted May 2025 at the Secretaría de Economía. Very young organization. Published output is still thin and its website is partly placeholder, so track via trade-press coverage rather than the site itself</t>
+          <t>Created the single most important legal record in loot-box research: KSA's 2018 interpretation, the €250K/week penalty on EA over FIFA packs, the 2020 district-court win, and the 2022 Council of State reversal that found packs can't be assessed as a separate game. Any comparative loot-box analysis runs through this case. The final ruling means loot boxes are not currently prohibited gambling in NL, which is widely misreported both ways. English coverage is partial.</t>
         </is>
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>MX</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="H192" s="3" t="inlineStr">
         <is>
-          <t>English; Spanish</t>
+          <t>Dutch; English</t>
         </is>
       </c>
       <c r="I192" s="3" t="inlineStr">
@@ -12819,7 +12811,7 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
-          <t>https://mexicogames.org/</t>
+          <t>https://kansspelautoriteit.nl/</t>
         </is>
       </c>
       <c r="K192" s="3" t="inlineStr"/>
@@ -12834,12 +12826,12 @@
     <row r="193">
       <c r="A193" s="3" t="inlineStr">
         <is>
-          <t>kansspelautoriteit-loot-box-enforcement-and-case-record</t>
+          <t>dutch-games-association</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
         <is>
-          <t>Kansspelautoriteit (KSA): loot-box enforcement and case record</t>
+          <t>Dutch Games Association (DGA)</t>
         </is>
       </c>
       <c r="C193" s="3" t="inlineStr">
@@ -12854,12 +12846,12 @@
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>Regulator</t>
+          <t>Industry association</t>
         </is>
       </c>
       <c r="F193" s="3" t="inlineStr">
         <is>
-          <t>Created the single most important legal record in loot-box research: KSA's 2018 interpretation, the €250K/week penalty on EA over FIFA packs, the 2020 district-court win, and the 2022 Council of State reversal that found packs can't be assessed as a separate game. Any comparative loot-box analysis runs through this case. The final ruling means loot boxes are not currently prohibited gambling in NL, which is widely misreported both ways. English coverage is partial.</t>
+          <t>The industry's voice and its main data publisher. Also runs mentor-network and industry-day initiatives. Custodian of the Games Monitor. Trade advocacy.</t>
         </is>
       </c>
       <c r="G193" s="3" t="inlineStr">
@@ -12879,7 +12871,7 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
-          <t>https://kansspelautoriteit.nl/</t>
+          <t>https://dutchgamesassociation.nl/</t>
         </is>
       </c>
       <c r="K193" s="3" t="inlineStr"/>
@@ -12894,12 +12886,12 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t>dutch-games-association</t>
+          <t>center-for-game-research</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>Dutch Games Association (DGA)</t>
+          <t>Center for Game Research (gameresearch.nl)</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
@@ -12914,12 +12906,12 @@
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>Industry association</t>
+          <t>Research institute</t>
         </is>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>The industry's voice and its main data publisher. Also runs mentor-network and industry-day initiatives. Custodian of the Games Monitor. Trade advocacy.</t>
+          <t>Reports on new studies, monitors and academic events. Useful entry point for peer-reviewed work on a market where industry data is thin. Utrecht-affiliated. Aggregator/network site, not a primary data producer.</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
@@ -12939,7 +12931,7 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
-          <t>https://dutchgamesassociation.nl/</t>
+          <t>https://gameresearch.nl/</t>
         </is>
       </c>
       <c r="K194" s="3" t="inlineStr"/>
@@ -12954,12 +12946,12 @@
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
         <is>
-          <t>center-for-game-research</t>
+          <t>dataspelsbranschen</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
         <is>
-          <t>Center for Game Research (gameresearch.nl)</t>
+          <t>Dataspelsbranschen (Swedish Games Industry)</t>
         </is>
       </c>
       <c r="C195" s="3" t="inlineStr">
@@ -12974,22 +12966,22 @@
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>Research institute</t>
+          <t>Industry association</t>
         </is>
       </c>
       <c r="F195" s="3" t="inlineStr">
         <is>
-          <t>Reports on new studies, monitors and academic events. Useful entry point for peer-reviewed work on a market where industry data is thin. Utrecht-affiliated. Aggregator/network site, not a primary data producer.</t>
+          <t>Sweden's industry voice and data publisher. Also produces sustainability/climate research on game development and policy analysis on EU regulation. Covers both developers (Spelplan-ASGD) and publishers and distributors (ANGI).</t>
         </is>
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>Nordics</t>
         </is>
       </c>
       <c r="H195" s="3" t="inlineStr">
         <is>
-          <t>Dutch; English</t>
+          <t>English; Swedish</t>
         </is>
       </c>
       <c r="I195" s="3" t="inlineStr">
@@ -12999,7 +12991,7 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
-          <t>https://gameresearch.nl/</t>
+          <t>https://www.dataspelsbranschen.se/</t>
         </is>
       </c>
       <c r="K195" s="3" t="inlineStr"/>
@@ -13014,12 +13006,12 @@
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
         <is>
-          <t>dataspelsbranschen</t>
+          <t>neogames-finland</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>Dataspelsbranschen (Swedish Games Industry)</t>
+          <t>Neogames Finland</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
@@ -13039,7 +13031,7 @@
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
-          <t>Sweden's industry voice and data publisher. Also produces sustainability/climate research on game development and policy analysis on EU regulation. Covers both developers (Spelplan-ASGD) and publishers and distributors (ANGI).</t>
+          <t>The most institutionally embedded games body in the bloc: publishes the national report, runs a weekly Finnish industry news bulletin, and represents Finland in EGDF and the Nordic Game Institute. The weekly roundup is a useful research feed. One of Finland's nine official Information Centres for the Arts, funded by the Ministry of Education and Culture. State-funded advocacy/coordination body.</t>
         </is>
       </c>
       <c r="G196" s="3" t="inlineStr">
@@ -13049,7 +13041,7 @@
       </c>
       <c r="H196" s="3" t="inlineStr">
         <is>
-          <t>English; Swedish</t>
+          <t>English; Finnish</t>
         </is>
       </c>
       <c r="I196" s="3" t="inlineStr">
@@ -13059,7 +13051,7 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
-          <t>https://www.dataspelsbranschen.se/</t>
+          <t>https://neogames.fi/</t>
         </is>
       </c>
       <c r="K196" s="3" t="inlineStr"/>
@@ -13074,12 +13066,12 @@
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
         <is>
-          <t>neogames-finland</t>
+          <t>nordic-game-institute-nordic-game-conference</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
         <is>
-          <t>Neogames Finland</t>
+          <t>Nordic Game Institute (NGI) / Nordic Game Conference</t>
         </is>
       </c>
       <c r="C197" s="3" t="inlineStr">
@@ -13099,7 +13091,7 @@
       </c>
       <c r="F197" s="3" t="inlineStr">
         <is>
-          <t>The most institutionally embedded games body in the bloc: publishes the national report, runs a weekly Finnish industry news bulletin, and represents Finland in EGDF and the Nordic Game Institute. The weekly roundup is a useful research feed. One of Finland's nine official Information Centres for the Arts, funded by the Ministry of Education and Culture. State-funded advocacy/coordination body.</t>
+          <t>The bloc's connective tissue, where the five national bodies coordinate and the venue where Nordic industry conditions get discussed publicly each year. Nordic Game Conference runs in Malmö. Institute output is thin publicly. Most value is in conference programming and the networks behind it</t>
         </is>
       </c>
       <c r="G197" s="3" t="inlineStr">
@@ -13109,17 +13101,17 @@
       </c>
       <c r="H197" s="3" t="inlineStr">
         <is>
-          <t>English; Finnish</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I197" s="3" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
-          <t>https://neogames.fi/</t>
+          <t>https://nordicgame.com/</t>
         </is>
       </c>
       <c r="K197" s="3" t="inlineStr"/>
@@ -13134,12 +13126,12 @@
     <row r="198">
       <c r="A198" s="3" t="inlineStr">
         <is>
-          <t>nordic-game-institute-nordic-game-conference</t>
+          <t>nimbi-gamelab</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>Nordic Game Institute (NGI) / Nordic Game Conference</t>
+          <t>NIMBI GameLab</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
@@ -13154,12 +13146,12 @@
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>Industry association</t>
+          <t>Government agency</t>
         </is>
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>The bloc's connective tissue, where the five national bodies coordinate and the venue where Nordic industry conditions get discussed publicly each year. Nordic Game Conference runs in Malmö. Institute output is thin publicly. Most value is in conference programming and the networks behind it</t>
+          <t>A state agency for game development and game culture, funding both artistic and commercial games plus export promotion and talent development. Established Aug 2024 under the Ministry of Culture with around 8 staff and a DKK 10.4m budget for 2026, described as the first dedicated national games agency of its kind in Europe. English coverage is partial. Focused on Denmark.</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
@@ -13169,17 +13161,17 @@
       </c>
       <c r="H198" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Danish; English</t>
         </is>
       </c>
       <c r="I198" s="3" t="inlineStr">
         <is>
-          <t>Freemium</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>https://nordicgame.com/</t>
+          <t>https://www.nimbi.dk/</t>
         </is>
       </c>
       <c r="K198" s="3" t="inlineStr"/>
@@ -13194,12 +13186,12 @@
     <row r="199">
       <c r="A199" s="3" t="inlineStr">
         <is>
-          <t>nimbi-gamelab</t>
+          <t>games-denmark</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
         <is>
-          <t>NIMBI GameLab</t>
+          <t>Games Denmark</t>
         </is>
       </c>
       <c r="C199" s="3" t="inlineStr">
@@ -13214,12 +13206,12 @@
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>Government agency</t>
+          <t>Industry association</t>
         </is>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>A state agency for game development and game culture, funding both artistic and commercial games plus export promotion and talent development. Established Aug 2024 under the Ministry of Culture with around 8 staff and a DKK 10.4m budget for 2026, described as the first dedicated national games agency of its kind in Europe. English coverage is partial. Focused on Denmark.</t>
+          <t>The Danish industry's newly organised voice. Established 2024 in partnership with Dansk Erhverv, the Danish Chamber of Commerce.</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
@@ -13229,7 +13221,7 @@
       </c>
       <c r="H199" s="3" t="inlineStr">
         <is>
-          <t>Danish; English</t>
+          <t>Danish</t>
         </is>
       </c>
       <c r="I199" s="3" t="inlineStr">
@@ -13239,7 +13231,7 @@
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
-          <t>https://www.nimbi.dk/</t>
+          <t>https://gamesdenmark.dk/</t>
         </is>
       </c>
       <c r="K199" s="3" t="inlineStr"/>
@@ -13254,12 +13246,12 @@
     <row r="200">
       <c r="A200" s="3" t="inlineStr">
         <is>
-          <t>games-denmark</t>
+          <t>virke-produsentforeningen-games-section</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>Games Denmark</t>
+          <t>Virke Produsentforeningen: games section (+ Spillprisen)</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
@@ -13279,7 +13271,7 @@
       </c>
       <c r="F200" s="3" t="inlineStr">
         <is>
-          <t>The Danish industry's newly organised voice. Established 2024 in partnership with Dansk Erhverv, the Danish Chamber of Commerce.</t>
+          <t>The organised centre of the Norwegian professional games industry. Spillprisen's annual entry list and winners are the clearest public index of what Norway actually shipped each year. Virke is Norway's main commerce and services federation. Spillprisen is run with Norsk filminstitutt and Nordic Game. Games are one section of a broader producers' association, so games-specific published data is thin. Norwegian-language.</t>
         </is>
       </c>
       <c r="G200" s="3" t="inlineStr">
@@ -13289,7 +13281,7 @@
       </c>
       <c r="H200" s="3" t="inlineStr">
         <is>
-          <t>Danish</t>
+          <t>Norwegian</t>
         </is>
       </c>
       <c r="I200" s="3" t="inlineStr">
@@ -13299,7 +13291,7 @@
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
-          <t>https://gamesdenmark.dk/</t>
+          <t>https://www.virke.no/pavirkningsarbeid/bransjer/produsentforeningen/spillprisen/</t>
         </is>
       </c>
       <c r="K200" s="3" t="inlineStr"/>
@@ -13314,12 +13306,12 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t>virke-produsentforeningen-games-section</t>
+          <t>noneda</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
         <is>
-          <t>Virke Produsentforeningen: games section (+ Spillprisen)</t>
+          <t>Noneda (Norwegian Network for Video Game Companies)</t>
         </is>
       </c>
       <c r="C201" s="3" t="inlineStr">
@@ -13339,7 +13331,7 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>The organised centre of the Norwegian professional games industry. Spillprisen's annual entry list and winners are the clearest public index of what Norway actually shipped each year. Virke is Norway's main commerce and services federation. Spillprisen is run with Norsk filminstitutt and Nordic Game. Games are one section of a broader producers' association, so games-specific published data is thin. Norwegian-language.</t>
+          <t>The working centre of the Norwegian games industry: Konsoll and Konsoll Connect (pitching, investors, publishers), plus skills programmes and investor-facing overviews of the national scene. Also the loudest public critic of Norwegian games policy: its statements on successive national budgets failing to fund industry-building are the clearest record of the state-support gap Norway has versus Sweden, Finland and Denmark. Established 2020 as Video Game Center. Konsoll is Norway's largest game development conference, held in Bergen each autumn. Membership body (NOK 490/yr) with limited published data. Its policy statements are advocacy.</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
@@ -13349,7 +13341,7 @@
       </c>
       <c r="H201" s="3" t="inlineStr">
         <is>
-          <t>Norwegian</t>
+          <t>English; Norwegian</t>
         </is>
       </c>
       <c r="I201" s="3" t="inlineStr">
@@ -13359,7 +13351,7 @@
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
-          <t>https://www.virke.no/pavirkningsarbeid/bransjer/produsentforeningen/spillprisen/</t>
+          <t>https://noneda.no/en/</t>
         </is>
       </c>
       <c r="K201" s="3" t="inlineStr"/>
@@ -13374,12 +13366,12 @@
     <row r="202">
       <c r="A202" s="3" t="inlineStr">
         <is>
-          <t>noneda</t>
+          <t>parp-polska-agencja-rozwoju-przedsiebiorczosci</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>Noneda (Norwegian Network for Video Game Companies)</t>
+          <t>PARP: Polska Agencja Rozwoju Przedsiębiorczości (games sector programme)</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
@@ -13394,22 +13386,22 @@
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>Industry association</t>
+          <t>Government agency</t>
         </is>
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>The working centre of the Norwegian games industry: Konsoll and Konsoll Connect (pitching, investors, publishers), plus skills programmes and investor-facing overviews of the national scene. Also the loudest public critic of Norwegian games policy: its statements on successive national budgets failing to fund industry-building are the clearest record of the state-support gap Norway has versus Sweden, Finland and Denmark. Established 2020 as Video Game Center. Konsoll is Norway's largest game development conference, held in Bergen each autumn. Membership body (NOK 490/yr) with limited published data. Its policy statements are advocacy.</t>
+          <t>The government's institutional home for games as an export industry, with EU structural funding attached. PARP offers the clearest view of how Poland positions gamedev in industrial policy. Its export promotion programme publishes the national games report. An economic-development agency, not a games regulator or culture body.</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>Nordics</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="H202" s="3" t="inlineStr">
         <is>
-          <t>English; Norwegian</t>
+          <t>English; Polish</t>
         </is>
       </c>
       <c r="I202" s="3" t="inlineStr">
@@ -13419,7 +13411,7 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
-          <t>https://noneda.no/en/</t>
+          <t>https://www.parp.gov.pl/</t>
         </is>
       </c>
       <c r="K202" s="3" t="inlineStr"/>
@@ -13434,12 +13426,12 @@
     <row r="203">
       <c r="A203" s="3" t="inlineStr">
         <is>
-          <t>parp-polska-agencja-rozwoju-przedsiebiorczosci</t>
+          <t>fundacja-indie-games-poland</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
         <is>
-          <t>PARP: Polska Agencja Rozwoju Przedsiębiorczości (games sector programme)</t>
+          <t>Fundacja Indie Games Poland</t>
         </is>
       </c>
       <c r="C203" s="3" t="inlineStr">
@@ -13454,12 +13446,12 @@
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>Government agency</t>
+          <t>Industry association</t>
         </is>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
-          <t>The government's institutional home for games as an export industry, with EU structural funding attached. PARP offers the clearest view of how Poland positions gamedev in industrial policy. Its export promotion programme publishes the national games report. An economic-development agency, not a games regulator or culture body.</t>
+          <t>The indie-side voice for the Polish market. Its people sit on the national sectoral council that maps industry workforce needs, and contribute to the PARP report. Co-organiser of Game Industry Conference. Advocacy body for a segment (indies), not the whole industry. Limited standalone data output</t>
         </is>
       </c>
       <c r="G203" s="3" t="inlineStr">
@@ -13479,7 +13471,7 @@
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
-          <t>https://www.parp.gov.pl/</t>
+          <t>https://igp.org.pl/en/</t>
         </is>
       </c>
       <c r="K203" s="3" t="inlineStr"/>
@@ -13494,12 +13486,12 @@
     <row r="204">
       <c r="A204" s="3" t="inlineStr">
         <is>
-          <t>fundacja-indie-games-poland</t>
+          <t>krakowski-park-technologiczny-games-sector</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>Fundacja Indie Games Poland</t>
+          <t>Krakowski Park Technologiczny (KPT): games sector</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
@@ -13514,12 +13506,12 @@
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>Industry association</t>
+          <t>Government agency</t>
         </is>
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>The indie-side voice for the Polish market. Its people sit on the national sectoral council that maps industry workforce needs, and contribute to the PARP report. Co-organiser of Game Industry Conference. Advocacy body for a segment (indies), not the whole industry. Limited standalone data output</t>
+          <t>The institutional engine of Polish games research and industry gathering. Digital Dragons and Digital Dragons Awards are where the sector's year gets assessed publicly. A technology park and games cluster. Publishes the national research series. Digital Dragons, Europe's major B2B games conference, runs in Kraków. Regional development body with EU/ministry funding, so its research is partly promotional infrastructure</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
@@ -13539,7 +13531,7 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
-          <t>https://igp.org.pl/en/</t>
+          <t>https://www.kpt.krakow.pl/</t>
         </is>
       </c>
       <c r="K204" s="3" t="inlineStr"/>
@@ -13554,12 +13546,12 @@
     <row r="205">
       <c r="A205" s="3" t="inlineStr">
         <is>
-          <t>krakowski-park-technologiczny-games-sector</t>
+          <t>polskie-towarzystwo-badania-gier</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
         <is>
-          <t>Krakowski Park Technologiczny (KPT): games sector</t>
+          <t>Polskie Towarzystwo Badania Gier (PTBG, Games Research Association of Poland)</t>
         </is>
       </c>
       <c r="C205" s="3" t="inlineStr">
@@ -13574,12 +13566,12 @@
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>Government agency</t>
+          <t>Learned society</t>
         </is>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>The institutional engine of Polish games research and industry gathering. Digital Dragons and Digital Dragons Awards are where the sector's year gets assessed publicly. A technology park and games cluster. Publishes the national research series. Digital Dragons, Europe's major B2B games conference, runs in Kraków. Regional development body with EU/ministry funding, so its research is partly promotional infrastructure</t>
+          <t>Poland's games research society, covering digital and analogue games, publishing the journal Homo Ludens and running an annual conference.</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
@@ -13599,7 +13591,7 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t>https://www.kpt.krakow.pl/</t>
+          <t>https://www.ptbg.org.pl/</t>
         </is>
       </c>
       <c r="K205" s="3" t="inlineStr"/>
@@ -13614,12 +13606,12 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t>polskie-towarzystwo-badania-gier</t>
+          <t>igrs-indonesia-game-rating-system</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>Polskie Towarzystwo Badania Gier (PTBG, Games Research Association of Poland)</t>
+          <t>IGRS: Indonesia Game Rating System (Komdigi; Perpres 19/2024 + Permenkominfo 2/2024)</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
@@ -13634,22 +13626,22 @@
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>Learned society</t>
+          <t>Rating body</t>
         </is>
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
-          <t>Poland's games research society, covering digital and analogue games, publishing the journal Homo Ludens and running an annual conference.</t>
+          <t>Every game distributed in the country requires official IGRS classification, with the same regulation doubling as industry-promotion policy (Perpres 19/2024). Also the anchor for child-protection rules under PP Tunas. Rating tiers are 3+/7+/13+/15+/18+ plus RC, with full enforcement from 2026. English coverage is partial.</t>
         </is>
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="H206" s="3" t="inlineStr">
         <is>
-          <t>English; Polish</t>
+          <t>Bahasa Indonesia; English</t>
         </is>
       </c>
       <c r="I206" s="3" t="inlineStr">
@@ -13659,7 +13651,7 @@
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
-          <t>https://www.ptbg.org.pl/</t>
+          <t>https://igrs.id/</t>
         </is>
       </c>
       <c r="K206" s="3" t="inlineStr"/>
@@ -13674,12 +13666,12 @@
     <row r="207">
       <c r="A207" s="3" t="inlineStr">
         <is>
-          <t>igrs-indonesia-game-rating-system</t>
+          <t>agi-asosiasi-game-indonesia</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
         <is>
-          <t>IGRS: Indonesia Game Rating System (Komdigi; Perpres 19/2024 + Permenkominfo 2/2024)</t>
+          <t>AGI: Asosiasi Game Indonesia</t>
         </is>
       </c>
       <c r="C207" s="3" t="inlineStr">
@@ -13694,12 +13686,12 @@
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>Rating body</t>
+          <t>Industry association</t>
         </is>
       </c>
       <c r="F207" s="3" t="inlineStr">
         <is>
-          <t>Every game distributed in the country requires official IGRS classification, with the same regulation doubling as industry-promotion policy (Perpres 19/2024). Also the anchor for child-protection rules under PP Tunas. Rating tiers are 3+/7+/13+/15+/18+ plus RC, with full enforcement from 2026. English coverage is partial.</t>
+          <t>The developer-side voice in Indonesian policy, the counterpart to Komdigi in IGRS consultations and the organizer presence behind IGDX, the national industry conference. Covers development and publishing. Founded 2013. Trade-body advocacy. Publishes positions and events rather than data series</t>
         </is>
       </c>
       <c r="G207" s="3" t="inlineStr">
@@ -13719,7 +13711,7 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
-          <t>https://igrs.id/</t>
+          <t>https://www.agi.or.id/</t>
         </is>
       </c>
       <c r="K207" s="3" t="inlineStr"/>
@@ -13734,12 +13726,12 @@
     <row r="208">
       <c r="A208" s="3" t="inlineStr">
         <is>
-          <t>agi-asosiasi-game-indonesia</t>
+          <t>pbesi-pengurus-besar-esports-indonesia</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>AGI: Asosiasi Game Indonesia</t>
+          <t>PBESI: Pengurus Besar Esports Indonesia (+ Garudaku platform)</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
@@ -13754,12 +13746,12 @@
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>Industry association</t>
+          <t>Esports body</t>
         </is>
       </c>
       <c r="F208" s="3" t="inlineStr">
         <is>
-          <t>The developer-side voice in Indonesian policy, the counterpart to Komdigi in IGRS consultations and the organizer presence behind IGDX, the national industry conference. Covers development and publishing. Founded 2013. Trade-body advocacy. Publishes positions and events rather than data series</t>
+          <t>Who governs Indonesian esports officially: provincial structures in all 34 provinces, national/student leagues, and athlete registration through Garudaku, unusually institutionalized for the region. KONI-recognized since 2020 and chaired by Budi Gunawan. Deeply state-embedded. Read output as government sports policy, not independent information.</t>
         </is>
       </c>
       <c r="G208" s="3" t="inlineStr">
@@ -13779,7 +13771,7 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
-          <t>https://www.agi.or.id/</t>
+          <t>https://www.instagram.com/pbesi_official/?hl=en</t>
         </is>
       </c>
       <c r="K208" s="3" t="inlineStr"/>
@@ -13794,12 +13786,12 @@
     <row r="209">
       <c r="A209" s="3" t="inlineStr">
         <is>
-          <t>pbesi-pengurus-besar-esports-indonesia</t>
+          <t>vietnam-decree-147-2024-n-cp</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
         <is>
-          <t>PBESI: Pengurus Besar Esports Indonesia (+ Garudaku platform)</t>
+          <t>Vietnam Decree 147/2024/NĐ-CP (online games &amp; internet services)</t>
         </is>
       </c>
       <c r="C209" s="3" t="inlineStr">
@@ -13809,17 +13801,17 @@
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>Organisation</t>
+          <t>Report or document</t>
         </is>
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>Esports body</t>
+          <t>Regulation or law</t>
         </is>
       </c>
       <c r="F209" s="3" t="inlineStr">
         <is>
-          <t>Who governs Indonesian esports officially: provincial structures in all 34 provinces, national/student leagues, and athlete registration through Garudaku, unusually institutionalized for the region. KONI-recognized since 2020 and chaired by Budi Gunawan. Deeply state-embedded. Read output as government sports policy, not independent information.</t>
+          <t>The single most consequential regulatory fact in SEA gaming: it forced Riot and Blizzard out of Vietnam while Garena and VNG consolidated, and it bans casino-style games from licensing entirely. In force 25 Dec 2024 with G1 to G4 licensing, a local-entity requirement for foreign publishers, under-18 playtime limits of 60 minutes per session and 180 per day, and app-store takedown powers. Enforcement against cross-border stores is ongoing and uneven Some English analyses.</t>
         </is>
       </c>
       <c r="G209" s="3" t="inlineStr">
@@ -13829,7 +13821,7 @@
       </c>
       <c r="H209" s="3" t="inlineStr">
         <is>
-          <t>Bahasa Indonesia; English</t>
+          <t>English; Vietnamese</t>
         </is>
       </c>
       <c r="I209" s="3" t="inlineStr">
@@ -13839,7 +13831,7 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pbesi_official/?hl=en</t>
+          <t>https://www.vietnam-briefing.com/news/vietnams-new-internet-regulation-decree-147-2024.html/</t>
         </is>
       </c>
       <c r="K209" s="3" t="inlineStr"/>
@@ -13854,12 +13846,12 @@
     <row r="210">
       <c r="A210" s="3" t="inlineStr">
         <is>
-          <t>vietnam-decree-147-2024-n-cp</t>
+          <t>depa-digital-economy-promotion-agency</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>Vietnam Decree 147/2024/NĐ-CP (online games &amp; internet services)</t>
+          <t>DEPA: Digital Economy Promotion Agency (+ Game Industry Promotion Act)</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
@@ -13869,17 +13861,17 @@
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>Report or document</t>
+          <t>Organisation</t>
         </is>
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>Regulation or law</t>
+          <t>Government agency</t>
         </is>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>The single most consequential regulatory fact in SEA gaming: it forced Riot and Blizzard out of Vietnam while Garena and VNG consolidated, and it bans casino-style games from licensing entirely. In force 25 Dec 2024 with G1 to G4 licensing, a local-entity requirement for foreign publishers, under-18 playtime limits of 60 minutes per session and 180 per day, and app-store takedown powers. Enforcement against cross-border stores is ongoing and uneven Some English analyses.</t>
+          <t>The center of Thai games policy: the in-progress Game Industry Promotion Act (registration regime and explicit targeting of "hidden gambling" mechanics, which would be ASEAN's first dedicated game law), plus official ecosystem sizing and state-backed event data Hosts gamescom asia x Thailand Game Show. Some English releases.</t>
         </is>
       </c>
       <c r="G210" s="3" t="inlineStr">
@@ -13889,7 +13881,7 @@
       </c>
       <c r="H210" s="3" t="inlineStr">
         <is>
-          <t>English; Vietnamese</t>
+          <t>English; Thai</t>
         </is>
       </c>
       <c r="I210" s="3" t="inlineStr">
@@ -13899,7 +13891,7 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>https://www.vietnam-briefing.com/news/vietnams-new-internet-regulation-decree-147-2024.html/</t>
+          <t>https://www.depa.or.th/</t>
         </is>
       </c>
       <c r="K210" s="3" t="inlineStr"/>
@@ -13914,12 +13906,12 @@
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t>depa-digital-economy-promotion-agency</t>
+          <t>mdec-malaysia-digital-economy-corporation</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
         <is>
-          <t>DEPA: Digital Economy Promotion Agency (+ Game Industry Promotion Act)</t>
+          <t>MDEC: Malaysia Digital Economy Corporation (LEVEL UP KL + DICE Roadmap)</t>
         </is>
       </c>
       <c r="C211" s="3" t="inlineStr">
@@ -13939,7 +13931,7 @@
       </c>
       <c r="F211" s="3" t="inlineStr">
         <is>
-          <t>The center of Thai games policy: the in-progress Game Industry Promotion Act (registration regime and explicit targeting of "hidden gambling" mechanics, which would be ASEAN's first dedicated game law), plus official ecosystem sizing and state-backed event data Hosts gamescom asia x Thailand Game Show. Some English releases.</t>
+          <t>Export figures (RM150M in opportunities from LEVEL UP KL 2025), funding programs (Digital Games Testbed, RM3.5M/yr), SEA Game Awards, and Malaysia's studio ecosystem strategy. Sits under the Ministry of Digital. Runs LEVEL UP KL, SEA's premier game development conference, 12th edition 2026, and the Digital Content Ecosystem (DICE) Roadmap 2026 to 2030. Advocacy numbers ("export opportunities" ≠ closed deals).</t>
         </is>
       </c>
       <c r="G211" s="3" t="inlineStr">
@@ -13949,7 +13941,7 @@
       </c>
       <c r="H211" s="3" t="inlineStr">
         <is>
-          <t>English; Thai</t>
+          <t>English; Malay</t>
         </is>
       </c>
       <c r="I211" s="3" t="inlineStr">
@@ -13959,7 +13951,7 @@
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
-          <t>https://www.depa.or.th/</t>
+          <t>https://www.mdec.my/levelupkl</t>
         </is>
       </c>
       <c r="K211" s="3" t="inlineStr"/>
@@ -13974,12 +13966,12 @@
     <row r="212">
       <c r="A212" s="3" t="inlineStr">
         <is>
-          <t>mdec-malaysia-digital-economy-corporation</t>
+          <t>toged-turkiye-oyun-gelistiricileri-dernegi</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>MDEC: Malaysia Digital Economy Corporation (LEVEL UP KL + DICE Roadmap)</t>
+          <t>TOGED: Türkiye Oyun Geliştiricileri Derneği</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
@@ -13994,22 +13986,22 @@
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>Government agency</t>
+          <t>Industry association</t>
         </is>
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>Export figures (RM150M in opportunities from LEVEL UP KL 2025), funding programs (Digital Games Testbed, RM3.5M/yr), SEA Game Awards, and Malaysia's studio ecosystem strategy. Sits under the Ministry of Digital. Runs LEVEL UP KL, SEA's premier game development conference, 12th edition 2026, and the Digital Content Ecosystem (DICE) Roadmap 2026 to 2030. Advocacy numbers ("export opportunities" ≠ closed deals).</t>
+          <t>The organized voice of Turkey's dev sector: trade delegations to GDC, legal-compliance briefings, education pipelines. The address for supply-side policy questions. Trade-body advocacy. Publishes positions and events rather than data series</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="H212" s="3" t="inlineStr">
         <is>
-          <t>English; Malay</t>
+          <t>Turkish</t>
         </is>
       </c>
       <c r="I212" s="3" t="inlineStr">
@@ -14019,7 +14011,7 @@
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
-          <t>https://www.mdec.my/levelupkl</t>
+          <t>https://toged.org/</t>
         </is>
       </c>
       <c r="K212" s="3" t="inlineStr"/>
@@ -14034,12 +14026,12 @@
     <row r="213">
       <c r="A213" s="3" t="inlineStr">
         <is>
-          <t>toged-turkiye-oyun-gelistiricileri-dernegi</t>
+          <t>tesfed-turkiye-espor-federasyonu</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
         <is>
-          <t>TOGED: Türkiye Oyun Geliştiricileri Derneği</t>
+          <t>TESFED: Türkiye Espor Federasyonu</t>
         </is>
       </c>
       <c r="C213" s="3" t="inlineStr">
@@ -14054,12 +14046,12 @@
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>Industry association</t>
+          <t>Esports body</t>
         </is>
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
-          <t>The organized voice of Turkey's dev sector: trade delegations to GDC, legal-compliance briefings, education pipelines. The address for supply-side policy questions. Trade-body advocacy. Publishes positions and events rather than data series</t>
+          <t>Recognized branches, licensed athletes, national teams and leagues. Turkey has one of the older state-embedded esports federations outside East Asia. Established 2018 under the Ministry of Youth and Sports as successor to the 2011 Digital Games Federation. Independent esports business analysis lives elsewhere</t>
         </is>
       </c>
       <c r="G213" s="3" t="inlineStr">
@@ -14079,7 +14071,7 @@
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
-          <t>https://toged.org/</t>
+          <t>https://tesfed.org.tr/</t>
         </is>
       </c>
       <c r="K213" s="3" t="inlineStr"/>
@@ -14094,12 +14086,12 @@
     <row r="214">
       <c r="A214" s="3" t="inlineStr">
         <is>
-          <t>tesfed-turkiye-espor-federasyonu</t>
+          <t>digital-game-rating-query-site</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>TESFED: Türkiye Espor Federasyonu</t>
+          <t>數位娛樂軟體分級查詢網 (Digital Game Rating Query Site): 數位發展部數位產業署</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
@@ -14114,22 +14106,22 @@
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>Esports body</t>
+          <t>Rating body</t>
         </is>
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>Recognized branches, licensed athletes, national teams and leagues. Turkey has one of the older state-embedded esports federations outside East Asia. Established 2018 under the Ministry of Youth and Sports as successor to the 2011 Digital Games Federation. Independent esports business analysis lives elsewhere</t>
+          <t>Taiwan's mandatory five-tier rating system (普 / 護 / 輔12 / 輔15 / 限) with a public lookup database, a Tier-A record of what was rated and when. Also now covers location-based VR/體感 venues, which must register site, equipment and content. Run by the Ministry of Digital Affairs (MODA), Administration for Digital Industries. The database interface is crazy dated.</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="H214" s="3" t="inlineStr">
         <is>
-          <t>Turkish</t>
+          <t>Traditional Chinese</t>
         </is>
       </c>
       <c r="I214" s="3" t="inlineStr">
@@ -14139,7 +14131,7 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
-          <t>https://tesfed.org.tr/</t>
+          <t>https://www.gamerating.org.tw/</t>
         </is>
       </c>
       <c r="K214" s="3" t="inlineStr"/>
@@ -14154,12 +14146,12 @@
     <row r="215">
       <c r="A215" s="3" t="inlineStr">
         <is>
-          <t>digital-game-rating-query-site</t>
+          <t>game-software-rating-management-regulations</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
         <is>
-          <t>數位娛樂軟體分級查詢網 (Digital Game Rating Query Site): 數位發展部數位產業署</t>
+          <t>遊戲軟體分級管理辦法 (Game Software Rating Management Regulations)</t>
         </is>
       </c>
       <c r="C215" s="3" t="inlineStr">
@@ -14169,17 +14161,17 @@
       </c>
       <c r="D215" s="3" t="inlineStr">
         <is>
-          <t>Organisation</t>
+          <t>Report or document</t>
         </is>
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>Rating body</t>
+          <t>Regulation or law</t>
         </is>
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>Taiwan's mandatory five-tier rating system (普 / 護 / 輔12 / 輔15 / 限) with a public lookup database, a Tier-A record of what was rated and when. Also now covers location-based VR/體感 venues, which must register site, equipment and content. Run by the Ministry of Digital Affairs (MODA), Administration for Digital Industries. The database interface is crazy dated.</t>
+          <t>Mandatory Chinese-language rating labels with specified minimum pixel/centimetre sizes, compulsory warnings about gambling use and paid-item spending, disclosure of rating level in advertising, and takedown powers over unrated foreign titles accessed online. Issued 2006 as 電腦軟體分級辦法, renamed and rewritten 2012, amended through 2019. Authority transferred from MOEA to MODA in August 2022.</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
@@ -14199,7 +14191,7 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
-          <t>https://www.gamerating.org.tw/</t>
+          <t>https://law.moda.gov.tw/LawContent.aspx?id=FL039733</t>
         </is>
       </c>
       <c r="K215" s="3" t="inlineStr"/>
@@ -14214,12 +14206,12 @@
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
         <is>
-          <t>game-software-rating-management-regulations</t>
+          <t>chinese-taipei-esports-association</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>遊戲軟體分級管理辦法 (Game Software Rating Management Regulations)</t>
+          <t>CTeSA: 中華民國電子競技運動協會 (Chinese Taipei Esports Association)</t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr">
@@ -14229,17 +14221,17 @@
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>Report or document</t>
+          <t>Organisation</t>
         </is>
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>Regulation or law</t>
+          <t>Esports body</t>
         </is>
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
-          <t>Mandatory Chinese-language rating labels with specified minimum pixel/centimetre sizes, compulsory warnings about gambling use and paid-item spending, disclosure of rating level in advertising, and takedown powers over unrated foreign titles accessed online. Issued 2006 as 電腦軟體分級辦法, renamed and rewritten 2012, amended through 2019. Authority transferred from MOEA to MODA in August 2022.</t>
+          <t>Taiwan's formal esports institution and the record of an unusual policy arc: an official 2017 assessment concluded esports was not a sport, then in November 2017 the legislature amended the Sports Industry Development Act to include esports, and CTeSA's own site documents both. Handles national team selection, IESF/AESF/GEF representation, and hosted the 2018 IESF World Championship in Kaohsiung (~50 countries, 700+ players). Established 10 Jan 2012, the sole designated esports agency of the Ministry of Sports and the Chinese Taipei Olympic Committee, and a founding member of IESF. Its chair is the chairman of Gamania (遊戲橘子), a listed publisher, so the national esports body is led by industry, a conflict worth stating. Also has a history of controversy (e.g. a public apology over an awards-show invitation)</t>
         </is>
       </c>
       <c r="G216" s="3" t="inlineStr">
@@ -14259,7 +14251,7 @@
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
-          <t>https://law.moda.gov.tw/LawContent.aspx?id=FL039733</t>
+          <t>https://ctesa.com.tw/</t>
         </is>
       </c>
       <c r="K216" s="3" t="inlineStr"/>
@@ -14274,12 +14266,12 @@
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
         <is>
-          <t>chinese-taipei-esports-association</t>
+          <t>ofcom-children-and-parents-media-use-and-attitudes</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
         <is>
-          <t>CTeSA: 中華民國電子競技運動協會 (Chinese Taipei Esports Association)</t>
+          <t>Ofcom: Children and Parents: Media Use and Attitudes</t>
         </is>
       </c>
       <c r="C217" s="3" t="inlineStr">
@@ -14289,27 +14281,27 @@
       </c>
       <c r="D217" s="3" t="inlineStr">
         <is>
-          <t>Organisation</t>
+          <t>Report or document</t>
         </is>
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
-          <t>Esports body</t>
+          <t>Report or data series</t>
         </is>
       </c>
       <c r="F217" s="3" t="inlineStr">
         <is>
-          <t>Taiwan's formal esports institution and the record of an unusual policy arc: an official 2017 assessment concluded esports was not a sport, then in November 2017 the legislature amended the Sports Industry Development Act to include esports, and CTeSA's own site documents both. Handles national team selection, IESF/AESF/GEF representation, and hosted the 2018 IESF World Championship in Kaohsiung (~50 countries, 700+ players). Established 10 Jan 2012, the sole designated esports agency of the Ministry of Sports and the Chinese Taipei Olympic Committee, and a founding member of IESF. Its chair is the chairman of Gamania (遊戲橘子), a listed publisher, so the national esports body is led by industry, a conflict worth stating. Also has a history of controversy (e.g. a public apology over an awards-show invitation)</t>
+          <t>The best free longitudinal dataset anywhere on children's media and gaming behaviour and parental attitudes, through Children's Media Lives, Online Nation and the media literacy series. UK-specific, don't export findings to other markets without flagging</t>
         </is>
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="H217" s="3" t="inlineStr">
         <is>
-          <t>Traditional Chinese</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I217" s="3" t="inlineStr">
@@ -14319,7 +14311,7 @@
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
-          <t>https://ctesa.com.tw/</t>
+          <t>https://www.ofcom.org.uk/</t>
         </is>
       </c>
       <c r="K217" s="3" t="inlineStr"/>
@@ -14334,12 +14326,12 @@
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
         <is>
-          <t>ofcom-children-and-parents-media-use-and-attitudes</t>
+          <t>ukie</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>Ofcom: Children and Parents: Media Use and Attitudes</t>
+          <t>Ukie</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
@@ -14349,17 +14341,17 @@
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>Report or document</t>
+          <t>Organisation</t>
         </is>
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>Report or data series</t>
+          <t>Industry association</t>
         </is>
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>The best free longitudinal dataset anywhere on children's media and gaming behaviour and parental attitudes, through Children's Media Lives, Online Nation and the media literacy series. UK-specific, don't export findings to other markets without flagging</t>
+          <t>UK games industry valuation, GSD sales data commentary, the UK Games Map, consumer market reports and policy positions. The UK counterpart to game in Germany and SELL in France. Also runs the UK Games Industry Census, the workforce broken out by ethnicity, gender, gender identity, sexuality, disability, caring responsibilities and social background by parental occupation and school type. Advocacy body.</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
@@ -14379,7 +14371,7 @@
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
-          <t>https://www.ofcom.org.uk/</t>
+          <t>https://ukie.org.uk/</t>
         </is>
       </c>
       <c r="K218" s="3" t="inlineStr"/>
@@ -14394,12 +14386,12 @@
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
         <is>
-          <t>ukie</t>
+          <t>tiga</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
         <is>
-          <t>Ukie</t>
+          <t>TIGA</t>
         </is>
       </c>
       <c r="C219" s="3" t="inlineStr">
@@ -14419,7 +14411,7 @@
       </c>
       <c r="F219" s="3" t="inlineStr">
         <is>
-          <t>UK games industry valuation, GSD sales data commentary, the UK Games Map, consumer market reports and policy positions. The UK counterpart to game in Germany and SELL in France. Also runs the UK Games Industry Census, the workforce broken out by ethnicity, gender, gender identity, sexuality, disability, caring responsibilities and social background by parental occupation and school type. Advocacy body.</t>
+          <t>Developer-side employment and production data. Tax-relief policy analysis. Advocacy body (developers), complements Ukie.</t>
         </is>
       </c>
       <c r="G219" s="3" t="inlineStr">
@@ -14439,7 +14431,7 @@
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
-          <t>https://ukie.org.uk/</t>
+          <t>https://tiga.org</t>
         </is>
       </c>
       <c r="K219" s="3" t="inlineStr"/>
@@ -14454,12 +14446,12 @@
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
         <is>
-          <t>tiga</t>
+          <t>games-rating-authority</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>TIGA</t>
+          <t>Games Rating Authority</t>
         </is>
       </c>
       <c r="C220" s="3" t="inlineStr">
@@ -14474,12 +14466,12 @@
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>Industry association</t>
+          <t>Rating body</t>
         </is>
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>Developer-side employment and production data. Tax-relief policy analysis. Advocacy body (developers), complements Ukie.</t>
+          <t>UK administrator of PEGI ratings, with rating criteria and search. Statutory role for boxed games. Digital storefronts use IARC.</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
@@ -14499,7 +14491,7 @@
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
-          <t>https://tiga.org</t>
+          <t>https://gamesratingauthority.org.uk</t>
         </is>
       </c>
       <c r="K220" s="3" t="inlineStr"/>
@@ -14514,12 +14506,12 @@
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
         <is>
-          <t>games-rating-authority</t>
+          <t>ask-about-games</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
         <is>
-          <t>Games Rating Authority</t>
+          <t>Ask About Games</t>
         </is>
       </c>
       <c r="C221" s="3" t="inlineStr">
@@ -14534,12 +14526,12 @@
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
-          <t>Rating body</t>
+          <t>Parent guidance platform</t>
         </is>
       </c>
       <c r="F221" s="3" t="inlineStr">
         <is>
-          <t>UK administrator of PEGI ratings, with rating criteria and search. Statutory role for boxed games. Digital storefronts use IARC.</t>
+          <t>Plain-English parent guidance on ratings, family controls, healthy play. Run by the GRA with industry involvement. Equivalent to France's PédaGoJeux.</t>
         </is>
       </c>
       <c r="G221" s="3" t="inlineStr">
@@ -14559,7 +14551,7 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
-          <t>https://gamesratingauthority.org.uk</t>
+          <t>https://www.askaboutgames.com</t>
         </is>
       </c>
       <c r="K221" s="3" t="inlineStr"/>
@@ -14574,12 +14566,12 @@
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
         <is>
-          <t>ask-about-games</t>
+          <t>internet-matters</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>Ask About Games</t>
+          <t>Internet Matters</t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
@@ -14594,12 +14586,12 @@
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>Parent guidance platform</t>
+          <t>Safety and advocacy org</t>
         </is>
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>Plain-English parent guidance on ratings, family controls, healthy play. Run by the GRA with industry involvement. Equivalent to France's PédaGoJeux.</t>
+          <t>Research and guidance on children's online safety incl. gaming (contact risk, spending, wellbeing). Industry-funded coalition. Research output is substantial.</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr">
@@ -14619,7 +14611,7 @@
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
-          <t>https://www.askaboutgames.com</t>
+          <t>https://www.internetmatters.org</t>
         </is>
       </c>
       <c r="K222" s="3" t="inlineStr"/>
@@ -14634,12 +14626,12 @@
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
         <is>
-          <t>internet-matters</t>
+          <t>thrive-digital-alliance</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
         <is>
-          <t>Internet Matters</t>
+          <t>Thrive Digital Alliance</t>
         </is>
       </c>
       <c r="C223" s="3" t="inlineStr">
@@ -14659,7 +14651,7 @@
       </c>
       <c r="F223" s="3" t="inlineStr">
         <is>
-          <t>Research and guidance on children's online safety incl. gaming (contact risk, spending, wellbeing). Industry-funded coalition. Research output is substantial.</t>
+          <t>Children's Digital Wellbeing Framework, a manifesto against protection-only design, and a Resource Bank of research and toolkits on children's digital play. Use it for the design-standards side of kids-and-games research, beside Internet Matters for safety and Ofcom for the data. | OWNERSHIP FLAG: hosted by Fundamentally Children, a UK child-development consultancy, and it sells accreditation against its own framework, so it has a stake in the standards it promotes.</t>
         </is>
       </c>
       <c r="G223" s="3" t="inlineStr">
@@ -14679,7 +14671,7 @@
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
-          <t>https://www.internetmatters.org</t>
+          <t>https://sites.google.com/fundamentallychildren.com/thrivedigitalalliance/home</t>
         </is>
       </c>
       <c r="K223" s="3" t="inlineStr"/>
@@ -14694,12 +14686,12 @@
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
         <is>
-          <t>thrive-digital-alliance</t>
+          <t>bafta-games</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
         <is>
-          <t>Thrive Digital Alliance</t>
+          <t>BAFTA Games</t>
         </is>
       </c>
       <c r="C224" s="3" t="inlineStr">
@@ -14714,12 +14706,12 @@
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>Safety and advocacy org</t>
+          <t>Event or awards</t>
         </is>
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>Children's Digital Wellbeing Framework, a manifesto against protection-only design, and a Resource Bank of research and toolkits on children's digital play. Use it for the design-standards side of kids-and-games research, beside Internet Matters for safety and Ofcom for the data. | OWNERSHIP FLAG: hosted by Fundamentally Children, a UK child-development consultancy, and it sells accreditation against its own framework, so it has a stake in the standards it promotes.</t>
+          <t>Cultural legitimacy via an awards archive, talent programs, YGD (young game designers). Awards body, not a data source. Useful for tracking what UK institutions canonize. Owned by BAFTA.</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
@@ -14739,7 +14731,7 @@
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
-          <t>https://sites.google.com/fundamentallychildren.com/thrivedigitalalliance/home</t>
+          <t>https://www.bafta.org/games</t>
         </is>
       </c>
       <c r="K224" s="3" t="inlineStr"/>
@@ -14754,12 +14746,12 @@
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
         <is>
-          <t>bafta-games</t>
+          <t>british-esports-federation</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
         <is>
-          <t>BAFTA Games</t>
+          <t>British Esports Federation</t>
         </is>
       </c>
       <c r="C225" s="3" t="inlineStr">
@@ -14774,12 +14766,12 @@
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>Event or awards</t>
+          <t>Esports body</t>
         </is>
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>Cultural legitimacy via an awards archive, talent programs, YGD (young game designers). Awards body, not a data source. Useful for tracking what UK institutions canonize. Owned by BAFTA.</t>
+          <t>National esports structures: schools/college competitions, the Sunderland national arena. Government-recognized body.</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr">
@@ -14799,7 +14791,7 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
-          <t>https://www.bafta.org/games</t>
+          <t>https://britishesports.org</t>
         </is>
       </c>
       <c r="K225" s="3" t="inlineStr"/>
@@ -14814,12 +14806,12 @@
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
         <is>
-          <t>british-esports-federation</t>
+          <t>iwgb-game-workers</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
         <is>
-          <t>British Esports Federation</t>
+          <t>IWGB Game Workers</t>
         </is>
       </c>
       <c r="C226" s="3" t="inlineStr">
@@ -14834,12 +14826,12 @@
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>Esports body</t>
+          <t>Union or worker organisation</t>
         </is>
       </c>
       <c r="F226" s="3" t="inlineStr">
         <is>
-          <t>National esports structures: schools/college competitions, the Sunderland national arena. Government-recognized body.</t>
+          <t>The largest UK game worker union, organising employees and contract workers. In August 2026 it won the UK tabletop sector's first recognition deal, covering pay, AI use policy and freelancer treatment. Its old microsite gameworkers.co.uk is abandoned, do not link it.</t>
         </is>
       </c>
       <c r="G226" s="3" t="inlineStr">
@@ -14859,7 +14851,7 @@
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
-          <t>https://britishesports.org</t>
+          <t>https://iwgb.org.uk/en/</t>
         </is>
       </c>
       <c r="K226" s="3" t="inlineStr"/>
@@ -14874,12 +14866,12 @@
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
         <is>
-          <t>iwgb-game-workers</t>
+          <t>nhs-national-centre-for-gaming-disorders</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>IWGB Game Workers</t>
+          <t>NHS National Centre for Gaming Disorders (CNWL)</t>
         </is>
       </c>
       <c r="C227" s="3" t="inlineStr">
@@ -14894,12 +14886,12 @@
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>Union or worker organisation</t>
+          <t>Research institute</t>
         </is>
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>The largest UK game worker union, organising employees and contract workers. In August 2026 it won the UK tabletop sector's first recognition deal, covering pay, AI use policy and freelancer treatment. Its old microsite gameworkers.co.uk is abandoned, do not link it.</t>
+          <t>The only NHS specialist gaming clinic in England, taking self-referrals from age 13. Its referral figures are the provider's own numbers.</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr">
@@ -14919,7 +14911,7 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
-          <t>https://iwgb.org.uk/en/</t>
+          <t>https://www.cnwl.nhs.uk/national-centre-gaming-disorders</t>
         </is>
       </c>
       <c r="K227" s="3" t="inlineStr"/>
@@ -14934,12 +14926,12 @@
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
         <is>
-          <t>nhs-national-centre-for-gaming-disorders</t>
+          <t>specialeffect</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
         <is>
-          <t>NHS National Centre for Gaming Disorders (CNWL)</t>
+          <t>SpecialEffect</t>
         </is>
       </c>
       <c r="C228" s="3" t="inlineStr">
@@ -14954,12 +14946,12 @@
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>Research institute</t>
+          <t>Safety and advocacy org</t>
         </is>
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
-          <t>The only NHS specialist gaming clinic in England, taking self-referrals from age 13. Its referral figures are the provider's own numbers.</t>
+          <t>Builds custom control setups for disabled players and publishes free per-game accessibility settings guides plus motor accessibility guidance for developers.</t>
         </is>
       </c>
       <c r="G228" s="3" t="inlineStr">
@@ -14979,7 +14971,7 @@
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
-          <t>https://www.cnwl.nhs.uk/national-centre-gaming-disorders</t>
+          <t>https://www.specialeffect.org.uk/</t>
         </is>
       </c>
       <c r="K228" s="3" t="inlineStr"/>
@@ -14994,12 +14986,12 @@
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>specialeffect</t>
+          <t>pegi</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
         <is>
-          <t>SpecialEffect</t>
+          <t>PEGI</t>
         </is>
       </c>
       <c r="C229" s="3" t="inlineStr">
@@ -15014,22 +15006,22 @@
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>Safety and advocacy org</t>
+          <t>Rating body</t>
         </is>
       </c>
       <c r="F229" s="3" t="inlineStr">
         <is>
-          <t>Builds custom control setups for disabled players and publishes free per-game accessibility settings guides plus motor accessibility guidance for developers.</t>
+          <t>Cross-EU rating records, with loot-box and in-game-purchase labels as a regulatory signal. The rating database France actually uses, since it has no national body like Germany's USK. Ratings signal, and enforcement varies by country. EN site is the primary version</t>
         </is>
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>DE; EU; FR; IT; UK</t>
         </is>
       </c>
       <c r="H229" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>English; Multilingual</t>
         </is>
       </c>
       <c r="I229" s="3" t="inlineStr">
@@ -15039,7 +15031,7 @@
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
-          <t>https://www.specialeffect.org.uk/</t>
+          <t>https://pegi.info/</t>
         </is>
       </c>
       <c r="K229" s="3" t="inlineStr"/>
@@ -15054,12 +15046,12 @@
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
         <is>
-          <t>pegi</t>
+          <t>gaconf</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
         <is>
-          <t>PEGI</t>
+          <t>GAconf</t>
         </is>
       </c>
       <c r="C230" s="3" t="inlineStr">
@@ -15074,22 +15066,22 @@
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>Rating body</t>
+          <t>Event or awards</t>
         </is>
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
-          <t>Cross-EU rating records, with loot-box and in-game-purchase labels as a regulatory signal. The rating database France actually uses, since it has no national body like Germany's USK. Ratings signal, and enforcement varies by country. EN site is the primary version</t>
+          <t>A free game accessibility conference, livestreamed at no cost, where developers and disabled players discuss access decisions directly.</t>
         </is>
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>DE; EU; FR; IT; UK</t>
+          <t>EU; UK; US</t>
         </is>
       </c>
       <c r="H230" s="3" t="inlineStr">
         <is>
-          <t>English; Multilingual</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I230" s="3" t="inlineStr">
@@ -15099,7 +15091,7 @@
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
-          <t>https://pegi.info/</t>
+          <t>https://www.gaconf.com/</t>
         </is>
       </c>
       <c r="K230" s="3" t="inlineStr"/>
@@ -15114,12 +15106,12 @@
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>gaconf</t>
+          <t>oxford-internet-institute-understanding-video-game-play-and</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
         <is>
-          <t>GAconf</t>
+          <t>Oxford Internet Institute, Understanding Video Game Play and Mental Health</t>
         </is>
       </c>
       <c r="C231" s="3" t="inlineStr">
@@ -15134,17 +15126,17 @@
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>Event or awards</t>
+          <t>Research institute</t>
         </is>
       </c>
       <c r="F231" s="3" t="inlineStr">
         <is>
-          <t>A free game accessibility conference, livestreamed at no cost, where developers and disabled players discuss access decisions directly.</t>
+          <t>The only games and wellbeing programme working from industry-supplied objective play telemetry rather than self-reported hours, with open datasets and open access papers. The named grant ran to December 2025.</t>
         </is>
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>EU; UK; US</t>
+          <t>Global; UK</t>
         </is>
       </c>
       <c r="H231" s="3" t="inlineStr">
@@ -15159,7 +15151,7 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>https://www.gaconf.com/</t>
+          <t>https://www.oii.ox.ac.uk/research/projects/understanding-video-game-play-and-mental-health/</t>
         </is>
       </c>
       <c r="K231" s="3" t="inlineStr"/>
@@ -15174,12 +15166,12 @@
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
         <is>
-          <t>oxford-internet-institute-understanding-video-game-play-and</t>
+          <t>game-accessibility-guidelines</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
         <is>
-          <t>Oxford Internet Institute, Understanding Video Game Play and Mental Health</t>
+          <t>Game Accessibility Guidelines</t>
         </is>
       </c>
       <c r="C232" s="3" t="inlineStr">
@@ -15189,17 +15181,17 @@
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>Organisation</t>
+          <t>Report or document</t>
         </is>
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>Research institute</t>
+          <t>Report or data series</t>
         </is>
       </c>
       <c r="F232" s="3" t="inlineStr">
         <is>
-          <t>The only games and wellbeing programme working from industry-supplied objective play telemetry rather than self-reported hours, with open datasets and open access papers. The named grant ran to December 2025.</t>
+          <t>A free tiered reference splitting accessibility provisions into Basic, Intermediate and Advanced, which shows what the industry treats as a baseline versus a specialist accommodation. The site names no version number or update date.</t>
         </is>
       </c>
       <c r="G232" s="3" t="inlineStr">
@@ -15219,7 +15211,7 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
-          <t>https://www.oii.ox.ac.uk/research/projects/understanding-video-game-play-and-mental-health/</t>
+          <t>https://gameaccessibilityguidelines.com/</t>
         </is>
       </c>
       <c r="K232" s="3" t="inlineStr"/>
@@ -15234,12 +15226,12 @@
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
         <is>
-          <t>game-accessibility-guidelines</t>
+          <t>women-in-games</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
         <is>
-          <t>Game Accessibility Guidelines</t>
+          <t>Women in Games</t>
         </is>
       </c>
       <c r="C233" s="3" t="inlineStr">
@@ -15249,17 +15241,17 @@
       </c>
       <c r="D233" s="3" t="inlineStr">
         <is>
-          <t>Report or document</t>
+          <t>Organisation</t>
         </is>
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
-          <t>Report or data series</t>
+          <t>Safety and advocacy org</t>
         </is>
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>A free tiered reference splitting accessibility provisions into Basic, Intermediate and Advanced, which shows what the industry treats as a baseline versus a specialist accommodation. The site names no version number or update date.</t>
+          <t>Publishes its own insight reports, most recently on the drop in women's representation from playing to workforce to ownership and investment.</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
@@ -15279,7 +15271,7 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
-          <t>https://gameaccessibilityguidelines.com/</t>
+          <t>https://www.womeningames.org/the-drop-off/</t>
         </is>
       </c>
       <c r="K233" s="3" t="inlineStr"/>
@@ -15294,12 +15286,12 @@
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
         <is>
-          <t>women-in-games</t>
+          <t>esa</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
         <is>
-          <t>Women in Games</t>
+          <t>ESA (Entertainment Software Association)</t>
         </is>
       </c>
       <c r="C234" s="3" t="inlineStr">
@@ -15314,17 +15306,17 @@
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>Safety and advocacy org</t>
+          <t>Industry association</t>
         </is>
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>Publishes its own insight reports, most recently on the drop in women's representation from playing to workforce to ownership and investment.</t>
+          <t>The annual Essential Facts survey, 2026 edition current, which provides the US player demographics the press cites all year, plus joint US spending data with Circana and Sensor Tower.</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>Global; UK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="H234" s="3" t="inlineStr">
@@ -15339,7 +15331,7 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
-          <t>https://www.womeningames.org/the-drop-off/</t>
+          <t>https://www.theesa.com/</t>
         </is>
       </c>
       <c r="K234" s="3" t="inlineStr"/>
@@ -15354,12 +15346,12 @@
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>esa</t>
+          <t>ftc</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
         <is>
-          <t>ESA (Entertainment Software Association)</t>
+          <t>FTC (US)</t>
         </is>
       </c>
       <c r="C235" s="3" t="inlineStr">
@@ -15374,12 +15366,12 @@
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
-          <t>Industry association</t>
+          <t>Regulator</t>
         </is>
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>The annual Essential Facts survey, 2026 edition current, which provides the US player demographics the press cites all year, plus joint US spending data with Circana and Sensor Tower.</t>
+          <t>Primary source for monetisation and child-privacy red flags. Enforcement actions on loot boxes, dark patterns and COPPA child privacy, including the loot-box workshop and the Epic and Fortnite settlements. Use for primary documents in monetization-risk research. Legal documents, slow-moving, US only</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
@@ -15399,7 +15391,7 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
-          <t>https://www.theesa.com/</t>
+          <t>https://www.ftc.gov/</t>
         </is>
       </c>
       <c r="K235" s="3" t="inlineStr"/>
@@ -15414,12 +15406,12 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>ftc</t>
+          <t>children-and-screens</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
         <is>
-          <t>FTC (US)</t>
+          <t>Children and Screens</t>
         </is>
       </c>
       <c r="C236" s="3" t="inlineStr">
@@ -15434,12 +15426,12 @@
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>Regulator</t>
+          <t>Research institute</t>
         </is>
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
-          <t>Primary source for monetisation and child-privacy red flags. Enforcement actions on loot boxes, dark patterns and COPPA child privacy, including the loot-box workshop and the Epic and Fortnite settlements. Use for primary documents in monetization-risk research. Legal documents, slow-moving, US only</t>
+          <t>Interdisciplinary research institute on digital media and child development.</t>
         </is>
       </c>
       <c r="G236" s="3" t="inlineStr">
@@ -15459,7 +15451,7 @@
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
-          <t>https://www.ftc.gov/</t>
+          <t>https://childrenandscreens.org</t>
         </is>
       </c>
       <c r="K236" s="3" t="inlineStr"/>
@@ -15474,12 +15466,12 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>children-and-screens</t>
+          <t>pew-research-center</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
         <is>
-          <t>Children and Screens</t>
+          <t>Pew Research Center</t>
         </is>
       </c>
       <c r="C237" s="3" t="inlineStr">
@@ -15499,7 +15491,7 @@
       </c>
       <c r="F237" s="3" t="inlineStr">
         <is>
-          <t>Interdisciplinary research institute on digital media and child development.</t>
+          <t>Free, transparent, longitudinal. The 'Teens, Social Media and Technology' series is the backbone for the young-people segment.</t>
         </is>
       </c>
       <c r="G237" s="3" t="inlineStr">
@@ -15519,7 +15511,7 @@
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
-          <t>https://childrenandscreens.org</t>
+          <t>https://pewresearch.org</t>
         </is>
       </c>
       <c r="K237" s="3" t="inlineStr"/>
@@ -15534,12 +15526,12 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>pew-research-center</t>
+          <t>american-academy-of-pediatrics</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
         <is>
-          <t>Pew Research Center</t>
+          <t>American Academy of Pediatrics</t>
         </is>
       </c>
       <c r="C238" s="3" t="inlineStr">
@@ -15554,12 +15546,12 @@
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>Research institute</t>
+          <t>Safety and advocacy org</t>
         </is>
       </c>
       <c r="F238" s="3" t="inlineStr">
         <is>
-          <t>Free, transparent, longitudinal. The 'Teens, Social Media and Technology' series is the backbone for the young-people segment.</t>
+          <t>Medical professional association. Clinical framing on media and children. Runs a Center of Excellence on Social Media and Youth Mental Health.</t>
         </is>
       </c>
       <c r="G238" s="3" t="inlineStr">
@@ -15579,7 +15571,7 @@
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
-          <t>https://pewresearch.org</t>
+          <t>https://aap.org</t>
         </is>
       </c>
       <c r="K238" s="3" t="inlineStr"/>
@@ -15594,12 +15586,12 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>american-academy-of-pediatrics</t>
+          <t>cdc-nchs</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
         <is>
-          <t>American Academy of Pediatrics</t>
+          <t>CDC / NCHS</t>
         </is>
       </c>
       <c r="C239" s="3" t="inlineStr">
@@ -15614,12 +15606,12 @@
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
-          <t>Safety and advocacy org</t>
+          <t>Government agency</t>
         </is>
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
-          <t>Medical professional association. Clinical framing on media and children. Runs a Center of Excellence on Social Media and Youth Mental Health.</t>
+          <t>Federal data on teen screen time and wellbeing. An independent check on both industry and advocacy claims.</t>
         </is>
       </c>
       <c r="G239" s="3" t="inlineStr">
@@ -15639,7 +15631,7 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
-          <t>https://aap.org</t>
+          <t>https://cdc.gov/nchs</t>
         </is>
       </c>
       <c r="K239" s="3" t="inlineStr"/>
@@ -15654,12 +15646,12 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>cdc-nchs</t>
+          <t>common-sense-media</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
         <is>
-          <t>CDC / NCHS</t>
+          <t>Common Sense Media</t>
         </is>
       </c>
       <c r="C240" s="3" t="inlineStr">
@@ -15674,12 +15666,12 @@
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>Government agency</t>
+          <t>Research institute</t>
         </is>
       </c>
       <c r="F240" s="3" t="inlineStr">
         <is>
-          <t>Federal data on teen screen time and wellbeing. An independent check on both industry and advocacy claims.</t>
+          <t>Free primary research. Nonprofit that also publishes family-facing media ratings.</t>
         </is>
       </c>
       <c r="G240" s="3" t="inlineStr">
@@ -15699,7 +15691,7 @@
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
-          <t>https://cdc.gov/nchs</t>
+          <t>https://commonsensemedia.org</t>
         </is>
       </c>
       <c r="K240" s="3" t="inlineStr"/>
@@ -15714,12 +15706,12 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>common-sense-media</t>
+          <t>fairplay</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
         <is>
-          <t>Common Sense Media</t>
+          <t>Fairplay</t>
         </is>
       </c>
       <c r="C241" s="3" t="inlineStr">
@@ -15734,12 +15726,12 @@
       </c>
       <c r="E241" s="3" t="inlineStr">
         <is>
-          <t>Research institute</t>
+          <t>Safety and advocacy org</t>
         </is>
       </c>
       <c r="F241" s="3" t="inlineStr">
         <is>
-          <t>Free primary research. Nonprofit that also publishes family-facing media ratings.</t>
+          <t>Advocacy, openly campaigning (formerly Campaign for a Commercial-Free Childhood). Shap articulation of the anti-commercialisation position.</t>
         </is>
       </c>
       <c r="G241" s="3" t="inlineStr">
@@ -15759,7 +15751,7 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
-          <t>https://commonsensemedia.org</t>
+          <t>https://fairplayforkids.org</t>
         </is>
       </c>
       <c r="K241" s="3" t="inlineStr"/>
@@ -15774,12 +15766,12 @@
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>fairplay</t>
+          <t>sec</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
         <is>
-          <t>Fairplay</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="C242" s="3" t="inlineStr">
@@ -15794,12 +15786,12 @@
       </c>
       <c r="E242" s="3" t="inlineStr">
         <is>
-          <t>Safety and advocacy org</t>
+          <t>Government agency</t>
         </is>
       </c>
       <c r="F242" s="3" t="inlineStr">
         <is>
-          <t>Advocacy, openly campaigning (formerly Campaign for a Commercial-Free Childhood). Shap articulation of the anti-commercialisation position.</t>
+          <t>An independent agency of the US government whose primary purpose is to enforce laws against market manipulation.</t>
         </is>
       </c>
       <c r="G242" s="3" t="inlineStr">
@@ -15819,7 +15811,7 @@
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
-          <t>https://fairplayforkids.org</t>
+          <t>https://www.sec.gov/</t>
         </is>
       </c>
       <c r="K242" s="3" t="inlineStr"/>
@@ -15834,12 +15826,12 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>sec</t>
+          <t>higher-education-video-game-alliance</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>Higher Education Video Game Alliance (HEVGA)</t>
         </is>
       </c>
       <c r="C243" s="3" t="inlineStr">
@@ -15854,12 +15846,12 @@
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
-          <t>Government agency</t>
+          <t>Learned society</t>
         </is>
       </c>
       <c r="F243" s="3" t="inlineStr">
         <is>
-          <t>An independent agency of the US government whose primary purpose is to enforce laws against market manipulation.</t>
+          <t>Periodic survey reports on university games programmes and graduate outcomes, the only systematic public data on the size and shape of games education in North America.</t>
         </is>
       </c>
       <c r="G243" s="3" t="inlineStr">
@@ -15879,7 +15871,7 @@
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/</t>
+          <t>https://hevga.org/</t>
         </is>
       </c>
       <c r="K243" s="3" t="inlineStr"/>
@@ -15894,12 +15886,12 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>higher-education-video-game-alliance</t>
+          <t>video-game-history-foundation</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
         <is>
-          <t>Higher Education Video Game Alliance (HEVGA)</t>
+          <t>Video Game History Foundation</t>
         </is>
       </c>
       <c r="C244" s="3" t="inlineStr">
@@ -15914,12 +15906,12 @@
       </c>
       <c r="E244" s="3" t="inlineStr">
         <is>
-          <t>Learned society</t>
+          <t>Archive or museum</t>
         </is>
       </c>
       <c r="F244" s="3" t="inlineStr">
         <is>
-          <t>Periodic survey reports on university games programmes and graduate outcomes, the only systematic public data on the size and shape of games education in North America.</t>
+          <t>Over 1,500 full-text searchable out-of-print game magazines plus unpublished development material, including the Mark Flitman papers and over 100 hours of Myst production footage. Open to any remote researcher with no account.</t>
         </is>
       </c>
       <c r="G244" s="3" t="inlineStr">
@@ -15939,7 +15931,7 @@
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
-          <t>https://hevga.org/</t>
+          <t>https://archive.gamehistory.org/</t>
         </is>
       </c>
       <c r="K244" s="3" t="inlineStr"/>
@@ -15954,12 +15946,12 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>video-game-history-foundation</t>
+          <t>the-strong-brian-sutton-smith-library-and-archives-of-play</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
         <is>
-          <t>Video Game History Foundation</t>
+          <t>The Strong, Brian Sutton-Smith Library and Archives of Play</t>
         </is>
       </c>
       <c r="C245" s="3" t="inlineStr">
@@ -15979,7 +15971,7 @@
       </c>
       <c r="F245" s="3" t="inlineStr">
         <is>
-          <t>Over 1,500 full-text searchable out-of-print game magazines plus unpublished development material, including the Mark Flitman papers and over 100 hours of Myst production footage. Open to any remote researcher with no account.</t>
+          <t>Corporate business records of Atari, Sierra On-Line, Brøderbund, Midway and Her Interactive, plus the personal papers of Ralph Baer, Jerry Lawson, Carol Shaw and Jordan Mechner. Onsite by appointment with two weeks' notice.</t>
         </is>
       </c>
       <c r="G245" s="3" t="inlineStr">
@@ -15999,7 +15991,7 @@
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
-          <t>https://archive.gamehistory.org/</t>
+          <t>https://www.museumofplay.org/collections/research-access/</t>
         </is>
       </c>
       <c r="K245" s="3" t="inlineStr"/>
@@ -16014,12 +16006,12 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>the-strong-brian-sutton-smith-library-and-archives-of-play</t>
+          <t>ablegamers</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
         <is>
-          <t>The Strong, Brian Sutton-Smith Library and Archives of Play</t>
+          <t>AbleGamers</t>
         </is>
       </c>
       <c r="C246" s="3" t="inlineStr">
@@ -16034,12 +16026,12 @@
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>Archive or museum</t>
+          <t>Safety and advocacy org</t>
         </is>
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
-          <t>Corporate business records of Atari, Sierra On-Line, Brøderbund, Midway and Her Interactive, plus the personal papers of Ralph Baer, Jerry Lawson, Carol Shaw and Jordan Mechner. Onsite by appointment with two weeks' notice.</t>
+          <t>The Accessible Player Experiences framework, organising barriers into Control, Presentation and Challenge, plus published grant and scholarship figures. The APX certification itself is a paid course.</t>
         </is>
       </c>
       <c r="G246" s="3" t="inlineStr">
@@ -16059,7 +16051,7 @@
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
-          <t>https://www.museumofplay.org/collections/research-access/</t>
+          <t>https://ablegamers.org/apx/</t>
         </is>
       </c>
       <c r="K246" s="3" t="inlineStr"/>
@@ -16074,12 +16066,12 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>ablegamers</t>
+          <t>adl-center-for-technology-and-society-games-research</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>AbleGamers</t>
+          <t>ADL Center for Technology and Society, games research</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
@@ -16089,17 +16081,17 @@
       </c>
       <c r="D247" s="3" t="inlineStr">
         <is>
-          <t>Organisation</t>
+          <t>Report or document</t>
         </is>
       </c>
       <c r="E247" s="3" t="inlineStr">
         <is>
-          <t>Safety and advocacy org</t>
+          <t>Report or data series</t>
         </is>
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>The Accessible Player Experiences framework, organising barriers into Control, Presentation and Challenge, plus published grant and scholarship figures. The APX certification itself is a paid course.</t>
+          <t>Five annual waves of nationally representative US data on identity-based harassment in multiplayer games, with oversampling of Jewish, Muslim, LGBTQ+, Black and Hispanic players.</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr">
@@ -16119,7 +16111,7 @@
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
-          <t>https://ablegamers.org/apx/</t>
+          <t>https://www.adl.org/resources/report/hate-no-game-hate-and-harassment-online-games-2023</t>
         </is>
       </c>
       <c r="K247" s="3" t="inlineStr"/>
@@ -16134,12 +16126,12 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>adl-center-for-technology-and-society-games-research</t>
+          <t>glaad-gaming</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
         <is>
-          <t>ADL Center for Technology and Society, games research</t>
+          <t>GLAAD Gaming</t>
         </is>
       </c>
       <c r="C248" s="3" t="inlineStr">
@@ -16159,7 +16151,7 @@
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
-          <t>Five annual waves of nationally representative US data on identity-based harassment in multiplayer games, with oversampling of Jewish, Muslim, LGBTQ+, Black and Hispanic players.</t>
+          <t>The only free report measuring LGBTQ representation in games against the LGBTQ share of players.</t>
         </is>
       </c>
       <c r="G248" s="3" t="inlineStr">
@@ -16179,7 +16171,7 @@
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
-          <t>https://www.adl.org/resources/report/hate-no-game-hate-and-harassment-online-games-2023</t>
+          <t>https://glaad.org/glaad-gaming/2024/</t>
         </is>
       </c>
       <c r="K248" s="3" t="inlineStr"/>
@@ -16194,12 +16186,12 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>glaad-gaming</t>
+          <t>esrb</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
         <is>
-          <t>GLAAD Gaming</t>
+          <t>ESRB</t>
         </is>
       </c>
       <c r="C249" s="3" t="inlineStr">
@@ -16209,22 +16201,22 @@
       </c>
       <c r="D249" s="3" t="inlineStr">
         <is>
-          <t>Report or document</t>
+          <t>Organisation</t>
         </is>
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
-          <t>Report or data series</t>
+          <t>Rating body</t>
         </is>
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
-          <t>The only free report measuring LGBTQ representation in games against the LGBTQ share of players.</t>
+          <t>US and Canadian rating records and marketing-compliance actions. The rating system actually used in Canada, since there is no national body and ESRB applies across North America. The US analogue to Japan's CERO and Korea's GRAC. Also runs COPPA safe-harbour privacy certification.</t>
         </is>
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA; US</t>
         </is>
       </c>
       <c r="H249" s="3" t="inlineStr">
@@ -16239,7 +16231,7 @@
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
-          <t>https://glaad.org/glaad-gaming/2024/</t>
+          <t>https://www.esrb.org/</t>
         </is>
       </c>
       <c r="K249" s="3" t="inlineStr"/>
@@ -16254,12 +16246,12 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>esrb</t>
+          <t>united-videogame-workers-cwa-local-9433</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
         <is>
-          <t>ESRB</t>
+          <t>United Videogame Workers, CWA Local 9433</t>
         </is>
       </c>
       <c r="C250" s="3" t="inlineStr">
@@ -16274,12 +16266,12 @@
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
-          <t>Rating body</t>
+          <t>Union or worker organisation</t>
         </is>
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>US and Canadian rating records and marketing-compliance actions. The rating system actually used in Canada, since there is no national body and ESRB applies across North America. The US analogue to Japan's CERO and Korea's GRAC. Also runs COPPA safe-harbour privacy certification.</t>
+          <t>A direct-join industry-wide union rather than a single-employer unit, publishing its own campaign documents including a Game Workers' Bill of Rights.</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
@@ -16299,7 +16291,7 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
-          <t>https://www.esrb.org/</t>
+          <t>https://uvw-cwa.org/</t>
         </is>
       </c>
       <c r="K250" s="3" t="inlineStr"/>
@@ -16314,12 +16306,12 @@
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
         <is>
-          <t>united-videogame-workers-cwa-local-9433</t>
+          <t>the-association-for-the-study-of-play</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
         <is>
-          <t>United Videogame Workers, CWA Local 9433</t>
+          <t>The Association for the Study of Play (TASP)</t>
         </is>
       </c>
       <c r="C251" s="3" t="inlineStr">
@@ -16334,17 +16326,17 @@
       </c>
       <c r="E251" s="3" t="inlineStr">
         <is>
-          <t>Union or worker organisation</t>
+          <t>Learned society</t>
         </is>
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>A direct-join industry-wide union rather than a single-employer unit, publishing its own campaign documents including a Game Workers' Bill of Rights.</t>
+          <t>The interdisciplinary society for play itself rather than for digital games, spanning anthropology, sociology, psychology and education. Its own materials do not claim digital games coverage, so read it as play studies.</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>CA; US</t>
+          <t>Global; US</t>
         </is>
       </c>
       <c r="H251" s="3" t="inlineStr">
@@ -16359,7 +16351,7 @@
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
-          <t>https://uvw-cwa.org/</t>
+          <t>https://studyofplay.org/</t>
         </is>
       </c>
       <c r="K251" s="3" t="inlineStr"/>
@@ -16374,12 +16366,12 @@
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>the-association-for-the-study-of-play</t>
+          <t>software-preservation-network</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr">
         <is>
-          <t>The Association for the Study of Play (TASP)</t>
+          <t>Software Preservation Network</t>
         </is>
       </c>
       <c r="C252" s="3" t="inlineStr">
@@ -16394,12 +16386,12 @@
       </c>
       <c r="E252" s="3" t="inlineStr">
         <is>
-          <t>Learned society</t>
+          <t>Safety and advocacy org</t>
         </is>
       </c>
       <c r="F252" s="3" t="inlineStr">
         <is>
-          <t>The interdisciplinary society for play itself rather than for digital games, spanning anthropology, sociology, psychology and education. Its own materials do not claim digital games coverage, so read it as play studies.</t>
+          <t>Runs the working group that petitions in the US DMCA exemption proceedings, and publishes the Code of Best Practices in Fair Use for Software Preservation, which tells an institution what it can defensibly do.</t>
         </is>
       </c>
       <c r="G252" s="3" t="inlineStr">
@@ -16419,7 +16411,7 @@
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
-          <t>https://studyofplay.org/</t>
+          <t>https://www.softwarepreservationnetwork.org/code-of-best-practices-for-fair-use-in-software-preservation/web-version/</t>
         </is>
       </c>
       <c r="K252" s="3" t="inlineStr"/>
@@ -16434,12 +16426,12 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>software-preservation-network</t>
+          <t>american-psychiatric-association-internet-gaming</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr">
         <is>
-          <t>Software Preservation Network</t>
+          <t>American Psychiatric Association, Internet Gaming</t>
         </is>
       </c>
       <c r="C253" s="3" t="inlineStr">
@@ -16449,17 +16441,17 @@
       </c>
       <c r="D253" s="3" t="inlineStr">
         <is>
-          <t>Organisation</t>
+          <t>Report or document</t>
         </is>
       </c>
       <c r="E253" s="3" t="inlineStr">
         <is>
-          <t>Safety and advocacy org</t>
+          <t>Regulation or law</t>
         </is>
       </c>
       <c r="F253" s="3" t="inlineStr">
         <is>
-          <t>Runs the working group that petitions in the US DMCA exemption proceedings, and publishes the Code of Best Practices in Fair Use for Software Preservation, which tells an institution what it can defensibly do.</t>
+          <t>States plainly that Internet Gaming Disorder is not a formal DSM diagnosis but a condition for further study, and that classification as an addiction is the subject of much debate. WHO and the APA disagree on status. Never cite either without naming which classification you mean.</t>
         </is>
       </c>
       <c r="G253" s="3" t="inlineStr">
@@ -16479,7 +16471,7 @@
       </c>
       <c r="J253" s="3" t="inlineStr">
         <is>
-          <t>https://www.softwarepreservationnetwork.org/code-of-best-practices-for-fair-use-in-software-preservation/web-version/</t>
+          <t>https://www.psychiatry.org/patients-families/internet-gaming</t>
         </is>
       </c>
       <c r="K253" s="3" t="inlineStr"/>
@@ -16494,12 +16486,12 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>american-psychiatric-association-internet-gaming</t>
+          <t>take-this</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr">
         <is>
-          <t>American Psychiatric Association, Internet Gaming</t>
+          <t>Take This</t>
         </is>
       </c>
       <c r="C254" s="3" t="inlineStr">
@@ -16509,17 +16501,17 @@
       </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
-          <t>Report or document</t>
+          <t>Organisation</t>
         </is>
       </c>
       <c r="E254" s="3" t="inlineStr">
         <is>
-          <t>Regulation or law</t>
+          <t>Safety and advocacy org</t>
         </is>
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
-          <t>States plainly that Internet Gaming Disorder is not a formal DSM diagnosis but a condition for further study, and that classification as an addiction is the subject of much debate. WHO and the APA disagree on status. Never cite either without naming which classification you mean.</t>
+          <t>Free research on mental health among game developers and players, plus the AFK Room programme at conventions. The only body in the field covering adult wellbeing rather than child safety.</t>
         </is>
       </c>
       <c r="G254" s="3" t="inlineStr">
@@ -16539,7 +16531,7 @@
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
-          <t>https://www.psychiatry.org/patients-families/internet-gaming</t>
+          <t>https://www.takethis.org/</t>
         </is>
       </c>
       <c r="K254" s="3" t="inlineStr"/>
@@ -16554,12 +16546,12 @@
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>take-this</t>
+          <t>xbox-accessibility-guidelines</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr">
         <is>
-          <t>Take This</t>
+          <t>Xbox Accessibility Guidelines</t>
         </is>
       </c>
       <c r="C255" s="3" t="inlineStr">
@@ -16569,17 +16561,17 @@
       </c>
       <c r="D255" s="3" t="inlineStr">
         <is>
-          <t>Organisation</t>
+          <t>Report or document</t>
         </is>
       </c>
       <c r="E255" s="3" t="inlineStr">
         <is>
-          <t>Safety and advocacy org</t>
+          <t>Report or data series</t>
         </is>
       </c>
       <c r="F255" s="3" t="inlineStr">
         <is>
-          <t>Free research on mental health among game developers and players, plus the AFK Room programme at conventions. The only body in the field covering adult wellbeing rather than child safety.</t>
+          <t>Numbered accessibility guidelines with a published version history, the only such document where each revision can be dated.</t>
         </is>
       </c>
       <c r="G255" s="3" t="inlineStr">
@@ -16599,7 +16591,7 @@
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
-          <t>https://www.takethis.org/</t>
+          <t>https://learn.microsoft.com/en-us/gaming/accessibility/xag-version-history</t>
         </is>
       </c>
       <c r="K255" s="3" t="inlineStr"/>
@@ -16614,12 +16606,12 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>xbox-accessibility-guidelines</t>
+          <t>lgbtq-video-game-archive</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr">
         <is>
-          <t>Xbox Accessibility Guidelines</t>
+          <t>LGBTQ Video Game Archive</t>
         </is>
       </c>
       <c r="C256" s="3" t="inlineStr">
@@ -16629,17 +16621,17 @@
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>Report or document</t>
+          <t>Organisation</t>
         </is>
       </c>
       <c r="E256" s="3" t="inlineStr">
         <is>
-          <t>Report or data series</t>
+          <t>Archive or museum</t>
         </is>
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
-          <t>Numbered accessibility guidelines with a published version history, the only such document where each revision can be dated.</t>
+          <t>A researched decade-by-decade catalogue of documented LGBTQ content in games, which lets a researcher check whether a claim about a game's queer content is documented before repeating it.</t>
         </is>
       </c>
       <c r="G256" s="3" t="inlineStr">
@@ -16659,7 +16651,7 @@
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/gaming/accessibility/xag-version-history</t>
+          <t>https://lgbtqgamearchive.com/</t>
         </is>
       </c>
       <c r="K256" s="3" t="inlineStr"/>
@@ -16674,12 +16666,12 @@
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>lgbtq-video-game-archive</t>
+          <t>digra-digital-library</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr">
         <is>
-          <t>LGBTQ Video Game Archive</t>
+          <t>DiGRA digital library</t>
         </is>
       </c>
       <c r="C257" s="3" t="inlineStr">
@@ -16689,22 +16681,22 @@
       </c>
       <c r="D257" s="3" t="inlineStr">
         <is>
-          <t>Organisation</t>
+          <t>Report or document</t>
         </is>
       </c>
       <c r="E257" s="3" t="inlineStr">
         <is>
-          <t>Archive or museum</t>
+          <t>Conference proceedings</t>
         </is>
       </c>
       <c r="F257" s="3" t="inlineStr">
         <is>
-          <t>A researched decade-by-decade catalogue of documented LGBTQ content in games, which lets a researcher check whether a claim about a game's queer content is documented before repeating it.</t>
+          <t>Open conference papers where emerging games-research topics appear first: the DiGRA and DiGRA/FDG proceedings. The papers carry no DOI, so citation indexes see few of them; search the library itself.</t>
         </is>
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>Global; US</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="H257" s="3" t="inlineStr">
@@ -16719,7 +16711,7 @@
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
-          <t>https://lgbtqgamearchive.com/</t>
+          <t>https://dl.digra.org</t>
         </is>
       </c>
       <c r="K257" s="3" t="inlineStr"/>
@@ -16734,12 +16726,12 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>digra-digital-library</t>
+          <t>belgian-gaming-commission</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>DiGRA digital library</t>
+          <t>Belgian Gaming Commission (Kansspelcommissie / Commission des jeux de hasard)</t>
         </is>
       </c>
       <c r="C258" s="3" t="inlineStr">
@@ -16749,27 +16741,27 @@
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
-          <t>Report or document</t>
+          <t>Organisation</t>
         </is>
       </c>
       <c r="E258" s="3" t="inlineStr">
         <is>
-          <t>Conference proceedings</t>
+          <t>Regulator</t>
         </is>
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>Open conference papers where emerging games-research topics appear first: the DiGRA and DiGRA/FDG proceedings. The papers carry no DOI, so citation indexes see few of them; search the library itself.</t>
+          <t>The Belgian regulator's own record on paid random items: its 2018 loot box report and its 2024 workshop report on paid random items are on the reports page, beside its formal advice to government and parliament and its enforcement decisions. Reports are Dutch and French only, and the English pages are thin.</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="H258" s="3" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Dutch; English; French</t>
         </is>
       </c>
       <c r="I258" s="3" t="inlineStr">
@@ -16779,7 +16771,7 @@
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
-          <t>https://dl.digra.org</t>
+          <t>https://www.gamingcommission.be/</t>
         </is>
       </c>
       <c r="K258" s="3" t="inlineStr"/>
@@ -16794,12 +16786,12 @@
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>belgian-gaming-commission</t>
+          <t>loot-box-state-of-play-leon-y-xiaos-annual-regulatory-review</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr">
         <is>
-          <t>Belgian Gaming Commission (Kansspelcommissie / Commission des jeux de hasard)</t>
+          <t>Loot Box State of Play: Leon Y. Xiao's annual regulatory review</t>
         </is>
       </c>
       <c r="C259" s="3" t="inlineStr">
@@ -16809,27 +16801,27 @@
       </c>
       <c r="D259" s="3" t="inlineStr">
         <is>
-          <t>Organisation</t>
+          <t>Report or document</t>
         </is>
       </c>
       <c r="E259" s="3" t="inlineStr">
         <is>
-          <t>Regulator</t>
+          <t>Report or data series</t>
         </is>
       </c>
       <c r="F259" s="3" t="inlineStr">
         <is>
-          <t>The Belgian regulator's own record on paid random items: its 2018 loot box report and its 2024 workshop report on paid random items are on the reports page, beside its formal advice to government and parliament and its enforcement decisions. Reports are Dutch and French only, and the English pages are thin.</t>
+          <t>Annual, jurisdiction-by-jurisdiction rundown of loot box law, regulation and enforcement by an academic lawyer, published each December on GamesIndustry.biz since 2022; the 2023 edition also ran as a Stanford TTLF working paper and in Gaming Law Review. Narrative rather than a count: it dates measures and court decisions but does not tally jurisdictions, so it feeds a timeline and not a chart. | The author is party to several of the enforcement complaints he reports and says so; not legal advice.</t>
         </is>
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="H259" s="3" t="inlineStr">
         <is>
-          <t>Dutch; English; French</t>
+          <t>English</t>
         </is>
       </c>
       <c r="I259" s="3" t="inlineStr">
@@ -16839,7 +16831,7 @@
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
-          <t>https://www.gamingcommission.be/</t>
+          <t>https://sites.google.com/view/leon-xiao/publications/popular-publications</t>
         </is>
       </c>
       <c r="K259" s="3" t="inlineStr"/>
@@ -16854,12 +16846,12 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>loot-box-state-of-play-leon-y-xiaos-annual-regulatory-review</t>
+          <t>gdc-state-of-the-game-industry</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr">
         <is>
-          <t>Loot Box State of Play: Leon Y. Xiao's annual regulatory review</t>
+          <t>GDC State of the Game Industry (annual survey)</t>
         </is>
       </c>
       <c r="C260" s="3" t="inlineStr">
@@ -16879,7 +16871,7 @@
       </c>
       <c r="F260" s="3" t="inlineStr">
         <is>
-          <t>Annual, jurisdiction-by-jurisdiction rundown of loot box law, regulation and enforcement by an academic lawyer, published each December on GamesIndustry.biz since 2022; the 2023 edition also ran as a Stanford TTLF working paper and in Gaming Law Review. Narrative rather than a count: it dates measures and court decisions but does not tally jurisdictions, so it feeds a timeline and not a chart. | The author is party to several of the enforcement complaints he reports and says so; not legal advice.</t>
+          <t>The annual survey of game developers run by the GDC Festival of Gaming, over 3,000 respondents in 2024 and over 2,300 in 2026, and the closest thing the industry has to a workforce series: in the 2026 edition 28% had been laid off in the past two years, 33% in the United States, and half worked for an employer that cut in the past 12 months. Also the source of the generative AI adoption percentages the trends quote. | The layoff question changes wording between editions (exposure in 2024, laid off that year in 2025, over two years in 2026), so the editions do not plot as one line. The full report sits behind a free registration form. Run by Informa, which also owns Game Developer.</t>
         </is>
       </c>
       <c r="G260" s="3" t="inlineStr">
@@ -16899,7 +16891,7 @@
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
-          <t>https://sites.google.com/view/leon-xiao/publications/popular-publications</t>
+          <t>https://gdconf.com/article/gdc-2026-state-of-the-game-industry-reveals-impact-of-layoffs-generative-ai-and-more/</t>
         </is>
       </c>
       <c r="K260" s="3" t="inlineStr"/>
@@ -16914,12 +16906,12 @@
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>gdc-state-of-the-game-industry</t>
+          <t>family-gaming-database</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr">
         <is>
-          <t>GDC State of the Game Industry (annual survey)</t>
+          <t>Family Gaming Database</t>
         </is>
       </c>
       <c r="C261" s="3" t="inlineStr">
@@ -16929,22 +16921,22 @@
       </c>
       <c r="D261" s="3" t="inlineStr">
         <is>
-          <t>Report or document</t>
+          <t>Organisation</t>
         </is>
       </c>
       <c r="E261" s="3" t="inlineStr">
         <is>
-          <t>Report or data series</t>
+          <t>Parent guidance platform</t>
         </is>
       </c>
       <c r="F261" s="3" t="inlineStr">
         <is>
-          <t>The annual survey of game developers run by the GDC Festival of Gaming, over 3,000 respondents in 2024 and over 2,300 in 2026, and the closest thing the industry has to a workforce series: in the 2026 edition 28% had been laid off in the past two years, 33% in the United States, and half worked for an employer that cut in the past 12 months. Also the source of the generative AI adoption percentages the trends quote. | The layoff question changes wording between editions (exposure in 2024, laid off that year in 2025, over two years in 2026), so the editions do not plot as one line. The full report sits behind a free registration form. Run by Informa, which also owns Game Developer.</t>
+          <t>A hand-curated, searchable database of about 3,600 video games and 200 board games, written for parents and carers: each entry carries age ratings, costs and in-game spending, and accessibility detail across difficulty, reading, navigation, controls, visuals, audio and communication, and the whole set filters by platform, age and those features. Founded and edited by the journalist Andy Robertson. Use it to see how a game is explained to a family audience, or to find games by accessibility feature. | Curated, not complete: the team picks the games that matter to families, so a game's absence says nothing about the game. Built in the UK but not UK-only; its partners include Australia's IGEA and the US ratings board. Says it is editorially independent, free and without adverts, and is funded by partnerships and labelled sponsored activity; the partners it names include PlayStation and Xbox, whose games it lists, plus HSBC UK, the VSC Rating Board, Hookshot Media, Kidas, IGEA and Ask About Games.</t>
         </is>
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Global; UK</t>
         </is>
       </c>
       <c r="H261" s="3" t="inlineStr">
@@ -16959,7 +16951,7 @@
       </c>
       <c r="J261" s="3" t="inlineStr">
         <is>
-          <t>https://gdconf.com/article/gdc-2026-state-of-the-game-industry-reveals-impact-of-layoffs-generative-ai-and-more/</t>
+          <t>https://www.familygamingdatabase.com/</t>
         </is>
       </c>
       <c r="K261" s="3" t="inlineStr"/>
@@ -67462,7 +67454,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>127</t>
         </is>
       </c>
     </row>
@@ -67534,7 +67526,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>49</t>
         </is>
       </c>
     </row>
@@ -67714,7 +67706,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>144</t>
         </is>
       </c>
     </row>
@@ -67732,7 +67724,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>116</t>
         </is>
       </c>
     </row>
@@ -69425,7 +69417,7 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Database</t>
+          <t>Genre taxonomy</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
@@ -69447,7 +69439,7 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Genre taxonomy</t>
+          <t>Adjacent research body</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
@@ -69469,12 +69461,12 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Adjacent research body</t>
+          <t>Database</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -69799,7 +69791,7 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Regulation or law</t>
+          <t>Parent guidance platform</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
@@ -69821,12 +69813,12 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>Parent guidance platform</t>
+          <t>Regulation or law</t>
         </is>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -71640,7 +71632,7 @@
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>502</t>
         </is>
       </c>
     </row>
@@ -71662,7 +71654,7 @@
       </c>
       <c r="D209" s="3" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>122</t>
         </is>
       </c>
     </row>

--- a/games-research-starter-pack.xlsx
+++ b/games-research-starter-pack.xlsx
@@ -59533,12 +59533,12 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Studio investment has fallen about 85% from its 2021 peak to below 2019 levels while revenues rose 30 to 40%, and Matthew Ball's 2026 report argues the industry now invests less in new game development, as a share of net revenue, than at any point on record. Marvel's Spider-Man went from just over $100M to more than $300M across three games without proportionate sales. Studios are shipping smaller. The argument is whether that is a chosen strategy or a budget line. The composition is moving as well as the total: Values Value's Talent Signals report, reported in September 2026, puts European studio spending on external talent up 63% in 2025 against 55% globally, and describes a two-tier team model of a small permanent core with a contractor periphery hired by project phase. A falling investment line and a rising outside-hands line are the same decision seen twice.</t>
+          <t>Big games cost more to make than ever, but outside investors are putting far less money into the studios that make them. Companies are still spending more on making games each year, but that spending is growing more slowly than revenue, and a growing share goes to outside contractors. Many studios are responding by making smaller games. The open question is whether that's a creative choice or simply what the budget allows.</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Determines how to read every “we are focusing on smaller experiences” statement of the next two years. Ball's own data shows capital contraction rather than a design movement, and the two produce identical press releases.</t>
+          <t>Over the next two years, expect many studios to say they're "focusing on smaller games." Analyst Matthew Ball's data suggests this is mostly about having less money, not a new creative direction. From the outside, both look the same.</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">

--- a/games-research-starter-pack.xlsx
+++ b/games-research-starter-pack.xlsx
@@ -59681,7 +59681,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>New games fight for playtime</t>
+          <t>Players keep playing old games</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -59701,12 +59701,12 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>New releases take 12 to 13% of total player time across PC and console and have for three years, with Xbox highest at 18% on Game Pass availability. Playtime is concentrated, 80% of it in 79 games on PC, 74 on PlayStation and 91 on Xbox, but that concentration loosened in 2025 and PC playtime growth since 2022 has come entirely from titles outside the top 20. Price architecture differs sharply: 76 to 79% of console revenue comes from games above $50, while PC splits near-evenly across sub-$30, $30 to $50 and above. On the money side, Alinea Analytics estimates Steam took more than $15 billion gross in the first eight months of 2026 with the top 100 new 2026 releases about 16 percent of it, Forza Horizon 6 the largest at roughly $210 million.</t>
+          <t>Games no longer leave the market, so every new release competes with everything ever released. About one hour in seven on Steam goes to a game released that year, and that share has held steady for three years. Playtime is also concentrated: fewer than a hundred games account for 80% of it on each platform. That grip loosened slightly in 2025, though the time moving away from the biggest games isn't going to brand-new ones. Money follows the same pattern. Of everything Steam earned in the first eight months of 2026, the hundred best-selling new games made up about a sixth.</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>A new game competes against the back catalogue for attention and against its own discounted history on price. “Record catalog revenue” in an earnings release and a struggling launch are often the same fact seen twice.</t>
+          <t>Most of the time people spend playing goes to games that have been out for years. A new game isn't just competing with other new games. It's competing with everything already installed, including older games now selling at a discount. This is why a publisher can report record earnings from its back catalog in the same quarter a new release disappoints. Those are the same fact seen twice.</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -62199,7 +62199,7 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>New games fight for playtime</t>
+          <t>Players keep playing old games</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -62222,7 +62222,7 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>New games fight for playtime</t>
+          <t>Players keep playing old games</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -62245,7 +62245,7 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>New games fight for playtime</t>
+          <t>Players keep playing old games</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">

--- a/games-research-starter-pack.xlsx
+++ b/games-research-starter-pack.xlsx
@@ -58295,7 +58295,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Monetization on flat player base</t>
+          <t>Fewer players, spending more</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -58315,12 +58315,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Analyst Matthew Ball's annual reports argue gaming's decade of growth engines is exhausted: revenue and cultural weight are at record highs, yet growth is elusive and player counts are retreating across much of the developed world, so revenue gains come from monetizing existing players harder rather than adding new ones. The revenue half of that picture has since softened in the largest market: Circana put US spending down 10% year-on-year in July 2026 at $4.5bn, with hardware down 29% and new physical software at an all-time July low, even as average hardware selling prices rose 16%.</t>
+          <t>Analyst Matthew Ball argues the industry's growth engines are spent. Revenue is at record highs, but the share of people who play is shrinking across most of the developed world, so the gains come from charging existing players more rather than finding new ones. The squeeze worked until 2026. Now even that is slowing. In the US, the largest market, spending fell sharply in mid-2026, with console hardware taking the worst of it even as console prices rose. The job cuts that came with all this are on the layoffs page.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Explains why record industry revenue coexists with layoffs and player complaints about aggressive monetization, which is the central paradox of the current era.</t>
+          <t>The games industry keeps posting record revenue while studios lay people off and players complain about being squeezed. Those facts fit together: in most rich countries, the share of people who play has been falling for years, so the money has to come from charging the remaining players more. That's the central puzzle of this era, and this page explains it.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -59925,7 +59925,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Monetization on flat player base</t>
+          <t>Fewer players, spending more</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -59948,7 +59948,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Monetization on flat player base</t>
+          <t>Fewer players, spending more</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -59971,7 +59971,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Monetization on flat player base</t>
+          <t>Fewer players, spending more</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">

--- a/games-research-starter-pack.xlsx
+++ b/games-research-starter-pack.xlsx
@@ -58421,7 +58421,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Subscriptions are plateauing</t>
+          <t>Subscriptions stopped adding players</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -58441,12 +58441,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Game Pass is reportedly down to about 30 million paying subscribers, against an internal projection of ~77 million by 2026 revealed in FTC proceedings, after a price hike to $29.99 a month in October 2025 drove churn; Microsoft rolled Ultimate back to $22.99 on 26 April 2026. Sony has stopped reporting PS Plus subscriber counts. From November 2026 Xbox meters cloud streaming rather than bundling it: 15 hours a month on Ultimate, 10 on Premium, 5 on Essential, with extra hours sold separately. Microsoft puts the affected share at 4% of subscribers. Within a week of the cloud cap Microsoft began offering lapsed and some current Ultimate subscribers 12-month discounts reported at $16 to $20 a month against list, a segmented win-back test rather than a price change. Price is now the stated reason: Circana's tracking, reported in September 2026, puts more than 40% of US cancellations of Xbox Game Pass, PlayStation Plus and Nintendo Switch Online down to cost. That is the share of reasons given by people who cancelled, not evidence that more of them are cancelling.</t>
+          <t>Xbox Game Pass is reported to have about 30 million paying subscribers, far below the 77 million Microsoft's own internal plan projected for this point. A steep price rise in late 2025 drove people away, and Microsoft partly reversed it in 2026. Sony has stopped publishing PlayStation Plus numbers altogether. Companies are now trimming what subscribers get rather than adding subscribers: from November 2026, Xbox limits how much cloud streaming each tier includes and sells extra hours separately.</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Tests the 'Netflix of games' thesis that drove a decade of acquisitions and strategy. Also a good case of consolidation-era promises meeting reality (no plan survives an encounter with the enemy)</t>
+          <t>For a decade, the industry bet that games would go the way of TV and music: one monthly fee for a big library. That belief drove enormous acquisitions, including Microsoft's $68.7 billion purchase of Activision. Subscriber numbers have since stalled well short of what the companies planned for, and they've raised prices instead. It's a clear case of promises made during a buying spree meeting reality.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -60132,7 +60132,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Subscriptions are plateauing</t>
+          <t>Subscriptions stopped adding players</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -60155,7 +60155,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Subscriptions are plateauing</t>
+          <t>Subscriptions stopped adding players</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -60178,7 +60178,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Subscriptions are plateauing</t>
+          <t>Subscriptions stopped adding players</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">

--- a/games-research-starter-pack.xlsx
+++ b/games-research-starter-pack.xlsx
@@ -58198,7 +58198,7 @@
   <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="56" customWidth="1" min="4" max="4"/>
@@ -58253,7 +58253,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Games industry layoffs, 2023–present</t>
+          <t>Games companies are still cutting jobs</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -58268,17 +58268,17 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Global; US</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>During the pandemic, people played more games, and companies hired and spent heavily to keep up. When that demand cooled and borrowing got more expensive, publishers cut staff, cancelled projects, and closed studios. While there is no official count of games layoffs, there are at least two public trackers (Amir Satvat's, Farhan Noor's). For scale, the ESA counts 82,930 people directly employed in US games in 2025. Global estimates vary and are not comparable across countries.</t>
+          <t>No official body counts games layoffs, but two public trackers do: Amir Satvat's and Farhan Noor's. Layoffs dipped in 2025 and rose again in 2026, so the dip was a low point, not an ending. Check the date on any claim that layoffs are slowing before repeating it. For scale, the ESA counts 82,930 people directly employed in US games in 2025. Global estimates vary and cannot be compared across countries.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Since 2023, the games industry has been cutting jobs at a pace it hadn't seen before. Most of the big business, labor, and creative stories of the last few years trace back to it, so it's useful background for almost everything else here. One caution: when layoffs dipped in 2025, many people took that as a sign the worst was over. In 2026 they rose again, so the dip was a low point, not an ending. Check the date on any “layoffs are slowing” claim before repeating it.</t>
+          <t>Games companies hired heavily during the pandemic, then began cutting jobs in 2023 as demand cooled and borrowing got more expensive. The cuts sit behind most of the industry's business, labor and creative stories since, so they are background for almost everything else here.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -58295,7 +58295,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Fewer players, spending more</t>
+          <t>Rich markets are losing players, and growth has moved elsewhere</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -58310,17 +58310,17 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>CA; CN; DE; FR; Global; IT; JP; KR; UK; US</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Analyst Matthew Ball argues the industry's growth engines are spent. Revenue is at record highs, but the share of people who play is shrinking across most of the developed world, so the gains come from charging existing players more rather than finding new ones. The squeeze worked until 2026. Now even that is slowing. In the US, the largest market, spending fell sharply in mid-2026, with console hardware taking the worst of it even as console prices rose. The job cuts that came with all this are on the layoffs page.</t>
+          <t>Matthew Ball, then an outside analyst and since May 2026 an Xbox executive, argues the industry's growth engines are spent. Worldwide revenue is at a record, but the share of people who play is shrinking across most of the developed world, and the eight rich markets spent less in 2025 than in 2021. Publishers there are trying to earn more from the players who remain. In the US, the largest market, spending fell sharply in mid-2026, worst for console hardware even as console prices rose. The job cuts that came with this are on the layoffs page.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>The games industry keeps posting record revenue while studios lay people off and players complain about being squeezed. Those facts fit together: in most rich countries, the share of people who play has been falling for years, so the money has to come from charging the remaining players more. That's the central puzzle of this era, and this page explains it.</t>
+          <t>The games industry posts record revenue while studios lay off staff. The facts fit together. In most rich countries fewer people play and spending is below its 2021 peak. The record comes from China and the rest of the world.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -58337,7 +58337,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Premium price ceiling</t>
+          <t>Game prices are stalling as hardware prices climb</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -58352,17 +58352,17 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>DE; FR; Global; JP; UK; US</t>
+          <t>EU; Global; JP; UK; US</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>GTA 6 launched at $80, settling speculation about $100 base games. Only Mario Kart World, GTA 6, and Elden Ring on Switch 2 have cleared $70 — Microsoft tried and retreated to $70 after backlash. Meanwhile a RAM-driven hardware crunch pushed consoles past $600 and GPUs, monitors, and memory sharply higher. Nintendo raised Switch 2 to $500 in the US, Canada and Europe from 1 September 2026 (Japan from 25 May), citing memory and component costs, and said the new price still does not cover build cost; it put the hardware-cost impact on FY2027 earnings at about ¥100bn. By September the crunch was moving both ways: Framework cut its LPCAMM2 memory prices retroactively while a 10 percent Intel CPU rise was reported for October and Chinese GPU prices rose again.</t>
+          <t>Nintendo's Mario Kart World reached $80 in 2025. Microsoft announced $80 games and backed down within three months. Grand Theft Auto 6, due in November 2026, is priced at $79.99, which ended speculation about a $100 game. Sony, Microsoft and Nintendo all raised console prices in 2025 and 2026, blaming memory chip costs, tariffs and the wider economy. Circana counted 39% fewer consoles sold in the US in July 2026 than a year earlier, at an average selling price of $542.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>The ceiling held on software but broke on hardware, and buyers responded by waiting. Very important for researchers tracking monetization, substitution behavior, or consumer resistance.</t>
+          <t>The price of a big new game has moved only once, from $70 to $80, and only for a handful of titles. Console prices have kept rising, and Americans are buying fewer consoles. The two prices a player pays have gone separate ways.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -58379,7 +58379,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Live-service retreat</t>
+          <t>Publishers are retreating from live-service games</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -58394,17 +58394,17 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>CN; Global; KR</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Live service means games built on an ongoing content and monetization cadence rather than a one-time sale. Entrants keep failing in a crowded field: Anthem went offline in January, Highguard lasted under two months. In 2026 the retreat sharpened — Guerrilla stripped live service out of Horizon Hunters Gathering mid-development, and Amazon exited MMO publishing entirely. In September 2026 Sega said it had cancelled its Super Game, a live-service project it judged too big to reach service scale, and Riot's co-founder said the free-to-play publisher is considering premium titles. The incumbents are not absorbing the space the entrants vacate: Newzoo's first-half 2026 read, reported in September 2026, found most established live-service and evergreen titles flat or down year on year, with growth confined to a handful of them.</t>
+          <t>Sony told investors in 2022 it would have twelve live-service games by March 2026. Reporters count eight canceled or withdrawn, a tally Sony has never confirmed. The pullback is wider than Sony. Warner Bros. wrote off $200 million on Suicide Squad, Ubisoft closed XDefiant along with two studios, and EA switched off Anthem. In 2026 a new shooter called Highguard closed after 45 days, and Amazon announced its exit from online role-playing games. None of these companies says it is leaving live service. Newzoo's 2026 market report found most established hits flat or down in the first half of the year, without giving figures.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>The pattern shapes what gets greenlit and which studios close. The portfolio math is under attack — greenlight fifteen, assume one hits — though developers argue saturation often just excuses bad games.</t>
+          <t>Live-service games are updated for years and earn money the whole time, like Fortnite. A hit can pay for a decade, so every big publisher wanted one. Many attempts have failed, and the failures decide which studios close and which games never get made.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -58421,7 +58421,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Subscriptions stopped adding players</t>
+          <t>Game subscriptions are stalling</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -58436,17 +58436,17 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Global; UK; US</t>
+          <t>Global; US</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Xbox Game Pass is reported to have about 30 million paying subscribers, far below the 77 million Microsoft's own internal plan projected for this point. A steep price rise in late 2025 drove people away, and Microsoft partly reversed it in 2026. Sony has stopped publishing PlayStation Plus numbers altogether. Companies are now trimming what subscribers get rather than adding subscribers: from November 2026, Xbox limits how much cloud streaming each tier includes and sells extra hours separately.</t>
+          <t>Xbox Game Pass is reported to have about 30 million paying subscribers, far below the 77 million Microsoft's internal plan projected for this point. A steep price rise in late 2025 drove people away, and Microsoft partly reversed it in 2026. Sony has stopped publishing PlayStation Plus numbers. Companies are now trimming what subscribers get. From November 2026, Xbox limits how much cloud streaming each tier includes and sells extra hours separately.</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>For a decade, the industry bet that games would go the way of TV and music: one monthly fee for a big library. That belief drove enormous acquisitions, including Microsoft's $68.7 billion purchase of Activision. Subscriber numbers have since stalled well short of what the companies planned for, and they've raised prices instead. It's a clear case of promises made during a buying spree meeting reality.</t>
+          <t>For a decade the industry bet that games would follow TV and music into one monthly fee for a big library, and that bet drove huge acquisitions. Subscriber numbers have since stalled well short of company plans, and prices have gone up instead.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -58463,7 +58463,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Creator platforms as sovereign economies</t>
+          <t>Roblox is rising and falling with its creators' hits</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -58483,12 +58483,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Roblox pays the users who build its games in a platform currency redeemable for cash (over US$1.5 billion in 2025, and $1.7 billion across the twelve months to September 2026 on the company’s own count). Distribution is extreme: the top 1,000 creators take roughly 73% of all payouts, while around 85% of developers earn under US$100 a month. At its September 2026 Developers Conference the platform began unbuilding its own walls: creators will be able to export a Roblox game as a standalone app for PC, console and mobile under a programme called Play Roblox Everywhere, and payouts move onto external rails through Roblox Wallet, which pays out every business day to a bank account, and Roblox Card, a debit card spending the Wallet balance directly. Both are US-only for creators 18 and over to start, with global expansion stated for 2027.</t>
+          <t>Roblox's accounts show payouts to creators growing from $112 million in 2019 to $1.5 billion in 2025, faster than player spending. The money is very unevenly spread. Roblox says its top 1,000 creators averaged $1.3 million in 2025, while the typical paid creator earned about $1,500 in the twelve months to June 2026. In mid-2026 Roblox withdrew its annual forecast after the viral games of 2025 faded. In September 2026 it said creators can release games as standalone apps and be paid in real currency every business day.</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>This economy has a business cycle. Roblox shed roughly US$70 billion in market value and pulled its full-year guidance in 2026 after creators failed to ship hits — i.e., they're a public company whose revenue depends on unsalaried teenagers. Youth labor, private currency, and regulatory scrutiny converge in one structure</t>
+          <t>Roblox makes no games. Its users build them and are paid in a currency they can exchange for dollars. In 2026 that economy had its first downturn, and it showed the risk of depending on hits made by people Roblox does not employ.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -58505,7 +58505,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Age checks arrive by court order</t>
+          <t>Regulators are forcing child-safety changes on platforms</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -58520,17 +58520,17 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>AU; CN; EU; Global; MENA; RU; TR; UK; US</t>
+          <t>AU; BR; EU; Global; MENA; RU; TR; UK; US</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Regulators shifted from suing Roblox to compelling it: state AG suits and a 148-case federal MDL were joined in August 2026 by a Senate Judiciary probe with a records deadline, while Australia's eSafety served transparency notices on Roblox, Minecraft, Fortnite and Steam and then extracted a court-enforceable undertaking. Roblox disputes the claims and now requires facial age estimation for chat. The mechanics followed the enforcement: Microsoft makes Australians verify age by selfie, ID or credit card before buying 18+ titles on the Xbox Store; in September 2026 Steam began requiring a credit card for R18+ purchases in Australia and the Epic Games Store announced age checks for R18+ titles, while Ofcom and the EU tighten in parallel. Elsewhere the response is blunter, with outright blocks in Turkey, Russia, Egypt and the Gulf. And it is no longer only Roblox: Brazil suspended Discord livestreaming after a teenager's death, and a Texas judge ordered Discord age checks.</t>
+          <t>Roblox faces 182 lawsuits before one US federal judge, suits from several states, and since August 2026 a Senate investigation. Roblox disputes the claims. In Australia it has made a court-enforceable promise to limit adults' contact with children and accept an outside audit. A Texas order requires age checks on Discord, and Brazil made Discord switch off livestreaming. Blocks are the blunter tool, and they do not always last. Russia lifted its block on Roblox after six months.</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>The defining child-safety story in games, and the one that turned age verification from platform policy into something players meet at the point of purchase. Community pushback centres on breach risk rather than on child safety.</t>
+          <t>Platforms where children play and chat, such as Roblox and Discord, spent years facing lawsuits and bad headlines over child safety. Governments are now ordering specific changes, some with deadlines attached. For players, the most visible result is being asked to prove their age.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -58547,12 +58547,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>India's real-money gaming ban</t>
+          <t>India has outlawed games played for money</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Emerging</t>
+          <t>Dominant</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -58567,12 +58567,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>India's parliament passed a law banning online games played with money, threatening the survival of the fantasy-gaming sector that had been projected to reach $3.6 billion by 2029. Industry groups are challenging it constitutionally, and critics argue players will shift to offshore platforms. The ban is also collapsing the disputes that sat above the sector: in September 2026 the Competition Commission of India closed WinZO’s antitrust case against Google, the market the complaint concerned having been legislated out of existence.</t>
+          <t>The law took effect on 1 May 2026, but operators closed their paid games within days of its passage in August 2025, as banks and payment companies cut them off. Dream11 said 95% of its revenue had gone, and Games24x7 laid off about 70% of its staff. The operators' challenge to the law is before the Supreme Court. Lumikai estimates that one in three players moved to offshore sites, a figure its own reporters treat as soft.</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>The largest single market prohibition in gaming, which makes it a template case for how fast a 'growth market' can be legislated away.</t>
+          <t>India had a large, fast-growing market for online games played for money, such as fantasy cricket and rummy. In August 2025 parliament banned them all. It is a rare test of what happens when a government removes a whole category of games.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -58609,12 +58609,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Games now carry different ratings, and different obligations, depending on where they are sold.</t>
+          <t>Brazil banned loot boxes in games children can reach in March 2026, and Belgium has treated them as gambling since 2018. South Korea requires the odds to be published, and in the first study of the law 84% of top-earning games with loot boxes did so. Australia rates such games M at minimum. From June 2026 PEGI rates new ones 16 across most of Europe, while Germany rates case by case through its own body. The Netherlands ruled in 2022 that loot boxes are not gambling, and the UK and Japan rely on the industry's own rules. So the same game carries different ratings, and different obligations, depending on where it is sold.</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Studios are redesigning their monetization strategy market by market to comply with differing rules, or exiting those markets entirely.</t>
+          <t>Loot boxes are paid items with random contents. Some countries ban them, some make publishers show the odds, and some say they are not gambling. Age ratings are the approach that is spreading, and publishers now change or withdraw games market by market.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -58631,7 +58631,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Playtime caps come for games</t>
+          <t>Governments are weighing legal caps on children's playtime</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -58646,17 +58646,17 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>CN; KR; VN</t>
+          <t>CN; EU; IN; JP; KR; US; VN</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>State-mandated limits on minors' play, now enforced through identity. China restricts minors to limited weekend/holiday hours behind real-name login; Vietnam's Decree 147 caps sessions at 60 minutes; South Korea repealed its shutdown law in 2021 — the region is not monolithic.</t>
+          <t>China allows under-18s three hours of online games a week, and Vietnam three hours a day across one company's games. South Korea repealed its midnight curfew in 2021. In 2026 the US House passed a bill requiring a parental timer, and the European Commission proposed time-management tools, but neither sets an hour limit or is law. On whether caps work, the largest study found no drop in heavy play after China's first rule but could not separate children from adults, while a later survey found children playing less.</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>No longer just a contrast case for the West. The US House-passed KIDS Act mandates default-on parental time controls, and the strongest evidence says caps do not actually reduce heavy play.</t>
+          <t>Only China and Vietnam cap children's playtime by law, checking every player's identity to enforce it. Elsewhere the idea has become advice or parental tools. The US and EU are now drafting rules, so whether caps work now matters, and the evidence is split.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -58673,7 +58673,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Publishers split on gambling money in esports</t>
+          <t>Game publishers are opening esports to licensed bookmakers</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -58688,17 +58688,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>BR; CN; EU; Global; US</t>
+          <t>BR; EU; Global; US</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Betting and skin-gambling money has long underwritten esports, but publishers are now moving in opposite directions. Valve's December 2025 licensing update barred case-opening, skin-trading and skin-gambling advertising in any capacity, jerseys included. Riot went the other way in January 2026, approving betting sponsors for the first time — Winamax with G2 and Team Heretics — while keeping the brands off jerseys and broadcasts.</t>
+          <t>In June 2025 Riot Games allowed betting companies to sponsor top League of Legends and Valorant teams, with logos kept off its own broadcasts. In December 2025 Valve barred sites that gamble with Counter-Strike's tradeable cosmetic items, known as skins, from jerseys and broadcasts. Valve still allows licensed bookmakers, so the two are closer than they look. Riot's rule keeps betting logos off jerseys, yet the bookmaker Winamax says its logo sits at the center of two teams' shirts. Esports Charts counts a betting brand as title sponsor of nine of the top ten Counter-Strike teams in the Americas. Nobody publishes how much esports income is gambling money.</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Follow the money: team solvency, youth exposure, and platform policy all hinge on gambling revenue. The argument has moved from whether to take it to who gets blamed for waiting.</t>
+          <t>Professional gaming teams have few ways to earn money, and betting companies are among the few sponsors still willing to pay. The companies that make the games decide which sponsors are allowed, and in 2025 the two most important ones moved in apparently opposite directions.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -58715,7 +58715,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Children's data, privacy &amp; the age-assurance bargain</t>
+          <t>Children's privacy rules are nudging games toward checking every player's age</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -58735,12 +58735,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>The FTC's amended COPPA Rule took effect June 23, 2025. Its April 22, 2026 compliance deadline has now passed, expanding protected data to biometrics and unbundling consent for child-directed services, including many games. Enforcement, not drafting, is now the story: TikTok settled with DOJ for $400M in August 2026, following Epic's $275M and HoYoverse's $20M. Parallel regimes - UK Age Appropriate Design Code, EU GDPR, and Australia's eSafety Act - are converging on audited age assurance rather than self-attestation. US state law is now a third layer beneath the federal rule: California enacted social media curbs for under-16s in September 2026, and Australia moved in the same week to require user control over algorithmic feeds, so a game with social features meets a different obligation in each jurisdiction it ships to.</t>
+          <t>The US rewrote its children's privacy rule in 2025, with compliance due by April 2026. It does not require age checks, but in February 2026 the Federal Trade Commission said it would not punish data collected only to check age. Roblox now asks anyone who wants to chat for a face scan or an ID, a step it took under the safety pressure covered on the child-safety page, not because a privacy law required it. The UK still accepts a stated age where risk is low, and the EU's guidelines are voluntary. Privacy groups object, and the first leaks have already happened.</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Data rules quietly determine what game features (chat, ads, AI) can legally exist for kids under 13 - and platforms are answering by collecting children's faces to prove they aren't collecting children's data, a trade the privacy-technical community is mobilizing against.</t>
+          <t>Laws protecting children's data limit what games offer young players. Applying them means knowing who is a child, and the surest checks are a face scan or an ID. So rules meant to collect less data are nudging platforms toward collecting more, from everyone.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -58757,7 +58757,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Addiction &amp; screen-time discourse</t>
+          <t>Problem-gaming research is shifting from hours to compulsion</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -58772,17 +58772,17 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>CN; Global; JP; KR; UK; US</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>The WHO's ICD-11 "gaming disorder" diagnosis remains scientifically contested, but the argument has moved underneath it. The live question in 2026 is no longer how many hours, it is whether use is compulsive and whether the product was built to make it so. A JAMA cohort of 4,300 youths tied addictive-use trajectories, not total screen time, to more than doubled suicide risk; an eight-year Finnish study found more screen time predicted better teen cognition. Regulation is following: US litigation, 100+ cases with two MDL denials, pleads predatory monetization rather than duration. Market framings still diverge (KR and CN pathologized and regulated, US and EU parenting anxiety, JP moderation by prefecture) but all four are time-based instruments now aimed at a design problem.</t>
+          <t>A 2025 study in JAMA followed 4,285 American children and tied suicidal behavior to compulsive use, not total screen time, with a weaker link for games than for social media and phones. The World Health Organization calls gaming disorder a diagnosis, while American psychiatry says it needs more study. More than 100 US lawsuits argue that games were designed to be addictive. How common it is remains unsettled, and the authors of the best-known estimate, about 3% of people, say such figures are inflated.</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Identical play data still reads as disease, discipline, or moral panic depending on the market. But every lens is migrating from "how long" to "how it was built," which moves the exposure from player behavior onto the design and monetization layer.</t>
+          <t>Whether too much play is an illness, a parenting problem or a product defect depends on where you are. The newest research says hours played is the wrong measure, and that matters because nearly every rule written so far measures hours.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -58799,12 +58799,12 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>China expands into premium games and IP</t>
+          <t>Chinese studios are trying to build premium global franchises</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Dominant</t>
+          <t>Emerging</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -58819,12 +58819,12 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Black Myth: Wukong, a 2024 action game based on a classic Chinese legend, proved a Chinese studio could make a global big-budget hit. Studios are now trying to turn that one success into lasting series. Its developer, Game Science, is following it with Black Myth: Zhong Kui, a game about a different figure from Chinese folklore rather than a direct sequel. That suggests it sees Chinese mythology as a deep source of future games, not a one-time hook. Other Chinese studios, including S-GAME, Everstone (working with NetEase), and miHoYo, are building original worlds of their own. The government is backing the shift: games are now part of China's 15th Five-Year Plan, its national economic roadmap. Chinese games also earned $12.37 billion outside China in the first half of 2026, up 30%.</t>
+          <t>Black Myth: Wukong, a 2024 action game based on a Chinese legend, proved a Chinese studio could make a global big-budget hit. Its developer, Game Science, is following it with Black Myth: Zhong Kui, built on a different figure from Chinese folklore. S-GAME, Everstone (working with NetEase) and miHoYo are building original worlds of their own. Everstone's Where Winds Meet reached a worldwide audience in late 2025, though as a free-to-play game. Games are now part of China's 15th Five-Year Plan, its national economic roadmap. For games sold up front, the evidence so far is one franchise. China's console market grew 55% in 2024 and 86% in 2025, to 8.36 billion yuan, on the official industry report's count, then fell 7% in the first half of 2026 as Wukong's sales faded.</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>China's games industry is known for free-to-play mobile games, and big-budget games you buy up front used to come mostly from Japan, the US, and Europe. That's changing, which affects who counts as a competitor, how China uses games to spread its culture abroad, and where skilled developers want to work. The first real limit on this growth is cost: studios themselves say big-budget games are getting more expensive to make.</t>
+          <t>China's games industry is known for free-to-play mobile games, while big-budget games bought up front came mostly from Japan, the US and Europe. Chinese studios now make them too. Studios say rising costs are the first real limit on that growth.</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -58841,7 +58841,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>The Gulf as the industry's biggest buyer</t>
+          <t>Saudi state money is buying major games companies</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -58856,17 +58856,17 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Global; MENA; US</t>
+          <t>CN; Global; JP; KR; MENA; US</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Saudi Arabia's PIF has assembled a layered gaming portfolio (Savvy, Scopely, ESL FACEIT, listed stakes) capped by taking EA private, closed August 2026. PIF holds 93.4% directly, held outside Savvy alongside Silver Lake and Affinity Partners. Roughly $20B of purchase debt now sits on EA's own books, so the debate has shifted from sportswashing and esports capture toward layoffs, cancelled projects, and quiet self-censorship. Brian Ward, who built the portfolio from 2021, stepped down as Savvy's CEO on 1 September 2026, twelve days after the EA deal closed; PIF deputy governor Turqi Alnowaiser took over on an interim basis, moving day-to-day control closer to the fund. Consolidation of the portfolio itself is now reportedly under discussion: in September 2026 Bloomberg reported, and several trade outlets relayed, that PIF is weighing a merger of EA with Savvy that would put EA Sports FC, Madden, Battlefield, The Sims, Pokémon Go and Monopoly Go under one company. Treat it as one outlet’s anonymous sourcing — EA, Savvy and PIF all declined to comment and no decision has been taken.</t>
+          <t>The Public Investment Fund owns 93.4% of EA, with two smaller partners, and holds it separately from Savvy Games Group, its own games company. EA has told lenders it will cut $700 million a year in costs. Bloomberg reports the fund is weighing a merger of the two, which nobody has confirmed. Naavik's Miikka Ahonen thinks the buying is nearly done, because the money Savvy committed is largely spent. Hard figures on whether the purchases pay their way are thin.</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Sovereign capital is now the industry's biggest single buyer, and it arrived leveraged. Ownership questions touch labor, esports, and content decisions across the West.</t>
+          <t>Since 2022 Saudi Arabia's sovereign wealth fund has bought across the games business, and in August 2026 it completed the purchase of Electronic Arts. Much of the price was borrowed, and EA now carries the debt.</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -58883,7 +58883,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Western publishers can't access Chinese growth</t>
+          <t>China's growth is going to Chinese-made games</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -58903,12 +58903,12 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>The games industry earned about $10 billion more in 2025 than in 2021. According to analyst Matthew Ball's analysis, about $4 billion of that increase came from China, and another $1.5 billion from Chinese-made games sold abroad. Inside China, about 83% of game revenue goes to Chinese-made games by the official industry report's 2025 count; Ball puts it at 84%. So much of the growth is in places many Western publishers can't compete. Research firm Niko Partners puts China's 2025 game revenue at $51.8 billion, up 5.4% and over $50 billion for the first time. The average player spent more than $70 that year, and mini games (small games played inside apps like WeChat, with no download) made up nearly a fifth of mobile spending. Niko expects $53.9 billion in 2026 and $59.8 billion by 2030.</t>
+          <t>The games industry earned about $10 billion more in 2025 than in 2021. According to analyst Matthew Ball's analysis, made when he was an outside analyst, before he became Xbox's chief strategy officer in May 2026, about $4 billion of that came from China, and another $1.5 billion from Chinese-made games sold abroad. Inside China, Chinese-made games take about 83% of revenue by the official industry report's 2025 count. Niko Partners puts China's 2025 game revenue at $51.8 billion, over $50 billion for the first time, and expects $53.9 billion in 2026.</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>When people say “the games industry is growing,” much of that growth is happening in China, where Western companies have limited access. The real story is the gap between where players are growing and where Western publishers can actually make money.</t>
+          <t>When people say the games industry is growing, much of that growth is in China, and most of it goes to Chinese-made games. What matters is the gap between where spending is growing and where Western publishers can actually make money.</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -58925,7 +58925,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>China throttles game approvals</t>
+          <t>China is using game approvals as a policy dial</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -58945,12 +58945,12 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Foreign games now get approved roughly every two months. The license itself is no longer the hardest part. The bigger hurdle now comes after approval: games must verify each player's real identity and automatically enforce the limits on how long and when minors can play.</t>
+          <t>China approved 1,676 domestic games in 2025, up from 468 in the freeze year of 2022, and Niko Partners expects 2026 to pass 2,000 licenses in all. Approvals stopped for nine months in 2018 and for eight months from August 2021, and about 14,000 small studios and related firms closed that year. Foreign games come through a thinner channel: 95 were approved in 2025. What follows approval, identity checks and limits on children's play, is on the playtime-caps page.</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>China controls how many games reach its market by adjusting how many licenses it approves. That license is called a banhao (版号), and China began issuing far fewer beginning in 2018.</t>
+          <t>Every game published in China needs a government license called a banhao (版号). China cut the number it issued sharply in 2018 and 2021, and has raised it every year since 2022. The size of each batch signals the state's mood toward games.</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -58967,7 +58967,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Generative AI in development: the enforcement turn</t>
+          <t>Developers are turning against generative AI</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -58982,17 +58982,17 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>EU; Global; JP</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Adoption keeps rising while sentiment collapses: 52% of surveyed game professionals now say generative AI is harming the industry, up from 30% the year before and 18% the year prior, with art and narrative roles most negative. Adoption is also moving below the studio's decision: in September 2026 Unity shipped a first-party agentic coding plugin with 29 built-in engine skills, so the question for a team using the engine moves from whether to adopt to whether to switch it off. Company-level use (52%) has decoupled from individual use (36%), and the argument has moved from opinion to enforcement. A European survey by Values Value and InGame Job, reported in September 2026, found the fear is pace before replacement: 61 percent expect generative AI to push them to work faster against 35 percent who fear for their role, and 35 percent of founders say they have already declined a hire because AI could do the work.</t>
+          <t>In the Game Developers Conference's yearly survey, 52% say generative AI is harming the industry, up from 18% two years earlier, though the 2026 survey asked a wider group than developers. The share who use it is 36%, unchanged from a year before, but that hides a split: 30% at game studios and 58% at the publishers and support firms around them. Steam has required developers to declare AI use since 2024, and Sulka Haro's count finds about one in three new releases does. Publishers have begun banning AI-made assets, and EU labeling rules apply from August 2026. Japan differs: 85.8% of developers there say they use it at work.</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Anti-AI clauses are now contract boilerplate, EU disclosure rules went live August 2, and players punish undisclosed AI at review-score speed. The conflict is being settled by lawyers and storefronts, not debate.</t>
+          <t>The share of developers who think generative AI harms the industry rose from 18% to 30% in a year, and a wider 2026 survey found 52%. The argument has moved from surveys into contracts, store rules and law.</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -59009,7 +59009,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>The rise of AI companions &amp; co-playable NPCs</t>
+          <t>AI teammates are reaching players in short tests</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -59024,17 +59024,17 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Global; JP; KR; US</t>
+          <t>Global; KR; US</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>LLM-driven characters have moved past dialogue into agency. Epic's Fortnite characters use AI voices licensed from consenting professional actors, while NVIDIA's ACE stack and KRAFTON's PUBG Ally put an on-device AI teammate that talks strategy, fetches items and revives you into a live shooter, with the same tooling opening to creators. Debate covers consent, live-speech moderation, child-facing risk, and disclosure.</t>
+          <t>An AI Darth Vader appeared in Fortnite in May 2025, was made to swear within hours, and drew a labor charge from the actors' union. In June 2026 Krafton put an AI squadmate into PUBG for a two-week test, and Epic has since given 36 Fortnite characters AI voices made with consenting actors. None is yet a permanent feature, and no company has said how many players used it. Quantic Foundry's survey found 83% of players opposed to AI-generated dialogue.</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>The first mass-market test of conversational AI inside play spaces heavily used by minors, landing in a community that now punishes undisclosed AI harder than AI itself. Safety, labor, and trust collide.</t>
+          <t>Game characters have always followed scripts. A new kind runs on chatbot technology: it listens, answers aloud and sometimes plays as a teammate. Several of the biggest companies are testing it, which raises questions about whose voice it uses and what it may say.</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -59051,7 +59051,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Who the AI agreement left out</t>
+          <t>Creative workers are fighting over AI consent and disclosure</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -59066,17 +59066,17 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>FR; PL; UK; US</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>SAG-AFTRA members ratified the 2025 Interactive Media Agreement, ending the nearly yearlong video game strike, with consent and disclosure requirements for digital-replica use plus pay increases.The live disputes now involve people the agreement never covered — non-union writers like Saber's Stella Sacco, streamers auto-enrolled in Amazon's AI training, modded voices, and now sports broadcasters: in September 2026 a commentator said EA had used generative AI to produce commentator voiceover in NHL 27, a category of voice the interactive agreement never reached. Studios deny AI use, get caught, and disclose late.</t>
+          <t>SAG-AFTRA's members ratified the 2025 Interactive Media Agreement in July 2025, with consent and disclosure rules for AI copies and a 15.17% pay rise. Since then a former Saber Interactive writer has said she was replaced with ChatGPT, which Saber denies, and Twitch has switched on AI training for all streamers' content by default. Several studios admitted AI use only after being caught. A voice actors' campaign group says 80% of voice work falls outside any union contract.</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>The question at hand is no longer consent on paper. Instead, it's disclosure, detection, and who's left outside the contract.</t>
+          <t>In 2025 US video game actors ended a strike of nearly a year with a contract requiring consent and disclosure before a studio uses an AI copy of a performer. Most arguments since involve people that contract does not cover, such as writers and streamers.</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -59093,7 +59093,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>App stores are unbundling under court supervision</t>
+          <t>Apple and Google are being forced to open their stores</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -59108,17 +59108,17 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>EU; JP; UK; US</t>
+          <t>EU; JP; KR; UK; US</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Courts are unwinding app-store control asymmetrically. Google, having lost on all counts, must carry rival stores inside Play/ Aptoide arrived in August, and a judge ordered install friction stripped within a week. Apple, having won most counts, is re-pricing rather than losing commissions: tiered external-link fees in the US, a flat 5% Core Technology Commission and a 15% steering fee replacing the EU's Core Technology Fee from 18 August 2026, terms eighteen developer groups including the EGDF rejected in September as a breach of the DMA's free-steering article. Enforcement is now continuous. Japan moved by statute rather than by court: the Mobile Software Competition Act took full effect on 18 December 2025, and Apple's Japan changes of the day before opened iOS to rival marketplaces and outside payments, with App Store commissions cut to 10% or 21%.</t>
+          <t>Google lost its US case outright and must carry rival stores inside its own. The first arrived in August 2026. Apple won most of its US case but was found in contempt in 2025 for getting around the one order it lost, and the Supreme Court will hear its appeal. Apple's new European terms start on 1 October 2026, and eighteen organizations say they still break the law. Few players have switched. Epic's Steve Allison says its mobile store is far short of its target.</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>he 30% cut shaped mobile game design for 15 years. Its replacement is a supervised patchwork of tiered fees — and gatekeeping has migrated from distribution to attestation.</t>
+          <t>Apple and Google long took up to 30% of spending in mobile games. Courts and lawmakers in the US, Europe, Japan and South Korea have ordered them to allow rival stores or outside payment, and both have answered with lower fees rather than none.</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -59135,7 +59135,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Streaming audiences split across platforms</t>
+          <t>Streamers are spreading across several platforms</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -59150,17 +59150,17 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>BR; Global; JP; KR; US</t>
+          <t>Global; KR</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Twitch is still the most-watched live-streaming platform, but it has been losing ground each year while its rivals grow. Most streamers now broadcast on several platforms at once, usually keeping Twitch as their main home. New viewers, though, tend to find them through short clips on TikTok and YouTube. The money is following: YouTube gaming creators now earn more per brand deal than Twitch streamers, so the platform with the most viewing is no longer the one that pays best.</t>
+          <t>Twitch is still the biggest platform for gaming streams, but across all live streaming YouTube Live and TikTok are now larger, and Twitch has lost ground each year. Streamers who broadcast on several platforms at once still spend most of their hours on Twitch. The money is moving too. YouTube gaming creators now earn more per brand deal than Twitch streamers, so the biggest gaming platform no longer pays best.</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Live-streaming viewers used to gather mostly on Twitch. Now they're spread across YouTube, TikTok, newer rivals like Kick, and local services in countries such as South Korea, and there's no sign they're coming back together. Any single platform now shows only part of the picture, and share charts can mislead, since platforms grow with different audiences.</t>
+          <t>Live-streaming viewers used to gather mostly on Twitch. Now they are spread across YouTube, TikTok, newer rivals such as Kick, and local services in countries like South Korea. Any one platform shows only part of the picture, and share charts can mislead.</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -59177,12 +59177,12 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Handheld PC resurgence</t>
+          <t>Handheld gaming PCs are losing momentum</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Emerging</t>
+          <t>Receding</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -59192,17 +59192,17 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>EU; Global; JP; US</t>
+          <t>Global; US</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Omdia forecasted 2.3 million PC gaming handhelds sold globally in 2025, up 32% from 1.7 million in 2024, boosted by Xbox-branded devices. Rival IDC data shows the category shrank in 2024 before recovering, volumes stay small next to consoles, and the Xbox-branded lift has since faded, with Steam Deck holding roughly half of shipments. Platform shift or niche remains the argument.</t>
+          <t>IDC's estimates, published by The Verge, have shipments peaking at 2.9 million in 2023 and falling by nearly half in 2024. A second firm, Omdia, counts differently and forecast growth for 2025. Nobody has published a figure since. In 2026 a memory chip shortage pushed the Steam Deck's price up by as much as $300 and left it out of stock for months. The firmer change is in software: Valve now lets other makers ship SteamOS, and Lenovo was the first to do so. Linux touched 5% of Steam users in March 2026 and was back under 4% by August, and most of those users are on desktop PCs.</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Handhelds are reshaping where PC play happens, and the firmer signal is software: SteamOS now ships beyond Valve hardware, and owners are re-flashing Windows devices themselves. Treat growth claims skeptically and cite whose numbers.</t>
+          <t>The Steam Deck showed in 2022 that PC games could run on a handheld the size of a Nintendo Switch, and Asus, Lenovo and others followed. Shipments peaked in 2023 and fell by nearly half in 2024, and nobody has published a count since.</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -59219,7 +59219,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Metaverse &amp; blockchain gaming hype</t>
+          <t>Investors are abandoning blockchain games</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -59239,12 +59239,12 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>The 2021 to 2022 wave of metaverse platforms and NFT/play-to-earn games has largely collapsed or rebranded. Matthew Ball's retrospective analysis groups web3 among growth engines that failed to deliver on their hype, leaving the industry stalled. Persistent worlds and UGC ideas have survived inside Roblox/Fortnite, but the token economics mostly did not. The exceptions are publisher-backed: Nexon's NEXPACE reported 30.98 million NXPC of first-half 2026 protocol revenue from MapleStory Universe, a running token economy inside a live IP.</t>
+          <t>Caladan's review of the sector estimates that investment in blockchain games fell from $4 billion in 2022 to about $0.36 billion in 2025, and cites a count finding 93% of more than 3,200 projects dead. DappRadar, which tracked the sector, closed in November 2025. The metaverse boom of the same years has shrunk too: Meta cut about 1,500 metaverse jobs in January 2026 and is turning Horizon Worlds into a phone app. The clearest exception is Nexon's MapleStory Universe, which reports a working token economy inside an established game.</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>You will hit mountains of 2021 to 2022 coverage presenting the metaverse as the future, but it's dated intel. The surviving ideas migrated to other places, games, and platforms.</t>
+          <t>In 2021 and 2022 blockchain games, where items trade for real money, were sold as the future of games, alongside the metaverse. Most of it failed. Confident coverage from those years is still online. Check the outcome before citing it.</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -59261,12 +59261,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Gaming is now cross-generational</t>
+          <t>Older players are a large audience the industry overlooks</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Emerging</t>
+          <t>Perennial</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -59276,17 +59276,17 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>DE; Global; JP; UK; US</t>
+          <t>DE; Global; UK; US</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>Play now spans generations: 212.3 million Americans play weekly, the average player age has risen to 37, half of Boomers play weekly, and over a third of adults 80+ play, with Boomer women out-playing Boomer men. Adults were always the core; what is new is the span at both ends. Earlier editions found most parent-players play with their kids. The unit of analysis is shifting from 'gamers' to households.</t>
+          <t>The ESA's 2026 survey puts the average US player at 37, and finds half of Boomers play weekly, women more than men. The ESA calls that a rise, but it printed the same 37 in 2011, its 29% share of players aged 50 and over is also what it printed in 2011, and its figures jumped in 2024 when it changed how it runs the survey. AARP's research counts 52.4 million American players over 50, most playing alone on a phone and feeling games are not made for them. In Germany the number of players over 60 rose from 6.4 million to 7.7 million in a year, on the trade body's count.</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>The youth-centric frame is obsolete, but a simple 'aging' frame is too. Co-play, generational span, and household spending are where audience research is heading.</t>
+          <t>The picture of a gamer as a teenage boy has long been wrong. Players aged 50 and over have been about a quarter of the American audience since 2006. They mostly play alone on a phone, and say games are not made for them.</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -59303,7 +59303,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Players fight for digital preservation</t>
+          <t>Campaigners are pressing to keep sold games playable</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -59318,17 +59318,17 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>EU; FR; Global; IT; UK; US</t>
+          <t>BR; EU; FR; Global; JP; UK; US</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>A long-running argument about whether buying a game confers ownership, reignited each time a publisher shuts down servers and renders a purchased title unplayable. Its most visible chapter, Stop Killing Games, gathered 1,294,188 verified signatures across 24 EU member states. On 16 June 2026 the Commission declined to propose a legal obligation, citing intellectual property constraints, offering a voluntary industry code of conduct instead; the campaign has pivoted to amending the Digital Fairness Act, due Q4 2026. The fight has since globalised into three tracks. Legislation: Brazil's PL 3612/2026 would mandate point-of-sale disclosure of server dependence, a two-year minimum support window, and a state preservation fund framed as digital cultural heritage. Litigation: UFC-Que Choisir is suing Ubisoft over The Crew, a Dutch class action targets the PlayStation Store, and in a US class action over the PlayStation Store’s “buy” button Sony argued in September 2026 that a reasonable consumer would not be misled into believing a digital purchase is owned — the first time the argument has been put on the record by a platform holder rather than inferred from a licence agreement. Archives: Japan mandates legal deposit yet bars access without rightsholder consent, pushing its Game Preservation Society to open a US office. Sony's 2028 disc cutoff has pulled the question mainstream. In September 2026 the argument reached the console itself: Xbox's Disc-to-Digital, which converts a disc into a digital licence, launched to Insiders with Sega, Square Enix, Ubisoft and Bandai Namco discs returning "not participating", while GOG began printing big-box artwork under its preservation programme.</t>
+          <t>No government yet requires it. The European Commission said in June 2026 that it cannot propose a legal duty to keep games playable, and offered talks on an industry code. The UK says its law will not change, and a California bill failed. Campaigners have moved to the courts: a French consumer group is suing Ubisoft over The Crew. Old games are a separate problem, about whether a game can still be bought, not whether it still runs. The Video Game History Foundation found 87% of US games released before 2010 can no longer be bought.</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>The clearest current test of what consumers believe they are buying, and a natural experiment in which legal systems convert organised player sentiment into binding rules. So far the answer is neither Brussels nor Washington, but civil-law jurisdictions using heritage framing and consumer litigation.</t>
+          <t>Many games need the publisher's servers to run, even when played alone. When the servers go off, the game stops working for everyone who paid for it. Players have organized against this, including a European petition with 1.29 million verified signatures.</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -59345,7 +59345,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Game labor is organizing</t>
+          <t>Game workers are winning union contracts</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -59360,17 +59360,17 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>CA; Nordics; UK; US</t>
+          <t>CA; EU; FR; Nordics; UK; US</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>Union drives hardened into institutions during the layoff era: 82% of US-based respondents to GDC's 2026 survey support unionisation, and one in four were laid off in the last two years. Microsoft's studios host the largest US unions and CWA's direct-join model now recruits across employers. Six European unions signed a cross-border action plan; France struck nationally. Nordic sectoral agreements remain the mature template. In September 2026 about 1,900 Blizzard workers ratified a CWA master contract with layoff recall rights, four extra weeks of severance and a duty on Microsoft to bargain over AI use, while the final tribunal hearing over Rockstar North's dismissal of union members opened in the UK, where the company confirmed it had kept an informant inside the union workers' Discord server for over two and a half years. Rockstar rejects the claims and says it will defend itself vigorously.</t>
+          <t>In September 2026 nearly 1,900 workers at Blizzard, which Microsoft owns, ratified their first union contracts, following a first contract at ZeniMax in 2025. Every US contract so far is at a studio Microsoft owns, and Microsoft had agreed not to campaign against union drives. The contracts give laid-off staff first call on new jobs and extra severance, and oblige the company to bargain over AI. In Britain, 31 union members dismissed by Rockstar argue at a tribunal that they were fired for organizing, which Rockstar denies. In the GDC's 2026 survey, 82% of US developers supported unions, but only about one in eight of all respondents belonged to one.</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Labor is becoming a durable counterparty on layoffs, AI disclosure, and crunch, with legal precedent now in play.</t>
+          <t>Most game developers long wanted a union, but almost none had one. Heavy layoffs changed that, and workers at some of the largest studios now have signed contracts. Employers and courts have not all gone along, so what unions can win is untested.</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -59387,7 +59387,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>The gaming culture war continues</t>
+          <t>Players are using review scores as a protest vote</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -59402,17 +59402,17 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Global; JP; UK; US</t>
+          <t>CN; Global; US</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>A recurring conflict over "politics in games," running from Gamergate through today. Peer-reviewed analysis finds critics perceive left-leaning "woke" perspectives as forced into games by an organized campaign, while opponents characterize the backlash as harassment. Japan's Assassin's Creed Shadows fight showed the same conflict refracted through national representation rather than US partisan lines. The current mutation is that the payload has moved from content to personnel: Slay the Spire 2 fell from "Overwhelmingly Positive" to "Mostly Negative" — roughly 65% of ~52,000 recent reviews — over a consultant credit, with nothing shipped. Platforms are responding by hiding the signal rather than policing it, and the tactic has proven politically portable, with anti-AI backlash using the same weapon.</t>
+          <t>In May 2026 Slay the Spire 2 was review-bombed after players noticed Anita Sarkeesian, a target of the 2014 Gamergate campaign, listed as a consultant. Nothing in the game had changed. Steam left the period out of the score, as it has done for such waves since 2019. Most large review bombs are not political: the biggest, against Helldivers 2 in 2024, was about an account requirement. Adam Ruch's study documents what the critics believe. Nobody measures how widely that view is held.</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Review scores, community sentiment, and marketing decisions are all contaminated by this topic — and the contamination now runs both ways, since a culture-war frame also makes ordinary criticism unspeakable, so the scores stop measuring the game at all.</t>
+          <t>A review bomb is a wave of negative user reviews that can sink a game's store rating in a day. Players use it as a protest vote, over prices, account rules and politics alike, so a review score may not be measuring the game.</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -59429,7 +59429,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Esports after the reckoning</t>
+          <t>Esports is running on Saudi money</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -59444,17 +59444,17 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>EU; Global; KR; MENA; US</t>
+          <t>EU; FR; Global; KR; MENA; US</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>The VC money is gone and the correction is over — this is the aftermath. What's left is a two-pillar economy: publisher-run circuits and Saudi-funded events (Esports World Cup, $75m prize pool, ~$20m distributed to 40 partner clubs). Global revenue is ~$5.34b and growing, but teams are the weakest link. Break-even is now a headline achievement, not a baseline: DRX is filing for a Singapore listing on the strength of $8.6m revenue and two consecutive break-even years. Franchising starts unwinding into open qualifiers in 2027. Streams Charts' read of EWC 2026's co-streams put India first by hours watched at 12.2 percent, the top three countries only 32 percent combined and English 30 percent of the language mix, before an audience 89 percent male and a third aged 20 to 24.</t>
+          <t>The Esports World Cup, funded by Saudi Arabia, has raised its prize money every year, to $75 million in 2026, and through its separate Club Partner Program pays 40 clubs a share of $20 million a year to promote it. Esports Charts calls Saudi capital the baseline funding source for the whole business. That carries risk: in 2026 the World Cup moved from Riyadh to Paris because of conflict in the region. Hours watched still grow. Teams are still cutting and selling cheap: Complexity was resold in 2024 for less than half its 2021 price, and Guild Esports closed in 2025. Both the boom coverage and the collapse coverage are out of date.</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Two traps. First, 2019-2021 "next NBA" content is worthless — but so is 2023-2024 "esports winter" content, which describes a collapse that already resolved. Second, sovereign capital is now the ecosystem's floor, which makes Gulf geopolitics a scheduling risk: the inaugural Esports Nations Cup just slipped a full year. Fans read consolidation and IPOs as founder exits, not growth.</t>
+          <t>Esports, organized competitive gaming for spectators, was sold to investors as the next sports league. By 2023 the money had run out, and teams cut staff or were sold for a fraction of old valuations. Most funding now comes from game makers and Saudi Arabia.</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -59471,12 +59471,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Games media captured by large corps</t>
+          <t>Games media is consolidating and shrinking</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Emerging</t>
+          <t>Dominant</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -59486,17 +59486,17 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>AU; BR; FR; Global; IN; MX; NL; TW; UK</t>
+          <t>AU; Global; UK; US</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Games outlets increasingly answer to parties with a direct stake in what they cover. Four owners — Ziff Davis, Fandom, Valnet, Future — hold most surviving English-language sites; publishers own the trade press. Dead and dying domains are bought for their residual search authority and refilled with AI-written casino and affiliate content. The prize has shifted from audience to citation: whoever owns the page owns what an AI says about a game. A worker-owned tier (Aftermath, Defector, Remap) is the only structurally independent alternative, at a fraction of the scale.</t>
+          <t>Ziff Davis owns IGN, Eurogamer and GamesIndustry.biz. Fandom owns GameSpot and Metacritic, Valnet owns Polygon and Game Rant, and Future owns PC Gamer and GamesRadar+. Press Engine's figures show the number of games journalists down 25% in two years. Jackson Ryan's investigation for Aftermath showed a marketing company buying a games site and filling it with casino articles under AI-generated bylines. The alternative so far is small reader-funded sites owned by their writers, such as Aftermath and Giant Bomb.</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Ownership now shapes what surfaces in AI answers, not just what gets published. Readers never see the masthead. Check who owns a source before citing it.</t>
+          <t>Most of what people read about games comes from a few websites, and most of the big ones have changed hands since 2022. Four companies now own the best-known names, and all four have cut staff. Check who owns a source before relying on it.</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -59513,7 +59513,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Studio investment in games plummets</t>
+          <t>Investors are pulling money out of studios</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -59533,12 +59533,12 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Big games cost more to make than ever, but outside investors are putting far less money into the studios that make them. Companies are still spending more on making games each year, but that spending is growing more slowly than revenue, and a growing share goes to outside contractors. Many studios are responding by making smaller games. The open question is whether that's a creative choice or simply what the budget allows.</t>
+          <t>Private investment in games companies fell from $12.0 billion in 2021 to $2.6 billion in 2025, on InvestGame's count. Matthew Ball's data, published while he was still an outside analyst, puts funding for studios down 85% since 2021. Companies still spend more on making games each year, but that spending grows more slowly than revenue, and a growing share goes to outside contractors. The move to smaller games looks mostly like having less money, not a new creative direction. A rebound in investment in 2026 has gone mostly to technology firms, not to studios.</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Over the next two years, expect many studios to say they're "focusing on smaller games." Analyst Matthew Ball's data suggests this is mostly about having less money, not a new creative direction. From the outside, both look the same.</t>
+          <t>Big games cost more to make than ever, but outside investors are putting far less money into the studios that make them. Many studios now say they are focusing on smaller games, and from the outside it is hard to tell choice from necessity.</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -59555,7 +59555,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Platforms bet on exclusivity again</t>
+          <t>Console makers are keeping games exclusive again</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -59570,17 +59570,17 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Global; JP; UK; US</t>
+          <t>Global; JP; US</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>After five years of dissolving platform walls, 2026 partly rebuilt them. Xbox, which had begun publishing on PlayStation and Nintendo, named Gears of War: E-Day and Clockwork Revolution as console exclusives that are not timed, while saying multiplayer and live-service titles stay multiplatform. Sony runs the mirror policy, multiplayer everywhere and single-player held back. Circana's Q1 2026 survey finds 41% of US players cite exclusives as their main reason for owning a console. The rebuilding is not one-directional. In September 2026 Kojima Productions said it had “unexpectedly received notice” from PlayStation that Physint, its Metal Gear successor, would be cancelled, and Xbox Game Studios took over publishing; reporting the following day attributed Sony's exit to budget overruns, missed deadlines, Death Stranding's revenue against expectations, and the fact that Physint was planned for PlayStation and PC rather than as a true exclusive. Read it as the limit of the policy: a platform holder will drop a marquee single-player project when the exclusivity it buys is partial and the budget is not.</t>
+          <t>In June 2026 Xbox named Gears of War: E-Day and Clockwork Revolution as permanent console exclusives, and said its multiplayer games will still be sold everywhere. Bloomberg's Jason Schreier reports that Sony's single-player games will stop coming to PC, which Sony has not announced. Circana's survey finds exclusives are still Americans' top reason for playing on a console, though fewer say so than a year ago. The change is narrow. Xbox has named only two games, and Halo, Forza Horizon 6 and Fable are all still headed to PlayStation 5.</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Cross-platform release had been read as a one-way ratchet. It is not, and the reversal is being argued on hardware economics rather than player demand: God of War Ragnarok drew about 300,000 PC players against 6.9 million on console.</t>
+          <t>For years the walls between consoles came down. Sony sold its biggest games on PC, and Microsoft put Xbox games on PlayStation. In 2026 Xbox named exclusives again, and Sony is reported to be doing the same, while multiplayer games still go everywhere.</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -59597,7 +59597,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Mobile has shifted from downloads to spending</t>
+          <t>Mobile games are struggling to find new players</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -59612,17 +59612,17 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>BR; CN; Global; IN; JP; KR; SEA; US</t>
+          <t>CN; Global; IN; US</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Mobile download growth has stopped while spending accelerates: downloads rose 0.8% year over year against a 10.6% rise in in-app purchases, and among the top ten markets only India and Pakistan grew downloads at all. Apps overtook games on mobile IAP revenue in 2025, $85.6B against $81.8B. Inside games, 4X strategy was the one genre adding both, up 5% on downloads and 5% on revenue in H1 2026 while mobile free-to-play downloads fell 12%, then turned in Q2, down 12% and 10% quarter on quarter.</t>
+          <t>Sensor Tower's figures show mobile game downloads falling from 57.6 billion in 2020 to 49.3 billion in 2024. Spending inside games peaked at $87.4 billion in 2021 and has stayed near $80 billion since. In the first half of 2026 both fell. Even the strongest genre, 4X strategy, turned down in mid-2026, according to Naavik's Max Abrahamsen. These figures count only Apple's and Google's stores, and Newzoo, which counts more widely, still expects mobile to grow in 2026.</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>The mobile question is no longer how many installs but what each installed player is worth, and the genre that answered it best is already cooling. Chinese publishers now hold most of the 4X top slots.</t>
+          <t>Mobile is the largest part of the games business, and it grew for years on rising downloads. That stopped in 2020. Advertising spending is rising while downloads fall, so each new player costs more to find.</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -59639,7 +59639,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Creators are how players find games</t>
+          <t>Steam's glut is making discovery the hard part</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -59654,17 +59654,17 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Global; US</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>Paid ads are reaching fewer players, and more people now find games through social media, streamers, and YouTubers. Developers now rate streamers as a better way to find players than paid advertising. Meanwhile, Steam releases far more games each year than it used to, so even good games launch to much smaller crowds. That has made free demos important: how many people play a demo is now the best early sign of how the full game will launch.</t>
+          <t>Steam released about 20,700 games in 2025, against about 7,000 in 2018, and almost half of 2025's releases drew fewer than ten user reviews. Developers say social media is their main way to find players, and they rate streamers above paid advertising. Because Steam releases far more games each year than it used to, even good games launch to much smaller crowds. That has made free demos important. How many people play a demo is now the best early sign of how the full game will launch.</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Making a game has gotten easier, and Steam, the store where most new PC games come out, now releases so many each year that the hard part is getting anyone to notice an individual title. The cheapest way to get noticed is a streamer or YouTuber choosing to play it, and money can't reliably buy that.</t>
+          <t>Making a game has become easier, and Steam, the main PC games store, now releases so many a year that the hard part is being noticed. A streamer playing a game is one way through, and Steam's own store is another.</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -59681,12 +59681,12 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Players keep playing old games</t>
+          <t>Old games take most of players' time</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Emerging</t>
+          <t>Perennial</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -59696,17 +59696,17 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Global; US</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Games no longer leave the market, so every new release competes with everything ever released. About one hour in seven on Steam goes to a game released that year, and that share has held steady for three years. Playtime is also concentrated: fewer than a hundred games account for 80% of it on each platform. That grip loosened slightly in 2025, though the time moving away from the biggest games isn't going to brand-new ones. Money follows the same pattern. Of everything Steam earned in the first eight months of 2026, the hundred best-selling new games made up about a sixth.</t>
+          <t>About one hour in seven on Steam goes to a game released that year. The share was 9%, 15% and 14% in the last three years. Playtime is also concentrated: fewer than a hundred games take 80% of it on each platform. That grip loosened slightly in 2025, but the time leaving the biggest games is not going to new ones. Of everything Steam earned in the first eight months of 2026, the hundred best-selling new games made up about a sixth.</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Most of the time people spend playing goes to games that have been out for years. A new game isn't just competing with other new games. It's competing with everything already installed, including older games now selling at a discount. This is why a publisher can report record earnings from its back catalog in the same quarter a new release disappoints. Those are the same fact seen twice.</t>
+          <t>Most time spent playing goes to games that have been out for years. A new game competes with everything already installed, including older games on discount. That is why a publisher can report record back-catalog earnings in the same quarter a new release disappoints.</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -59723,7 +59723,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>The rise of friendslop</t>
+          <t>Cheap co-op games are topping Steam's charts</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -59738,17 +59738,17 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Global; US</t>
+          <t>Global; JP</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Cheap co-op games built for friend groups and streamers took the top of the 2025 charts. R.E.P.O. and PEAK were two of the three best-selling new PC and console releases of the year by units alongside Battlefield 6, and at least five of the top twenty Steam releases were co-op, every one of which passed two million copies. PEAK was built in about four months by two small studios after a bet between their leads, and outsold both their previous games combined. Co-op took $4.1B on Steam in H1 2025, the genre's highest half-year on record.</t>
+          <t>R.E.P.O. and PEAK, at $7.99 each, were among Steam's best-selling new games of 2025. PEAK was built mostly in a month by seven people for under $200,000. The wave grew in 2026, and Chris Zukowski's count finds each new record crowd larger than the last. Players leave fast: AppMagic finds about 3% still playing after a month, and GameDiscoverCo's Simon Carless compares hits to lightning strikes. Copies are not revenue, and at these prices a chart-topper can sit well down the earnings table.</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>The clearest counter-case to budget-led thinking, and the industry is arguing about what to call it: an investor has publicly asked the trade to drop “friendslop” as a term that devalues the work.</t>
+          <t>Friendslop is players' slang for cheap, chaotic co-op games made to play with friends and watch on streams. They sell for $5 to $10, are made by small teams, and since 2025 have been among the best sellers on Steam, the main PC games store.</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -59765,7 +59765,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Live ops is becoming a playbook</t>
+          <t>Mobile live events are converging on one playbook</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -59785,12 +59785,12 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>Live operations — i.e., the events, offers, experiments and content cadence that keep a running game running — has hardened into a standing production function rather than a series of updates, and the practices are converging. Naavik's read of the top mobile puzzle titles finds Match-3, Merge and Blast games landing on the same event grammar: daily jackpots, hybrid competition-and-achievement weeklies, and endless album collections replacing finite two-month seasons. Their retention curves converge too, at roughly 25% D90-to-D1 and about 38 minutes a day.</t>
+          <t>Naavik's Harshal Karvande finds that the three main kinds of mobile puzzle game now run the same events: daily jackpots, contests against other players and endless sticker albums. AppMagic counted events launched by top games in 2025, and the monthly average rose from 73 to 89. Royal Match, a leading puzzle game, runs 14 recurring events a week. In 2026 the developer of Last War, a top strategy game, said the pace of spending had started to feel overwhelming.</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Distinct from the retreat from live-service business models: the model narrowed while the craft professionalised. Convergent playbooks also mean these games increasingly differ by theme rather than by shape.</t>
+          <t>Live ops means the events, offers and updates that keep a game earning after launch. Naavik's Harshal Karvande argues that in mobile puzzle games this work now matters more than the game underneath. The top games run the same few events.</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -59819,7 +59819,7 @@
   <dimension ref="A1:E111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -59856,7 +59856,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Games industry layoffs, 2023–present</t>
+          <t>Games companies are still cutting jobs</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -59879,7 +59879,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Games industry layoffs, 2023–present</t>
+          <t>Games companies are still cutting jobs</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -59902,7 +59902,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Games industry layoffs, 2023–present</t>
+          <t>Games companies are still cutting jobs</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -59925,12 +59925,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Fewer players, spending more</t>
+          <t>Rich markets are losing players, and growth has moved elsewhere</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Matthew Ball / Epyllion, industry report, May 2026</t>
+          <t>The State of Video Gaming in 2026 (Matthew Ball / Epyllion)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -59948,7 +59948,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Fewer players, spending more</t>
+          <t>Rich markets are losing players, and growth has moved elsewhere</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -59971,7 +59971,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Fewer players, spending more</t>
+          <t>Rich markets are losing players, and growth has moved elsewhere</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -59994,7 +59994,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Premium price ceiling</t>
+          <t>Game prices are stalling as hardware prices climb</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -60017,7 +60017,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Premium price ceiling</t>
+          <t>Game prices are stalling as hardware prices climb</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -60040,7 +60040,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Premium price ceiling</t>
+          <t>Game prices are stalling as hardware prices climb</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -60063,7 +60063,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Live-service retreat</t>
+          <t>Publishers are retreating from live-service games</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -60086,7 +60086,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Live-service retreat</t>
+          <t>Publishers are retreating from live-service games</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -60109,7 +60109,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Live-service retreat</t>
+          <t>Publishers are retreating from live-service games</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -60132,7 +60132,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Subscriptions stopped adding players</t>
+          <t>Game subscriptions are stalling</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -60155,7 +60155,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Subscriptions stopped adding players</t>
+          <t>Game subscriptions are stalling</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -60178,7 +60178,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Subscriptions stopped adding players</t>
+          <t>Game subscriptions are stalling</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -60201,7 +60201,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Creator platforms as sovereign economies</t>
+          <t>Roblox is rising and falling with its creators' hits</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -60224,7 +60224,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Creator platforms as sovereign economies</t>
+          <t>Roblox is rising and falling with its creators' hits</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -60247,7 +60247,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Creator platforms as sovereign economies</t>
+          <t>Roblox is rising and falling with its creators' hits</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -60270,7 +60270,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Age checks arrive by court order</t>
+          <t>Regulators are forcing child-safety changes on platforms</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -60293,7 +60293,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Age checks arrive by court order</t>
+          <t>Regulators are forcing child-safety changes on platforms</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -60316,7 +60316,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Age checks arrive by court order</t>
+          <t>Regulators are forcing child-safety changes on platforms</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -60339,7 +60339,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>India's real-money gaming ban</t>
+          <t>India has outlawed games played for money</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -60362,7 +60362,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>India's real-money gaming ban</t>
+          <t>India has outlawed games played for money</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -60385,7 +60385,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>India's real-money gaming ban</t>
+          <t>India has outlawed games played for money</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -60477,12 +60477,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Playtime caps come for games</t>
+          <t>Governments are weighing legal caps on children's playtime</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Tech Policy Press, policy tracker updated intermittently, Feb 2026</t>
+          <t>Tracking Efforts To Restrict Or Ban Teens from Social Media Across the Globe</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -60500,7 +60500,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Playtime caps come for games</t>
+          <t>Governments are weighing legal caps on children's playtime</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -60523,7 +60523,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Playtime caps come for games</t>
+          <t>Governments are weighing legal caps on children's playtime</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -60546,7 +60546,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Publishers split on gambling money in esports</t>
+          <t>Game publishers are opening esports to licensed bookmakers</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -60569,7 +60569,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Publishers split on gambling money in esports</t>
+          <t>Game publishers are opening esports to licensed bookmakers</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -60592,7 +60592,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Publishers split on gambling money in esports</t>
+          <t>Game publishers are opening esports to licensed bookmakers</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -60619,7 +60619,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Children's data, privacy &amp; the age-assurance bargain</t>
+          <t>Children's privacy rules are nudging games toward checking every player's age</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -60642,7 +60642,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Children's data, privacy &amp; the age-assurance bargain</t>
+          <t>Children's privacy rules are nudging games toward checking every player's age</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -60665,7 +60665,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Children's data, privacy &amp; the age-assurance bargain</t>
+          <t>Children's privacy rules are nudging games toward checking every player's age</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -60688,7 +60688,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Addiction &amp; screen-time discourse</t>
+          <t>Problem-gaming research is shifting from hours to compulsion</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -60711,7 +60711,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Addiction &amp; screen-time discourse</t>
+          <t>Problem-gaming research is shifting from hours to compulsion</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -60734,7 +60734,7 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Addiction &amp; screen-time discourse</t>
+          <t>Problem-gaming research is shifting from hours to compulsion</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -60757,7 +60757,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>China expands into premium games and IP</t>
+          <t>Chinese studios are trying to build premium global franchises</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -60780,7 +60780,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>China expands into premium games and IP</t>
+          <t>Chinese studios are trying to build premium global franchises</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -60803,7 +60803,7 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>China expands into premium games and IP</t>
+          <t>Chinese studios are trying to build premium global franchises</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -60830,12 +60830,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>The Gulf as the industry's biggest buyer</t>
+          <t>Saudi state money is buying major games companies</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Naavik, industry analysis, May 2026</t>
+          <t>Inside Saudi Arabia's $38 Billion Gaming Empire</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -60853,7 +60853,7 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>The Gulf as the industry's biggest buyer</t>
+          <t>Saudi state money is buying major games companies</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -60876,7 +60876,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>The Gulf as the industry's biggest buyer</t>
+          <t>Saudi state money is buying major games companies</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -60899,12 +60899,12 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Western publishers can't access Chinese growth</t>
+          <t>China's growth is going to Chinese-made games</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>The Game Business, interview/analysis, Feb 2026</t>
+          <t>The state of video games with Matthew Ball, Part One</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -60922,7 +60922,7 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Western publishers can't access Chinese growth</t>
+          <t>China's growth is going to Chinese-made games</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -60945,12 +60945,12 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>China throttles game approvals</t>
+          <t>China is using game approvals as a policy dial</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Niko Partners, analyst research note, Jan 2026</t>
+          <t>China's NPPA approved 1,771 video games in 2025</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -60968,7 +60968,7 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>China throttles game approvals</t>
+          <t>China is using game approvals as a policy dial</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -60991,7 +60991,7 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>China throttles game approvals</t>
+          <t>China is using game approvals as a policy dial</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -61014,7 +61014,7 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Generative AI in development: the enforcement turn</t>
+          <t>Developers are turning against generative AI</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -61037,7 +61037,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Generative AI in development: the enforcement turn</t>
+          <t>Developers are turning against generative AI</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -61060,7 +61060,7 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>Generative AI in development: the enforcement turn</t>
+          <t>Developers are turning against generative AI</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -61083,7 +61083,7 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>The rise of AI companions &amp; co-playable NPCs</t>
+          <t>AI teammates are reaching players in short tests</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -61106,7 +61106,7 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>The rise of AI companions &amp; co-playable NPCs</t>
+          <t>AI teammates are reaching players in short tests</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -61129,7 +61129,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>The rise of AI companions &amp; co-playable NPCs</t>
+          <t>AI teammates are reaching players in short tests</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -61156,7 +61156,7 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>Who the AI agreement left out</t>
+          <t>Creative workers are fighting over AI consent and disclosure</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -61179,7 +61179,7 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>Who the AI agreement left out</t>
+          <t>Creative workers are fighting over AI consent and disclosure</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -61202,7 +61202,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Who the AI agreement left out</t>
+          <t>Creative workers are fighting over AI consent and disclosure</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -61225,7 +61225,7 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>App stores are unbundling under court supervision</t>
+          <t>Apple and Google are being forced to open their stores</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -61248,7 +61248,7 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>App stores are unbundling under court supervision</t>
+          <t>Apple and Google are being forced to open their stores</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -61271,7 +61271,7 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>App stores are unbundling under court supervision</t>
+          <t>Apple and Google are being forced to open their stores</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -61294,7 +61294,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>Streaming audiences split across platforms</t>
+          <t>Streamers are spreading across several platforms</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -61317,7 +61317,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Streaming audiences split across platforms</t>
+          <t>Streamers are spreading across several platforms</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -61340,7 +61340,7 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>Streaming audiences split across platforms</t>
+          <t>Streamers are spreading across several platforms</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -61363,7 +61363,7 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>Handheld PC resurgence</t>
+          <t>Handheld gaming PCs are losing momentum</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -61386,7 +61386,7 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Handheld PC resurgence</t>
+          <t>Handheld gaming PCs are losing momentum</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -61409,7 +61409,7 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>Handheld PC resurgence</t>
+          <t>Handheld gaming PCs are losing momentum</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -61436,30 +61436,30 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>Metaverse &amp; blockchain gaming hype</t>
+          <t>Investors are abandoning blockchain games</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Matthew Ball / Epyllion, industry report, May 2026</t>
+          <t>$12 Billion In, 93% Dead: The Real Story of Web3 Gaming</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Analysis</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr"/>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>https://www.matthewball.co/all/presentation-the-state-of-video-gaming-in-2026</t>
+          <t>https://caladan.xyz/12-billion-in-93-percent-dead-web3-gaming/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>Metaverse &amp; blockchain gaming hype</t>
+          <t>Investors are abandoning blockchain games</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -61482,7 +61482,7 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>Metaverse &amp; blockchain gaming hype</t>
+          <t>Investors are abandoning blockchain games</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -61505,7 +61505,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>Gaming is now cross-generational</t>
+          <t>Older players are a large audience the industry overlooks</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -61528,7 +61528,7 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>Gaming is now cross-generational</t>
+          <t>Older players are a large audience the industry overlooks</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -61555,7 +61555,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>Gaming is now cross-generational</t>
+          <t>Older players are a large audience the industry overlooks</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -61578,7 +61578,7 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>Players fight for digital preservation</t>
+          <t>Campaigners are pressing to keep sold games playable</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -61601,7 +61601,7 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Players fight for digital preservation</t>
+          <t>Campaigners are pressing to keep sold games playable</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -61624,7 +61624,7 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>Players fight for digital preservation</t>
+          <t>Campaigners are pressing to keep sold games playable</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -61647,7 +61647,7 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>Game labor is organizing</t>
+          <t>Game workers are winning union contracts</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -61670,7 +61670,7 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>Game labor is organizing</t>
+          <t>Game workers are winning union contracts</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -61693,7 +61693,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>Game labor is organizing</t>
+          <t>Game workers are winning union contracts</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -61716,7 +61716,7 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>The gaming culture war continues</t>
+          <t>Players are using review scores as a protest vote</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -61739,7 +61739,7 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>The gaming culture war continues</t>
+          <t>Players are using review scores as a protest vote</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -61762,7 +61762,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>The gaming culture war continues</t>
+          <t>Players are using review scores as a protest vote</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -61785,7 +61785,7 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>Esports after the reckoning</t>
+          <t>Esports is running on Saudi money</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -61808,7 +61808,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>Esports after the reckoning</t>
+          <t>Esports is running on Saudi money</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -61831,7 +61831,7 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>Esports after the reckoning</t>
+          <t>Esports is running on Saudi money</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -61854,12 +61854,12 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>Games media captured by large corps</t>
+          <t>Games media is consolidating and shrinking</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Aftermath (Jackson Ryan), eight-month investigation, Mar 2026</t>
+          <t>The Secretive Company Filling Video Game Sites With Gambling And AI</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -61877,12 +61877,12 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>Games media captured by large corps</t>
+          <t>Games media is consolidating and shrinking</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>our Companies Control Your Favorite Gaming Media</t>
+          <t>Four Companies Control Your Favorite Gaming Media</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -61900,7 +61900,7 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>Games media captured by large corps</t>
+          <t>Games media is consolidating and shrinking</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -61923,7 +61923,7 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>Studio investment in games plummets</t>
+          <t>Investors are pulling money out of studios</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -61946,12 +61946,12 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>Studio investment in games plummets</t>
+          <t>Investors are pulling money out of studios</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>The state of video games with Matthew Ball – Part One</t>
+          <t>The state of video games with Matthew Ball, Part One</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -61969,7 +61969,7 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>Studio investment in games plummets</t>
+          <t>Investors are pulling money out of studios</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -61992,7 +61992,7 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Platforms bet on exclusivity again</t>
+          <t>Console makers are keeping games exclusive again</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -62015,7 +62015,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>Platforms bet on exclusivity again</t>
+          <t>Console makers are keeping games exclusive again</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -62038,7 +62038,7 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>Platforms bet on exclusivity again</t>
+          <t>Console makers are keeping games exclusive again</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -62061,7 +62061,7 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>Mobile has shifted from downloads to spending</t>
+          <t>Mobile games are struggling to find new players</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -62084,7 +62084,7 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>Mobile has shifted from downloads to spending</t>
+          <t>Mobile games are struggling to find new players</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -62107,7 +62107,7 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>Mobile has shifted from downloads to spending</t>
+          <t>Mobile games are struggling to find new players</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -62130,7 +62130,7 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>Creators are how players find games</t>
+          <t>Steam's glut is making discovery the hard part</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -62153,7 +62153,7 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>Creators are how players find games</t>
+          <t>Steam's glut is making discovery the hard part</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -62176,30 +62176,30 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>Creators are how players find games</t>
+          <t>Steam's glut is making discovery the hard part</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>H1 2026: 4X Strategy's UA Reckoning</t>
+          <t>How many games were released in 2025?</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Analysis</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr"/>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>https://naavik.co/f2p-mobile/h1-2026-4x-strategys-ua-reckoning/</t>
+          <t>https://howtomarketagame.com/2026/01/08/how-many-games-were-released-in-2025/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>Players keep playing old games</t>
+          <t>Old games take most of players' time</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -62222,7 +62222,7 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>Players keep playing old games</t>
+          <t>Old games take most of players' time</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -62245,7 +62245,7 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>Players keep playing old games</t>
+          <t>Old games take most of players' time</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -62268,7 +62268,7 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>The rise of friendslop</t>
+          <t>Cheap co-op games are topping Steam's charts</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -62291,7 +62291,7 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>The rise of friendslop</t>
+          <t>Cheap co-op games are topping Steam's charts</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -62314,7 +62314,7 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>The rise of friendslop</t>
+          <t>Cheap co-op games are topping Steam's charts</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -62337,7 +62337,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>Live ops is becoming a playbook</t>
+          <t>Mobile live events are converging on one playbook</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -62360,7 +62360,7 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>Live ops is becoming a playbook</t>
+          <t>Mobile live events are converging on one playbook</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -62383,7 +62383,7 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>Live ops is becoming a playbook</t>
+          <t>Mobile live events are converging on one playbook</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -71206,7 +71206,7 @@
       </c>
       <c r="D187" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -71219,12 +71219,12 @@
       <c r="B188" s="3" t="inlineStr"/>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>Emerging</t>
+          <t>Perennial</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -71237,12 +71237,12 @@
       <c r="B189" s="3" t="inlineStr"/>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>Perennial</t>
+          <t>Emerging</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -71260,7 +71260,7 @@
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>

--- a/games-research-starter-pack.xlsx
+++ b/games-research-starter-pack.xlsx
@@ -19,8 +19,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$R$924</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Trends'!$A$1:$H$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Trend reading'!$A$1:$E$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Trends'!$A$1:$H$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Trend reading'!$A$1:$E$114</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Platforms'!$A$1:$F$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Genres'!$A$1:$E$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Example games'!$A$1:$D$91</definedName>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -58195,7 +58195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -58982,7 +58982,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>EU; Global; JP</t>
+          <t>CN; EU; Global; JP</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -59024,7 +59024,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Global; KR; US</t>
+          <t>EU; Global; KR; US</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -59804,8 +59804,50 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Publishers are reviving dormant franchises instead of starting new ones</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Emerging</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Money &amp; business model</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Global; JP; KR; US</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Publishers are treating unused franchises as a balance-sheet asset. Capcom said in September 2026 that it is focusing on re-activating IPs it has not launched recently, after Onimusha: Way of the Sword sold a million copies on its first day. Blizzard is bringing StarCraft back as a shooter for 2030. Nintendo has dated a remake of a 1998 Zelda. Nexon has licensed its catalog to outside developers, and Nex Playground says every major publisher has asked about old Kinect and Wii games.</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Making a new game costs more and fails more often, so publishers are going back to franchises they already own and left alone for years. For players the schedule fills with familiar names, and a studio pitching something new has a harder sell.</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>GamesIndustry.biz, Video Games Chronicle, Gematsu, Inven Global, publisher investor days</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H38"/>
+  <autoFilter ref="A1:H39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -59816,7 +59858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -62403,8 +62445,77 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>Publishers are reviving dormant franchises instead of starting new ones</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>Capcom says it will focus on reviving dormant IPs after Onimusha: Way of the Sword breakout launch</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr"/>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gamesindustry.biz/capcom-says-it-will-focus-on-reviving-dormant-ips-after-onimusha-way-of-the-swords-breakout-launch</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>Publishers are reviving dormant franchises instead of starting new ones</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>"Every major publisher has approached us to review their old Kinect and Wii catalogue" - Nex Playground is spoilt for choice as its international rollout continues</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr"/>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gamesindustry.biz/every-major-publisher-has-approached-us-to-review-their-old-kinect-and-wii-catalogue-nex-playground-is-spoilt-for-choice-as-its-international-rollout-continues</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>Publishers are reviving dormant franchises instead of starting new ones</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>New StarCraft title to launch in 2030, will be an open-world FPS</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr"/>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gamesindustry.biz/new-starcraft-title-to-launch-in-2030-will-be-an-open-world-fps</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E111"/>
+  <autoFilter ref="A1:E114"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -71219,7 +71330,7 @@
       <c r="B188" s="3" t="inlineStr"/>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>Perennial</t>
+          <t>Emerging</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
@@ -71237,12 +71348,12 @@
       <c r="B189" s="3" t="inlineStr"/>
       <c r="C189" s="3" t="inlineStr">
         <is>
-          <t>Emerging</t>
+          <t>Perennial</t>
         </is>
       </c>
       <c r="D189" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -71278,7 +71389,7 @@
       </c>
       <c r="D191" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
     </row>

--- a/games-research-starter-pack.xlsx
+++ b/games-research-starter-pack.xlsx
@@ -59807,7 +59807,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Publishers are reviving dormant franchises instead of starting new ones</t>
+          <t>Publishers are reviving dormant franchises</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -59827,12 +59827,12 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>Publishers are treating unused franchises as a balance-sheet asset. Capcom said in September 2026 that it is focusing on re-activating IPs it has not launched recently, after Onimusha: Way of the Sword sold a million copies on its first day. Blizzard is bringing StarCraft back as a shooter for 2030. Nintendo has dated a remake of a 1998 Zelda. Nexon has licensed its catalog to outside developers, and Nex Playground says every major publisher has asked about old Kinect and Wii games.</t>
+          <t>Publishers are treating unused intellectual property, or IP, franchises they own but have not used in years, as an asset, while money for new studios thins, as the investment page shows. Capcom said in September 2026, after a million-copy launch day for Onimusha, that it is re-activating IPs it has not launched recently, alongside its new releases. Blizzard is bringing StarCraft back as a shooter for 2030, Nintendo has dated a remake of a 1998 Zelda, and Nexon has licensed its catalog to outside developers.</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Making a new game costs more and fails more often, so publishers are going back to franchises they already own and left alone for years. For players the schedule fills with familiar names, and a studio pitching something new has a harder sell.</t>
+          <t>Publishers are going back to franchises they own and left alone for years, beside their new releases rather than in place of them, and Capcom now says so in a plan for investors. For players the schedule fills with names they know.</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -62448,7 +62448,7 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>Publishers are reviving dormant franchises instead of starting new ones</t>
+          <t>Publishers are reviving dormant franchises</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -62471,46 +62471,46 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>Publishers are reviving dormant franchises instead of starting new ones</t>
+          <t>Publishers are reviving dormant franchises</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>"Every major publisher has approached us to review their old Kinect and Wii catalogue" - Nex Playground is spoilt for choice as its international rollout continues</t>
+          <t>Onimusha: Way of the Sword surpasses one million units on launch day; Capcom to focus on re-activating IPs</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Primary</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr"/>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>https://www.gamesindustry.biz/every-major-publisher-has-approached-us-to-review-their-old-kinect-and-wii-catalogue-nex-playground-is-spoilt-for-choice-as-its-international-rollout-continues</t>
+          <t>https://www.capcom.co.jp/ir/english/news/html/e260907.html</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>Publishers are reviving dormant franchises instead of starting new ones</t>
+          <t>Publishers are reviving dormant franchises</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>New StarCraft title to launch in 2030, will be an open-world FPS</t>
+          <t>Gamers spend twice as much on remakes as remasters</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr"/>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>https://www.gamesindustry.biz/new-starcraft-title-to-launch-in-2030-will-be-an-open-world-fps</t>
+          <t>https://www.ampereanalysis.com/insight/gamers-spend-twice-as-much-on-remakes-as-remasters</t>
         </is>
       </c>
     </row>

--- a/games-research-starter-pack.xlsx
+++ b/games-research-starter-pack.xlsx
@@ -474,7 +474,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Compiled from the research workbook of 2026-09-17. https://games.thisisdelightful.com</t>
+          <t>Last updated 2026-09-27. https://games.thisisdelightful.com</t>
         </is>
       </c>
     </row>

--- a/games-research-starter-pack.xlsx
+++ b/games-research-starter-pack.xlsx
@@ -474,7 +474,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Last updated 2026-09-27. https://games.thisisdelightful.com</t>
+          <t>Last updated 2026-09-28. https://games.thisisdelightful.com</t>
         </is>
       </c>
     </row>
@@ -15272,7 +15272,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>DE; EU; FR; IT; UK</t>
+          <t>EU; FR; IT; UK</t>
         </is>
       </c>
       <c r="H233" s="3" t="inlineStr">
@@ -68509,7 +68509,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>48</t>
         </is>
       </c>
     </row>
@@ -69023,7 +69023,7 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>48</t>
         </is>
       </c>
     </row>

--- a/games-research-starter-pack.xlsx
+++ b/games-research-starter-pack.xlsx
@@ -19,8 +19,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Sources'!$A$1:$R$937</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Trends'!$A$1:$H$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Trend reading'!$A$1:$E$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Trends'!$A$1:$L$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Trend reading'!$A$1:$F$114</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Platforms'!$A$1:$F$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Genres'!$A$1:$E$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Example games'!$A$1:$D$91</definedName>
@@ -528,7 +528,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>The trends currently moving the industry. One row per trend.</t>
+          <t>The trends currently moving the industry, each with its place on the Three Horizons. One row per trend.</t>
         </is>
       </c>
     </row>
@@ -59015,56 +59015,80 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="56" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="56" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
+          <t>slug</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>horizon</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>horizon_group</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>horizon_line</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>markets</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>what_it_is</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>why_it_matters</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>where_to_follow</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>as_of</t>
         </is>
@@ -59073,40 +59097,56 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
+          <t>industry-layoff-era</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
           <t>Games companies are still cutting jobs</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Dominant</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Money &amp; business model</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>The clearest symptom of the pandemic-era model unwinding.</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Global; US</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>No official body counts games layoffs, but two public trackers do: Amir Satvat's and Farhan Noor's. Layoffs dipped in 2025 and rose again in 2026, so the dip was a low point, not an ending. Check the date on any claim that layoffs are slowing before repeating it. For scale, the ESA counts 82,930 people directly employed in US games in 2025. Global estimates vary and cannot be compared across countries.</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Games companies hired heavily during the pandemic, then began cutting jobs in 2023 as demand cooled and borrowing got more expensive. The cuts sit behind most of the industry's business, labor and creative stories since, so they are background for almost everything else here.</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>Game Developer's business desk, GDC State of the Game Industry (annual), Satvat's layoff tracker, Farhan Noor's videogamelayoffs.com tracker, GamesIndustry.biz</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -59115,40 +59155,56 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>monetization-on-flat-player-base</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
           <t>Rich markets are losing players, and growth has moved elsewhere</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Dominant</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Money &amp; business model</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>The Western growth engine this system was built on has stalled.</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>CA; CN; DE; FR; Global; IT; JP; KR; UK; US</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Matthew Ball, then an outside analyst and since May 2026 an Xbox executive, argues the industry's growth engines are spent. Worldwide revenue is at a record, but the share of people who play is shrinking across most of the developed world, and the eight rich markets spent less in 2025 than in 2021. Publishers there are trying to earn more from the players who remain. In the US, the largest market, spending fell sharply in mid-2026, worst for console hardware even as console prices rose. The job cuts that came with this are on the layoffs page.</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>The games industry posts record revenue while studios lay off staff. The facts fit together. In most rich countries fewer people play and spending is below its 2021 peak. The record comes from China and the rest of the world.</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Matthew Ball / Epyllion annual State of Video Gaming, The Game Business (Christopher Dring), Circana (Mat Piscatella), Newzoo</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -59157,40 +59213,56 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>premium-price-ceiling</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
           <t>Game prices are stalling as hardware prices climb</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Dominant</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Money &amp; business model</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>The premium console bundle is squeezed from both sides.</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>EU; Global; JP; UK; US</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Nintendo's Mario Kart World reached $80 in 2025. Microsoft announced $80 games and backed down within three months. Grand Theft Auto 6, due in November 2026, is priced at $79.99, which ended speculation about a $100 game. Sony, Microsoft and Nintendo all raised console prices in 2025 and 2026, blaming memory chip costs, tariffs and the wider economy. Circana counted 39% fewer consoles sold in the US in July 2026 than a year earlier, at an average selling price of $542.</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>The price of a big new game has moved only once, from $70 to $80, and only for a handful of titles. Console prices have kept rising, and Americans are buying fewer consoles. The two prices a player pays have gone separate ways.</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>GamesRadar and Eurogamer business coverage, Circana US sales data, Ars Technica gaming desk</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -59199,40 +59271,56 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>live-service-retreat</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
           <t>Publishers are retreating from live-service games</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Dominant</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Money &amp; business model</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>The flagship bet of this system, now failing more often than it hits.</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>CN; Global; KR</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>Sony told investors in 2022 it would have twelve live-service games by March 2026. Reporters count eight canceled or withdrawn, a tally Sony has never confirmed. The pullback is wider than Sony. Warner Bros. wrote off $200 million on Suicide Squad, Ubisoft closed XDefiant along with two studios, and EA switched off Anthem. In 2026 a new shooter called Highguard closed after 45 days, and Amazon announced its exit from online role-playing games. None of these companies says it is leaving live service. Newzoo's 2026 market report found most established hits flat or down in the first half of the year, without giving figures.</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Live-service games are updated for years and earn money the whole time, like Fortnite. A hit can pay for a decade, so every big publisher wanted one. Many attempts have failed, and the failures decide which studios close and which games never get made.</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>Game Developer post-mortems, Circana engagement data, publisher earnings calls (Sony, EA, Take-Two)</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -59241,40 +59329,60 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
+          <t>subscription-plateau</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
           <t>Game subscriptions are stalling</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Money &amp; business model</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>stalled-bets</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>The one-fee-for-everything bet. Subscribers stalled well short of plan, and prices rose instead.</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Global; US</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>Xbox Game Pass is reported to have about 30 million paying subscribers, far below the 77 million Microsoft's internal plan projected for this point. A steep price rise in late 2025 drove people away, and Microsoft partly reversed it in 2026. Sony has stopped publishing PlayStation Plus numbers. Companies are now trimming what subscribers get. From November 2026, Xbox limits how much cloud streaming each tier includes and sells extra hours separately.</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>For a decade the industry bet that games would follow TV and music into one monthly fee for a big library, and that bet drove huge acquisitions. Subscriber numbers have since stalled well short of company plans, and prices have gone up instead.</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>The Verge Xbox coverage, WSJ tech desk, Circana subscription spending data, Microsoft earnings</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -59283,40 +59391,56 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
+          <t>creator-platforms-as-sovereign-economies</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
           <t>Roblox is rising and falling with its creators' hits</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Money &amp; business model</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>h3</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Players as producers. Volatile, but pointing the right way.</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Global; US</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>Roblox's accounts show payouts to creators growing from $112 million in 2019 to $1.5 billion in 2025, faster than player spending. The money is very unevenly spread. Roblox says its top 1,000 creators averaged $1.3 million in 2025, while the typical paid creator earned about $1,500 in the twelve months to June 2026. In mid-2026 Roblox withdrew its annual forecast after the viral games of 2025 faded. In September 2026 it said creators can release games as standalone apps and be paid in real currency every business day.</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>Roblox makes no games. Its users build them and are paid in a currency they can exchange for dollars. In 2026 that economy had its first downturn, and it showed the risk of depending on hits made by people Roblox does not employ.</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>Roblox quarterly earnings and annual reports, Game Developer, Naavik deep dives, Matthew Ball</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -59325,40 +59449,60 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>child-safety-enforcement-in-game-platforms</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
           <t>Regulators are forcing child-safety changes on platforms</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Dominant</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Regulation, safety &amp; age</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>rewriting-rules</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Forces identity and safety infrastructure onto open, player-built platforms.</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>AU; BR; EU; Global; MENA; RU; TR; UK; US</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>Roblox faces 182 lawsuits before one US federal judge, suits from several states, and since August 2026 a Senate investigation. Roblox disputes the claims. In Australia it has made a court-enforceable promise to limit adults' contact with children and accept an outside audit. A Texas order requires age checks on Discord, and Brazil made Discord switch off livestreaming. Blocks are the blunter tool, and they do not always last. Russia lifted its block on Roblox after six months.</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>Platforms where children play and chat, such as Roblox and Discord, spent years facing lawsuits and bad headlines over child safety. Governments are now ordering specific changes, some with deadlines attached. For players, the most visible result is being asked to prove their age.</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>eSafety Commissioner (AU), Ofcom Online Safety Act updates (UK), state AG press offices, The Guardian tech desk, Roblox's safety blog and earnings calls</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -59367,40 +59511,60 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t>indias-real-money-gaming-ban</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
           <t>India has outlawed games played for money</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Dominant</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Regulation, safety &amp; age</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>rewriting-rules</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>A natural experiment: regulation can delete a whole category overnight.</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>The law took effect on 1 May 2026, but operators closed their paid games within days of its passage in August 2025, as banks and payment companies cut them off. Dream11 said 95% of its revenue had gone, and Games24x7 laid off about 70% of its staff. The operators' challenge to the law is before the Supreme Court. Lumikai estimates that one in three players moved to offshore sites, a figure its own reporters treat as soft.</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>India had a large, fast-growing market for online games played for money, such as fantasy cricket and rummy. In August 2025 parliament banned them all. It is a rare test of what happens when a government removes a whole category of games.</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>Reuters India tech desk, MediaNama, AGB (Asia Gaming Brief), Indian Supreme Court proceedings</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -59409,40 +59573,56 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
+          <t>the-loot-box-age-gate</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
           <t>Regulators are age-gating loot boxes</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Perennial</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Regulation, safety &amp; age</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>perennial</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>A recurring regulatory cycle that follows monetization wherever it goes.</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>AU; BE; BR; DE; ES; EU; Global; JP; KR; NL; PL; UK; US</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>Brazil banned loot boxes in games children can reach in March 2026, and Belgium has treated them as gambling since 2018. South Korea requires the odds to be published, and in the first study of the law 84% of top-earning games with loot boxes did so. Australia rates such games M at minimum. From June 2026 PEGI rates new ones 16 across most of Europe, while Germany rates case by case through its own body. The Netherlands ruled in 2022 that loot boxes are not gambling, and the UK and Japan rely on the industry's own rules. So the same game carries different ratings, and different obligations, depending on where it is sold.</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>Loot boxes are paid items with random contents. Some countries ban them, some make publishers show the odds, and some say they are not gambling. Age ratings are the approach that is spreading, and publishers now change or withdraw games market by market.</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>Leon Y. Xiao's annual 'Loot Box State of Play' papers, Gaming Law Review, PEGI/ESRB notices, national regulators (Belgian Gaming Commission, Kansspelautoriteit)</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -59451,40 +59631,56 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>playtime-caps-and-age-gates-for-minors</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
           <t>Governments are weighing legal caps on children's playtime</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Perennial</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Regulation, safety &amp; age</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>perennial</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Comes back every time a new worry about children and screens arrives.</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>CN; EU; IN; JP; KR; US; VN</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>China allows under-18s three hours of online games a week, and Vietnam three hours a day across one company's games. South Korea repealed its midnight curfew in 2021. In 2026 the US House passed a bill requiring a parental timer, and the European Commission proposed time-management tools, but neither sets an hour limit or is law. On whether caps work, the largest study found no drop in heavy play after China's first rule but could not separate children from adults, while a later survey found children playing less.</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>Only China and Vietnam cap children's playtime by law, checking every player's identity to enforce it. Elsewhere the idea has become advice or parental tools. The US and EU are now drafting rules, so whether caps work now matters, and the evidence is split.</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>Niko Partners China/SEA research, TechNode, AGB, national regulator announcements (NPPA, Vietnam MIC); see also the age-checks row for verification mechanics</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -59493,40 +59689,60 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
+          <t>publishers-split-on-gambling-money-in-esports</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
           <t>Game publishers are opening esports to licensed bookmakers</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Perennial</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Regulation, safety &amp; age</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>prolongs-h1</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Publishers choosing which betting money keeps their leagues alive.</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>BR; EU; Global; US</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>In June 2025 Riot Games allowed betting companies to sponsor top League of Legends and Valorant teams, with logos kept off its own broadcasts. In December 2025 Valve barred sites that gamble with Counter-Strike's tradeable cosmetic items, known as skins, from jerseys and broadcasts. Valve still allows licensed bookmakers, so the two are closer than they look. Riot's rule keeps betting logos off jerseys, yet the bookmaker Winamax says its logo sits at the center of two teams' shirts. Esports Charts counts a betting brand as title sponsor of nine of the top ten Counter-Strike teams in the Americas. Nobody publishes how much esports income is gambling money.</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>Professional gaming teams have few ways to earn money, and betting companies are among the few sponsors still willing to pay. The companies that make the games decide which sponsors are allowed, and in 2025 the two most important ones moved in apparently opposite directions.</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>Esports Charts sponsorship analyses, HLTV Counter-Strike business coverage, Esports Legal News, SportBusiness</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -59535,40 +59751,56 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t>childrens-data-privacy-and-the-age-assurance-bargain</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Children's privacy rules are nudging games toward checking every player's age</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Perennial</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Regulation, safety &amp; age</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>perennial</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>The paradox that keeps returning: less data about children means more checks on everyone.</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
         <is>
           <t>EU; UK; US</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>The US rewrote its children's privacy rule in 2025, with compliance due by April 2026. It does not require age checks, but in February 2026 the Federal Trade Commission said it would not punish data collected only to check age. Roblox now asks anyone who wants to chat for a face scan or an ID, a step it took under the safety pressure covered on the child-safety page, not because a privacy law required it. The UK still accepts a stated age where risk is low, and the EU's guidelines are voluntary. Privacy groups object, and the first leaks have already happened.</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>Laws protecting children's data limit what games offer young players. Applying them means knowing who is a child, and the surest checks are a face scan or an ID. So rules meant to collect less data are nudging platforms toward collecting more, from everyone.</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>FTC press releases and enforcement actions, IAPP coverage, ICO (UK), law-firm COPPA trackers</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -59577,40 +59809,56 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
+          <t>addiction-and-screen-time-discourse</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
           <t>Problem-gaming research is shifting from hours to compulsion</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Perennial</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Regulation, safety &amp; age</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>perennial</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>A long-running debate whose unit of measure is finally changing.</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>CN; Global; JP; KR; UK; US</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>A 2025 study in JAMA followed 4,285 American children and tied suicidal behavior to compulsive use, not total screen time, with a weaker link for games than for social media and phones. The World Health Organization calls gaming disorder a diagnosis, while American psychiatry says it needs more study. More than 100 US lawsuits argue that games were designed to be addictive. How common it is remains unsettled, and the authors of the best-known estimate, about 3% of people, say such figures are inflated.</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>Whether too much play is an illness, a parenting problem or a product defect depends on where you are. The newest research says hours played is the wrong measure, and that matters because nearly every rule written so far measures hours.</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>Journal of Behavioral Addictions, BMC Psychiatry, Oxford Internet Institute (Przybylski), KOCCA white papers for the Korean framing</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -59619,40 +59867,60 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>chinas-original-ip-franchise-build-out</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
           <t>Chinese studios are trying to build premium global franchises</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Geography &amp; power</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>prolongs-h1</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>New studios betting on the big-budget model, and meeting its costs.</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>CN; Global</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>Black Myth: Wukong, a 2024 action game based on a Chinese legend, proved a Chinese studio could make a global big-budget hit. Its developer, Game Science, is following it with Black Myth: Zhong Kui, built on a different figure from Chinese folklore. S-GAME, Everstone (working with NetEase) and miHoYo are building original worlds of their own. Everstone's Where Winds Meet reached a worldwide audience in late 2025, though as a free-to-play game. Games are now part of China's 15th Five-Year Plan, its national economic roadmap. For games sold up front, the evidence so far is one franchise. China's console market grew 55% in 2024 and 86% in 2025, to 8.36 billion yuan, on the official industry report's count, then fell 7% in the first half of 2026 as Wukong's sales faded.</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>China's games industry is known for free-to-play mobile games, while big-budget games bought up front came mostly from Japan, the US and Europe. Chinese studios now make them too. Studios say rising costs are the first real limit on that growth.</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>Rest of World China tech desk, Niko Partners, SCMP tech coverage, Naavik</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -59661,40 +59929,60 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>gulf-capital-and-the-leveraged-ea-buyout</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
           <t>Saudi state money is buying major games companies</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Dominant</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Geography &amp; power</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>prolongs-h1</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Patron capital extends the old model rather than changing it, and the debt makes it more fragile.</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>CN; Global; JP; KR; MENA; US</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>The Public Investment Fund owns 93.4% of EA, with two smaller partners, and holds it separately from Savvy Games Group, its own games company. EA has told lenders it will cut $700 million a year in costs. Bloomberg reports the fund is weighing a merger of the two, which nobody has confirmed. Naavik's Miikka Ahonen thinks the buying is nearly done, because the money Savvy committed is largely spent. Hard figures on whether the purchases pay their way are thin.</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>Since 2022 Saudi Arabia's sovereign wealth fund has bought across the games business, and in August 2026 it completed the purchase of Electronic Arts. Much of the price was borrowed, and EA now carries the debt.</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>Naavik, SportBusiness esports desk, Reuters M&amp;A coverage, Esports Insider</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -59703,40 +59991,56 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>growth-without-western-access</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
           <t>China's growth is going to Chinese-made games</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Geography &amp; power</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr"/>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>The growth moved to a market Western publishers can barely reach.</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>CN; Global</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>The games industry earned about $10 billion more in 2025 than in 2021. According to analyst Matthew Ball's analysis, made when he was an outside analyst, before he became Xbox's chief strategy officer in May 2026, about $4 billion of that came from China, and another $1.5 billion from Chinese-made games sold abroad. Inside China, Chinese-made games take about 83% of revenue by the official industry report's 2025 count. Niko Partners puts China's 2025 game revenue at $51.8 billion, over $50 billion for the first time, and expects $53.9 billion in 2026.</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>When people say the games industry is growing, much of that growth is in China, and most of it goes to Chinese-made games. What matters is the gap between where spending is growing and where Western publishers can actually make money.</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>The Game Business (Dring), Matthew Ball / Epyllion, Niko Partners, Newzoo regional reports</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -59745,40 +60049,56 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
+          <t>chinas-banhao-throttles-games</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
           <t>China is using game approvals as a policy dial</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Perennial</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Geography &amp; power</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>perennial</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>A standing lever the state turns up and down.</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
         <is>
           <t>CN</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>China approved 1,676 domestic games in 2025, up from 468 in the freeze year of 2022, and Niko Partners expects 2026 to pass 2,000 licenses in all. Approvals stopped for nine months in 2018 and for eight months from August 2021, and about 14,000 small studios and related firms closed that year. Foreign games come through a thinner channel: 95 were approved in 2025. What follows approval, identity checks and limits on children's play, is on the playtime-caps page.</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>Every game published in China needs a government license called a banhao (版号). China cut the number it issued sharply in 2018 and 2021, and has raised it every year since 2022. The size of each batch signals the state's mood toward games.</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>Niko Partners' monthly approval trackers, TechNode, Digital Policy Alert, SCMP</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -59787,40 +60107,60 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t>generative-ai-in-development-the-enforcement-turn</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
           <t>Developers are turning against generative AI</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Dominant</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>rewriting-rules</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Contested. It slows careless adoption and steers AI toward consented, disclosed uses.</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>CN; EU; Global; JP</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>In the Game Developers Conference's yearly survey, 52% say generative AI is harming the industry, up from 18% two years earlier, though the 2026 survey asked a wider group than developers. The share who use it is 36%, unchanged from a year before, but that hides a split: 30% at game studios and 58% at the publishers and support firms around them. Steam has required developers to declare AI use since 2024, and Sulka Haro's count finds about one in three new releases does. Publishers have begun banning AI-made assets, and EU labeling rules apply from August 2026. Japan differs: 85.8% of developers there say they use it at work.</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>The share of developers who think generative AI harms the industry rose from 18% to 30% in a year, and a wider 2026 survey found 52%. The argument has moved from surveys into contracts, store rules and law.</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>GDC State of the Game Industry (annual), Game Developer, Wired gaming/AI coverage, a16z Games (for the pro-adoption view)</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -59829,40 +60169,60 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
+          <t>the-rise-of-ai-companions-and-co-playable-npcs</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
           <t>AI teammates are reaching players in short tests</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>prolongs-h1</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Tested inside Fortnite and PUBG, where it fills a team. Nothing is a permanent feature yet.</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>EU; Global; KR; US</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>An AI Darth Vader appeared in Fortnite in May 2025, was made to swear within hours, and drew a labor charge from the actors' union. In June 2026 Krafton put an AI squadmate into PUBG for a two-week test, and Epic has since given 36 Fortnite characters AI voices made with consenting actors. None is yet a permanent feature, and no company has said how many players used it. Quantic Foundry's survey found 83% of players opposed to AI-generated dialogue.</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>Game characters have always followed scripts. A new kind runs on chatbot technology: it listens, answers aloud and sometimes plays as a teammate. Several of the biggest companies are testing it, which raises questions about whose voice it uses and what it may say.</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>VGC and The Verge AI-in-games coverage, Epic's Creator ecosystem announcements, Inworld/ElevenLabs product news, Kotaku (critical coverage)</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -59871,40 +60231,60 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
+          <t>ai-disclosure-fights-and-unprotected-creative-labor</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
           <t>Creative workers are fighting over AI consent and disclosure</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>rewriting-rules</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Writes the rules any AI-native future will have to follow.</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>FR; PL; UK; US</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>SAG-AFTRA's members ratified the 2025 Interactive Media Agreement in July 2025, with consent and disclosure rules for AI copies and a 15.17% pay rise. Since then a former Saber Interactive writer has said she was replaced with ChatGPT, which Saber denies, and Twitch has switched on AI training for all streamers' content by default. Several studios admitted AI use only after being caught. A voice actors' campaign group says 80% of voice work falls outside any union contract.</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>In 2025 US video game actors ended a strike of nearly a year with a contract requiring consent and disclosure before a studio uses an AI copy of a performer. Most arguments since involve people that contract does not cover, such as writers and streamers.</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>SAG-AFTRA's interactive media page, Deadline/Variety labor desks, Game Developer labor coverage</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -59913,40 +60293,60 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
+          <t>app-store-unbundling-under-court-supervision</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
           <t>Apple and Google are being forced to open their stores</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Dominant</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Platform &amp; distribution</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>rewriting-rules</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Six years of lawsuits have cut the platform tax by a few points. So far Apple and Google are containing the rest.</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>EU; JP; KR; UK; US</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>Google lost its US case outright and must carry rival stores inside its own. The first arrived in August 2026. Apple won most of its US case but was found in contempt in 2025 for getting around the one order it lost, and the Supreme Court will hear its appeal. Apple's new European terms start on 1 October 2026, and eighteen organizations say they still break the law. Few players have switched. Epic's Steve Allison says its mobile store is far short of its target.</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>Apple and Google long took up to 30% of spending in mobile games. Courts and lawmakers in the US, Europe, Japan and South Korea have ordered them to allow rival stores or outside payment, and both have answered with lower fees rather than none.</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>The Verge policy desk, MacRumors legal coverage, mobilegamer.biz, European Commission DMA enforcement updates, Japan Fair Trade Commission MSCA enforcement</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -59955,40 +60355,60 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
+          <t>streaming-fragmentation-and-the-multi-homed-creator</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
           <t>Streamers are spreading across several platforms</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Dominant</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Platform &amp; distribution</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>makes-room</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Discovery follows creators, wherever they are.</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>Global; KR</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>Twitch is still the biggest platform for gaming streams, but across all live streaming YouTube Live and TikTok are now larger, and Twitch has lost ground each year. Streamers who broadcast on several platforms at once still spend most of their hours on Twitch. The money is moving too. YouTube gaming creators now earn more per brand deal than Twitch streamers, so the biggest gaming platform no longer pays best.</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>Live-streaming viewers used to gather mostly on Twitch. Now they are spread across YouTube, TikTok, newer rivals such as Kick, and local services in countries like South Korea. Any one platform shows only part of the picture, and share charts can mislead.</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>Stream Hatchet quarterly and annual reports, Streams Charts, Netinfluencer, Bloomberg's creator-economy coverage</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="L23" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -59997,40 +60417,60 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
+          <t>handheld-pc-resurgence</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
           <t>Handheld gaming PCs are losing momentum</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Receding</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Platform &amp; distribution</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>stalled-bets</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>A real form factor that plateaued. SteamOS may still carry the idea forward.</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>Global; US</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>IDC's estimates, published by The Verge, have shipments peaking at 2.9 million in 2023 and falling by nearly half in 2024. A second firm, Omdia, counts differently and forecast growth for 2025. Nobody has published a figure since. In 2026 a memory chip shortage pushed the Steam Deck's price up by as much as $300 and left it out of stock for months. The firmer change is in software: Valve now lets other makers ship SteamOS, and Lenovo was the first to do so. Linux touched 5% of Steam users in March 2026 and was back under 4% by August, and most of those users are on desktop PCs.</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>The Steam Deck showed in 2022 that PC games could run on a handheld the size of a Nintendo Switch, and Asus, Lenovo and others followed. Shipments peaked in 2023 and fell by nearly half in 2024, and nobody has published a count since.</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr">
         <is>
           <t>Omdia games research, The Verge hardware desk, Circana (Piscatella), Valve Steam Hardware Survey</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="L24" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -60039,40 +60479,60 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
+          <t>metaverse-and-blockchain-gaming-hype</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
           <t>Investors are abandoning blockchain games</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Receding</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Platform &amp; distribution</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>stalled-bets</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>The transition that never delivered. Worth keeping as a cautionary pattern.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>Caladan's review of the sector estimates that investment in blockchain games fell from $4 billion in 2022 to about $0.36 billion in 2025, and cites a count finding 93% of more than 3,200 projects dead. DappRadar, which tracked the sector, closed in November 2025. The metaverse boom of the same years has shrunk too: Meta cut about 1,500 metaverse jobs in January 2026 and is turning Horizon Worlds into a phone app. The clearest exception is Nexon's MapleStory Universe, which reports a working token economy inside an established game.</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>In 2021 and 2022 blockchain games, where items trade for real money, were sold as the future of games, alongside the metaverse. Most of it failed. Confident coverage from those years is still online. Check the outcome before citing it.</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>Matthew Ball (who wrote the book and the post-mortems), Naavik, Digiday's Gaming Advertising coverage for brand-metaverse residue</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="L25" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -60081,40 +60541,56 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
+          <t>multigenerational-play-and-the-household-question</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
           <t>Older players are a large audience the industry overlooks</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Perennial</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Culture &amp; audience</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>perennial</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>The biggest overlooked audience. They still pay full price for single-player games, and most play alone.</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>DE; Global; UK; US</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>The ESA's 2026 survey puts the average US player at 37, and finds half of Boomers play weekly, women more than men. The ESA calls that a rise, but it printed the same 37 in 2011, its 29% share of players aged 50 and over is also what it printed in 2011, and its figures jumped in 2024 when it changed how it runs the survey. AARP's research counts 52.4 million American players over 50, most playing alone on a phone and feeling games are not made for them. In Germany the number of players over 60 rose from 6.4 million to 7.7 million in a year, on the trade body's count.</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>The picture of a gamer as a teenage boy has long been wrong. Players aged 50 and over have been about a quarter of the American audience since 2006. They mostly play alone on a phone, and say games are not made for them.</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>ESA Essential Facts (annual), Circana demographics, VGM/GWI audience panels, Pew Research internet &amp; tech</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -60123,40 +60599,56 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
+          <t>game-preservation-and-digital-ownership</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
           <t>Campaigners are pressing to keep sold games playable</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Perennial</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Culture &amp; audience</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>perennial</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Ownership pressure on live service, and a value the next model can adopt.</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>BR; EU; FR; Global; JP; UK; US</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>No government yet requires it. The European Commission said in June 2026 that it cannot propose a legal duty to keep games playable, and offered talks on an industry code. The UK says its law will not change, and a California bill failed. Campaigners have moved to the courts: a French consumer group is suing Ubisoft over The Crew. Old games are a separate problem, about whether a game can still be bought, not whether it still runs. The Video Game History Foundation found 87% of US games released before 2010 can no longer be bought.</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>Many games need the publisher's servers to run, even when played alone. When the servers go off, the game stops working for everyone who paid for it. Players have organized against this, including a European petition with 1.29 million verified signatures.</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>European Citizens' Initiative register, stopkillinggames.com, r/StopKillingGames, Bellular News (YouTube), Digital Fairness Act consultations, UFC-Que Choisir, Video Games Europe statements</t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="L27" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -60165,40 +60657,60 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
+          <t>organized-game-labor</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
           <t>Game workers are winning union contracts</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Dominant</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Culture &amp; audience</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>rewriting-rules</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Contracts now set terms for layoffs and AI inside big studios. Small teams and creators are outside them.</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>CA; EU; FR; Nordics; UK; US</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>In September 2026 nearly 1,900 workers at Blizzard, which Microsoft owns, ratified their first union contracts, following a first contract at ZeniMax in 2025. Every US contract so far is at a studio Microsoft owns, and Microsoft had agreed not to campaign against union drives. The contracts give laid-off staff first call on new jobs and extra severance, and oblige the company to bargain over AI. In Britain, 31 union members dismissed by Rockstar argue at a tribunal that they were fired for organizing, which Rockstar denies. In the GDC's 2026 survey, 82% of US developers supported unions, but only about one in eight of all respondents belonged to one.</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr">
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>Most game developers long wanted a union, but almost none had one. Heavy layoffs changed that, and workers at some of the largest studios now have signed contracts. Employers and courts have not all gone along, so what unions can win is untested.</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="K28" s="3" t="inlineStr">
         <is>
           <t>Game Workers of America / CWA announcements, Game Developer labor desk, GDC State of the Game Industry, IGDA</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="L28" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -60207,40 +60719,56 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
+          <t>culture-war-discourse-and-the-weaponized-review-score</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
           <t>Players are using review scores as a protest vote</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>Perennial</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Culture &amp; audience</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>perennial</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Players' standing veto, and it applies across every horizon.</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>CN; Global; US</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>In May 2026 Slay the Spire 2 was review-bombed after players noticed Anita Sarkeesian, a target of the 2014 Gamergate campaign, listed as a consultant. Nothing in the game had changed. Steam left the period out of the score, as it has done for such waves since 2019. Most large review bombs are not political: the biggest, against Helldivers 2 in 2024, was about an account requirement. Adam Ruch's study documents what the critics believe. Nobody measures how widely that view is held.</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>A review bomb is a wave of negative user reviews that can sink a game's store rating in a day. Players use it as a protest vote, over prices, account rules and politics alike, so a review score may not be measuring the game.</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
         <is>
           <t>IJoC and Games &amp; Culture (scholarly), Aftermath and 404 Media (critical journalism), Wired culture desk, SteamDB review-anomaly data</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="L29" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -60249,40 +60777,60 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
+          <t>esports-after-the-reckoning</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
           <t>Esports is running on Saudi money</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>Receding</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Culture &amp; audience</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>stalled-bets</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>A transition that stalled, kept alive by a patron.</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>EU; FR; Global; KR; MENA; US</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>The Esports World Cup, funded by Saudi Arabia, has raised its prize money every year, to $75 million in 2026, and through its separate Club Partner Program pays 40 clubs a share of $20 million a year to promote it. Esports Charts calls Saudi capital the baseline funding source for the whole business. That carries risk: in 2026 the World Cup moved from Riyadh to Paris because of conflict in the region. Hours watched still grow. Teams are still cutting and selling cheap: Complexity was resold in 2024 for less than half its 2021 price, and Guild Esports closed in 2025. Both the boom coverage and the collapse coverage are out of date.</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>Esports, organized competitive gaming for spectators, was sold to investors as the next sports league. By 2023 the money had run out, and teams cut staff or were sold for a fraction of old valuations. Most funding now comes from game makers and Saudi Arabia.</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="K30" s="3" t="inlineStr">
         <is>
           <t>SportBusiness, Esports Insider, Sports Business Journal esports desk, Esports Charts viewership data</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="L30" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -60291,40 +60839,56 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
+          <t>games-media-capture</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
           <t>Games media is consolidating and shrinking</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Dominant</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Culture &amp; audience</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>The old coverage and discovery layer is hollowing out.</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>AU; Global; UK; US</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>Ziff Davis owns IGN, Eurogamer and GamesIndustry.biz. Fandom owns GameSpot and Metacritic, Valnet owns Polygon and Game Rant, and Future owns PC Gamer and GamesRadar+. Press Engine's figures show the number of games journalists down 25% in two years. Jackson Ryan's investigation for Aftermath showed a marketing company buying a games site and filling it with casino articles under AI-generated bylines. The alternative so far is small reader-funded sites owned by their writers, such as Aftermath and Giant Bomb.</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>Most of what people read about games comes from a few websites, and most of the big ones have changed hands since 2022. Four companies now own the best-known names, and all four have cut staff. Check who owns a source before relying on it.</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>Aftermath, Press Gazette (media business beat), Game File, local trade-body statements, WHOIS/company filings for suspect domains</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="L31" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -60333,40 +60897,56 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
+          <t>studio-investment-in-games-plummets</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
           <t>Investors are pulling money out of studios</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>Dominant</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Money &amp; business model</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr"/>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Capital is leaving the old model before a new one is proven.</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>Private investment in games companies fell from $12.0 billion in 2021 to $2.6 billion in 2025, on InvestGame's count. Matthew Ball's data, published while he was still an outside analyst, puts funding for studios down 85% since 2021. Companies still spend more on making games each year, but that spending grows more slowly than revenue, and a growing share goes to outside contractors. The move to smaller games looks mostly like having less money, not a new creative direction. A rebound in investment in 2026 has gone mostly to technology firms, not to studios.</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>Big games cost more to make than ever, but outside investors are putting far less money into the studios that make them. Many studios now say they are focusing on smaller games, and from the outside it is hard to tell choice from necessity.</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="K32" s="3" t="inlineStr">
         <is>
           <t>Matthew Ball / Epyllion annual State of Video Gaming, The Game Business (Christopher Dring), Game Developer's business desk, GameDiscoverCo</t>
         </is>
       </c>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="L32" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -60375,40 +60955,60 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
+          <t>platforms-bet-on-exclusivity-again</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
           <t>Console makers are keeping games exclusive again</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Platform &amp; distribution</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>prolongs-h1</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Platform holders reaching back for an old lever.</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>Global; JP; US</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>In June 2026 Xbox named Gears of War: E-Day and Clockwork Revolution as permanent console exclusives, and said its multiplayer games will still be sold everywhere. Bloomberg's Jason Schreier reports that Sony's single-player games will stop coming to PC, which Sony has not announced. Circana's survey finds exclusives are still Americans' top reason for playing on a console, though fewer say so than a year ago. The change is narrow. Xbox has named only two games, and Halo, Forza Horizon 6 and Fable are all still headed to PlayStation 5.</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>For years the walls between consoles came down. Sony sold its biggest games on PC, and Microsoft put Xbox games on PlayStation. In 2026 Xbox named exclusives again, and Sony is reported to be doing the same, while multiplayer games still go everywhere.</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="K33" s="3" t="inlineStr">
         <is>
           <t>The Game Business (Christopher Dring), Game File (Stephen Totilo), Video Games Chronicle, Circana consumer surveys</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="L33" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -60417,40 +61017,56 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
+          <t>mobile-has-shifted-from-downloads-to-spending</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
           <t>Mobile games are struggling to find new players</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>Dominant</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Money &amp; business model</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>h1</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr"/>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Paying to acquire players is hitting diminishing returns.</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>CN; Global; IN; US</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>Sensor Tower's figures show mobile game downloads falling from 57.6 billion in 2020 to 49.3 billion in 2024. Spending inside games peaked at $87.4 billion in 2021 and has stayed near $80 billion since. In the first half of 2026 both fell. Even the strongest genre, 4X strategy, turned down in mid-2026, according to Naavik's Max Abrahamsen. These figures count only Apple's and Google's stores, and Newzoo, which counts more widely, still expects mobile to grow in 2026.</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr">
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>Mobile is the largest part of the games business, and it grew for years on rising downloads. That stopped in 2020. Advertising spending is rising while downloads fall, so each new player costs more to find.</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="K34" s="3" t="inlineStr">
         <is>
           <t>Sensor Tower State of Mobile (annual), Naavik, Deconstructor of Fun, PocketGamer.biz monthly charts, AppMagic</t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="L34" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -60459,40 +61075,60 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
+          <t>creators-are-how-players-find-games</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
           <t>Steam's glut is making discovery the hard part</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>Dominant</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Platform &amp; distribution</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>makes-room</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Abundance shifts power from making games to getting them found.</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>Global</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
         <is>
           <t>Steam released about 20,700 games in 2025, against about 7,000 in 2018, and almost half of 2025's releases drew fewer than ten user reviews. Developers say social media is their main way to find players, and they rate streamers above paid advertising. Because Steam releases far more games each year than it used to, even good games launch to much smaller crowds. That has made free demos important. How many people play a demo is now the best early sign of how the full game will launch.</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>Making a game has become easier, and Steam, the main PC games store, now releases so many a year that the hard part is being noticed. A streamer playing a game is one way through, and Steam's own store is another.</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="K35" s="3" t="inlineStr">
         <is>
           <t>GameDiscoverCo (Simon Carless), Naavik, GDC State of the Game Industry (annual), Gamalytic, SteamDB</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="L35" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -60501,40 +61137,56 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
+          <t>new-games-fight-for-playtime</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
           <t>Old games take most of players' time</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>Perennial</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Platform &amp; distribution</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>perennial</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>The structural fact the current system fights and the next one designs around.</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>Global; US</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="I36" s="3" t="inlineStr">
         <is>
           <t>About one hour in seven on Steam goes to a game released that year. The share was 9%, 15% and 14% in the last three years. Playtime is also concentrated: fewer than a hundred games take 80% of it on each platform. That grip loosened slightly in 2025, but the time leaving the biggest games is not going to new ones. Of everything Steam earned in the first eight months of 2026, the hundred best-selling new games made up about a sixth.</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>Most time spent playing goes to games that have been out for years. A new game competes with everything already installed, including older games on discount. That is why a publisher can report record back-catalog earnings in the same quarter a new release disappoints.</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr">
+      <c r="K36" s="3" t="inlineStr">
         <is>
           <t>Newzoo PC and Console Gaming Report (annual), GameDiscoverCo, Circana Player Engagement Tracker, Valve's Steam Replay</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="L36" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -60543,40 +61195,56 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
+          <t>the-rise-of-friendslop</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
           <t>Cheap co-op games are topping Steam's charts</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Culture &amp; audience</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>h3</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Small teams, low prices, social play, built to be watched. The clearest prototype of what comes next.</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>Global; JP</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="I37" s="3" t="inlineStr">
         <is>
           <t>R.E.P.O. and PEAK, at $7.99 each, were among Steam's best-selling new games of 2025. PEAK was built mostly in a month by seven people for under $200,000. The wave grew in 2026, and Chris Zukowski's count finds each new record crowd larger than the last. Players leave fast: AppMagic finds about 3% still playing after a month, and GameDiscoverCo's Simon Carless compares hits to lightning strikes. Copies are not revenue, and at these prices a chart-topper can sit well down the earnings table.</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>Friendslop is players' slang for cheap, chaotic co-op games made to play with friends and watch on streams. They sell for $5 to $10, are made by small teams, and since 2025 have been among the best sellers on Steam, the main PC games store.</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="K37" s="3" t="inlineStr">
         <is>
           <t>GameDiscoverCo's annual PC and console sales roundups, Game Developer's design desk, PC Gamer, AppMagic retention studies</t>
         </is>
       </c>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="L37" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -60585,40 +61253,60 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
+          <t>live-ops-is-becoming-a-playbook</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
           <t>Mobile live events are converging on one playbook</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Money &amp; business model</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>prolongs-h1</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Optimizing the existing model, not inventing a new one.</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>Global; US</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="I38" s="3" t="inlineStr">
         <is>
           <t>Naavik's Harshal Karvande finds that the three main kinds of mobile puzzle game now run the same events: daily jackpots, contests against other players and endless sticker albums. AppMagic counted events launched by top games in 2025, and the monthly average rose from 73 to 89. Royal Match, a leading puzzle game, runs 14 recurring events a week. In 2026 the developer of Last War, a top strategy game, said the pace of spending had started to feel overwhelming.</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="J38" s="3" t="inlineStr">
         <is>
           <t>Live ops means the events, offers and updates that keep a game earning after launch. Naavik's Harshal Karvande argues that in mobile puzzle games this work now matters more than the game underneath. The top games run the same few events.</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="K38" s="3" t="inlineStr">
         <is>
           <t>Naavik, Deconstructor of Fun, PocketGamer.biz, GDC live ops talks, Game Developer's production desk</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="L38" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
@@ -60627,47 +61315,67 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
+          <t>dormant-ip-revival</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
           <t>Publishers are reviving dormant franchises</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>Emerging</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Money &amp; business model</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>h2</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>prolongs-h1</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Risk minimization: familiar names in place of new bets.</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
         <is>
           <t>DE; Global; JP; KR; US</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="I39" s="3" t="inlineStr">
         <is>
           <t>Publishers are treating unused intellectual property, or IP, franchises they own but have not used in years, as an asset, while money for new studios thins, as the investment page shows. Capcom said in September 2026, after a million-copy launch day for Onimusha, that it is re-activating IPs it has not launched recently, alongside its new releases. Blizzard is bringing StarCraft back as a shooter for 2030, Nintendo has dated a remake of a 1998 Zelda, and Nexon has licensed its catalog to outside developers.</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="J39" s="3" t="inlineStr">
         <is>
           <t>Publishers are going back to franchises they own and left alone for years, beside their new releases rather than in place of them, and Capcom now says so in a plan for investors. For players the schedule fills with names they know.</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="K39" s="3" t="inlineStr">
         <is>
           <t>GamesIndustry.biz, Video Games Chronicle, Gematsu, Inven Global, publisher investor days</t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="L39" s="3" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H39"/>
+  <autoFilter ref="A1:L39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -60678,38 +61386,44 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E114"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
+          <t>trend_slug</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
           <t>trend</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>format</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>link</t>
         </is>
@@ -60718,21 +61432,26 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
+          <t>industry-layoff-era</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
           <t>Games companies are still cutting jobs</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Data points to slowing layoffs, but doesn't capture true harm to game industry</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr"/>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>https://www.gamedeveloper.com/business/industry-layoffs-are-seemingly-slowing-but-the-damage-has-already-been-done</t>
         </is>
@@ -60741,21 +61460,26 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>industry-layoff-era</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
           <t>Games companies are still cutting jobs</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>GDC 2026 State of the Game Industry Reveals Impact of Layoffs</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>https://gdconf.com/article/gdc-2026-state-of-the-game-industry-reveals-impact-of-layoffs-generative-ai-and-more/</t>
         </is>
@@ -60764,21 +61488,26 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>industry-layoff-era</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
           <t>Games companies are still cutting jobs</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Amir Satvat: Layoffs in the Gaming Industry in 2026</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>https://gamedevreports.substack.com/p/amir-satvat-layoffs-in-the-gaming</t>
         </is>
@@ -60787,21 +61516,26 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>monetization-on-flat-player-base</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
           <t>Rich markets are losing players, and growth has moved elsewhere</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>The State of Video Gaming in 2026 (Matthew Ball / Epyllion)</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>https://www.matthewball.co/all/presentation-the-state-of-video-gaming-in-2026</t>
         </is>
@@ -60810,21 +61544,26 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
+          <t>monetization-on-flat-player-base</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
           <t>Rich markets are losing players, and growth has moved elsewhere</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Roblox chose retention over short-term spend</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>https://www.pcgamer.com/games/roblox-shares-plummet-by-70-percent-after-the-company-reports-persistent-decline-in-player-numbers-and-of-course-the-solution-involves-ai/</t>
         </is>
@@ -60833,21 +61572,26 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
+          <t>monetization-on-flat-player-base</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
           <t>Rich markets are losing players, and growth has moved elsewhere</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>What is a monetization scheme you actually support?</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Community</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>https://www.reddit.com/r/pcgaming/comments/1vqka44/what_is_a_monetization_scheme_you_actually_support/</t>
         </is>
@@ -60856,21 +61600,26 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>premium-price-ceiling</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
           <t>Game prices are stalling as hardware prices climb</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Nintendo exec says Mario Kart World justifies its shock $80 price</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>https://www.gamesradar.com/games/racing/amid-switch-2-price-backlash-nintendo-exec-says-mario-kart-world-justifies-its-shock-usd80-price-because-its-probably-the-richest-mario-kart-experience-fans-will-have-ever-had/</t>
         </is>
@@ -60879,21 +61628,26 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t>premium-price-ceiling</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
           <t>Game prices are stalling as hardware prices climb</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Grand Theft Auto 6's $80 price settles the $100 question</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>https://www.gamedeveloper.com/console/grand-theft-auto-6-s-80-price-settles-the-100-question</t>
         </is>
@@ -60902,21 +61656,26 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
+          <t>premium-price-ceiling</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
           <t>Game prices are stalling as hardware prices climb</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>How a surge in memory prices will affect the games industry</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr"/>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>https://www.gamedeveloper.com/business/how-a-surge-in-memory-prices-will-affect-the-games-industry</t>
         </is>
@@ -60925,21 +61684,26 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>live-service-retreat</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
           <t>Publishers are retreating from live-service games</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Sony will continue to develop live services despite failures</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>https://www.pcgamer.com/gaming-industry/sony-games-boss-says-company-will-bravely-keep-sending-live-services-over-the-top-despite-cancelling-8-of-the-12-ones-planned-for-2025-and-wiping-out-most-of-destiny-2s-developers/</t>
         </is>
@@ -60948,21 +61712,26 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
+          <t>live-service-retreat</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
           <t>Publishers are retreating from live-service games</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Newzoo: Most established live-service and evergreen titles were flat or down year over year in H1 2026</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr"/>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>https://www.gamesindustry.biz/newzoo-most-established-live-service-and-evergreen-titles-were-flat-or-down-year-over-year-in-h1-2026</t>
         </is>
@@ -60971,21 +61740,26 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t>live-service-retreat</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Publishers are retreating from live-service games</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Sega cancelled its "risky" Super Game project</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr"/>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>https://www.gamesindustry.biz/sega-cancelled-its-risky-super-game-project-as-it-would-have-to-grow-enormously-to-match-the-scale-of-the-service</t>
         </is>
@@ -60994,21 +61768,26 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
+          <t>subscription-plateau</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
           <t>Game subscriptions are stalling</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Microsoft's Game Pass performance is far below expectations</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr"/>
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>https://www.wsj.com/tech/microsoft-layoffs-xbox-59e7f6df</t>
         </is>
@@ -61017,21 +61796,26 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>subscription-plateau</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
           <t>Game subscriptions are stalling</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Subscriptions are the only growing segment, but barely, inside a market down 21%</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr"/>
+      <c r="F15" s="3" t="inlineStr">
         <is>
           <t>https://gamedevreports.substack.com/p/circana-the-us-video-game-market</t>
         </is>
@@ -61040,21 +61824,26 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>subscription-plateau</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
           <t>Game subscriptions are stalling</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>More than 40% of people cancelling Xbox Game Pass, PlayStation Plus and Nintendo Switch Online subscriptions blame rising costs</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr"/>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr"/>
+      <c r="F16" s="3" t="inlineStr">
         <is>
           <t>https://www.eurogamer.net/xbox-game-pass-playstation-plus-nintendo-cancellations-rising-costs</t>
         </is>
@@ -61063,21 +61852,26 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>creator-platforms-as-sovereign-economies</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
           <t>Roblox is rising and falling with its creators' hits</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Roblox loses $70 billion in value as company blames lack of viral games</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr">
         <is>
           <t>https://www.dexerto.com/roblox/roblox-loses-70-billion-in-value-as-company-blames-lack-of-viral-games-3395064/</t>
         </is>
@@ -61086,21 +61880,26 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
+          <t>creator-platforms-as-sovereign-economies</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
           <t>Roblox is rising and falling with its creators' hits</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Annual Roblox Economic Impact Report</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Primary</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr"/>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>https://about.roblox.com/newsroom/2025/09/roblox-annual-economic-impact-report</t>
         </is>
@@ -61109,21 +61908,26 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t>creator-platforms-as-sovereign-economies</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
           <t>Roblox is rising and falling with its creators' hits</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Roblox says it'll help developers release their games as standalone apps across PC, mobile, and consoles</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr"/>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>https://www.tubefilter.com/2026/09/11/roblox-developers-conference-2026-game-apps-creator-payouts-roblox-wallet-roblox-card/</t>
         </is>
@@ -61132,21 +61936,26 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
+          <t>child-safety-enforcement-in-game-platforms</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
           <t>Regulators are forcing child-safety changes on platforms</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>eSafety secures court-enforceable undertaking from Roblox</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Primary</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>https://www.esafety.gov.au/newsroom/media-releases/esafety-secures-court-enforceable-undertaking-from-roblox-to-do-more-to-protect-australian-kids-from-grooming-and-sexual-exploitation</t>
         </is>
@@ -61155,21 +61964,26 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
+          <t>child-safety-enforcement-in-game-platforms</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
           <t>Regulators are forcing child-safety changes on platforms</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Australians must now prove their age to buy R18+ games</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>https://www.pcgamer.com/gaming-industry/australians-must-now-prove-their-age-to-buy-r18-games-on-the-xbox-store/</t>
         </is>
@@ -61178,21 +61992,26 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
+          <t>child-safety-enforcement-in-game-platforms</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
           <t>Regulators are forcing child-safety changes on platforms</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Steam implements age verification for R18+ games in Australia, credit card required</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr"/>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr"/>
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>https://thisweekinvideogames.com/news/steam-implements-age-verification-for-r18-games-in-australia-credit-card-required/</t>
         </is>
@@ -61201,21 +62020,26 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
+          <t>indias-real-money-gaming-ban</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
           <t>India has outlawed games played for money</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>India bans real-money gaming, threatening a $23 billion industry</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>https://techcrunch.com/2025/08/20/india-bans-real-money-gaming-threatening-a-23-billion-industry</t>
         </is>
@@ -61224,21 +62048,26 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
+          <t>indias-real-money-gaming-ban</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
           <t>India has outlawed games played for money</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Challenge to the Promotion and Regulation of Online Gaming Act, 2025</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr"/>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>https://www.scobserver.in/cases/challenge-to-the-promotion-and-regulation-of-online-gaming-act-2025/</t>
         </is>
@@ -61247,21 +62076,26 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
+          <t>indias-real-money-gaming-ban</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
           <t>India has outlawed games played for money</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>CCI Closes Winzo's Google Antitrust Case After Money Gaming Ban</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>https://respawn.outlookindia.com/gaming/gaming-news/cci-closes-winzos-google-antitrust-case-after-money-gaming-ban</t>
         </is>
@@ -61270,21 +62104,26 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
+          <t>the-loot-box-age-gate</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
           <t>Regulators are age-gating loot boxes</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>All games with loot boxes in them will be rated minimum PEGI 16, starting this summer</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr"/>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>https://www.videogameschronicle.com/news/all-games-with-loot-boxes-in-them-will-be-rated-minimum-pegi-16-starting-this-summer/</t>
         </is>
@@ -61293,21 +62132,26 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
+          <t>the-loot-box-age-gate</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
           <t>Regulators are age-gating loot boxes</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>South Korea's loot box law shows strong results, but players still left in the dark</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>https://techxplore.com/news/2025-09-south-korea-loot-law-strong.html</t>
         </is>
@@ -61316,21 +62160,26 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
+          <t>the-loot-box-age-gate</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
           <t>Regulators are age-gating loot boxes</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>TIL, in Brazil, most gacha games are +18 due to the loot box mechanic</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Community</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr"/>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr"/>
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>https://x.com/genshinmains_/status/2091189145381323092</t>
         </is>
@@ -61339,21 +62188,26 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
+          <t>playtime-caps-and-age-gates-for-minors</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
           <t>Governments are weighing legal caps on children's playtime</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>Tracking Efforts To Restrict Or Ban Teens from Social Media Across the Globe</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>https://www.techpolicy.press/tracking-efforts-to-restrict-or-ban-teens-from-social-media-across-the-globe/</t>
         </is>
@@ -61362,21 +62216,26 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
+          <t>playtime-caps-and-age-gates-for-minors</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
           <t>Governments are weighing legal caps on children's playtime</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>No evidence that Chinese playtime mandates reduced heavy gaming</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr"/>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr"/>
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>https://www.nature.com/articles/s41562-023-01669-8</t>
         </is>
@@ -61385,21 +62244,26 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
+          <t>playtime-caps-and-age-gates-for-minors</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
           <t>Governments are weighing legal caps on children's playtime</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Age verification = Digital ID</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>Community</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr"/>
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>https://www.reddit.com/r/playstation/comments/1vtgdzh/age_verification_digital_id/</t>
         </is>
@@ -61408,21 +62272,26 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
+          <t>publishers-split-on-gambling-money-in-esports</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
           <t>Game publishers are opening esports to licensed bookmakers</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>CS2 Sponsorship Landscape 2026: Gambling Brands Control Majority of Title Sponsorships</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr"/>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr"/>
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>https://escharts.com/news/betting-and-gambling-companies-lead-title-sponsorships-2026-counter-strike-esports</t>
         </is>
@@ -61431,21 +62300,26 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
+          <t>publishers-split-on-gambling-money-in-esports</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
           <t>Game publishers are opening esports to licensed bookmakers</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>Why We're Opening Betting Sponsorships in Esports &amp; How We're Doing It Responsibly</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Primary</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr">
         <is>
           <t>https://www.riotgames.com/en/news/esports-betting-sponsorships</t>
         </is>
@@ -61454,25 +62328,30 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
+          <t>publishers-split-on-gambling-money-in-esports</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
           <t>Game publishers are opening esports to licensed bookmakers</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>The only companies that want to sponsor me are gambling companies</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>Community</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@nathanli1236/video/7671398335902895368</t>
         </is>
@@ -61481,21 +62360,26 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
+          <t>childrens-data-privacy-and-the-age-assurance-bargain</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
           <t>Children's privacy rules are nudging games toward checking every player's age</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>Roblox to face external audits to prove it is safe for Australian children</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E35" s="3" t="inlineStr"/>
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>https://www.abc.net.au/news/2026-08-20/roblox-esafety-court-enforceable-undertaking/107056294</t>
         </is>
@@ -61504,21 +62388,26 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
+          <t>childrens-data-privacy-and-the-age-assurance-bargain</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
           <t>Children's privacy rules are nudging games toward checking every player's age</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>Understanding the updated COPPA rules and their impact on child safety</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr"/>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr"/>
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>https://gamesbeat.com/understanding-the-updated-coppa-rules-and-their-impact-on-child-safety/</t>
         </is>
@@ -61527,21 +62416,26 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
+          <t>childrens-data-privacy-and-the-age-assurance-bargain</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
           <t>Children's privacy rules are nudging games toward checking every player's age</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>California enacts new social media curbs for children under 16</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E37" s="3" t="inlineStr"/>
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>https://www.pocketgamer.biz/california-enacts-new-social-media-curbs-for-children-under-16/</t>
         </is>
@@ -61550,21 +62444,26 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
+          <t>addiction-and-screen-time-discourse</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
           <t>Problem-gaming research is shifting from hours to compulsion</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>Study Finds Addictive Screen Use, Not Total Screen Time, Linked to Youth Suicide Risk</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr"/>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr"/>
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>https://news.weill.cornell.edu/news/2025/06/study-finds-addictive-screen-use-not-total-screen-time-linked-to-youth-suicide-risk</t>
         </is>
@@ -61573,21 +62472,26 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
+          <t>addiction-and-screen-time-discourse</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
           <t>Problem-gaming research is shifting from hours to compulsion</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>W66 days clean. I might stop. This is just not doing anything for me (r/StopGaming)</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Community</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr"/>
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>https://www.reddit.com/r/StopGaming/comments/1vuf5jh/66_days_clean_i_might_stop_this_is_just_not_doing/</t>
         </is>
@@ -61596,21 +62500,26 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
+          <t>addiction-and-screen-time-discourse</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
           <t>Problem-gaming research is shifting from hours to compulsion</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>New Study Challenges Common Assumptions About Screen Time For Kids</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
         <is>
           <t>Community</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr"/>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr"/>
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>https://hardware.slashdot.org/story/26/08/19/2231240/new-study-challenges-common-assumptions-about-screen-time-for-kids</t>
         </is>
@@ -61619,21 +62528,26 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
+          <t>chinas-original-ip-franchise-build-out</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
           <t>Chinese studios are trying to build premium global franchises</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>“China’s K-pop moment”: Wukong’s global success sparks government embrace of video games as soft power</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr"/>
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>https://restofworld.org/2024/wukong-china-gaming-strategy/</t>
         </is>
@@ -61642,21 +62556,26 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
+          <t>chinas-original-ip-franchise-build-out</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
           <t>Chinese studios are trying to build premium global franchises</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>China's game makers split as giants chase prestige and others target profit</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr"/>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="E42" s="3" t="inlineStr"/>
+      <c r="F42" s="3" t="inlineStr">
         <is>
           <t>https://kr-asia.com/chinas-game-makers-split-as-giants-chase-prestige-and-others-target-profit</t>
         </is>
@@ -61665,25 +62584,30 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
+          <t>chinas-original-ip-franchise-build-out</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
           <t>Chinese studios are trying to build premium global franchises</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>Black Myth: Zhong Kui might be the best looking game ever made... Chinese devs are cooking</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Community</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="F43" s="3" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@okami.games/video/7675962319934852365</t>
         </is>
@@ -61692,21 +62616,26 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
+          <t>gulf-capital-and-the-leveraged-ea-buyout</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
           <t>Saudi state money is buying major games companies</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>Inside Saudi Arabia's $38 Billion Gaming Empire</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr"/>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr">
         <is>
           <t>https://naavik.co/digest/inside-saudi-arabias-38-billion-gaming-empire/</t>
         </is>
@@ -61715,21 +62644,26 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
+          <t>gulf-capital-and-the-leveraged-ea-buyout</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
           <t>Saudi state money is buying major games companies</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>Saudi Arabia's PIF reportedly considering to combine EA with Savvy Games Group</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr"/>
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>https://www.gamesindustry.biz/saudi-arabias-pif-reportedly-considering-to-combine-ea-with-savvy-games-group</t>
         </is>
@@ -61738,21 +62672,26 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
+          <t>gulf-capital-and-the-leveraged-ea-buyout</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
           <t>Saudi state money is buying major games companies</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>Saudi video game giant Savvy CEO Brian Ward is stepping down</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr"/>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr"/>
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>https://www.bloomberg.com/news/articles/2026-09-01/saudi-video-game-giant-savvy-ceo-brian-ward-is-stepping-down</t>
         </is>
@@ -61761,21 +62700,26 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
+          <t>growth-without-western-access</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
           <t>China's growth is going to Chinese-made games</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>The state of video games with Matthew Ball, Part One</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr"/>
+      <c r="F47" s="3" t="inlineStr">
         <is>
           <t>https://www.thegamebusiness.com/p/the-state-of-video-games-with-matthew</t>
         </is>
@@ -61784,21 +62728,26 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
+          <t>growth-without-western-access</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
           <t>China's growth is going to Chinese-made games</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>Chinese gaming market surpasses $50 billion</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr"/>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr"/>
+      <c r="F48" s="3" t="inlineStr">
         <is>
           <t>https://nikopartners.com/chinese-gaming-market-surpasses-50-billion-as-ai-premium-gaming-and-new-monetization-models-reshape-growth/</t>
         </is>
@@ -61807,21 +62756,26 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
+          <t>chinas-banhao-throttles-games</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
           <t>China is using game approvals as a policy dial</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>China's NPPA approved 1,771 video games in 2025</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr"/>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr"/>
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>https://substack.nikopartners.com/p/chinas-nppa-approved-1771-video-games</t>
         </is>
@@ -61830,21 +62784,26 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
+          <t>chinas-banhao-throttles-games</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
           <t>China is using game approvals as a policy dial</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>Chinese gacha games recorded an 8.97% decline, despite growth in the gaming industry as a whole</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>Community</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr"/>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr"/>
+      <c r="F50" s="3" t="inlineStr">
         <is>
           <t>https://www.reddit.com/r/gachagaming/comments/1vauysu/china_game_industry_report_for_januaryjune_2026/</t>
         </is>
@@ -61853,21 +62812,26 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
+          <t>chinas-banhao-throttles-games</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
           <t>China is using game approvals as a policy dial</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>China Game Approval (Banhao) requirements for apps in CN, 2026</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>Primary</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr"/>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr"/>
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>https://clearlaunch.dev/regulations/china-game-approval</t>
         </is>
@@ -61876,21 +62840,26 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
+          <t>generative-ai-in-development-the-enforcement-turn</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
           <t>Developers are turning against generative AI</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>GDC 2026 State of the Game Industry Reveals Impact of Layoffs, Generative AI, and More</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>Primary</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr"/>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="E52" s="3" t="inlineStr"/>
+      <c r="F52" s="3" t="inlineStr">
         <is>
           <t>https://gdconf.com/article/gdc-2026-state-of-the-game-industry-reveals-impact-of-layoffs-generative-ai-and-more/</t>
         </is>
@@ -61899,21 +62868,26 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
+          <t>generative-ai-in-development-the-enforcement-turn</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
           <t>Developers are turning against generative AI</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>AI is a copyright landmine: "I think we're going to see lawsuits"</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr"/>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr">
         <is>
           <t>https://www.gamesradar.com/games/echoing-palworld-dev-video-game-lawyer-says-all-her-clients-have-anti-ai-contracts-because-gamers-hate-it-and-its-a-copyright-landmine-i-think-were-going-to-see-lawsuits/</t>
         </is>
@@ -61922,21 +62896,26 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
+          <t>generative-ai-in-development-the-enforcement-turn</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
           <t>Developers are turning against generative AI</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>European game developers are more concerned that AI will pressure them to work faster rather than take their job</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr"/>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="E54" s="3" t="inlineStr"/>
+      <c r="F54" s="3" t="inlineStr">
         <is>
           <t>https://www.gamesindustry.biz/european-game-developers-are-more-concerned-that-ai-will-pressure-them-to-work-faster-rather-than-take-their-job</t>
         </is>
@@ -61945,21 +62924,26 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
+          <t>the-rise-of-ai-companions-and-co-playable-npcs</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
           <t>AI teammates are reaching players in short tests</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>How KRAFTON Built PUBG Ally, a Co-Playable Character Powered by NVIDIA ACE</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr"/>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="E55" s="3" t="inlineStr"/>
+      <c r="F55" s="3" t="inlineStr">
         <is>
           <t>https://developer.nvidia.com/blog/how-krafton-built-pubg-ally-a-co-playable-character-powered-by-nvidia-ace/</t>
         </is>
@@ -61968,21 +62952,26 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
+          <t>the-rise-of-ai-companions-and-co-playable-npcs</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
           <t>AI teammates are reaching players in short tests</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>r/gamedev Policy on AI Use</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
         <is>
           <t>Community</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr"/>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="E56" s="3" t="inlineStr"/>
+      <c r="F56" s="3" t="inlineStr">
         <is>
           <t>https://www.reddit.com/r/gamedev/comments/1vrnqyt/rgamedev_policy_on_ai_use/</t>
         </is>
@@ -61991,25 +62980,30 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
+          <t>the-rise-of-ai-companions-and-co-playable-npcs</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
           <t>AI teammates are reaching players in short tests</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>dev stress-tests their game's voice recognition after a player calls it bad</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>Community</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="F57" s="3" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@monchiistudio/video/7676265366301019393</t>
         </is>
@@ -62018,21 +63012,26 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
+          <t>ai-disclosure-fights-and-unprotected-creative-labor</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
           <t>Creative workers are fighting over AI consent and disclosure</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>SAG-AFTRA Overwhelmingly Approves Video Game Agreement, Marking Official End To Nearly Yearlong Strike</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr"/>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="E58" s="3" t="inlineStr"/>
+      <c r="F58" s="3" t="inlineStr">
         <is>
           <t>https://deadline.com/2025/07/sag-aftra-video-game-agreement-approved-strike-1236453741/</t>
         </is>
@@ -62041,21 +63040,26 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
+          <t>ai-disclosure-fights-and-unprotected-creative-labor</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
           <t>Creative workers are fighting over AI consent and disclosure</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>Saber's AI Rideshare Stimulator controversy almost closes on high note</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr"/>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr"/>
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>https://www.pcgamer.com/gaming-industry/sabers-ai-rideshare-stimulator-controversy-almost-closes-on-high-note-with-ceo-apology-then-he-calls-portal-scribe-who-mocked-him-an-unsuccessful-writer/</t>
         </is>
@@ -62064,21 +63068,26 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
+          <t>ai-disclosure-fights-and-unprotected-creative-labor</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
           <t>Creative workers are fighting over AI consent and disclosure</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>Report: EA's NHL 27 is using genAI to create voiceover, claims a sports commentator</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr"/>
-      <c r="E60" s="3" t="inlineStr">
+      <c r="E60" s="3" t="inlineStr"/>
+      <c r="F60" s="3" t="inlineStr">
         <is>
           <t>https://www.gamedeveloper.com/business/report-ea-s-nhl-27-is-using-genai-to-create-voiceover-claims-a-sports-commentator</t>
         </is>
@@ -62087,21 +63096,26 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
+          <t>app-store-unbundling-under-court-supervision</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
           <t>Apple and Google are being forced to open their stores</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>Following Epic loss, Google has started hosting rival app stores in Play Store</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr"/>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="E61" s="3" t="inlineStr"/>
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>https://arstechnica.com/gadgets/2026/08/third-party-app-stores-are-rolling-out-in-google-play-but-theres-only-one-right-now/</t>
         </is>
@@ -62110,21 +63124,26 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
+          <t>app-store-unbundling-under-court-supervision</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
           <t>Apple and Google are being forced to open their stores</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>'That is not acceptable': Judge orders Google to make rival app store installs easier</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
         <is>
           <t>Community</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr"/>
-      <c r="E62" s="3" t="inlineStr">
+      <c r="E62" s="3" t="inlineStr"/>
+      <c r="F62" s="3" t="inlineStr">
         <is>
           <t>https://www.theverge.com/policy/979852/that-is-not-acceptable-judge-orders-google-to-make-rival-app-store-installs-easier</t>
         </is>
@@ -62133,21 +63152,26 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
+          <t>app-store-unbundling-under-court-supervision</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
           <t>Apple and Google are being forced to open their stores</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>Apple announces changes to iOS in Japan</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>Community</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr"/>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr"/>
+      <c r="F63" s="3" t="inlineStr">
         <is>
           <t>https://www.apple.com/newsroom/2025/12/apple-announces-changes-to-ios-in-japan/</t>
         </is>
@@ -62156,21 +63180,26 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
+          <t>streaming-fragmentation-and-the-multi-homed-creator</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
           <t>Streamers are spreading across several platforms</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>Multistreaming Audience Split: Twitch, YouTube &amp; Kick in H1 2026</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr"/>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="E64" s="3" t="inlineStr"/>
+      <c r="F64" s="3" t="inlineStr">
         <is>
           <t>https://streamscharts.com/news/multistreaming-audience-split-twitch-youtube-kick-h1-2026</t>
         </is>
@@ -62179,21 +63208,26 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
+          <t>streaming-fragmentation-and-the-multi-homed-creator</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
           <t>Streamers are spreading across several platforms</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>SOOP Korea and Chzzk: One Year After Twitch's Shutdown</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr"/>
-      <c r="E65" s="3" t="inlineStr">
+      <c r="E65" s="3" t="inlineStr"/>
+      <c r="F65" s="3" t="inlineStr">
         <is>
           <t>https://streamhatchet.com/blog/the-state-of-korean-live-streaming/</t>
         </is>
@@ -62202,21 +63236,26 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
+          <t>streaming-fragmentation-and-the-multi-homed-creator</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
           <t>Streamers are spreading across several platforms</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>YouTube gaming creators "command 23% higher deal rates than Twitch"</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr"/>
-      <c r="E66" s="3" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr"/>
+      <c r="F66" s="3" t="inlineStr">
         <is>
           <t>https://www.pocketgamer.biz/youtube-gaming-creators-command-23-higher-deal-rates-than-twitch/</t>
         </is>
@@ -62225,21 +63264,26 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
+          <t>handheld-pc-resurgence</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
           <t>Handheld gaming PCs are losing momentum</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>Asus ROG Xbox Ally sales stall with Steam Deck still the preferred handheld gaming PC</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr"/>
-      <c r="E67" s="3" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr"/>
+      <c r="F67" s="3" t="inlineStr">
         <is>
           <t>https://www.notebookcheck.net/Asus-ROG-Xbox-Ally-sales-stall-with-Steam-Deck-still-the-preferred-handheld-gaming-PC.1230155.0.html</t>
         </is>
@@ -62248,21 +63292,26 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
+          <t>handheld-pc-resurgence</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
           <t>Handheld gaming PCs are losing momentum</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>SteamOS expands beyond Steam Deck</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>Primary</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr"/>
-      <c r="E68" s="3" t="inlineStr">
+      <c r="E68" s="3" t="inlineStr"/>
+      <c r="F68" s="3" t="inlineStr">
         <is>
           <t>https://store.steampowered.com/news/app/593110/view/529834914570306831</t>
         </is>
@@ -62271,25 +63320,30 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
+          <t>handheld-pc-resurgence</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
           <t>Handheld gaming PCs are losing momentum</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>PC Gaming Handhelds just keep getting better</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>Community</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="F69" s="3" t="inlineStr">
         <is>
           <t>https://www.tiktok.com/@gg.sheed/video/7675986246526700814</t>
         </is>
@@ -62298,21 +63352,26 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
+          <t>metaverse-and-blockchain-gaming-hype</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
           <t>Investors are abandoning blockchain games</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>$12 Billion In, 93% Dead: The Real Story of Web3 Gaming</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr"/>
-      <c r="E70" s="3" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr"/>
+      <c r="F70" s="3" t="inlineStr">
         <is>
           <t>https://caladan.xyz/12-billion-in-93-percent-dead-web3-gaming/</t>
         </is>
@@ -62321,21 +63380,26 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
+          <t>metaverse-and-blockchain-gaming-hype</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
           <t>Investors are abandoning blockchain games</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>More than 90% of Web3 games failed after $15 billion boom</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr"/>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr"/>
+      <c r="F71" s="3" t="inlineStr">
         <is>
           <t>https://www.coindesk.com/markets/2026/04/23/more-than-90-of-web3-games-failed-after-usd15-billion-boom-as-gamers-never-showed-up-caladan</t>
         </is>
@@ -62344,21 +63408,26 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
+          <t>metaverse-and-blockchain-gaming-hype</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
           <t>Investors are abandoning blockchain games</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>NEXPACE posts 30.98 million NXPC in first-half protocol revenue</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr"/>
-      <c r="E72" s="3" t="inlineStr">
+      <c r="E72" s="3" t="inlineStr"/>
+      <c r="F72" s="3" t="inlineStr">
         <is>
           <t>https://www.invenglobal.com/articles/25725/nexpace-posts-3098-million-nxpc-in-first-half-protocol-revenue</t>
         </is>
@@ -62367,21 +63436,26 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
+          <t>multigenerational-play-and-the-household-question</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
           <t>Older players are a large audience the industry overlooks</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>2026 Essential Facts About the U.S. Video Game Industry</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr"/>
-      <c r="E73" s="3" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr"/>
+      <c r="F73" s="3" t="inlineStr">
         <is>
           <t>https://www.theesa.com/resources/essential-facts-about-the-us-video-game-industry/2026-data/</t>
         </is>
@@ -62390,25 +63464,30 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
+          <t>multigenerational-play-and-the-household-question</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
           <t>Older players are a large audience the industry overlooks</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>The Myth of the Aging Playerbase</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="E74" s="3" t="inlineStr">
         <is>
           <t>video</t>
         </is>
       </c>
-      <c r="E74" s="3" t="inlineStr">
+      <c r="F74" s="3" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=N8tdqi-x9OI</t>
         </is>
@@ -62417,21 +63496,26 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
+          <t>multigenerational-play-and-the-household-question</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
           <t>Older players are a large audience the industry overlooks</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>Why older gamers could be the key to saving the games industry</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr"/>
-      <c r="E75" s="3" t="inlineStr">
+      <c r="E75" s="3" t="inlineStr"/>
+      <c r="F75" s="3" t="inlineStr">
         <is>
           <t>https://news.northeastern.edu/2026/06/02/old-gamers-video-game-industry/</t>
         </is>
@@ -62440,21 +63524,26 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
+          <t>game-preservation-and-digital-ownership</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
           <t>Campaigners are pressing to keep sold games playable</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>Stop Destroying Videogames - Commission's reply to the European citizens' initiative</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
         <is>
           <t>Primary</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr"/>
-      <c r="E76" s="3" t="inlineStr">
+      <c r="E76" s="3" t="inlineStr"/>
+      <c r="F76" s="3" t="inlineStr">
         <is>
           <t>https://citizens-initiative.europa.eu/stop-destroying-videogames-commissions-reply-european-citizens-initiative_en</t>
         </is>
@@ -62463,21 +63552,26 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
+          <t>game-preservation-and-digital-ownership</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
           <t>Campaigners are pressing to keep sold games playable</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>GOG brings back "big box" PC games, one printable template at a time</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr"/>
-      <c r="E77" s="3" t="inlineStr">
+      <c r="E77" s="3" t="inlineStr"/>
+      <c r="F77" s="3" t="inlineStr">
         <is>
           <t>https://arstechnica.com/gaming/2026/09/gog-brings-back-big-box-pc-games-one-printable-template-at-a-time/</t>
         </is>
@@ -62486,21 +63580,26 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
+          <t>game-preservation-and-digital-ownership</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
           <t>Campaigners are pressing to keep sold games playable</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>Projeto de lei inspirado no Stop Killing Games é apresentado no Brasil para evitar que jogos morram</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr"/>
-      <c r="E78" s="3" t="inlineStr">
+      <c r="E78" s="3" t="inlineStr"/>
+      <c r="F78" s="3" t="inlineStr">
         <is>
           <t>https://www.tecmundo.com.br/voxel/504819-projeto-de-lei-inspirado-no-stop-killing-games-e-apresentado-no-brasil-para-evitar-que-jogos-morram.htm</t>
         </is>
@@ -62509,21 +63608,26 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
+          <t>organized-game-labor</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
           <t>Game workers are winning union contracts</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>Game Worker Solidarity: Mapping and documenting collective movements by game workers</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>Primary</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr"/>
-      <c r="E79" s="3" t="inlineStr">
+      <c r="E79" s="3" t="inlineStr"/>
+      <c r="F79" s="3" t="inlineStr">
         <is>
           <t>https://gameworkersolidarity.com/</t>
         </is>
@@ -62532,21 +63636,26 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
+          <t>organized-game-labor</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
           <t>Game workers are winning union contracts</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>One industry, one fight – Video Game Unions Present a United Front Across Western Europe</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>Primary</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr"/>
-      <c r="E80" s="3" t="inlineStr">
+      <c r="E80" s="3" t="inlineStr"/>
+      <c r="F80" s="3" t="inlineStr">
         <is>
           <t>https://www.stjv.fr/en/2025/12/one-industry-one-fight-video-game-unions-present-a-united-front-across-western-europe/</t>
         </is>
@@ -62555,21 +63664,26 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
+          <t>organized-game-labor</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
           <t>Game workers are winning union contracts</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>Blizzard union workers ratify historic contract covering 1,900 employees</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D81" s="3" t="inlineStr"/>
-      <c r="E81" s="3" t="inlineStr">
+      <c r="E81" s="3" t="inlineStr"/>
+      <c r="F81" s="3" t="inlineStr">
         <is>
           <t>https://www.gamedeveloper.com/production/blizzard-union-workers-ratify-historic-contract-covering-1-900-employees</t>
         </is>
@@ -62578,21 +63692,26 @@
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
+          <t>culture-war-discourse-and-the-weaponized-review-score</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
           <t>Players are using review scores as a protest vote</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t>Forced: Perceptions of “Woke” Politics in Video Games</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr">
         <is>
           <t>Research</t>
         </is>
       </c>
-      <c r="D82" s="3" t="inlineStr"/>
-      <c r="E82" s="3" t="inlineStr">
+      <c r="E82" s="3" t="inlineStr"/>
+      <c r="F82" s="3" t="inlineStr">
         <is>
           <t>https://ijoc.org/index.php/ijoc/article/view/23165</t>
         </is>
@@ -62601,21 +63720,26 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
+          <t>culture-war-discourse-and-the-weaponized-review-score</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
           <t>Players are using review scores as a protest vote</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t>Steam review bombing is gaming's most powerful method of protest</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr"/>
-      <c r="E83" s="3" t="inlineStr">
+      <c r="E83" s="3" t="inlineStr"/>
+      <c r="F83" s="3" t="inlineStr">
         <is>
           <t>https://www.pcgamer.com/games/third-person-shooter/steam-review-bombing-is-gamings-most-powerful-method-of-protest-3-takeaways-from-helldivers-2s-weekend-meltdown/</t>
         </is>
@@ -62624,21 +63748,26 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
+          <t>culture-war-discourse-and-the-weaponized-review-score</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
           <t>Players are using review scores as a protest vote</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>I hate what the culture wars have done to the discourse surrounding this game</t>
         </is>
       </c>
-      <c r="C84" s="3" t="inlineStr">
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>Community</t>
         </is>
       </c>
-      <c r="D84" s="3" t="inlineStr"/>
-      <c r="E84" s="3" t="inlineStr">
+      <c r="E84" s="3" t="inlineStr"/>
+      <c r="F84" s="3" t="inlineStr">
         <is>
           <t>https://www.reddit.com/r/ShitHaloSays/comments/1vaslzl/i_hate_what_the_culture_wars_have_done_to_the/</t>
         </is>
@@ -62647,21 +63776,26 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
+          <t>esports-after-the-reckoning</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
           <t>Esports is running on Saudi money</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t>Esports Business H1 2026: 4 Shifts Reshaping the Industry</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D85" s="3" t="inlineStr"/>
-      <c r="E85" s="3" t="inlineStr">
+      <c r="E85" s="3" t="inlineStr"/>
+      <c r="F85" s="3" t="inlineStr">
         <is>
           <t>https://escharts.com/news/esports-business-h1-2026</t>
         </is>
@@ -62670,21 +63804,26 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
+          <t>esports-after-the-reckoning</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
           <t>Esports is running on Saudi money</t>
         </is>
       </c>
-      <c r="B86" s="3" t="inlineStr">
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t>Kiwoom aims to become the first publicly listed Korean eSports team</t>
         </is>
       </c>
-      <c r="C86" s="3" t="inlineStr">
+      <c r="D86" s="3" t="inlineStr">
         <is>
           <t>Community</t>
         </is>
       </c>
-      <c r="D86" s="3" t="inlineStr"/>
-      <c r="E86" s="3" t="inlineStr">
+      <c r="E86" s="3" t="inlineStr"/>
+      <c r="F86" s="3" t="inlineStr">
         <is>
           <t>https://www.reddit.com/r/leagueoflegends/comments/1v46rdr/investchosun_kiwoom_drx_krx_files_for_ipo_on_the/</t>
         </is>
@@ -62693,21 +63832,26 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
+          <t>esports-after-the-reckoning</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
           <t>Esports is running on Saudi money</t>
         </is>
       </c>
-      <c r="B87" s="3" t="inlineStr">
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t>Who watched EWC 2026 co-streams? Audience demographics and key markets</t>
         </is>
       </c>
-      <c r="C87" s="3" t="inlineStr">
+      <c r="D87" s="3" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="D87" s="3" t="inlineStr"/>
-      <c r="E87" s="3" t="inlineStr">
+      <c r="E87" s="3" t="inlineStr"/>
+      <c r="F87" s="3" t="inlineStr">
         <is>
           <t>https://streamscharts.com/news/who-watched-ewc-2026-co-streams</t>
         </is>
@@ -62716,21 +63860,26 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
+          <t>games-media-capture</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
           <t>Games media is consolidating and shrinking</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>The Secretive Company Filling Video Game Sites With Gambling And AI</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
+      <c r="D88" s="3" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D88" s="3" t="inlineStr"/>
-      <c r="E88" s="3" t="inlineStr">
+      <c r="E88" s="3" t="inlineStr"/>
+      <c r="F88" s="3" t="inlineStr">
         <is>
           <t>https://aftermath.site/gameshub-clickout-media-seo-gambling-ai/</t>
         </is>
@@ -62739,21 +63888,26 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
+          <t>games-media-capture</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
           <t>Games media is consolidating and shrinking</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>Four Companies Control Your Favorite Gaming Media</t>
         </is>
       </c>
-      <c r="C89" s="3" t="inlineStr">
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D89" s="3" t="inlineStr"/>
-      <c r="E89" s="3" t="inlineStr">
+      <c r="E89" s="3" t="inlineStr"/>
+      <c r="F89" s="3" t="inlineStr">
         <is>
           <t>https://spilled.gg/companies-gaming-media/</t>
         </is>
@@ -62762,21 +63916,26 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
+          <t>games-media-capture</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
           <t>Games media is consolidating and shrinking</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>Future, Ziff Davis to Struggle Most From Traffic Drops</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr"/>
-      <c r="E90" s="3" t="inlineStr">
+      <c r="E90" s="3" t="inlineStr"/>
+      <c r="F90" s="3" t="inlineStr">
         <is>
           <t>https://www.amediaoperator.com/analysis/future-ziff-davis-to-struggle-most-from-traffic-drops/</t>
         </is>
@@ -62785,21 +63944,26 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
+          <t>studio-investment-in-games-plummets</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
           <t>Investors are pulling money out of studios</t>
         </is>
       </c>
-      <c r="B91" s="3" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>The State of Video Gaming in 2026 (Matthew Ball / Epyllion)</t>
         </is>
       </c>
-      <c r="C91" s="3" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="D91" s="3" t="inlineStr"/>
-      <c r="E91" s="3" t="inlineStr">
+      <c r="E91" s="3" t="inlineStr"/>
+      <c r="F91" s="3" t="inlineStr">
         <is>
           <t>https://www.matthewball.co/all/presentation-the-state-of-video-gaming-in-2026</t>
         </is>
@@ -62808,21 +63972,26 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
+          <t>studio-investment-in-games-plummets</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
           <t>Investors are pulling money out of studios</t>
         </is>
       </c>
-      <c r="B92" s="3" t="inlineStr">
+      <c r="C92" s="3" t="inlineStr">
         <is>
           <t>The state of video games with Matthew Ball, Part One</t>
         </is>
       </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D92" s="3" t="inlineStr"/>
-      <c r="E92" s="3" t="inlineStr">
+      <c r="E92" s="3" t="inlineStr"/>
+      <c r="F92" s="3" t="inlineStr">
         <is>
           <t>https://www.thegamebusiness.com/p/the-state-of-video-games-with-matthew</t>
         </is>
@@ -62831,21 +64000,26 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
+          <t>studio-investment-in-games-plummets</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
           <t>Investors are pulling money out of studios</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="C93" s="3" t="inlineStr">
         <is>
           <t>European studio expenditure on external talent rises 63% in 2025</t>
         </is>
       </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="D93" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr"/>
-      <c r="E93" s="3" t="inlineStr">
+      <c r="E93" s="3" t="inlineStr"/>
+      <c r="F93" s="3" t="inlineStr">
         <is>
           <t>https://www.gamesindustry.biz/european-studio-expenditure-on-external-talent-rises-63-in-2025</t>
         </is>
@@ -62854,21 +64028,26 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
+          <t>platforms-bet-on-exclusivity-again</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
           <t>Console makers are keeping games exclusive again</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="C94" s="3" t="inlineStr">
         <is>
           <t>Should PlayStation and Xbox change their plans on exclusive games?</t>
         </is>
       </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D94" s="3" t="inlineStr"/>
-      <c r="E94" s="3" t="inlineStr">
+      <c r="E94" s="3" t="inlineStr"/>
+      <c r="F94" s="3" t="inlineStr">
         <is>
           <t>https://www.thegamebusiness.com/p/should-playstation-and-xbox-change</t>
         </is>
@@ -62877,21 +64056,26 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
+          <t>platforms-bet-on-exclusivity-again</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
           <t>Console makers are keeping games exclusive again</t>
         </is>
       </c>
-      <c r="B95" s="3" t="inlineStr">
+      <c r="C95" s="3" t="inlineStr">
         <is>
           <t>Xbox console exclusives are returning on a ‘case-by-case’ basis</t>
         </is>
       </c>
-      <c r="C95" s="3" t="inlineStr">
+      <c r="D95" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D95" s="3" t="inlineStr"/>
-      <c r="E95" s="3" t="inlineStr">
+      <c r="E95" s="3" t="inlineStr"/>
+      <c r="F95" s="3" t="inlineStr">
         <is>
           <t>https://www.gamedeveloper.com/business/xbox-console-exclusives-are-returning-on-a-case-by-case-basis</t>
         </is>
@@ -62900,21 +64084,26 @@
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
+          <t>platforms-bet-on-exclusivity-again</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
           <t>Console makers are keeping games exclusive again</t>
         </is>
       </c>
-      <c r="B96" s="3" t="inlineStr">
+      <c r="C96" s="3" t="inlineStr">
         <is>
           <t>Xbox to publish Kojima Productions' Physint after PlayStation said it would cancel the project</t>
         </is>
       </c>
-      <c r="C96" s="3" t="inlineStr">
+      <c r="D96" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D96" s="3" t="inlineStr"/>
-      <c r="E96" s="3" t="inlineStr">
+      <c r="E96" s="3" t="inlineStr"/>
+      <c r="F96" s="3" t="inlineStr">
         <is>
           <t>https://www.gamesindustry.biz/xbox-to-publish-kojima-productions-physint-after-it-unexpectedly-received-notice-from-playstation-that-it-would-cancel-the-project</t>
         </is>
@@ -62923,21 +64112,26 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
+          <t>mobile-has-shifted-from-downloads-to-spending</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
           <t>Mobile games are struggling to find new players</t>
         </is>
       </c>
-      <c r="B97" s="3" t="inlineStr">
+      <c r="C97" s="3" t="inlineStr">
         <is>
           <t>State of Mobile 2026: 9 Key Trends</t>
         </is>
       </c>
-      <c r="C97" s="3" t="inlineStr">
+      <c r="D97" s="3" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="D97" s="3" t="inlineStr"/>
-      <c r="E97" s="3" t="inlineStr">
+      <c r="E97" s="3" t="inlineStr"/>
+      <c r="F97" s="3" t="inlineStr">
         <is>
           <t>https://www.deconstructoroffun.com/blog/2026/2/2/state-of-mobile-2026</t>
         </is>
@@ -62946,21 +64140,26 @@
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
+          <t>mobile-has-shifted-from-downloads-to-spending</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
           <t>Mobile games are struggling to find new players</t>
         </is>
       </c>
-      <c r="B98" s="3" t="inlineStr">
+      <c r="C98" s="3" t="inlineStr">
         <is>
           <t>H1 2026: 4X Strategy's UA Reckoning</t>
         </is>
       </c>
-      <c r="C98" s="3" t="inlineStr">
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D98" s="3" t="inlineStr"/>
-      <c r="E98" s="3" t="inlineStr">
+      <c r="E98" s="3" t="inlineStr"/>
+      <c r="F98" s="3" t="inlineStr">
         <is>
           <t>https://naavik.co/f2p-mobile/h1-2026-4x-strategys-ua-reckoning/</t>
         </is>
@@ -62969,21 +64168,26 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
+          <t>mobile-has-shifted-from-downloads-to-spending</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
           <t>Mobile games are struggling to find new players</t>
         </is>
       </c>
-      <c r="B99" s="3" t="inlineStr">
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t>H1 2026 genre analysis: strategy stumbles, RPGs fall, and puzzle revenue ramps up</t>
         </is>
       </c>
-      <c r="C99" s="3" t="inlineStr">
+      <c r="D99" s="3" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="D99" s="3" t="inlineStr"/>
-      <c r="E99" s="3" t="inlineStr">
+      <c r="E99" s="3" t="inlineStr"/>
+      <c r="F99" s="3" t="inlineStr">
         <is>
           <t>https://www.pocketgamer.biz/h1-2026-genre-analysis-strategy-stumbles-rpgs-fall-and-puzzle-revenue-ramps-up/</t>
         </is>
@@ -62992,21 +64196,26 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
+          <t>creators-are-how-players-find-games</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
           <t>Steam's glut is making discovery the hard part</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr">
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>GDC: The State of the Game Industry 2026</t>
         </is>
       </c>
-      <c r="C100" s="3" t="inlineStr">
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="D100" s="3" t="inlineStr"/>
-      <c r="E100" s="3" t="inlineStr">
+      <c r="E100" s="3" t="inlineStr"/>
+      <c r="F100" s="3" t="inlineStr">
         <is>
           <t>https://gamedevreports.substack.com/p/gdc-the-state-of-the-game-industry-fcf</t>
         </is>
@@ -63015,21 +64224,26 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
+          <t>creators-are-how-players-find-games</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
           <t>Steam's glut is making discovery the hard part</t>
         </is>
       </c>
-      <c r="B101" s="3" t="inlineStr">
+      <c r="C101" s="3" t="inlineStr">
         <is>
           <t>Does your Steam demo CCU 'predict' your game's success?</t>
         </is>
       </c>
-      <c r="C101" s="3" t="inlineStr">
+      <c r="D101" s="3" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="D101" s="3" t="inlineStr"/>
-      <c r="E101" s="3" t="inlineStr">
+      <c r="E101" s="3" t="inlineStr"/>
+      <c r="F101" s="3" t="inlineStr">
         <is>
           <t>https://newsletter.gamediscover.co/p/does-your-steam-demo-ccu-predict</t>
         </is>
@@ -63038,21 +64252,26 @@
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
+          <t>creators-are-how-players-find-games</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
           <t>Steam's glut is making discovery the hard part</t>
         </is>
       </c>
-      <c r="B102" s="3" t="inlineStr">
+      <c r="C102" s="3" t="inlineStr">
         <is>
           <t>How many games were released in 2025?</t>
         </is>
       </c>
-      <c r="C102" s="3" t="inlineStr">
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D102" s="3" t="inlineStr"/>
-      <c r="E102" s="3" t="inlineStr">
+      <c r="E102" s="3" t="inlineStr"/>
+      <c r="F102" s="3" t="inlineStr">
         <is>
           <t>https://howtomarketagame.com/2026/01/08/how-many-games-were-released-in-2025/</t>
         </is>
@@ -63061,21 +64280,26 @@
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
+          <t>new-games-fight-for-playtime</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
           <t>Old games take most of players' time</t>
         </is>
       </c>
-      <c r="B103" s="3" t="inlineStr">
+      <c r="C103" s="3" t="inlineStr">
         <is>
           <t>Newzoo: PC and Console Market in 2026</t>
         </is>
       </c>
-      <c r="C103" s="3" t="inlineStr">
+      <c r="D103" s="3" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="D103" s="3" t="inlineStr"/>
-      <c r="E103" s="3" t="inlineStr">
+      <c r="E103" s="3" t="inlineStr"/>
+      <c r="F103" s="3" t="inlineStr">
         <is>
           <t>https://gamedevreports.substack.com/p/newzoo-pc-and-console-market-in-2026</t>
         </is>
@@ -63084,21 +64308,26 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
+          <t>new-games-fight-for-playtime</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
           <t>Old games take most of players' time</t>
         </is>
       </c>
-      <c r="B104" s="3" t="inlineStr">
+      <c r="C104" s="3" t="inlineStr">
         <is>
           <t>Why older games rule – and new games drool – in Discoveryland</t>
         </is>
       </c>
-      <c r="C104" s="3" t="inlineStr">
+      <c r="D104" s="3" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D104" s="3" t="inlineStr"/>
-      <c r="E104" s="3" t="inlineStr">
+      <c r="E104" s="3" t="inlineStr"/>
+      <c r="F104" s="3" t="inlineStr">
         <is>
           <t>https://newsletter.gamediscover.co/p/why-older-games-rule-and-new-games</t>
         </is>
@@ -63107,21 +64336,26 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
+          <t>new-games-fight-for-playtime</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
           <t>Old games take most of players' time</t>
         </is>
       </c>
-      <c r="B105" s="3" t="inlineStr">
+      <c r="C105" s="3" t="inlineStr">
         <is>
           <t>Valve has reportedly made £11bn from Steam already in 2026, and biggest earning new arrival is Forza Horizon 6</t>
         </is>
       </c>
-      <c r="C105" s="3" t="inlineStr">
+      <c r="D105" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D105" s="3" t="inlineStr"/>
-      <c r="E105" s="3" t="inlineStr">
+      <c r="E105" s="3" t="inlineStr"/>
+      <c r="F105" s="3" t="inlineStr">
         <is>
           <t>https://www.eurogamer.net/forza-horizon-6-biggest-steam-new-release-11-billion-gbp</t>
         </is>
@@ -63130,21 +64364,26 @@
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
+          <t>the-rise-of-friendslop</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
           <t>Cheap co-op games are topping Steam's charts</t>
         </is>
       </c>
-      <c r="B106" s="3" t="inlineStr">
+      <c r="C106" s="3" t="inlineStr">
         <is>
           <t>GameDiscoverCo: Most successful new releases on PC and Consoles in 2025</t>
         </is>
       </c>
-      <c r="C106" s="3" t="inlineStr">
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="D106" s="3" t="inlineStr"/>
-      <c r="E106" s="3" t="inlineStr">
+      <c r="E106" s="3" t="inlineStr"/>
+      <c r="F106" s="3" t="inlineStr">
         <is>
           <t>https://gamedevreports.substack.com/p/gamediscoverco-most-successful-new</t>
         </is>
@@ -63153,21 +64392,26 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
+          <t>the-rise-of-friendslop</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
           <t>Cheap co-op games are topping Steam's charts</t>
         </is>
       </c>
-      <c r="B107" s="3" t="inlineStr">
+      <c r="C107" s="3" t="inlineStr">
         <is>
           <t>What developers can learn from indie social co-op</t>
         </is>
       </c>
-      <c r="C107" s="3" t="inlineStr">
+      <c r="D107" s="3" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D107" s="3" t="inlineStr"/>
-      <c r="E107" s="3" t="inlineStr">
+      <c r="E107" s="3" t="inlineStr"/>
+      <c r="F107" s="3" t="inlineStr">
         <is>
           <t>https://www.gamedeveloper.com/design/what-developers-can-learn-from-the-indie-social-co-op-games-topping-the-steam-charts</t>
         </is>
@@ -63176,21 +64420,26 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
+          <t>the-rise-of-friendslop</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
           <t>Cheap co-op games are topping Steam's charts</t>
         </is>
       </c>
-      <c r="B108" s="3" t="inlineStr">
+      <c r="C108" s="3" t="inlineStr">
         <is>
           <t>Calling games like Peak and REPO ‘friendslop’ devalues the developer, investor says</t>
         </is>
       </c>
-      <c r="C108" s="3" t="inlineStr">
+      <c r="D108" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D108" s="3" t="inlineStr"/>
-      <c r="E108" s="3" t="inlineStr">
+      <c r="E108" s="3" t="inlineStr"/>
+      <c r="F108" s="3" t="inlineStr">
         <is>
           <t>https://www.gamesradar.com/games/co-op/calling-steam-games-like-peak-and-repo-friendslop-devalues-the-skill-of-the-developer-industry-investor-says-so-lets-collectively-kill-the-term-before-its-too-late/</t>
         </is>
@@ -63199,21 +64448,26 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
+          <t>live-ops-is-becoming-a-playbook</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
           <t>Mobile live events are converging on one playbook</t>
         </is>
       </c>
-      <c r="B109" s="3" t="inlineStr">
+      <c r="C109" s="3" t="inlineStr">
         <is>
           <t>Converging Live Ops Trends in Mobile Puzzle</t>
         </is>
       </c>
-      <c r="C109" s="3" t="inlineStr">
+      <c r="D109" s="3" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D109" s="3" t="inlineStr"/>
-      <c r="E109" s="3" t="inlineStr">
+      <c r="E109" s="3" t="inlineStr"/>
+      <c r="F109" s="3" t="inlineStr">
         <is>
           <t>https://naavik.co/digest/live-ops-trends-powering-mobile-puzzle/</t>
         </is>
@@ -63222,21 +64476,26 @@
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
+          <t>live-ops-is-becoming-a-playbook</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
           <t>Mobile live events are converging on one playbook</t>
         </is>
       </c>
-      <c r="B110" s="3" t="inlineStr">
+      <c r="C110" s="3" t="inlineStr">
         <is>
           <t>H1 2026: 4X Strategy's UA Reckoning</t>
         </is>
       </c>
-      <c r="C110" s="3" t="inlineStr">
+      <c r="D110" s="3" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="D110" s="3" t="inlineStr"/>
-      <c r="E110" s="3" t="inlineStr">
+      <c r="E110" s="3" t="inlineStr"/>
+      <c r="F110" s="3" t="inlineStr">
         <is>
           <t>https://naavik.co/f2p-mobile/h1-2026-4x-strategys-ua-reckoning/</t>
         </is>
@@ -63245,21 +64504,26 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
+          <t>live-ops-is-becoming-a-playbook</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
           <t>Mobile live events are converging on one playbook</t>
         </is>
       </c>
-      <c r="B111" s="3" t="inlineStr">
+      <c r="C111" s="3" t="inlineStr">
         <is>
           <t>Book Excerpt: Running a Successful Live Service Game</t>
         </is>
       </c>
-      <c r="C111" s="3" t="inlineStr">
+      <c r="D111" s="3" t="inlineStr">
         <is>
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D111" s="3" t="inlineStr"/>
-      <c r="E111" s="3" t="inlineStr">
+      <c r="E111" s="3" t="inlineStr"/>
+      <c r="F111" s="3" t="inlineStr">
         <is>
           <t>https://www.gamedeveloper.com/business/book-excerpt-running-a-successful-live-service-game</t>
         </is>
@@ -63268,21 +64532,26 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
+          <t>dormant-ip-revival</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
           <t>Publishers are reviving dormant franchises</t>
         </is>
       </c>
-      <c r="B112" s="3" t="inlineStr">
+      <c r="C112" s="3" t="inlineStr">
         <is>
           <t>Capcom says it will focus on reviving dormant IPs after Onimusha: Way of the Sword breakout launch</t>
         </is>
       </c>
-      <c r="C112" s="3" t="inlineStr">
+      <c r="D112" s="3" t="inlineStr">
         <is>
           <t>Reporting</t>
         </is>
       </c>
-      <c r="D112" s="3" t="inlineStr"/>
-      <c r="E112" s="3" t="inlineStr">
+      <c r="E112" s="3" t="inlineStr"/>
+      <c r="F112" s="3" t="inlineStr">
         <is>
           <t>https://www.gamesindustry.biz/capcom-says-it-will-focus-on-reviving-dormant-ips-after-onimusha-way-of-the-swords-breakout-launch</t>
         </is>
@@ -63291,21 +64560,26 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
+          <t>dormant-ip-revival</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
           <t>Publishers are reviving dormant franchises</t>
         </is>
       </c>
-      <c r="B113" s="3" t="inlineStr">
+      <c r="C113" s="3" t="inlineStr">
         <is>
           <t>Onimusha: Way of the Sword surpasses one million units on launch day; Capcom to focus on re-activating IPs</t>
         </is>
       </c>
-      <c r="C113" s="3" t="inlineStr">
+      <c r="D113" s="3" t="inlineStr">
         <is>
           <t>Primary</t>
         </is>
       </c>
-      <c r="D113" s="3" t="inlineStr"/>
-      <c r="E113" s="3" t="inlineStr">
+      <c r="E113" s="3" t="inlineStr"/>
+      <c r="F113" s="3" t="inlineStr">
         <is>
           <t>https://www.capcom.co.jp/ir/english/news/html/e260907.html</t>
         </is>
@@ -63314,28 +64588,33 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
+          <t>dormant-ip-revival</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
           <t>Publishers are reviving dormant franchises</t>
         </is>
       </c>
-      <c r="B114" s="3" t="inlineStr">
+      <c r="C114" s="3" t="inlineStr">
         <is>
           <t>Gamers spend twice as much on remakes as remasters</t>
         </is>
       </c>
-      <c r="C114" s="3" t="inlineStr">
+      <c r="D114" s="3" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="D114" s="3" t="inlineStr"/>
-      <c r="E114" s="3" t="inlineStr">
+      <c r="E114" s="3" t="inlineStr"/>
+      <c r="F114" s="3" t="inlineStr">
         <is>
           <t>https://www.ampereanalysis.com/insight/gamers-spend-twice-as-much-on-remakes-as-remasters</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E114"/>
+  <autoFilter ref="A1:F114"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
